--- a/ANNEX H-1 - CS Form No. 212 Revised 2025 - Personal Data Sheet.xlsx
+++ b/ANNEX H-1 - CS Form No. 212 Revised 2025 - Personal Data Sheet.xlsx
@@ -3518,37 +3518,42 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="55" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="31" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3559,362 +3564,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3922,113 +3582,20 @@
     <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="5" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4045,10 +3612,20 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -4086,6 +3663,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -4096,6 +3685,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4111,35 +3704,531 @@
     <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="18" fillId="5" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="55" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4156,26 +4245,23 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4200,10 +4286,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4211,12 +4293,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4227,157 +4303,62 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4392,36 +4373,30 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
@@ -4429,6 +4404,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4436,9 +4423,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4462,6 +4446,18 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -4485,128 +4481,67 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4614,276 +4549,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -4901,46 +4572,375 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -10090,20 +10090,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="361"/>
-      <c r="B1" s="362"/>
-      <c r="C1" s="362"/>
-      <c r="D1" s="362"/>
-      <c r="E1" s="362"/>
-      <c r="F1" s="362"/>
-      <c r="G1" s="362"/>
-      <c r="H1" s="362"/>
-      <c r="I1" s="362"/>
-      <c r="J1" s="362"/>
-      <c r="K1" s="362"/>
-      <c r="L1" s="362"/>
-      <c r="M1" s="362"/>
-      <c r="N1" s="363"/>
+      <c r="A1" s="381"/>
+      <c r="B1" s="382"/>
+      <c r="C1" s="382"/>
+      <c r="D1" s="382"/>
+      <c r="E1" s="382"/>
+      <c r="F1" s="382"/>
+      <c r="G1" s="382"/>
+      <c r="H1" s="382"/>
+      <c r="I1" s="382"/>
+      <c r="J1" s="382"/>
+      <c r="K1" s="382"/>
+      <c r="L1" s="382"/>
+      <c r="M1" s="382"/>
+      <c r="N1" s="383"/>
     </row>
     <row r="2" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="169"/>
@@ -10133,58 +10133,58 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="364" t="s">
+      <c r="A3" s="384" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="365"/>
-      <c r="C3" s="365"/>
-      <c r="D3" s="365"/>
-      <c r="E3" s="365"/>
-      <c r="F3" s="365"/>
-      <c r="G3" s="365"/>
-      <c r="H3" s="365"/>
-      <c r="I3" s="365"/>
-      <c r="J3" s="365"/>
-      <c r="K3" s="365"/>
-      <c r="L3" s="365"/>
-      <c r="M3" s="365"/>
-      <c r="N3" s="366"/>
+      <c r="B3" s="385"/>
+      <c r="C3" s="385"/>
+      <c r="D3" s="385"/>
+      <c r="E3" s="385"/>
+      <c r="F3" s="385"/>
+      <c r="G3" s="385"/>
+      <c r="H3" s="385"/>
+      <c r="I3" s="385"/>
+      <c r="J3" s="385"/>
+      <c r="K3" s="385"/>
+      <c r="L3" s="385"/>
+      <c r="M3" s="385"/>
+      <c r="N3" s="386"/>
     </row>
     <row r="4" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="397" t="s">
+      <c r="A4" s="415" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="398"/>
-      <c r="C4" s="398"/>
-      <c r="D4" s="398"/>
-      <c r="E4" s="398"/>
-      <c r="F4" s="398"/>
-      <c r="G4" s="398"/>
-      <c r="H4" s="398"/>
-      <c r="I4" s="398"/>
-      <c r="J4" s="398"/>
-      <c r="K4" s="398"/>
-      <c r="L4" s="398"/>
-      <c r="M4" s="398"/>
-      <c r="N4" s="399"/>
+      <c r="B4" s="416"/>
+      <c r="C4" s="416"/>
+      <c r="D4" s="416"/>
+      <c r="E4" s="416"/>
+      <c r="F4" s="416"/>
+      <c r="G4" s="416"/>
+      <c r="H4" s="416"/>
+      <c r="I4" s="416"/>
+      <c r="J4" s="416"/>
+      <c r="K4" s="416"/>
+      <c r="L4" s="416"/>
+      <c r="M4" s="416"/>
+      <c r="N4" s="417"/>
     </row>
     <row r="5" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="437" t="s">
+      <c r="A5" s="299" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="438"/>
-      <c r="C5" s="438"/>
-      <c r="D5" s="438"/>
-      <c r="E5" s="438"/>
-      <c r="F5" s="438"/>
-      <c r="G5" s="438"/>
-      <c r="H5" s="438"/>
-      <c r="I5" s="438"/>
-      <c r="J5" s="438"/>
-      <c r="K5" s="438"/>
-      <c r="L5" s="438"/>
-      <c r="M5" s="438"/>
-      <c r="N5" s="439"/>
+      <c r="B5" s="300"/>
+      <c r="C5" s="300"/>
+      <c r="D5" s="300"/>
+      <c r="E5" s="300"/>
+      <c r="F5" s="300"/>
+      <c r="G5" s="300"/>
+      <c r="H5" s="300"/>
+      <c r="I5" s="300"/>
+      <c r="J5" s="300"/>
+      <c r="K5" s="300"/>
+      <c r="L5" s="300"/>
+      <c r="M5" s="300"/>
+      <c r="N5" s="301"/>
     </row>
     <row r="6" spans="1:18" ht="3" hidden="1" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A6" s="205"/>
@@ -10221,42 +10221,42 @@
       <c r="N8" s="164"/>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="367" t="s">
+      <c r="A9" s="387" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="368"/>
-      <c r="C9" s="368"/>
-      <c r="D9" s="368"/>
-      <c r="E9" s="368"/>
-      <c r="F9" s="368"/>
-      <c r="G9" s="368"/>
-      <c r="H9" s="368"/>
-      <c r="I9" s="368"/>
-      <c r="J9" s="368"/>
-      <c r="K9" s="368"/>
-      <c r="L9" s="368"/>
-      <c r="M9" s="368"/>
-      <c r="N9" s="369"/>
+      <c r="B9" s="388"/>
+      <c r="C9" s="388"/>
+      <c r="D9" s="388"/>
+      <c r="E9" s="388"/>
+      <c r="F9" s="388"/>
+      <c r="G9" s="388"/>
+      <c r="H9" s="388"/>
+      <c r="I9" s="388"/>
+      <c r="J9" s="388"/>
+      <c r="K9" s="388"/>
+      <c r="L9" s="388"/>
+      <c r="M9" s="388"/>
+      <c r="N9" s="389"/>
     </row>
     <row r="10" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="174" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="387" t="s">
+      <c r="B10" s="405" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="388"/>
-      <c r="D10" s="378"/>
-      <c r="E10" s="378"/>
-      <c r="F10" s="378"/>
-      <c r="G10" s="378"/>
-      <c r="H10" s="378"/>
-      <c r="I10" s="378"/>
-      <c r="J10" s="378"/>
-      <c r="K10" s="378"/>
-      <c r="L10" s="378"/>
-      <c r="M10" s="378"/>
-      <c r="N10" s="379"/>
+      <c r="C10" s="339"/>
+      <c r="D10" s="398"/>
+      <c r="E10" s="398"/>
+      <c r="F10" s="398"/>
+      <c r="G10" s="398"/>
+      <c r="H10" s="398"/>
+      <c r="I10" s="398"/>
+      <c r="J10" s="398"/>
+      <c r="K10" s="398"/>
+      <c r="L10" s="398"/>
+      <c r="M10" s="398"/>
+      <c r="N10" s="399"/>
       <c r="P10" s="96" t="s">
         <v>11</v>
       </c>
@@ -10265,10 +10265,10 @@
       <c r="A11" s="174" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="389" t="s">
+      <c r="B11" s="406" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="390"/>
+      <c r="C11" s="407"/>
       <c r="D11" s="213"/>
       <c r="E11" s="214"/>
       <c r="F11" s="214"/>
@@ -10277,11 +10277,11 @@
       <c r="I11" s="214"/>
       <c r="J11" s="214"/>
       <c r="K11" s="214"/>
-      <c r="L11" s="409" t="s">
+      <c r="L11" s="340" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="410"/>
-      <c r="N11" s="411"/>
+      <c r="M11" s="341"/>
+      <c r="N11" s="342"/>
       <c r="P11" s="97" t="s">
         <v>15</v>
       </c>
@@ -10291,10 +10291,10 @@
     </row>
     <row r="12" spans="1:18" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="175"/>
-      <c r="B12" s="391" t="s">
+      <c r="B12" s="408" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="392"/>
+      <c r="C12" s="409"/>
       <c r="D12" s="210"/>
       <c r="E12" s="211"/>
       <c r="F12" s="211"/>
@@ -10317,23 +10317,23 @@
       <c r="A13" s="250" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="467" t="s">
+      <c r="B13" s="338" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="388"/>
-      <c r="D13" s="412"/>
-      <c r="E13" s="412"/>
-      <c r="F13" s="413"/>
+      <c r="C13" s="339"/>
+      <c r="D13" s="343"/>
+      <c r="E13" s="343"/>
+      <c r="F13" s="344"/>
       <c r="G13" s="103" t="s">
         <v>22</v>
       </c>
       <c r="H13" s="148"/>
       <c r="I13" s="148"/>
-      <c r="J13" s="419"/>
-      <c r="K13" s="420"/>
-      <c r="L13" s="420"/>
-      <c r="M13" s="420"/>
-      <c r="N13" s="421"/>
+      <c r="J13" s="350"/>
+      <c r="K13" s="351"/>
+      <c r="L13" s="351"/>
+      <c r="M13" s="351"/>
+      <c r="N13" s="352"/>
       <c r="P13" s="97" t="s">
         <v>23</v>
       </c>
@@ -10367,21 +10367,21 @@
         <v>26</v>
       </c>
       <c r="C15" s="98"/>
-      <c r="D15" s="432"/>
-      <c r="E15" s="432"/>
-      <c r="F15" s="433"/>
-      <c r="G15" s="417" t="s">
+      <c r="D15" s="368"/>
+      <c r="E15" s="368"/>
+      <c r="F15" s="369"/>
+      <c r="G15" s="348" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="418"/>
-      <c r="I15" s="418"/>
+      <c r="H15" s="349"/>
+      <c r="I15" s="349"/>
       <c r="J15" s="149"/>
       <c r="K15" s="150"/>
-      <c r="L15" s="422" t="s">
+      <c r="L15" s="354" t="s">
         <v>28</v>
       </c>
-      <c r="M15" s="422"/>
-      <c r="N15" s="423"/>
+      <c r="M15" s="354"/>
+      <c r="N15" s="355"/>
       <c r="P15" s="97" t="s">
         <v>29</v>
       </c>
@@ -10397,14 +10397,14 @@
         <v>32</v>
       </c>
       <c r="C16" s="99"/>
-      <c r="D16" s="380"/>
-      <c r="E16" s="380"/>
-      <c r="F16" s="381"/>
-      <c r="G16" s="414" t="s">
+      <c r="D16" s="400"/>
+      <c r="E16" s="400"/>
+      <c r="F16" s="401"/>
+      <c r="G16" s="345" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="415"/>
-      <c r="I16" s="416"/>
+      <c r="H16" s="346"/>
+      <c r="I16" s="347"/>
       <c r="N16" s="164"/>
       <c r="P16" s="97" t="s">
         <v>34</v>
@@ -10414,49 +10414,49 @@
       </c>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="454">
+      <c r="A17" s="321">
         <v>6</v>
       </c>
-      <c r="B17" s="463" t="s">
+      <c r="B17" s="334" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="464"/>
-      <c r="D17" s="462"/>
-      <c r="E17" s="462"/>
-      <c r="F17" s="462"/>
+      <c r="C17" s="335"/>
+      <c r="D17" s="332"/>
+      <c r="E17" s="332"/>
+      <c r="F17" s="332"/>
       <c r="G17" s="104" t="s">
         <v>37</v>
       </c>
       <c r="H17" s="105"/>
-      <c r="I17" s="342"/>
-      <c r="J17" s="343"/>
-      <c r="K17" s="343"/>
-      <c r="L17" s="343"/>
-      <c r="M17" s="343"/>
-      <c r="N17" s="344"/>
+      <c r="I17" s="364"/>
+      <c r="J17" s="356"/>
+      <c r="K17" s="356"/>
+      <c r="L17" s="356"/>
+      <c r="M17" s="356"/>
+      <c r="N17" s="357"/>
       <c r="Q17" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="455"/>
-      <c r="B18" s="465"/>
-      <c r="C18" s="466"/>
-      <c r="D18" s="385"/>
-      <c r="E18" s="385"/>
-      <c r="F18" s="385"/>
+      <c r="A18" s="322"/>
+      <c r="B18" s="336"/>
+      <c r="C18" s="337"/>
+      <c r="D18" s="333"/>
+      <c r="E18" s="333"/>
+      <c r="F18" s="333"/>
       <c r="G18" s="157"/>
       <c r="H18" s="106"/>
-      <c r="I18" s="425" t="s">
+      <c r="I18" s="359" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="426"/>
-      <c r="K18" s="426"/>
-      <c r="L18" s="426" t="s">
+      <c r="J18" s="302"/>
+      <c r="K18" s="302"/>
+      <c r="L18" s="302" t="s">
         <v>40</v>
       </c>
-      <c r="M18" s="426"/>
-      <c r="N18" s="427"/>
+      <c r="M18" s="302"/>
+      <c r="N18" s="303"/>
       <c r="Q18" s="3" t="s">
         <v>41</v>
       </c>
@@ -10470,100 +10470,100 @@
       <c r="F19" s="165"/>
       <c r="G19" s="157"/>
       <c r="H19" s="106"/>
-      <c r="I19" s="440"/>
-      <c r="J19" s="441"/>
-      <c r="K19" s="441"/>
-      <c r="L19" s="444"/>
-      <c r="M19" s="441"/>
-      <c r="N19" s="445"/>
+      <c r="I19" s="304"/>
+      <c r="J19" s="305"/>
+      <c r="K19" s="305"/>
+      <c r="L19" s="308"/>
+      <c r="M19" s="305"/>
+      <c r="N19" s="309"/>
       <c r="Q19" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="455"/>
+      <c r="A20" s="322"/>
       <c r="B20" s="229"/>
       <c r="C20" s="140"/>
       <c r="D20" s="141"/>
-      <c r="E20" s="385"/>
-      <c r="F20" s="385"/>
+      <c r="E20" s="333"/>
+      <c r="F20" s="333"/>
       <c r="G20" s="155"/>
       <c r="H20" s="163"/>
-      <c r="I20" s="442"/>
-      <c r="J20" s="443"/>
-      <c r="K20" s="443"/>
-      <c r="L20" s="443"/>
-      <c r="M20" s="443"/>
-      <c r="N20" s="446"/>
+      <c r="I20" s="306"/>
+      <c r="J20" s="307"/>
+      <c r="K20" s="307"/>
+      <c r="L20" s="307"/>
+      <c r="M20" s="307"/>
+      <c r="N20" s="310"/>
       <c r="Q20" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="456"/>
+      <c r="A21" s="323"/>
       <c r="B21" s="230"/>
       <c r="C21" s="138"/>
       <c r="D21" s="142"/>
-      <c r="E21" s="386"/>
-      <c r="F21" s="386"/>
+      <c r="E21" s="404"/>
+      <c r="F21" s="404"/>
       <c r="G21" s="155"/>
       <c r="H21" s="163"/>
-      <c r="I21" s="447" t="s">
+      <c r="I21" s="311" t="s">
         <v>44</v>
       </c>
-      <c r="J21" s="448"/>
-      <c r="K21" s="448"/>
-      <c r="L21" s="339" t="s">
+      <c r="J21" s="312"/>
+      <c r="K21" s="312"/>
+      <c r="L21" s="438" t="s">
         <v>45</v>
       </c>
-      <c r="M21" s="340"/>
-      <c r="N21" s="341"/>
+      <c r="M21" s="439"/>
+      <c r="N21" s="440"/>
       <c r="Q21" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="460" t="s">
+      <c r="A22" s="330" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="404" t="s">
+      <c r="B22" s="297" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="405"/>
-      <c r="D22" s="400"/>
-      <c r="E22" s="400"/>
-      <c r="F22" s="400"/>
+      <c r="C22" s="298"/>
+      <c r="D22" s="375"/>
+      <c r="E22" s="375"/>
+      <c r="F22" s="375"/>
       <c r="G22" s="155"/>
       <c r="H22" s="163"/>
-      <c r="I22" s="342"/>
-      <c r="J22" s="343"/>
-      <c r="K22" s="343"/>
-      <c r="L22" s="343"/>
-      <c r="M22" s="343"/>
-      <c r="N22" s="344"/>
+      <c r="I22" s="364"/>
+      <c r="J22" s="356"/>
+      <c r="K22" s="356"/>
+      <c r="L22" s="356"/>
+      <c r="M22" s="356"/>
+      <c r="N22" s="357"/>
       <c r="Q22" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="461"/>
-      <c r="B23" s="406"/>
-      <c r="C23" s="407"/>
-      <c r="D23" s="401"/>
-      <c r="E23" s="401"/>
-      <c r="F23" s="401"/>
+      <c r="A23" s="331"/>
+      <c r="B23" s="376"/>
+      <c r="C23" s="377"/>
+      <c r="D23" s="316"/>
+      <c r="E23" s="316"/>
+      <c r="F23" s="316"/>
       <c r="G23" s="155"/>
       <c r="H23" s="163"/>
-      <c r="I23" s="347" t="s">
+      <c r="I23" s="443" t="s">
         <v>50</v>
       </c>
-      <c r="J23" s="348"/>
-      <c r="K23" s="348"/>
-      <c r="L23" s="345" t="s">
+      <c r="J23" s="444"/>
+      <c r="K23" s="444"/>
+      <c r="L23" s="441" t="s">
         <v>51</v>
       </c>
-      <c r="M23" s="345"/>
-      <c r="N23" s="346"/>
+      <c r="M23" s="441"/>
+      <c r="N23" s="442"/>
       <c r="Q23" s="3" t="s">
         <v>52</v>
       </c>
@@ -10572,132 +10572,132 @@
       <c r="A24" s="174" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="394" t="s">
+      <c r="B24" s="378" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="395"/>
-      <c r="D24" s="424"/>
-      <c r="E24" s="424"/>
-      <c r="F24" s="424"/>
-      <c r="G24" s="354" t="s">
+      <c r="C24" s="379"/>
+      <c r="D24" s="358"/>
+      <c r="E24" s="358"/>
+      <c r="F24" s="358"/>
+      <c r="G24" s="410" t="s">
         <v>55</v>
       </c>
-      <c r="H24" s="332"/>
-      <c r="I24" s="355"/>
-      <c r="J24" s="356"/>
-      <c r="K24" s="356"/>
-      <c r="L24" s="356"/>
-      <c r="M24" s="356"/>
-      <c r="N24" s="357"/>
+      <c r="H24" s="411"/>
+      <c r="I24" s="365"/>
+      <c r="J24" s="366"/>
+      <c r="K24" s="366"/>
+      <c r="L24" s="366"/>
+      <c r="M24" s="366"/>
+      <c r="N24" s="367"/>
       <c r="Q24" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="402" t="s">
+      <c r="A25" s="313" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="404" t="s">
+      <c r="B25" s="297" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="405"/>
-      <c r="D25" s="449"/>
-      <c r="E25" s="449"/>
-      <c r="F25" s="449"/>
+      <c r="C25" s="298"/>
+      <c r="D25" s="315"/>
+      <c r="E25" s="315"/>
+      <c r="F25" s="315"/>
       <c r="G25" s="111" t="s">
         <v>59</v>
       </c>
       <c r="H25" s="100"/>
-      <c r="I25" s="358"/>
-      <c r="J25" s="352"/>
-      <c r="K25" s="352"/>
-      <c r="L25" s="352"/>
-      <c r="M25" s="352"/>
-      <c r="N25" s="353"/>
+      <c r="I25" s="370"/>
+      <c r="J25" s="371"/>
+      <c r="K25" s="371"/>
+      <c r="L25" s="371"/>
+      <c r="M25" s="371"/>
+      <c r="N25" s="448"/>
       <c r="Q25" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="403"/>
-      <c r="B26" s="406"/>
-      <c r="C26" s="407"/>
-      <c r="D26" s="401"/>
-      <c r="E26" s="401"/>
-      <c r="F26" s="401"/>
+      <c r="A26" s="314"/>
+      <c r="B26" s="376"/>
+      <c r="C26" s="377"/>
+      <c r="D26" s="316"/>
+      <c r="E26" s="316"/>
+      <c r="F26" s="316"/>
       <c r="G26" s="155"/>
       <c r="H26" s="163"/>
-      <c r="I26" s="425" t="s">
+      <c r="I26" s="359" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="426"/>
-      <c r="K26" s="426"/>
-      <c r="L26" s="426" t="s">
+      <c r="J26" s="302"/>
+      <c r="K26" s="302"/>
+      <c r="L26" s="302" t="s">
         <v>40</v>
       </c>
-      <c r="M26" s="426"/>
-      <c r="N26" s="427"/>
+      <c r="M26" s="302"/>
+      <c r="N26" s="303"/>
       <c r="Q26" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="402" t="s">
+      <c r="A27" s="313" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="408" t="s">
+      <c r="B27" s="380" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="405"/>
-      <c r="D27" s="449"/>
-      <c r="E27" s="449"/>
-      <c r="F27" s="449"/>
+      <c r="C27" s="298"/>
+      <c r="D27" s="315"/>
+      <c r="E27" s="315"/>
+      <c r="F27" s="315"/>
       <c r="G27" s="157"/>
       <c r="H27" s="106"/>
-      <c r="I27" s="358"/>
-      <c r="J27" s="352"/>
-      <c r="K27" s="352"/>
-      <c r="L27" s="352"/>
-      <c r="M27" s="352"/>
-      <c r="N27" s="353"/>
+      <c r="I27" s="370"/>
+      <c r="J27" s="371"/>
+      <c r="K27" s="371"/>
+      <c r="L27" s="371"/>
+      <c r="M27" s="371"/>
+      <c r="N27" s="448"/>
       <c r="Q27" s="3" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="403"/>
-      <c r="B28" s="406"/>
-      <c r="C28" s="407"/>
-      <c r="D28" s="401"/>
-      <c r="E28" s="401"/>
-      <c r="F28" s="401"/>
+      <c r="A28" s="314"/>
+      <c r="B28" s="376"/>
+      <c r="C28" s="377"/>
+      <c r="D28" s="316"/>
+      <c r="E28" s="316"/>
+      <c r="F28" s="316"/>
       <c r="G28" s="157"/>
       <c r="H28" s="106"/>
-      <c r="I28" s="428" t="s">
+      <c r="I28" s="360" t="s">
         <v>44</v>
       </c>
-      <c r="J28" s="429"/>
-      <c r="K28" s="429"/>
-      <c r="L28" s="430" t="s">
+      <c r="J28" s="361"/>
+      <c r="K28" s="361"/>
+      <c r="L28" s="362" t="s">
         <v>45</v>
       </c>
-      <c r="M28" s="429"/>
-      <c r="N28" s="431"/>
+      <c r="M28" s="361"/>
+      <c r="N28" s="363"/>
       <c r="Q28" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="402" t="s">
+      <c r="A29" s="313" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="404" t="s">
+      <c r="B29" s="297" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="405"/>
-      <c r="D29" s="450"/>
-      <c r="E29" s="449"/>
-      <c r="F29" s="451"/>
+      <c r="C29" s="298"/>
+      <c r="D29" s="317"/>
+      <c r="E29" s="315"/>
+      <c r="F29" s="318"/>
       <c r="G29" s="157"/>
       <c r="H29" s="167"/>
       <c r="I29" s="159"/>
@@ -10711,24 +10711,24 @@
       </c>
     </row>
     <row r="30" spans="1:17" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="403"/>
-      <c r="B30" s="406"/>
-      <c r="C30" s="407"/>
-      <c r="D30" s="452"/>
-      <c r="E30" s="401"/>
-      <c r="F30" s="453"/>
+      <c r="A30" s="314"/>
+      <c r="B30" s="376"/>
+      <c r="C30" s="377"/>
+      <c r="D30" s="319"/>
+      <c r="E30" s="316"/>
+      <c r="F30" s="320"/>
       <c r="G30" s="157"/>
       <c r="H30" s="167"/>
-      <c r="I30" s="349" t="s">
+      <c r="I30" s="445" t="s">
         <v>50</v>
       </c>
-      <c r="J30" s="349"/>
-      <c r="K30" s="349"/>
-      <c r="L30" s="349" t="s">
+      <c r="J30" s="445"/>
+      <c r="K30" s="445"/>
+      <c r="L30" s="445" t="s">
         <v>51</v>
       </c>
-      <c r="M30" s="349"/>
-      <c r="N30" s="350"/>
+      <c r="M30" s="445"/>
+      <c r="N30" s="446"/>
       <c r="Q30" s="3" t="s">
         <v>69</v>
       </c>
@@ -10741,19 +10741,19 @@
         <v>71</v>
       </c>
       <c r="C31" s="99"/>
-      <c r="D31" s="384"/>
-      <c r="E31" s="384"/>
-      <c r="F31" s="384"/>
-      <c r="G31" s="354" t="s">
+      <c r="D31" s="353"/>
+      <c r="E31" s="353"/>
+      <c r="F31" s="353"/>
+      <c r="G31" s="410" t="s">
         <v>55</v>
       </c>
-      <c r="H31" s="332"/>
-      <c r="I31" s="347"/>
-      <c r="J31" s="348"/>
-      <c r="K31" s="348"/>
-      <c r="L31" s="339"/>
-      <c r="M31" s="339"/>
-      <c r="N31" s="351"/>
+      <c r="H31" s="411"/>
+      <c r="I31" s="443"/>
+      <c r="J31" s="444"/>
+      <c r="K31" s="444"/>
+      <c r="L31" s="438"/>
+      <c r="M31" s="438"/>
+      <c r="N31" s="447"/>
       <c r="Q31" s="3" t="s">
         <v>72</v>
       </c>
@@ -10766,42 +10766,42 @@
         <v>74</v>
       </c>
       <c r="C32" s="99"/>
-      <c r="D32" s="424"/>
-      <c r="E32" s="424"/>
-      <c r="F32" s="424"/>
+      <c r="D32" s="358"/>
+      <c r="E32" s="358"/>
+      <c r="F32" s="358"/>
       <c r="G32" s="154" t="s">
         <v>75</v>
       </c>
       <c r="H32" s="158"/>
-      <c r="I32" s="355"/>
-      <c r="J32" s="356"/>
-      <c r="K32" s="356"/>
-      <c r="L32" s="356"/>
-      <c r="M32" s="356"/>
-      <c r="N32" s="357"/>
+      <c r="I32" s="365"/>
+      <c r="J32" s="366"/>
+      <c r="K32" s="366"/>
+      <c r="L32" s="366"/>
+      <c r="M32" s="366"/>
+      <c r="N32" s="367"/>
       <c r="Q32" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="393" t="s">
+      <c r="A33" s="413" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="394"/>
-      <c r="C33" s="395"/>
-      <c r="D33" s="396"/>
-      <c r="E33" s="396"/>
-      <c r="F33" s="396"/>
+      <c r="B33" s="378"/>
+      <c r="C33" s="379"/>
+      <c r="D33" s="414"/>
+      <c r="E33" s="414"/>
+      <c r="F33" s="414"/>
       <c r="G33" s="212" t="s">
         <v>78</v>
       </c>
       <c r="H33" s="156"/>
-      <c r="I33" s="355"/>
-      <c r="J33" s="356"/>
-      <c r="K33" s="356"/>
-      <c r="L33" s="356"/>
-      <c r="M33" s="356"/>
-      <c r="N33" s="357"/>
+      <c r="I33" s="365"/>
+      <c r="J33" s="366"/>
+      <c r="K33" s="366"/>
+      <c r="L33" s="366"/>
+      <c r="M33" s="366"/>
+      <c r="N33" s="367"/>
       <c r="Q33" s="3" t="s">
         <v>79</v>
       </c>
@@ -10812,19 +10812,19 @@
       </c>
       <c r="B34" s="231"/>
       <c r="C34" s="161"/>
-      <c r="D34" s="384"/>
-      <c r="E34" s="384"/>
-      <c r="F34" s="384"/>
+      <c r="D34" s="353"/>
+      <c r="E34" s="353"/>
+      <c r="F34" s="353"/>
       <c r="G34" s="111" t="s">
         <v>81</v>
       </c>
       <c r="H34" s="100"/>
-      <c r="I34" s="434"/>
-      <c r="J34" s="435"/>
-      <c r="K34" s="435"/>
-      <c r="L34" s="435"/>
-      <c r="M34" s="435"/>
-      <c r="N34" s="436"/>
+      <c r="I34" s="372"/>
+      <c r="J34" s="373"/>
+      <c r="K34" s="373"/>
+      <c r="L34" s="373"/>
+      <c r="M34" s="373"/>
+      <c r="N34" s="374"/>
       <c r="Q34" s="3" t="s">
         <v>82</v>
       </c>
@@ -10858,21 +10858,21 @@
         <v>86</v>
       </c>
       <c r="C36" s="236"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="458"/>
-      <c r="F36" s="458"/>
-      <c r="G36" s="458"/>
-      <c r="H36" s="459"/>
-      <c r="I36" s="359" t="s">
+      <c r="D36" s="324"/>
+      <c r="E36" s="325"/>
+      <c r="F36" s="325"/>
+      <c r="G36" s="325"/>
+      <c r="H36" s="326"/>
+      <c r="I36" s="449" t="s">
         <v>87</v>
       </c>
-      <c r="J36" s="359"/>
-      <c r="K36" s="359"/>
-      <c r="L36" s="360"/>
-      <c r="M36" s="372" t="s">
+      <c r="J36" s="449"/>
+      <c r="K36" s="449"/>
+      <c r="L36" s="450"/>
+      <c r="M36" s="392" t="s">
         <v>88</v>
       </c>
-      <c r="N36" s="373"/>
+      <c r="N36" s="393"/>
       <c r="Q36" s="3" t="s">
         <v>89</v>
       </c>
@@ -10883,17 +10883,17 @@
         <v>90</v>
       </c>
       <c r="C37" s="167"/>
-      <c r="D37" s="295"/>
-      <c r="E37" s="296"/>
-      <c r="F37" s="297"/>
-      <c r="G37" s="311" t="s">
+      <c r="D37" s="327"/>
+      <c r="E37" s="328"/>
+      <c r="F37" s="329"/>
+      <c r="G37" s="412" t="s">
         <v>91</v>
       </c>
-      <c r="H37" s="311"/>
-      <c r="I37" s="293"/>
-      <c r="J37" s="293"/>
-      <c r="K37" s="293"/>
-      <c r="L37" s="294"/>
+      <c r="H37" s="412"/>
+      <c r="I37" s="284"/>
+      <c r="J37" s="284"/>
+      <c r="K37" s="284"/>
+      <c r="L37" s="285"/>
       <c r="M37" s="291"/>
       <c r="N37" s="292"/>
       <c r="Q37" s="3" t="s">
@@ -10906,15 +10906,15 @@
         <v>93</v>
       </c>
       <c r="C38" s="226"/>
-      <c r="D38" s="295"/>
-      <c r="E38" s="296"/>
-      <c r="F38" s="296"/>
-      <c r="G38" s="296"/>
-      <c r="H38" s="297"/>
-      <c r="I38" s="293"/>
-      <c r="J38" s="293"/>
-      <c r="K38" s="293"/>
-      <c r="L38" s="294"/>
+      <c r="D38" s="327"/>
+      <c r="E38" s="328"/>
+      <c r="F38" s="328"/>
+      <c r="G38" s="328"/>
+      <c r="H38" s="329"/>
+      <c r="I38" s="284"/>
+      <c r="J38" s="284"/>
+      <c r="K38" s="284"/>
+      <c r="L38" s="285"/>
       <c r="M38" s="291"/>
       <c r="N38" s="292"/>
       <c r="Q38" s="3" t="s">
@@ -10927,15 +10927,15 @@
         <v>95</v>
       </c>
       <c r="C39" s="99"/>
-      <c r="D39" s="295"/>
-      <c r="E39" s="296"/>
-      <c r="F39" s="296"/>
-      <c r="G39" s="296"/>
-      <c r="H39" s="297"/>
-      <c r="I39" s="293"/>
-      <c r="J39" s="293"/>
-      <c r="K39" s="293"/>
-      <c r="L39" s="294"/>
+      <c r="D39" s="327"/>
+      <c r="E39" s="328"/>
+      <c r="F39" s="328"/>
+      <c r="G39" s="328"/>
+      <c r="H39" s="329"/>
+      <c r="I39" s="284"/>
+      <c r="J39" s="284"/>
+      <c r="K39" s="284"/>
+      <c r="L39" s="285"/>
       <c r="M39" s="291"/>
       <c r="N39" s="292"/>
       <c r="Q39" s="3" t="s">
@@ -10948,15 +10948,15 @@
         <v>97</v>
       </c>
       <c r="C40" s="99"/>
-      <c r="D40" s="295"/>
-      <c r="E40" s="296"/>
-      <c r="F40" s="296"/>
-      <c r="G40" s="296"/>
-      <c r="H40" s="297"/>
-      <c r="I40" s="293"/>
-      <c r="J40" s="293"/>
-      <c r="K40" s="293"/>
-      <c r="L40" s="294"/>
+      <c r="D40" s="327"/>
+      <c r="E40" s="328"/>
+      <c r="F40" s="328"/>
+      <c r="G40" s="328"/>
+      <c r="H40" s="329"/>
+      <c r="I40" s="284"/>
+      <c r="J40" s="284"/>
+      <c r="K40" s="284"/>
+      <c r="L40" s="285"/>
       <c r="M40" s="291"/>
       <c r="N40" s="292"/>
       <c r="Q40" s="3" t="s">
@@ -10969,15 +10969,15 @@
         <v>99</v>
       </c>
       <c r="C41" s="99"/>
-      <c r="D41" s="295"/>
-      <c r="E41" s="296"/>
-      <c r="F41" s="296"/>
-      <c r="G41" s="296"/>
-      <c r="H41" s="297"/>
-      <c r="I41" s="293"/>
-      <c r="J41" s="293"/>
-      <c r="K41" s="293"/>
-      <c r="L41" s="294"/>
+      <c r="D41" s="327"/>
+      <c r="E41" s="328"/>
+      <c r="F41" s="328"/>
+      <c r="G41" s="328"/>
+      <c r="H41" s="329"/>
+      <c r="I41" s="284"/>
+      <c r="J41" s="284"/>
+      <c r="K41" s="284"/>
+      <c r="L41" s="285"/>
       <c r="M41" s="291"/>
       <c r="N41" s="292"/>
       <c r="Q41" s="3" t="s">
@@ -10990,15 +10990,15 @@
         <v>101</v>
       </c>
       <c r="C42" s="139"/>
-      <c r="D42" s="295"/>
-      <c r="E42" s="296"/>
-      <c r="F42" s="296"/>
-      <c r="G42" s="296"/>
-      <c r="H42" s="297"/>
-      <c r="I42" s="293"/>
-      <c r="J42" s="293"/>
-      <c r="K42" s="293"/>
-      <c r="L42" s="294"/>
+      <c r="D42" s="327"/>
+      <c r="E42" s="328"/>
+      <c r="F42" s="328"/>
+      <c r="G42" s="328"/>
+      <c r="H42" s="329"/>
+      <c r="I42" s="284"/>
+      <c r="J42" s="284"/>
+      <c r="K42" s="284"/>
+      <c r="L42" s="285"/>
       <c r="M42" s="291"/>
       <c r="N42" s="292"/>
       <c r="Q42" s="3" t="s">
@@ -11013,15 +11013,15 @@
         <v>104</v>
       </c>
       <c r="C43" s="105"/>
-      <c r="D43" s="295"/>
-      <c r="E43" s="296"/>
-      <c r="F43" s="296"/>
-      <c r="G43" s="296"/>
-      <c r="H43" s="297"/>
-      <c r="I43" s="293"/>
-      <c r="J43" s="293"/>
-      <c r="K43" s="293"/>
-      <c r="L43" s="294"/>
+      <c r="D43" s="327"/>
+      <c r="E43" s="328"/>
+      <c r="F43" s="328"/>
+      <c r="G43" s="328"/>
+      <c r="H43" s="329"/>
+      <c r="I43" s="284"/>
+      <c r="J43" s="284"/>
+      <c r="K43" s="284"/>
+      <c r="L43" s="285"/>
       <c r="M43" s="291"/>
       <c r="N43" s="292"/>
       <c r="Q43" s="3" t="s">
@@ -11034,17 +11034,17 @@
         <v>13</v>
       </c>
       <c r="C44" s="163"/>
-      <c r="D44" s="295"/>
-      <c r="E44" s="296"/>
-      <c r="F44" s="297"/>
-      <c r="G44" s="311" t="s">
+      <c r="D44" s="327"/>
+      <c r="E44" s="328"/>
+      <c r="F44" s="329"/>
+      <c r="G44" s="412" t="s">
         <v>106</v>
       </c>
-      <c r="H44" s="311"/>
-      <c r="I44" s="293"/>
-      <c r="J44" s="293"/>
-      <c r="K44" s="293"/>
-      <c r="L44" s="294"/>
+      <c r="H44" s="412"/>
+      <c r="I44" s="284"/>
+      <c r="J44" s="284"/>
+      <c r="K44" s="284"/>
+      <c r="L44" s="285"/>
       <c r="M44" s="291"/>
       <c r="N44" s="292"/>
       <c r="Q44" s="3" t="s">
@@ -11057,15 +11057,15 @@
         <v>17</v>
       </c>
       <c r="C45" s="219"/>
-      <c r="D45" s="295"/>
-      <c r="E45" s="296"/>
-      <c r="F45" s="296"/>
-      <c r="G45" s="296"/>
-      <c r="H45" s="297"/>
-      <c r="I45" s="293"/>
-      <c r="J45" s="293"/>
-      <c r="K45" s="293"/>
-      <c r="L45" s="294"/>
+      <c r="D45" s="327"/>
+      <c r="E45" s="328"/>
+      <c r="F45" s="328"/>
+      <c r="G45" s="328"/>
+      <c r="H45" s="329"/>
+      <c r="I45" s="284"/>
+      <c r="J45" s="284"/>
+      <c r="K45" s="284"/>
+      <c r="L45" s="285"/>
       <c r="M45" s="291"/>
       <c r="N45" s="292"/>
       <c r="Q45" s="3" t="s">
@@ -11076,19 +11076,19 @@
       <c r="A46" s="155" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="404" t="s">
+      <c r="B46" s="297" t="s">
         <v>110</v>
       </c>
-      <c r="C46" s="404"/>
-      <c r="D46" s="404"/>
-      <c r="E46" s="404"/>
-      <c r="F46" s="404"/>
-      <c r="G46" s="404"/>
-      <c r="H46" s="405"/>
-      <c r="I46" s="293"/>
-      <c r="J46" s="293"/>
-      <c r="K46" s="293"/>
-      <c r="L46" s="294"/>
+      <c r="C46" s="297"/>
+      <c r="D46" s="297"/>
+      <c r="E46" s="297"/>
+      <c r="F46" s="297"/>
+      <c r="G46" s="297"/>
+      <c r="H46" s="298"/>
+      <c r="I46" s="284"/>
+      <c r="J46" s="284"/>
+      <c r="K46" s="284"/>
+      <c r="L46" s="285"/>
       <c r="M46" s="291"/>
       <c r="N46" s="292"/>
       <c r="Q46" s="3" t="s">
@@ -11101,15 +11101,15 @@
         <v>10</v>
       </c>
       <c r="C47" s="163"/>
-      <c r="D47" s="308"/>
-      <c r="E47" s="309"/>
-      <c r="F47" s="309"/>
-      <c r="G47" s="309"/>
-      <c r="H47" s="310"/>
-      <c r="I47" s="293"/>
-      <c r="J47" s="293"/>
-      <c r="K47" s="293"/>
-      <c r="L47" s="294"/>
+      <c r="D47" s="471"/>
+      <c r="E47" s="472"/>
+      <c r="F47" s="472"/>
+      <c r="G47" s="472"/>
+      <c r="H47" s="473"/>
+      <c r="I47" s="284"/>
+      <c r="J47" s="284"/>
+      <c r="K47" s="284"/>
+      <c r="L47" s="285"/>
       <c r="M47" s="291"/>
       <c r="N47" s="292"/>
       <c r="Q47" s="3" t="s">
@@ -11122,15 +11122,15 @@
         <v>13</v>
       </c>
       <c r="C48" s="163"/>
-      <c r="D48" s="308"/>
-      <c r="E48" s="309"/>
-      <c r="F48" s="309"/>
-      <c r="G48" s="309"/>
-      <c r="H48" s="310"/>
-      <c r="I48" s="293"/>
-      <c r="J48" s="293"/>
-      <c r="K48" s="293"/>
-      <c r="L48" s="294"/>
+      <c r="D48" s="471"/>
+      <c r="E48" s="472"/>
+      <c r="F48" s="472"/>
+      <c r="G48" s="472"/>
+      <c r="H48" s="473"/>
+      <c r="I48" s="284"/>
+      <c r="J48" s="284"/>
+      <c r="K48" s="284"/>
+      <c r="L48" s="285"/>
       <c r="M48" s="291"/>
       <c r="N48" s="292"/>
       <c r="Q48" s="3" t="s">
@@ -11143,19 +11143,19 @@
         <v>17</v>
       </c>
       <c r="C49" s="221"/>
-      <c r="D49" s="470"/>
-      <c r="E49" s="471"/>
-      <c r="F49" s="471"/>
-      <c r="G49" s="471"/>
-      <c r="H49" s="472"/>
-      <c r="I49" s="468" t="s">
+      <c r="D49" s="288"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="289"/>
+      <c r="G49" s="289"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="286" t="s">
         <v>114</v>
       </c>
-      <c r="J49" s="468"/>
-      <c r="K49" s="468"/>
-      <c r="L49" s="468"/>
-      <c r="M49" s="468"/>
-      <c r="N49" s="469"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="286"/>
+      <c r="L49" s="286"/>
+      <c r="M49" s="286"/>
+      <c r="N49" s="287"/>
       <c r="Q49" s="3" t="s">
         <v>115</v>
       </c>
@@ -11171,47 +11171,47 @@
       <c r="F50" s="102"/>
       <c r="G50" s="102"/>
       <c r="H50" s="102"/>
-      <c r="I50" s="382" t="s">
+      <c r="I50" s="402" t="s">
         <v>117</v>
       </c>
-      <c r="J50" s="382"/>
-      <c r="K50" s="382"/>
-      <c r="L50" s="382"/>
-      <c r="M50" s="382"/>
-      <c r="N50" s="383"/>
+      <c r="J50" s="402"/>
+      <c r="K50" s="402"/>
+      <c r="L50" s="402"/>
+      <c r="M50" s="402"/>
+      <c r="N50" s="403"/>
       <c r="Q50" s="3" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="374" t="s">
+      <c r="A51" s="394" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="327" t="s">
+      <c r="B51" s="421" t="s">
         <v>120</v>
       </c>
-      <c r="C51" s="327"/>
-      <c r="D51" s="312" t="s">
+      <c r="C51" s="421"/>
+      <c r="D51" s="424" t="s">
         <v>121</v>
       </c>
-      <c r="E51" s="313"/>
-      <c r="F51" s="330"/>
-      <c r="G51" s="312" t="s">
+      <c r="E51" s="425"/>
+      <c r="F51" s="426"/>
+      <c r="G51" s="424" t="s">
         <v>122</v>
       </c>
-      <c r="H51" s="313"/>
-      <c r="I51" s="314"/>
-      <c r="J51" s="473" t="s">
+      <c r="H51" s="425"/>
+      <c r="I51" s="474"/>
+      <c r="J51" s="293" t="s">
         <v>123</v>
       </c>
-      <c r="K51" s="474"/>
-      <c r="L51" s="303" t="s">
+      <c r="K51" s="294"/>
+      <c r="L51" s="466" t="s">
         <v>124</v>
       </c>
-      <c r="M51" s="376" t="s">
+      <c r="M51" s="396" t="s">
         <v>125</v>
       </c>
-      <c r="N51" s="370" t="s">
+      <c r="N51" s="390" t="s">
         <v>126</v>
       </c>
       <c r="Q51" s="3" t="s">
@@ -11219,43 +11219,43 @@
       </c>
     </row>
     <row r="52" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="375"/>
-      <c r="B52" s="328"/>
-      <c r="C52" s="328"/>
-      <c r="D52" s="315"/>
-      <c r="E52" s="316"/>
-      <c r="F52" s="331"/>
-      <c r="G52" s="315"/>
-      <c r="H52" s="316"/>
-      <c r="I52" s="317"/>
-      <c r="J52" s="475"/>
-      <c r="K52" s="476"/>
-      <c r="L52" s="303"/>
-      <c r="M52" s="376"/>
-      <c r="N52" s="370"/>
+      <c r="A52" s="395"/>
+      <c r="B52" s="422"/>
+      <c r="C52" s="422"/>
+      <c r="D52" s="427"/>
+      <c r="E52" s="428"/>
+      <c r="F52" s="429"/>
+      <c r="G52" s="427"/>
+      <c r="H52" s="428"/>
+      <c r="I52" s="475"/>
+      <c r="J52" s="295"/>
+      <c r="K52" s="296"/>
+      <c r="L52" s="466"/>
+      <c r="M52" s="396"/>
+      <c r="N52" s="390"/>
       <c r="Q52" s="3" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="234"/>
-      <c r="B53" s="329"/>
-      <c r="C53" s="329"/>
-      <c r="D53" s="318"/>
-      <c r="E53" s="319"/>
-      <c r="F53" s="332"/>
-      <c r="G53" s="318"/>
-      <c r="H53" s="319"/>
-      <c r="I53" s="320"/>
+      <c r="B53" s="423"/>
+      <c r="C53" s="423"/>
+      <c r="D53" s="430"/>
+      <c r="E53" s="431"/>
+      <c r="F53" s="411"/>
+      <c r="G53" s="430"/>
+      <c r="H53" s="431"/>
+      <c r="I53" s="476"/>
       <c r="J53" s="107" t="s">
         <v>129</v>
       </c>
       <c r="K53" s="108" t="s">
         <v>130</v>
       </c>
-      <c r="L53" s="304"/>
-      <c r="M53" s="377"/>
-      <c r="N53" s="371"/>
+      <c r="L53" s="467"/>
+      <c r="M53" s="397"/>
+      <c r="N53" s="391"/>
       <c r="O53" s="109"/>
       <c r="P53" s="109"/>
       <c r="Q53" s="3" t="s">
@@ -11268,12 +11268,12 @@
         <v>132</v>
       </c>
       <c r="C54" s="240"/>
-      <c r="D54" s="333"/>
-      <c r="E54" s="334"/>
-      <c r="F54" s="335"/>
-      <c r="G54" s="305"/>
-      <c r="H54" s="306"/>
-      <c r="I54" s="307"/>
+      <c r="D54" s="432"/>
+      <c r="E54" s="433"/>
+      <c r="F54" s="434"/>
+      <c r="G54" s="468"/>
+      <c r="H54" s="469"/>
+      <c r="I54" s="470"/>
       <c r="J54" s="23"/>
       <c r="K54" s="233"/>
       <c r="L54" s="168"/>
@@ -11289,12 +11289,12 @@
         <v>134</v>
       </c>
       <c r="C55" s="240"/>
-      <c r="D55" s="333"/>
-      <c r="E55" s="334"/>
-      <c r="F55" s="335"/>
-      <c r="G55" s="305"/>
-      <c r="H55" s="306"/>
-      <c r="I55" s="307"/>
+      <c r="D55" s="432"/>
+      <c r="E55" s="433"/>
+      <c r="F55" s="434"/>
+      <c r="G55" s="468"/>
+      <c r="H55" s="469"/>
+      <c r="I55" s="470"/>
       <c r="J55" s="23"/>
       <c r="K55" s="24"/>
       <c r="L55" s="243"/>
@@ -11310,12 +11310,12 @@
         <v>136</v>
       </c>
       <c r="C56" s="240"/>
-      <c r="D56" s="333"/>
-      <c r="E56" s="334"/>
-      <c r="F56" s="335"/>
-      <c r="G56" s="321"/>
-      <c r="H56" s="322"/>
-      <c r="I56" s="323"/>
+      <c r="D56" s="432"/>
+      <c r="E56" s="433"/>
+      <c r="F56" s="434"/>
+      <c r="G56" s="281"/>
+      <c r="H56" s="282"/>
+      <c r="I56" s="283"/>
       <c r="J56" s="23"/>
       <c r="K56" s="24"/>
       <c r="L56" s="168"/>
@@ -11331,12 +11331,12 @@
         <v>138</v>
       </c>
       <c r="C57" s="240"/>
-      <c r="D57" s="333"/>
-      <c r="E57" s="334"/>
-      <c r="F57" s="335"/>
-      <c r="G57" s="321"/>
-      <c r="H57" s="322"/>
-      <c r="I57" s="323"/>
+      <c r="D57" s="432"/>
+      <c r="E57" s="433"/>
+      <c r="F57" s="434"/>
+      <c r="G57" s="281"/>
+      <c r="H57" s="282"/>
+      <c r="I57" s="283"/>
       <c r="J57" s="23"/>
       <c r="K57" s="24"/>
       <c r="L57" s="168"/>
@@ -11352,12 +11352,12 @@
         <v>140</v>
       </c>
       <c r="C58" s="242"/>
-      <c r="D58" s="336"/>
-      <c r="E58" s="337"/>
-      <c r="F58" s="338"/>
-      <c r="G58" s="324"/>
-      <c r="H58" s="325"/>
-      <c r="I58" s="326"/>
+      <c r="D58" s="435"/>
+      <c r="E58" s="436"/>
+      <c r="F58" s="437"/>
+      <c r="G58" s="418"/>
+      <c r="H58" s="419"/>
+      <c r="I58" s="420"/>
       <c r="J58" s="237"/>
       <c r="K58" s="238"/>
       <c r="L58" s="17"/>
@@ -11368,68 +11368,68 @@
       </c>
     </row>
     <row r="59" spans="1:17" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="285" t="s">
+      <c r="A59" s="455" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="286"/>
-      <c r="C59" s="286"/>
-      <c r="D59" s="286"/>
-      <c r="E59" s="286"/>
-      <c r="F59" s="286"/>
-      <c r="G59" s="286"/>
-      <c r="H59" s="286"/>
-      <c r="I59" s="286"/>
-      <c r="J59" s="286"/>
-      <c r="K59" s="286"/>
-      <c r="L59" s="286"/>
-      <c r="M59" s="286"/>
-      <c r="N59" s="287"/>
+      <c r="B59" s="456"/>
+      <c r="C59" s="456"/>
+      <c r="D59" s="456"/>
+      <c r="E59" s="456"/>
+      <c r="F59" s="456"/>
+      <c r="G59" s="456"/>
+      <c r="H59" s="456"/>
+      <c r="I59" s="456"/>
+      <c r="J59" s="456"/>
+      <c r="K59" s="456"/>
+      <c r="L59" s="456"/>
+      <c r="M59" s="456"/>
+      <c r="N59" s="457"/>
       <c r="Q59" s="3" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="282" t="s">
+      <c r="A60" s="452" t="s">
         <v>143</v>
       </c>
-      <c r="B60" s="283"/>
-      <c r="C60" s="284"/>
-      <c r="D60" s="298" t="s">
+      <c r="B60" s="453"/>
+      <c r="C60" s="454"/>
+      <c r="D60" s="461" t="s">
         <v>144</v>
       </c>
-      <c r="E60" s="299"/>
-      <c r="F60" s="299"/>
-      <c r="G60" s="299"/>
-      <c r="H60" s="299"/>
-      <c r="I60" s="300"/>
-      <c r="J60" s="301" t="s">
+      <c r="E60" s="462"/>
+      <c r="F60" s="462"/>
+      <c r="G60" s="462"/>
+      <c r="H60" s="462"/>
+      <c r="I60" s="463"/>
+      <c r="J60" s="464" t="s">
         <v>145</v>
       </c>
-      <c r="K60" s="302"/>
-      <c r="L60" s="288"/>
-      <c r="M60" s="289"/>
-      <c r="N60" s="290"/>
+      <c r="K60" s="465"/>
+      <c r="L60" s="458"/>
+      <c r="M60" s="459"/>
+      <c r="N60" s="460"/>
       <c r="Q60" s="3" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="146" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="281" t="s">
+      <c r="A61" s="451" t="s">
         <v>404</v>
       </c>
-      <c r="B61" s="281"/>
-      <c r="C61" s="281"/>
-      <c r="D61" s="281"/>
-      <c r="E61" s="281"/>
-      <c r="F61" s="281"/>
-      <c r="G61" s="281"/>
-      <c r="H61" s="281"/>
-      <c r="I61" s="281"/>
-      <c r="J61" s="281"/>
-      <c r="K61" s="281"/>
-      <c r="L61" s="281"/>
-      <c r="M61" s="281"/>
-      <c r="N61" s="281"/>
+      <c r="B61" s="451"/>
+      <c r="C61" s="451"/>
+      <c r="D61" s="451"/>
+      <c r="E61" s="451"/>
+      <c r="F61" s="451"/>
+      <c r="G61" s="451"/>
+      <c r="H61" s="451"/>
+      <c r="I61" s="451"/>
+      <c r="J61" s="451"/>
+      <c r="K61" s="451"/>
+      <c r="L61" s="451"/>
+      <c r="M61" s="451"/>
+      <c r="N61" s="451"/>
       <c r="Q61" s="256" t="s">
         <v>147</v>
       </c>
@@ -15158,15 +15158,113 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="140">
-    <mergeCell ref="G57:I57"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I49:N49"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="J51:K52"/>
-    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="A61:N61"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A59:N59"/>
+    <mergeCell ref="L60:N60"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="M45:N45"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="L51:L53"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="G51:I53"/>
+    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="G58:I58"/>
+    <mergeCell ref="B51:C53"/>
+    <mergeCell ref="D51:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="I32:N32"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="N51:N53"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="M51:M53"/>
+    <mergeCell ref="D10:N10"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="I50:N50"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="E20:F21"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="D22:F23"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C26"/>
+    <mergeCell ref="B27:C28"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I24:N24"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I33:N33"/>
+    <mergeCell ref="I34:N34"/>
     <mergeCell ref="I41:L41"/>
     <mergeCell ref="M41:N41"/>
     <mergeCell ref="M42:N42"/>
@@ -15191,113 +15289,15 @@
     <mergeCell ref="D17:F18"/>
     <mergeCell ref="B17:C18"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I24:N24"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I33:N33"/>
-    <mergeCell ref="I34:N34"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="D22:F23"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C26"/>
-    <mergeCell ref="B27:C28"/>
-    <mergeCell ref="B29:C30"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="N51:N53"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="M51:M53"/>
-    <mergeCell ref="D10:N10"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="I50:N50"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="E20:F21"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="G58:I58"/>
-    <mergeCell ref="B51:C53"/>
-    <mergeCell ref="D51:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="I32:N32"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="A61:N61"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A59:N59"/>
-    <mergeCell ref="L60:N60"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="M45:N45"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="L51:L53"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="G51:I53"/>
-    <mergeCell ref="G55:I55"/>
-    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="G57:I57"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="I49:N49"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="J51:K52"/>
+    <mergeCell ref="B46:H46"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -15806,68 +15806,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="477"/>
-      <c r="B1" s="478"/>
-      <c r="C1" s="478"/>
-      <c r="D1" s="478"/>
-      <c r="E1" s="478"/>
-      <c r="F1" s="478"/>
-      <c r="G1" s="478"/>
-      <c r="H1" s="478"/>
-      <c r="I1" s="478"/>
-      <c r="J1" s="478"/>
-      <c r="K1" s="479"/>
+      <c r="A1" s="504"/>
+      <c r="B1" s="505"/>
+      <c r="C1" s="505"/>
+      <c r="D1" s="505"/>
+      <c r="E1" s="505"/>
+      <c r="F1" s="505"/>
+      <c r="G1" s="505"/>
+      <c r="H1" s="505"/>
+      <c r="I1" s="505"/>
+      <c r="J1" s="505"/>
+      <c r="K1" s="506"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="489" t="s">
+      <c r="A2" s="515" t="s">
         <v>304</v>
       </c>
-      <c r="B2" s="490"/>
-      <c r="C2" s="490"/>
-      <c r="D2" s="490"/>
-      <c r="E2" s="490"/>
-      <c r="F2" s="490"/>
-      <c r="G2" s="490"/>
-      <c r="H2" s="490"/>
-      <c r="I2" s="490"/>
-      <c r="J2" s="490"/>
-      <c r="K2" s="491"/>
+      <c r="B2" s="516"/>
+      <c r="C2" s="516"/>
+      <c r="D2" s="516"/>
+      <c r="E2" s="516"/>
+      <c r="F2" s="516"/>
+      <c r="G2" s="516"/>
+      <c r="H2" s="516"/>
+      <c r="I2" s="516"/>
+      <c r="J2" s="516"/>
+      <c r="K2" s="517"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="143" t="s">
         <v>305</v>
       </c>
-      <c r="B3" s="480" t="s">
+      <c r="B3" s="507" t="s">
         <v>306</v>
       </c>
-      <c r="C3" s="480"/>
-      <c r="D3" s="480"/>
-      <c r="E3" s="481"/>
-      <c r="F3" s="488" t="s">
+      <c r="C3" s="507"/>
+      <c r="D3" s="507"/>
+      <c r="E3" s="508"/>
+      <c r="F3" s="511" t="s">
         <v>307</v>
       </c>
-      <c r="G3" s="484" t="s">
+      <c r="G3" s="509" t="s">
         <v>308</v>
       </c>
-      <c r="H3" s="481"/>
-      <c r="I3" s="488" t="s">
+      <c r="H3" s="508"/>
+      <c r="I3" s="511" t="s">
         <v>309</v>
       </c>
-      <c r="J3" s="486" t="s">
+      <c r="J3" s="513" t="s">
         <v>310</v>
       </c>
-      <c r="K3" s="487"/>
+      <c r="K3" s="514"/>
     </row>
     <row r="4" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
-      <c r="B4" s="482"/>
-      <c r="C4" s="482"/>
-      <c r="D4" s="482"/>
-      <c r="E4" s="483"/>
-      <c r="F4" s="595"/>
-      <c r="G4" s="485"/>
-      <c r="H4" s="483"/>
-      <c r="I4" s="595"/>
+      <c r="B4" s="496"/>
+      <c r="C4" s="496"/>
+      <c r="D4" s="496"/>
+      <c r="E4" s="497"/>
+      <c r="F4" s="512"/>
+      <c r="G4" s="510"/>
+      <c r="H4" s="497"/>
+      <c r="I4" s="512"/>
       <c r="J4" s="5" t="s">
         <v>311</v>
       </c>
@@ -15876,125 +15876,125 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="533"/>
-      <c r="B5" s="536"/>
-      <c r="C5" s="536"/>
-      <c r="D5" s="536"/>
-      <c r="E5" s="534"/>
+      <c r="A5" s="527"/>
+      <c r="B5" s="528"/>
+      <c r="C5" s="528"/>
+      <c r="D5" s="528"/>
+      <c r="E5" s="529"/>
       <c r="F5" s="13"/>
-      <c r="G5" s="502"/>
-      <c r="H5" s="503"/>
+      <c r="G5" s="525"/>
+      <c r="H5" s="526"/>
       <c r="I5" s="274"/>
       <c r="J5" s="8"/>
       <c r="K5" s="19"/>
     </row>
     <row r="6" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="495"/>
-      <c r="B6" s="496"/>
-      <c r="C6" s="496"/>
-      <c r="D6" s="496"/>
-      <c r="E6" s="496"/>
+      <c r="A6" s="521"/>
+      <c r="B6" s="477"/>
+      <c r="C6" s="477"/>
+      <c r="D6" s="477"/>
+      <c r="E6" s="477"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="502"/>
-      <c r="H6" s="503"/>
+      <c r="G6" s="525"/>
+      <c r="H6" s="526"/>
       <c r="I6" s="274"/>
       <c r="J6" s="8"/>
       <c r="K6" s="19"/>
     </row>
     <row r="7" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="495"/>
-      <c r="B7" s="496"/>
-      <c r="C7" s="496"/>
-      <c r="D7" s="496"/>
-      <c r="E7" s="496"/>
+      <c r="A7" s="521"/>
+      <c r="B7" s="477"/>
+      <c r="C7" s="477"/>
+      <c r="D7" s="477"/>
+      <c r="E7" s="477"/>
       <c r="F7" s="13"/>
-      <c r="G7" s="494"/>
-      <c r="H7" s="494"/>
+      <c r="G7" s="520"/>
+      <c r="H7" s="520"/>
       <c r="I7" s="274"/>
       <c r="J7" s="8"/>
       <c r="K7" s="19"/>
     </row>
     <row r="8" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="495"/>
-      <c r="B8" s="496"/>
-      <c r="C8" s="496"/>
-      <c r="D8" s="496"/>
-      <c r="E8" s="496"/>
+      <c r="A8" s="521"/>
+      <c r="B8" s="477"/>
+      <c r="C8" s="477"/>
+      <c r="D8" s="477"/>
+      <c r="E8" s="477"/>
       <c r="F8" s="13"/>
-      <c r="G8" s="494"/>
-      <c r="H8" s="494"/>
+      <c r="G8" s="520"/>
+      <c r="H8" s="520"/>
       <c r="I8" s="274"/>
       <c r="J8" s="8"/>
       <c r="K8" s="19"/>
     </row>
     <row r="9" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="495"/>
-      <c r="B9" s="496"/>
-      <c r="C9" s="496"/>
-      <c r="D9" s="496"/>
-      <c r="E9" s="496"/>
+      <c r="A9" s="521"/>
+      <c r="B9" s="477"/>
+      <c r="C9" s="477"/>
+      <c r="D9" s="477"/>
+      <c r="E9" s="477"/>
       <c r="F9" s="13"/>
-      <c r="G9" s="494"/>
-      <c r="H9" s="494"/>
+      <c r="G9" s="520"/>
+      <c r="H9" s="520"/>
       <c r="I9" s="274"/>
       <c r="J9" s="8"/>
       <c r="K9" s="19"/>
     </row>
     <row r="10" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="495"/>
-      <c r="B10" s="496"/>
-      <c r="C10" s="496"/>
-      <c r="D10" s="496"/>
-      <c r="E10" s="496"/>
+      <c r="A10" s="521"/>
+      <c r="B10" s="477"/>
+      <c r="C10" s="477"/>
+      <c r="D10" s="477"/>
+      <c r="E10" s="477"/>
       <c r="F10" s="13"/>
-      <c r="G10" s="494"/>
-      <c r="H10" s="494"/>
+      <c r="G10" s="520"/>
+      <c r="H10" s="520"/>
       <c r="I10" s="274"/>
       <c r="J10" s="8"/>
       <c r="K10" s="19"/>
     </row>
     <row r="11" spans="1:11" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="509"/>
-      <c r="B11" s="510"/>
-      <c r="C11" s="510"/>
-      <c r="D11" s="510"/>
-      <c r="E11" s="510"/>
+      <c r="A11" s="493"/>
+      <c r="B11" s="484"/>
+      <c r="C11" s="484"/>
+      <c r="D11" s="484"/>
+      <c r="E11" s="484"/>
       <c r="F11" s="14"/>
-      <c r="G11" s="517"/>
-      <c r="H11" s="517"/>
+      <c r="G11" s="489"/>
+      <c r="H11" s="489"/>
       <c r="I11" s="275"/>
       <c r="J11" s="10"/>
       <c r="K11" s="20"/>
     </row>
     <row r="12" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="511" t="s">
+      <c r="A12" s="498" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="512"/>
-      <c r="C12" s="512"/>
-      <c r="D12" s="512"/>
-      <c r="E12" s="512"/>
-      <c r="F12" s="512"/>
-      <c r="G12" s="512"/>
-      <c r="H12" s="512"/>
-      <c r="I12" s="512"/>
-      <c r="J12" s="512"/>
-      <c r="K12" s="513"/>
+      <c r="B12" s="499"/>
+      <c r="C12" s="499"/>
+      <c r="D12" s="499"/>
+      <c r="E12" s="499"/>
+      <c r="F12" s="499"/>
+      <c r="G12" s="499"/>
+      <c r="H12" s="499"/>
+      <c r="I12" s="499"/>
+      <c r="J12" s="499"/>
+      <c r="K12" s="500"/>
     </row>
     <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="514" t="s">
+      <c r="A13" s="501" t="s">
         <v>313</v>
       </c>
-      <c r="B13" s="515"/>
-      <c r="C13" s="515"/>
-      <c r="D13" s="515"/>
-      <c r="E13" s="515"/>
-      <c r="F13" s="515"/>
-      <c r="G13" s="515"/>
-      <c r="H13" s="515"/>
-      <c r="I13" s="515"/>
-      <c r="J13" s="515"/>
-      <c r="K13" s="516"/>
+      <c r="B13" s="502"/>
+      <c r="C13" s="502"/>
+      <c r="D13" s="502"/>
+      <c r="E13" s="502"/>
+      <c r="F13" s="502"/>
+      <c r="G13" s="502"/>
+      <c r="H13" s="502"/>
+      <c r="I13" s="502"/>
+      <c r="J13" s="502"/>
+      <c r="K13" s="503"/>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="218" t="s">
@@ -16015,449 +16015,449 @@
       <c r="A15" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="B15" s="500" t="s">
+      <c r="B15" s="494" t="s">
         <v>315</v>
       </c>
-      <c r="C15" s="501"/>
-      <c r="D15" s="499" t="s">
+      <c r="C15" s="495"/>
+      <c r="D15" s="524" t="s">
         <v>316</v>
       </c>
-      <c r="E15" s="500"/>
-      <c r="F15" s="501"/>
-      <c r="G15" s="499" t="s">
+      <c r="E15" s="494"/>
+      <c r="F15" s="495"/>
+      <c r="G15" s="524" t="s">
         <v>317</v>
       </c>
-      <c r="H15" s="500"/>
-      <c r="I15" s="501"/>
-      <c r="J15" s="520" t="s">
+      <c r="H15" s="494"/>
+      <c r="I15" s="495"/>
+      <c r="J15" s="482" t="s">
         <v>318</v>
       </c>
-      <c r="K15" s="492" t="s">
+      <c r="K15" s="518" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="482"/>
-      <c r="C16" s="483"/>
-      <c r="D16" s="499"/>
-      <c r="E16" s="500"/>
-      <c r="F16" s="501"/>
-      <c r="G16" s="499"/>
-      <c r="H16" s="500"/>
-      <c r="I16" s="501"/>
-      <c r="J16" s="520"/>
-      <c r="K16" s="492"/>
+      <c r="B16" s="496"/>
+      <c r="C16" s="497"/>
+      <c r="D16" s="524"/>
+      <c r="E16" s="494"/>
+      <c r="F16" s="495"/>
+      <c r="G16" s="524"/>
+      <c r="H16" s="494"/>
+      <c r="I16" s="495"/>
+      <c r="J16" s="482"/>
+      <c r="K16" s="518"/>
     </row>
     <row r="17" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="497" t="s">
+      <c r="A17" s="522" t="s">
         <v>129</v>
       </c>
-      <c r="B17" s="498"/>
+      <c r="B17" s="523"/>
       <c r="C17" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D17" s="485"/>
-      <c r="E17" s="482"/>
-      <c r="F17" s="483"/>
-      <c r="G17" s="485"/>
-      <c r="H17" s="482"/>
-      <c r="I17" s="483"/>
-      <c r="J17" s="521"/>
-      <c r="K17" s="493"/>
+      <c r="D17" s="510"/>
+      <c r="E17" s="496"/>
+      <c r="F17" s="497"/>
+      <c r="G17" s="510"/>
+      <c r="H17" s="496"/>
+      <c r="I17" s="497"/>
+      <c r="J17" s="483"/>
+      <c r="K17" s="519"/>
     </row>
     <row r="18" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="507"/>
-      <c r="B18" s="508"/>
+      <c r="A18" s="478"/>
+      <c r="B18" s="479"/>
       <c r="C18" s="21"/>
-      <c r="D18" s="496"/>
-      <c r="E18" s="496"/>
-      <c r="F18" s="496"/>
-      <c r="G18" s="496"/>
-      <c r="H18" s="496"/>
-      <c r="I18" s="496"/>
+      <c r="D18" s="477"/>
+      <c r="E18" s="477"/>
+      <c r="F18" s="477"/>
+      <c r="G18" s="477"/>
+      <c r="H18" s="477"/>
+      <c r="I18" s="477"/>
       <c r="J18" s="8"/>
       <c r="K18" s="9"/>
     </row>
     <row r="19" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="507"/>
-      <c r="B19" s="508"/>
+      <c r="A19" s="478"/>
+      <c r="B19" s="479"/>
       <c r="C19" s="21"/>
-      <c r="D19" s="496"/>
-      <c r="E19" s="496"/>
-      <c r="F19" s="496"/>
-      <c r="G19" s="496"/>
-      <c r="H19" s="496"/>
-      <c r="I19" s="496"/>
+      <c r="D19" s="477"/>
+      <c r="E19" s="477"/>
+      <c r="F19" s="477"/>
+      <c r="G19" s="477"/>
+      <c r="H19" s="477"/>
+      <c r="I19" s="477"/>
       <c r="J19" s="8"/>
       <c r="K19" s="9"/>
     </row>
     <row r="20" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="507"/>
-      <c r="B20" s="508"/>
+      <c r="A20" s="478"/>
+      <c r="B20" s="479"/>
       <c r="C20" s="21"/>
-      <c r="D20" s="496"/>
-      <c r="E20" s="496"/>
-      <c r="F20" s="496"/>
-      <c r="G20" s="496"/>
-      <c r="H20" s="496"/>
-      <c r="I20" s="496"/>
+      <c r="D20" s="477"/>
+      <c r="E20" s="477"/>
+      <c r="F20" s="477"/>
+      <c r="G20" s="477"/>
+      <c r="H20" s="477"/>
+      <c r="I20" s="477"/>
       <c r="J20" s="8"/>
       <c r="K20" s="9"/>
     </row>
     <row r="21" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="507"/>
-      <c r="B21" s="508"/>
+      <c r="A21" s="478"/>
+      <c r="B21" s="479"/>
       <c r="C21" s="21"/>
-      <c r="D21" s="496"/>
-      <c r="E21" s="496"/>
-      <c r="F21" s="496"/>
-      <c r="G21" s="496"/>
-      <c r="H21" s="496"/>
-      <c r="I21" s="496"/>
+      <c r="D21" s="477"/>
+      <c r="E21" s="477"/>
+      <c r="F21" s="477"/>
+      <c r="G21" s="477"/>
+      <c r="H21" s="477"/>
+      <c r="I21" s="477"/>
       <c r="J21" s="8"/>
       <c r="K21" s="9"/>
     </row>
     <row r="22" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="507"/>
-      <c r="B22" s="508"/>
+      <c r="A22" s="478"/>
+      <c r="B22" s="479"/>
       <c r="C22" s="21"/>
-      <c r="D22" s="496"/>
-      <c r="E22" s="496"/>
-      <c r="F22" s="496"/>
-      <c r="G22" s="496"/>
-      <c r="H22" s="496"/>
-      <c r="I22" s="496"/>
+      <c r="D22" s="477"/>
+      <c r="E22" s="477"/>
+      <c r="F22" s="477"/>
+      <c r="G22" s="477"/>
+      <c r="H22" s="477"/>
+      <c r="I22" s="477"/>
       <c r="J22" s="8"/>
       <c r="K22" s="9"/>
     </row>
     <row r="23" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="507"/>
-      <c r="B23" s="508"/>
+      <c r="A23" s="478"/>
+      <c r="B23" s="479"/>
       <c r="C23" s="21"/>
-      <c r="D23" s="496"/>
-      <c r="E23" s="496"/>
-      <c r="F23" s="496"/>
-      <c r="G23" s="496"/>
-      <c r="H23" s="496"/>
-      <c r="I23" s="496"/>
+      <c r="D23" s="477"/>
+      <c r="E23" s="477"/>
+      <c r="F23" s="477"/>
+      <c r="G23" s="477"/>
+      <c r="H23" s="477"/>
+      <c r="I23" s="477"/>
       <c r="J23" s="8"/>
       <c r="K23" s="9"/>
     </row>
     <row r="24" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="507"/>
-      <c r="B24" s="508"/>
+      <c r="A24" s="478"/>
+      <c r="B24" s="479"/>
       <c r="C24" s="21"/>
-      <c r="D24" s="496"/>
-      <c r="E24" s="496"/>
-      <c r="F24" s="496"/>
-      <c r="G24" s="496"/>
-      <c r="H24" s="496"/>
-      <c r="I24" s="496"/>
+      <c r="D24" s="477"/>
+      <c r="E24" s="477"/>
+      <c r="F24" s="477"/>
+      <c r="G24" s="477"/>
+      <c r="H24" s="477"/>
+      <c r="I24" s="477"/>
       <c r="J24" s="8"/>
       <c r="K24" s="9"/>
     </row>
     <row r="25" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="507"/>
-      <c r="B25" s="508"/>
+      <c r="A25" s="478"/>
+      <c r="B25" s="479"/>
       <c r="C25" s="21"/>
-      <c r="D25" s="496"/>
-      <c r="E25" s="496"/>
-      <c r="F25" s="496"/>
-      <c r="G25" s="496"/>
-      <c r="H25" s="496"/>
-      <c r="I25" s="496"/>
+      <c r="D25" s="477"/>
+      <c r="E25" s="477"/>
+      <c r="F25" s="477"/>
+      <c r="G25" s="477"/>
+      <c r="H25" s="477"/>
+      <c r="I25" s="477"/>
       <c r="J25" s="8"/>
       <c r="K25" s="9"/>
     </row>
     <row r="26" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="507"/>
-      <c r="B26" s="508"/>
+      <c r="A26" s="478"/>
+      <c r="B26" s="479"/>
       <c r="C26" s="21"/>
-      <c r="D26" s="496"/>
-      <c r="E26" s="496"/>
-      <c r="F26" s="496"/>
-      <c r="G26" s="496"/>
-      <c r="H26" s="496"/>
-      <c r="I26" s="496"/>
+      <c r="D26" s="477"/>
+      <c r="E26" s="477"/>
+      <c r="F26" s="477"/>
+      <c r="G26" s="477"/>
+      <c r="H26" s="477"/>
+      <c r="I26" s="477"/>
       <c r="J26" s="8"/>
       <c r="K26" s="9"/>
     </row>
     <row r="27" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="507"/>
-      <c r="B27" s="508"/>
+      <c r="A27" s="478"/>
+      <c r="B27" s="479"/>
       <c r="C27" s="21"/>
-      <c r="D27" s="496"/>
-      <c r="E27" s="496"/>
-      <c r="F27" s="496"/>
-      <c r="G27" s="496"/>
-      <c r="H27" s="496"/>
-      <c r="I27" s="496"/>
+      <c r="D27" s="477"/>
+      <c r="E27" s="477"/>
+      <c r="F27" s="477"/>
+      <c r="G27" s="477"/>
+      <c r="H27" s="477"/>
+      <c r="I27" s="477"/>
       <c r="J27" s="8"/>
       <c r="K27" s="9"/>
     </row>
     <row r="28" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="507"/>
-      <c r="B28" s="508"/>
+      <c r="A28" s="478"/>
+      <c r="B28" s="479"/>
       <c r="C28" s="21"/>
-      <c r="D28" s="496"/>
-      <c r="E28" s="496"/>
-      <c r="F28" s="496"/>
-      <c r="G28" s="496"/>
-      <c r="H28" s="496"/>
-      <c r="I28" s="496"/>
+      <c r="D28" s="477"/>
+      <c r="E28" s="477"/>
+      <c r="F28" s="477"/>
+      <c r="G28" s="477"/>
+      <c r="H28" s="477"/>
+      <c r="I28" s="477"/>
       <c r="J28" s="8"/>
       <c r="K28" s="9"/>
     </row>
     <row r="29" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="507"/>
-      <c r="B29" s="508"/>
+      <c r="A29" s="478"/>
+      <c r="B29" s="479"/>
       <c r="C29" s="21"/>
-      <c r="D29" s="496"/>
-      <c r="E29" s="496"/>
-      <c r="F29" s="496"/>
-      <c r="G29" s="496"/>
-      <c r="H29" s="496"/>
-      <c r="I29" s="496"/>
+      <c r="D29" s="477"/>
+      <c r="E29" s="477"/>
+      <c r="F29" s="477"/>
+      <c r="G29" s="477"/>
+      <c r="H29" s="477"/>
+      <c r="I29" s="477"/>
       <c r="J29" s="8"/>
       <c r="K29" s="9"/>
     </row>
     <row r="30" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="507"/>
-      <c r="B30" s="508"/>
+      <c r="A30" s="478"/>
+      <c r="B30" s="479"/>
       <c r="C30" s="21"/>
-      <c r="D30" s="496"/>
-      <c r="E30" s="496"/>
-      <c r="F30" s="496"/>
-      <c r="G30" s="496"/>
-      <c r="H30" s="496"/>
-      <c r="I30" s="496"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
+      <c r="G30" s="477"/>
+      <c r="H30" s="477"/>
+      <c r="I30" s="477"/>
       <c r="J30" s="8"/>
       <c r="K30" s="9"/>
     </row>
     <row r="31" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="507"/>
-      <c r="B31" s="508"/>
+      <c r="A31" s="478"/>
+      <c r="B31" s="479"/>
       <c r="C31" s="21"/>
-      <c r="D31" s="496"/>
-      <c r="E31" s="496"/>
-      <c r="F31" s="496"/>
-      <c r="G31" s="496"/>
-      <c r="H31" s="496"/>
-      <c r="I31" s="496"/>
+      <c r="D31" s="477"/>
+      <c r="E31" s="477"/>
+      <c r="F31" s="477"/>
+      <c r="G31" s="477"/>
+      <c r="H31" s="477"/>
+      <c r="I31" s="477"/>
       <c r="J31" s="8"/>
       <c r="K31" s="9"/>
     </row>
     <row r="32" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="507"/>
-      <c r="B32" s="508"/>
+      <c r="A32" s="478"/>
+      <c r="B32" s="479"/>
       <c r="C32" s="21"/>
-      <c r="D32" s="496"/>
-      <c r="E32" s="496"/>
-      <c r="F32" s="496"/>
-      <c r="G32" s="496"/>
-      <c r="H32" s="496"/>
-      <c r="I32" s="496"/>
+      <c r="D32" s="477"/>
+      <c r="E32" s="477"/>
+      <c r="F32" s="477"/>
+      <c r="G32" s="477"/>
+      <c r="H32" s="477"/>
+      <c r="I32" s="477"/>
       <c r="J32" s="8"/>
       <c r="K32" s="9"/>
     </row>
     <row r="33" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="507"/>
-      <c r="B33" s="508"/>
+      <c r="A33" s="478"/>
+      <c r="B33" s="479"/>
       <c r="C33" s="21"/>
-      <c r="D33" s="496"/>
-      <c r="E33" s="496"/>
-      <c r="F33" s="496"/>
-      <c r="G33" s="496"/>
-      <c r="H33" s="496"/>
-      <c r="I33" s="496"/>
+      <c r="D33" s="477"/>
+      <c r="E33" s="477"/>
+      <c r="F33" s="477"/>
+      <c r="G33" s="477"/>
+      <c r="H33" s="477"/>
+      <c r="I33" s="477"/>
       <c r="J33" s="8"/>
       <c r="K33" s="9"/>
     </row>
     <row r="34" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="507"/>
-      <c r="B34" s="508"/>
+      <c r="A34" s="478"/>
+      <c r="B34" s="479"/>
       <c r="C34" s="21"/>
-      <c r="D34" s="496"/>
-      <c r="E34" s="496"/>
-      <c r="F34" s="496"/>
-      <c r="G34" s="496"/>
-      <c r="H34" s="496"/>
-      <c r="I34" s="496"/>
+      <c r="D34" s="477"/>
+      <c r="E34" s="477"/>
+      <c r="F34" s="477"/>
+      <c r="G34" s="477"/>
+      <c r="H34" s="477"/>
+      <c r="I34" s="477"/>
       <c r="J34" s="8"/>
       <c r="K34" s="9"/>
     </row>
     <row r="35" spans="1:12" s="12" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="507"/>
-      <c r="B35" s="508"/>
+      <c r="A35" s="478"/>
+      <c r="B35" s="479"/>
       <c r="C35" s="21"/>
-      <c r="D35" s="496"/>
-      <c r="E35" s="496"/>
-      <c r="F35" s="496"/>
-      <c r="G35" s="496"/>
-      <c r="H35" s="496"/>
-      <c r="I35" s="496"/>
+      <c r="D35" s="477"/>
+      <c r="E35" s="477"/>
+      <c r="F35" s="477"/>
+      <c r="G35" s="477"/>
+      <c r="H35" s="477"/>
+      <c r="I35" s="477"/>
       <c r="J35" s="8"/>
       <c r="K35" s="9"/>
     </row>
     <row r="36" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="507"/>
-      <c r="B36" s="508"/>
+      <c r="A36" s="478"/>
+      <c r="B36" s="479"/>
       <c r="C36" s="21"/>
-      <c r="D36" s="496"/>
-      <c r="E36" s="496"/>
-      <c r="F36" s="496"/>
-      <c r="G36" s="496"/>
-      <c r="H36" s="496"/>
-      <c r="I36" s="496"/>
+      <c r="D36" s="477"/>
+      <c r="E36" s="477"/>
+      <c r="F36" s="477"/>
+      <c r="G36" s="477"/>
+      <c r="H36" s="477"/>
+      <c r="I36" s="477"/>
       <c r="J36" s="8"/>
       <c r="K36" s="9"/>
     </row>
     <row r="37" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="507"/>
-      <c r="B37" s="508"/>
+      <c r="A37" s="478"/>
+      <c r="B37" s="479"/>
       <c r="C37" s="21"/>
-      <c r="D37" s="496"/>
-      <c r="E37" s="496"/>
-      <c r="F37" s="496"/>
-      <c r="G37" s="496"/>
-      <c r="H37" s="496"/>
-      <c r="I37" s="496"/>
+      <c r="D37" s="477"/>
+      <c r="E37" s="477"/>
+      <c r="F37" s="477"/>
+      <c r="G37" s="477"/>
+      <c r="H37" s="477"/>
+      <c r="I37" s="477"/>
       <c r="J37" s="8"/>
       <c r="K37" s="9"/>
     </row>
     <row r="38" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="507"/>
-      <c r="B38" s="508"/>
+      <c r="A38" s="478"/>
+      <c r="B38" s="479"/>
       <c r="C38" s="21"/>
-      <c r="D38" s="496"/>
-      <c r="E38" s="496"/>
-      <c r="F38" s="496"/>
-      <c r="G38" s="496"/>
-      <c r="H38" s="496"/>
-      <c r="I38" s="496"/>
+      <c r="D38" s="477"/>
+      <c r="E38" s="477"/>
+      <c r="F38" s="477"/>
+      <c r="G38" s="477"/>
+      <c r="H38" s="477"/>
+      <c r="I38" s="477"/>
       <c r="J38" s="8"/>
       <c r="K38" s="9"/>
     </row>
     <row r="39" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="507"/>
-      <c r="B39" s="508"/>
+      <c r="A39" s="478"/>
+      <c r="B39" s="479"/>
       <c r="C39" s="21"/>
-      <c r="D39" s="496"/>
-      <c r="E39" s="496"/>
-      <c r="F39" s="496"/>
-      <c r="G39" s="496"/>
-      <c r="H39" s="496"/>
-      <c r="I39" s="496"/>
+      <c r="D39" s="477"/>
+      <c r="E39" s="477"/>
+      <c r="F39" s="477"/>
+      <c r="G39" s="477"/>
+      <c r="H39" s="477"/>
+      <c r="I39" s="477"/>
       <c r="J39" s="8"/>
       <c r="K39" s="9"/>
     </row>
     <row r="40" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="507"/>
-      <c r="B40" s="508"/>
+      <c r="A40" s="478"/>
+      <c r="B40" s="479"/>
       <c r="C40" s="21"/>
-      <c r="D40" s="496"/>
-      <c r="E40" s="496"/>
-      <c r="F40" s="496"/>
-      <c r="G40" s="496"/>
-      <c r="H40" s="496"/>
-      <c r="I40" s="496"/>
+      <c r="D40" s="477"/>
+      <c r="E40" s="477"/>
+      <c r="F40" s="477"/>
+      <c r="G40" s="477"/>
+      <c r="H40" s="477"/>
+      <c r="I40" s="477"/>
       <c r="J40" s="8"/>
       <c r="K40" s="9"/>
     </row>
     <row r="41" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="507"/>
-      <c r="B41" s="508"/>
+      <c r="A41" s="478"/>
+      <c r="B41" s="479"/>
       <c r="C41" s="21"/>
-      <c r="D41" s="496"/>
-      <c r="E41" s="496"/>
-      <c r="F41" s="496"/>
-      <c r="G41" s="496"/>
-      <c r="H41" s="496"/>
-      <c r="I41" s="496"/>
+      <c r="D41" s="477"/>
+      <c r="E41" s="477"/>
+      <c r="F41" s="477"/>
+      <c r="G41" s="477"/>
+      <c r="H41" s="477"/>
+      <c r="I41" s="477"/>
       <c r="J41" s="8"/>
       <c r="K41" s="9"/>
     </row>
     <row r="42" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="507"/>
-      <c r="B42" s="508"/>
+      <c r="A42" s="478"/>
+      <c r="B42" s="479"/>
       <c r="C42" s="21"/>
-      <c r="D42" s="496"/>
-      <c r="E42" s="496"/>
-      <c r="F42" s="496"/>
-      <c r="G42" s="496"/>
-      <c r="H42" s="496"/>
-      <c r="I42" s="496"/>
+      <c r="D42" s="477"/>
+      <c r="E42" s="477"/>
+      <c r="F42" s="477"/>
+      <c r="G42" s="477"/>
+      <c r="H42" s="477"/>
+      <c r="I42" s="477"/>
       <c r="J42" s="8"/>
       <c r="K42" s="9"/>
     </row>
     <row r="43" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="507"/>
-      <c r="B43" s="508"/>
+      <c r="A43" s="478"/>
+      <c r="B43" s="479"/>
       <c r="C43" s="21"/>
-      <c r="D43" s="496"/>
-      <c r="E43" s="496"/>
-      <c r="F43" s="496"/>
-      <c r="G43" s="496"/>
-      <c r="H43" s="496"/>
-      <c r="I43" s="496"/>
+      <c r="D43" s="477"/>
+      <c r="E43" s="477"/>
+      <c r="F43" s="477"/>
+      <c r="G43" s="477"/>
+      <c r="H43" s="477"/>
+      <c r="I43" s="477"/>
       <c r="J43" s="8"/>
       <c r="K43" s="9"/>
     </row>
     <row r="44" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="507"/>
-      <c r="B44" s="508"/>
+      <c r="A44" s="478"/>
+      <c r="B44" s="479"/>
       <c r="C44" s="21"/>
-      <c r="D44" s="496"/>
-      <c r="E44" s="496"/>
-      <c r="F44" s="496"/>
-      <c r="G44" s="496"/>
-      <c r="H44" s="496"/>
-      <c r="I44" s="496"/>
+      <c r="D44" s="477"/>
+      <c r="E44" s="477"/>
+      <c r="F44" s="477"/>
+      <c r="G44" s="477"/>
+      <c r="H44" s="477"/>
+      <c r="I44" s="477"/>
       <c r="J44" s="8"/>
       <c r="K44" s="9"/>
     </row>
     <row r="45" spans="1:12" s="12" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="518"/>
-      <c r="B45" s="519"/>
+      <c r="A45" s="480"/>
+      <c r="B45" s="481"/>
       <c r="C45" s="22"/>
-      <c r="D45" s="510"/>
-      <c r="E45" s="510"/>
-      <c r="F45" s="510"/>
-      <c r="G45" s="510"/>
-      <c r="H45" s="510"/>
-      <c r="I45" s="510"/>
+      <c r="D45" s="484"/>
+      <c r="E45" s="484"/>
+      <c r="F45" s="484"/>
+      <c r="G45" s="484"/>
+      <c r="H45" s="484"/>
+      <c r="I45" s="484"/>
       <c r="J45" s="10"/>
       <c r="K45" s="11"/>
     </row>
     <row r="46" spans="1:12" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="522" t="s">
+      <c r="A46" s="485" t="s">
         <v>114</v>
       </c>
-      <c r="B46" s="523"/>
-      <c r="C46" s="523"/>
-      <c r="D46" s="523"/>
-      <c r="E46" s="523"/>
-      <c r="F46" s="523"/>
-      <c r="G46" s="523"/>
-      <c r="H46" s="523"/>
-      <c r="I46" s="523"/>
-      <c r="J46" s="524"/>
-      <c r="K46" s="525"/>
+      <c r="B46" s="486"/>
+      <c r="C46" s="486"/>
+      <c r="D46" s="486"/>
+      <c r="E46" s="486"/>
+      <c r="F46" s="486"/>
+      <c r="G46" s="486"/>
+      <c r="H46" s="486"/>
+      <c r="I46" s="486"/>
+      <c r="J46" s="487"/>
+      <c r="K46" s="488"/>
     </row>
     <row r="47" spans="1:12" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="282" t="s">
+      <c r="A47" s="452" t="s">
         <v>143</v>
       </c>
-      <c r="B47" s="283"/>
-      <c r="C47" s="284"/>
-      <c r="D47" s="504" t="s">
+      <c r="B47" s="453"/>
+      <c r="C47" s="454"/>
+      <c r="D47" s="490" t="s">
         <v>144</v>
       </c>
-      <c r="E47" s="505"/>
-      <c r="F47" s="505"/>
-      <c r="G47" s="505"/>
-      <c r="H47" s="506"/>
+      <c r="E47" s="491"/>
+      <c r="F47" s="491"/>
+      <c r="G47" s="491"/>
+      <c r="H47" s="492"/>
       <c r="I47" s="252" t="s">
         <v>145</v>
       </c>
@@ -16466,19 +16466,19 @@
       <c r="L47" s="254"/>
     </row>
     <row r="48" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="281" t="s">
+      <c r="A48" s="451" t="s">
         <v>403</v>
       </c>
-      <c r="B48" s="281"/>
-      <c r="C48" s="281"/>
-      <c r="D48" s="281"/>
-      <c r="E48" s="281"/>
-      <c r="F48" s="281"/>
-      <c r="G48" s="281"/>
-      <c r="H48" s="281"/>
-      <c r="I48" s="281"/>
-      <c r="J48" s="281"/>
-      <c r="K48" s="281"/>
+      <c r="B48" s="451"/>
+      <c r="C48" s="451"/>
+      <c r="D48" s="451"/>
+      <c r="E48" s="451"/>
+      <c r="F48" s="451"/>
+      <c r="G48" s="451"/>
+      <c r="H48" s="451"/>
+      <c r="I48" s="451"/>
+      <c r="J48" s="451"/>
+      <c r="K48" s="451"/>
       <c r="L48" s="257"/>
     </row>
   </sheetData>
@@ -16492,6 +16492,99 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="117">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B3:E4"/>
+    <mergeCell ref="G3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="K15:K17"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D15:F17"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="G15:I17"/>
+    <mergeCell ref="A48:K48"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B15:C16"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="D44:F44"/>
     <mergeCell ref="G44:I44"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="D37:F37"/>
@@ -16516,99 +16609,6 @@
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="D42:F42"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G41:I41"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="A48:K48"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B15:C16"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B3:E4"/>
-    <mergeCell ref="G3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="K15:K17"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D15:F17"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="G15:I17"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -16640,280 +16640,280 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="561"/>
-      <c r="B1" s="562"/>
-      <c r="C1" s="562"/>
-      <c r="D1" s="562"/>
-      <c r="E1" s="562"/>
-      <c r="F1" s="562"/>
-      <c r="G1" s="562"/>
-      <c r="H1" s="562"/>
-      <c r="I1" s="562"/>
-      <c r="J1" s="562"/>
-      <c r="K1" s="563"/>
+      <c r="A1" s="553"/>
+      <c r="B1" s="554"/>
+      <c r="C1" s="554"/>
+      <c r="D1" s="554"/>
+      <c r="E1" s="554"/>
+      <c r="F1" s="554"/>
+      <c r="G1" s="554"/>
+      <c r="H1" s="554"/>
+      <c r="I1" s="554"/>
+      <c r="J1" s="554"/>
+      <c r="K1" s="555"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="583" t="s">
+      <c r="A2" s="580" t="s">
         <v>320</v>
       </c>
-      <c r="B2" s="584"/>
-      <c r="C2" s="584"/>
-      <c r="D2" s="584"/>
-      <c r="E2" s="584"/>
-      <c r="F2" s="584"/>
-      <c r="G2" s="584"/>
-      <c r="H2" s="584"/>
-      <c r="I2" s="584"/>
-      <c r="J2" s="584"/>
-      <c r="K2" s="585"/>
+      <c r="B2" s="581"/>
+      <c r="C2" s="581"/>
+      <c r="D2" s="581"/>
+      <c r="E2" s="581"/>
+      <c r="F2" s="581"/>
+      <c r="G2" s="581"/>
+      <c r="H2" s="581"/>
+      <c r="I2" s="581"/>
+      <c r="J2" s="581"/>
+      <c r="K2" s="582"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="569" t="s">
+      <c r="A3" s="564" t="s">
         <v>321</v>
       </c>
-      <c r="B3" s="571" t="s">
+      <c r="B3" s="565" t="s">
         <v>322</v>
       </c>
-      <c r="C3" s="571"/>
-      <c r="D3" s="572"/>
-      <c r="E3" s="480" t="s">
+      <c r="C3" s="565"/>
+      <c r="D3" s="566"/>
+      <c r="E3" s="507" t="s">
         <v>323</v>
       </c>
-      <c r="F3" s="481"/>
-      <c r="G3" s="543" t="s">
+      <c r="F3" s="508"/>
+      <c r="G3" s="589" t="s">
         <v>324</v>
       </c>
-      <c r="H3" s="484" t="s">
+      <c r="H3" s="509" t="s">
         <v>325</v>
       </c>
-      <c r="I3" s="578"/>
-      <c r="J3" s="578"/>
-      <c r="K3" s="579"/>
+      <c r="I3" s="575"/>
+      <c r="J3" s="575"/>
+      <c r="K3" s="576"/>
     </row>
     <row r="4" spans="1:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="570"/>
-      <c r="B4" s="573"/>
-      <c r="C4" s="573"/>
-      <c r="D4" s="574"/>
-      <c r="E4" s="482"/>
-      <c r="F4" s="483"/>
-      <c r="G4" s="544"/>
-      <c r="H4" s="580"/>
-      <c r="I4" s="564"/>
-      <c r="J4" s="564"/>
-      <c r="K4" s="581"/>
+      <c r="A4" s="552"/>
+      <c r="B4" s="567"/>
+      <c r="C4" s="567"/>
+      <c r="D4" s="568"/>
+      <c r="E4" s="496"/>
+      <c r="F4" s="497"/>
+      <c r="G4" s="590"/>
+      <c r="H4" s="577"/>
+      <c r="I4" s="556"/>
+      <c r="J4" s="556"/>
+      <c r="K4" s="578"/>
     </row>
     <row r="5" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="25"/>
-      <c r="B5" s="586"/>
-      <c r="C5" s="586"/>
-      <c r="D5" s="587"/>
+      <c r="B5" s="583"/>
+      <c r="C5" s="583"/>
+      <c r="D5" s="584"/>
       <c r="E5" s="26" t="s">
         <v>129</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G5" s="545"/>
-      <c r="H5" s="582"/>
-      <c r="I5" s="340"/>
-      <c r="J5" s="340"/>
-      <c r="K5" s="341"/>
+      <c r="G5" s="591"/>
+      <c r="H5" s="579"/>
+      <c r="I5" s="439"/>
+      <c r="J5" s="439"/>
+      <c r="K5" s="440"/>
     </row>
     <row r="6" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="540"/>
-      <c r="B6" s="541"/>
-      <c r="C6" s="541"/>
-      <c r="D6" s="542"/>
+      <c r="A6" s="572"/>
+      <c r="B6" s="573"/>
+      <c r="C6" s="573"/>
+      <c r="D6" s="574"/>
       <c r="E6" s="35"/>
       <c r="F6" s="35"/>
       <c r="G6" s="36"/>
-      <c r="H6" s="546"/>
-      <c r="I6" s="547"/>
-      <c r="J6" s="547"/>
-      <c r="K6" s="548"/>
+      <c r="H6" s="559"/>
+      <c r="I6" s="560"/>
+      <c r="J6" s="560"/>
+      <c r="K6" s="561"/>
     </row>
     <row r="7" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="540"/>
-      <c r="B7" s="541"/>
-      <c r="C7" s="541"/>
-      <c r="D7" s="542"/>
+      <c r="A7" s="572"/>
+      <c r="B7" s="573"/>
+      <c r="C7" s="573"/>
+      <c r="D7" s="574"/>
       <c r="E7" s="35"/>
       <c r="F7" s="35"/>
       <c r="G7" s="36"/>
-      <c r="H7" s="546"/>
-      <c r="I7" s="547"/>
-      <c r="J7" s="547"/>
-      <c r="K7" s="548"/>
+      <c r="H7" s="559"/>
+      <c r="I7" s="560"/>
+      <c r="J7" s="560"/>
+      <c r="K7" s="561"/>
     </row>
     <row r="8" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="540"/>
-      <c r="B8" s="541"/>
-      <c r="C8" s="541"/>
-      <c r="D8" s="542"/>
+      <c r="A8" s="572"/>
+      <c r="B8" s="573"/>
+      <c r="C8" s="573"/>
+      <c r="D8" s="574"/>
       <c r="E8" s="35"/>
       <c r="F8" s="35"/>
       <c r="G8" s="36"/>
-      <c r="H8" s="546"/>
-      <c r="I8" s="547"/>
-      <c r="J8" s="547"/>
-      <c r="K8" s="548"/>
+      <c r="H8" s="559"/>
+      <c r="I8" s="560"/>
+      <c r="J8" s="560"/>
+      <c r="K8" s="561"/>
     </row>
     <row r="9" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="540"/>
-      <c r="B9" s="541"/>
-      <c r="C9" s="541"/>
-      <c r="D9" s="542"/>
+      <c r="A9" s="572"/>
+      <c r="B9" s="573"/>
+      <c r="C9" s="573"/>
+      <c r="D9" s="574"/>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
       <c r="G9" s="36"/>
-      <c r="H9" s="546"/>
-      <c r="I9" s="547"/>
-      <c r="J9" s="547"/>
-      <c r="K9" s="548"/>
+      <c r="H9" s="559"/>
+      <c r="I9" s="560"/>
+      <c r="J9" s="560"/>
+      <c r="K9" s="561"/>
     </row>
     <row r="10" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="540"/>
-      <c r="B10" s="541"/>
-      <c r="C10" s="541"/>
-      <c r="D10" s="542"/>
+      <c r="A10" s="572"/>
+      <c r="B10" s="573"/>
+      <c r="C10" s="573"/>
+      <c r="D10" s="574"/>
       <c r="E10" s="35"/>
       <c r="F10" s="35"/>
       <c r="G10" s="36"/>
-      <c r="H10" s="546"/>
-      <c r="I10" s="547"/>
-      <c r="J10" s="547"/>
-      <c r="K10" s="548"/>
+      <c r="H10" s="559"/>
+      <c r="I10" s="560"/>
+      <c r="J10" s="560"/>
+      <c r="K10" s="561"/>
     </row>
     <row r="11" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="540"/>
-      <c r="B11" s="541"/>
-      <c r="C11" s="541"/>
-      <c r="D11" s="542"/>
+      <c r="A11" s="572"/>
+      <c r="B11" s="573"/>
+      <c r="C11" s="573"/>
+      <c r="D11" s="574"/>
       <c r="E11" s="35"/>
       <c r="F11" s="35"/>
       <c r="G11" s="36"/>
-      <c r="H11" s="546"/>
-      <c r="I11" s="547"/>
-      <c r="J11" s="547"/>
-      <c r="K11" s="548"/>
+      <c r="H11" s="559"/>
+      <c r="I11" s="560"/>
+      <c r="J11" s="560"/>
+      <c r="K11" s="561"/>
     </row>
     <row r="12" spans="1:11" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="575"/>
-      <c r="B12" s="576"/>
-      <c r="C12" s="576"/>
-      <c r="D12" s="577"/>
+      <c r="A12" s="569"/>
+      <c r="B12" s="570"/>
+      <c r="C12" s="570"/>
+      <c r="D12" s="571"/>
       <c r="E12" s="35"/>
       <c r="F12" s="35"/>
       <c r="G12" s="37"/>
-      <c r="H12" s="588"/>
-      <c r="I12" s="589"/>
-      <c r="J12" s="589"/>
-      <c r="K12" s="590"/>
+      <c r="H12" s="530"/>
+      <c r="I12" s="531"/>
+      <c r="J12" s="531"/>
+      <c r="K12" s="532"/>
     </row>
     <row r="13" spans="1:11" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="511" t="s">
+      <c r="A13" s="498" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="512"/>
-      <c r="C13" s="512"/>
-      <c r="D13" s="512"/>
-      <c r="E13" s="512"/>
-      <c r="F13" s="512"/>
-      <c r="G13" s="512"/>
-      <c r="H13" s="512"/>
-      <c r="I13" s="512"/>
-      <c r="J13" s="512"/>
-      <c r="K13" s="513"/>
+      <c r="B13" s="499"/>
+      <c r="C13" s="499"/>
+      <c r="D13" s="499"/>
+      <c r="E13" s="499"/>
+      <c r="F13" s="499"/>
+      <c r="G13" s="499"/>
+      <c r="H13" s="499"/>
+      <c r="I13" s="499"/>
+      <c r="J13" s="499"/>
+      <c r="K13" s="500"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="591" t="s">
+      <c r="A14" s="533" t="s">
         <v>326</v>
       </c>
-      <c r="B14" s="592"/>
-      <c r="C14" s="592"/>
-      <c r="D14" s="592"/>
-      <c r="E14" s="592"/>
-      <c r="F14" s="592"/>
-      <c r="G14" s="592"/>
-      <c r="H14" s="592"/>
-      <c r="I14" s="592"/>
-      <c r="J14" s="592"/>
-      <c r="K14" s="593"/>
+      <c r="B14" s="534"/>
+      <c r="C14" s="534"/>
+      <c r="D14" s="534"/>
+      <c r="E14" s="534"/>
+      <c r="F14" s="534"/>
+      <c r="G14" s="534"/>
+      <c r="H14" s="534"/>
+      <c r="I14" s="534"/>
+      <c r="J14" s="534"/>
+      <c r="K14" s="535"/>
     </row>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="570" t="s">
+      <c r="A15" s="552" t="s">
         <v>327</v>
       </c>
-      <c r="B15" s="500" t="s">
+      <c r="B15" s="494" t="s">
         <v>328</v>
       </c>
-      <c r="C15" s="564"/>
-      <c r="D15" s="565"/>
-      <c r="E15" s="500" t="s">
+      <c r="C15" s="556"/>
+      <c r="D15" s="557"/>
+      <c r="E15" s="494" t="s">
         <v>329</v>
       </c>
-      <c r="F15" s="501"/>
-      <c r="G15" s="594" t="s">
+      <c r="F15" s="495"/>
+      <c r="G15" s="539" t="s">
         <v>324</v>
       </c>
-      <c r="H15" s="567" t="s">
+      <c r="H15" s="562" t="s">
         <v>330</v>
       </c>
-      <c r="I15" s="499" t="s">
+      <c r="I15" s="524" t="s">
         <v>331</v>
       </c>
-      <c r="J15" s="564"/>
-      <c r="K15" s="581"/>
+      <c r="J15" s="556"/>
+      <c r="K15" s="578"/>
     </row>
     <row r="16" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="570"/>
-      <c r="B16" s="564"/>
-      <c r="C16" s="564"/>
-      <c r="D16" s="565"/>
-      <c r="E16" s="482"/>
-      <c r="F16" s="483"/>
-      <c r="G16" s="594"/>
-      <c r="H16" s="567"/>
-      <c r="I16" s="580"/>
-      <c r="J16" s="564"/>
-      <c r="K16" s="581"/>
+      <c r="A16" s="552"/>
+      <c r="B16" s="556"/>
+      <c r="C16" s="556"/>
+      <c r="D16" s="557"/>
+      <c r="E16" s="496"/>
+      <c r="F16" s="497"/>
+      <c r="G16" s="539"/>
+      <c r="H16" s="562"/>
+      <c r="I16" s="577"/>
+      <c r="J16" s="556"/>
+      <c r="K16" s="578"/>
     </row>
     <row r="17" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="25"/>
-      <c r="B17" s="340"/>
-      <c r="C17" s="340"/>
-      <c r="D17" s="566"/>
+      <c r="B17" s="439"/>
+      <c r="C17" s="439"/>
+      <c r="D17" s="558"/>
       <c r="E17" s="26" t="s">
         <v>129</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G17" s="595"/>
-      <c r="H17" s="568"/>
-      <c r="I17" s="582"/>
-      <c r="J17" s="340"/>
-      <c r="K17" s="341"/>
+      <c r="G17" s="512"/>
+      <c r="H17" s="563"/>
+      <c r="I17" s="579"/>
+      <c r="J17" s="439"/>
+      <c r="K17" s="440"/>
     </row>
     <row r="18" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="549"/>
-      <c r="B18" s="550"/>
-      <c r="C18" s="550"/>
-      <c r="D18" s="551"/>
+      <c r="A18" s="543"/>
+      <c r="B18" s="544"/>
+      <c r="C18" s="544"/>
+      <c r="D18" s="545"/>
       <c r="E18" s="27"/>
       <c r="F18" s="27"/>
       <c r="G18" s="29"/>
       <c r="H18" s="28"/>
-      <c r="I18" s="555"/>
-      <c r="J18" s="556"/>
-      <c r="K18" s="557"/>
+      <c r="I18" s="540"/>
+      <c r="J18" s="541"/>
+      <c r="K18" s="542"/>
     </row>
     <row r="19" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="552"/>
-      <c r="B19" s="553"/>
-      <c r="C19" s="553"/>
-      <c r="D19" s="554"/>
+      <c r="A19" s="536"/>
+      <c r="B19" s="537"/>
+      <c r="C19" s="537"/>
+      <c r="D19" s="538"/>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
       <c r="G19" s="29"/>
@@ -16923,10 +16923,10 @@
       <c r="K19" s="32"/>
     </row>
     <row r="20" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="552"/>
-      <c r="B20" s="553"/>
-      <c r="C20" s="553"/>
-      <c r="D20" s="554"/>
+      <c r="A20" s="536"/>
+      <c r="B20" s="537"/>
+      <c r="C20" s="537"/>
+      <c r="D20" s="538"/>
       <c r="E20" s="27"/>
       <c r="F20" s="27"/>
       <c r="G20" s="29"/>
@@ -16936,10 +16936,10 @@
       <c r="K20" s="32"/>
     </row>
     <row r="21" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="552"/>
-      <c r="B21" s="553"/>
-      <c r="C21" s="553"/>
-      <c r="D21" s="554"/>
+      <c r="A21" s="536"/>
+      <c r="B21" s="537"/>
+      <c r="C21" s="537"/>
+      <c r="D21" s="538"/>
       <c r="E21" s="27"/>
       <c r="F21" s="27"/>
       <c r="G21" s="29"/>
@@ -16949,10 +16949,10 @@
       <c r="K21" s="32"/>
     </row>
     <row r="22" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="552"/>
-      <c r="B22" s="553"/>
-      <c r="C22" s="553"/>
-      <c r="D22" s="554"/>
+      <c r="A22" s="536"/>
+      <c r="B22" s="537"/>
+      <c r="C22" s="537"/>
+      <c r="D22" s="538"/>
       <c r="E22" s="27"/>
       <c r="F22" s="27"/>
       <c r="G22" s="29"/>
@@ -16962,10 +16962,10 @@
       <c r="K22" s="32"/>
     </row>
     <row r="23" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="552"/>
-      <c r="B23" s="553"/>
-      <c r="C23" s="553"/>
-      <c r="D23" s="554"/>
+      <c r="A23" s="536"/>
+      <c r="B23" s="537"/>
+      <c r="C23" s="537"/>
+      <c r="D23" s="538"/>
       <c r="E23" s="27"/>
       <c r="F23" s="27"/>
       <c r="G23" s="29"/>
@@ -16975,10 +16975,10 @@
       <c r="K23" s="32"/>
     </row>
     <row r="24" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="552"/>
-      <c r="B24" s="553"/>
-      <c r="C24" s="553"/>
-      <c r="D24" s="554"/>
+      <c r="A24" s="536"/>
+      <c r="B24" s="537"/>
+      <c r="C24" s="537"/>
+      <c r="D24" s="538"/>
       <c r="E24" s="27"/>
       <c r="F24" s="27"/>
       <c r="G24" s="29"/>
@@ -16988,10 +16988,10 @@
       <c r="K24" s="32"/>
     </row>
     <row r="25" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="552"/>
-      <c r="B25" s="553"/>
-      <c r="C25" s="553"/>
-      <c r="D25" s="554"/>
+      <c r="A25" s="536"/>
+      <c r="B25" s="537"/>
+      <c r="C25" s="537"/>
+      <c r="D25" s="538"/>
       <c r="E25" s="27"/>
       <c r="F25" s="27"/>
       <c r="G25" s="29"/>
@@ -17001,43 +17001,43 @@
       <c r="K25" s="32"/>
     </row>
     <row r="26" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="549"/>
-      <c r="B26" s="550"/>
-      <c r="C26" s="550"/>
-      <c r="D26" s="551"/>
+      <c r="A26" s="543"/>
+      <c r="B26" s="544"/>
+      <c r="C26" s="544"/>
+      <c r="D26" s="545"/>
       <c r="E26" s="27"/>
       <c r="F26" s="27"/>
       <c r="G26" s="29"/>
       <c r="H26" s="28"/>
-      <c r="I26" s="555"/>
-      <c r="J26" s="556"/>
-      <c r="K26" s="557"/>
+      <c r="I26" s="540"/>
+      <c r="J26" s="541"/>
+      <c r="K26" s="542"/>
     </row>
     <row r="27" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="549"/>
-      <c r="B27" s="550"/>
-      <c r="C27" s="550"/>
-      <c r="D27" s="551"/>
+      <c r="A27" s="543"/>
+      <c r="B27" s="544"/>
+      <c r="C27" s="544"/>
+      <c r="D27" s="545"/>
       <c r="E27" s="27"/>
       <c r="F27" s="27"/>
       <c r="G27" s="29"/>
       <c r="H27" s="28"/>
-      <c r="I27" s="555"/>
-      <c r="J27" s="556"/>
-      <c r="K27" s="557"/>
+      <c r="I27" s="540"/>
+      <c r="J27" s="541"/>
+      <c r="K27" s="542"/>
     </row>
     <row r="28" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="549"/>
-      <c r="B28" s="550"/>
-      <c r="C28" s="550"/>
-      <c r="D28" s="551"/>
+      <c r="A28" s="543"/>
+      <c r="B28" s="544"/>
+      <c r="C28" s="544"/>
+      <c r="D28" s="545"/>
       <c r="E28" s="27"/>
       <c r="F28" s="27"/>
       <c r="G28" s="29"/>
       <c r="H28" s="28"/>
-      <c r="I28" s="555"/>
-      <c r="J28" s="556"/>
-      <c r="K28" s="557"/>
+      <c r="I28" s="540"/>
+      <c r="J28" s="541"/>
+      <c r="K28" s="542"/>
     </row>
     <row r="29" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="202"/>
@@ -17118,86 +17118,86 @@
       <c r="K34" s="32"/>
     </row>
     <row r="35" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="549"/>
-      <c r="B35" s="550"/>
-      <c r="C35" s="550"/>
-      <c r="D35" s="551"/>
+      <c r="A35" s="543"/>
+      <c r="B35" s="544"/>
+      <c r="C35" s="544"/>
+      <c r="D35" s="545"/>
       <c r="E35" s="27"/>
       <c r="F35" s="27"/>
       <c r="G35" s="29"/>
       <c r="H35" s="28"/>
-      <c r="I35" s="555"/>
-      <c r="J35" s="556"/>
-      <c r="K35" s="557"/>
+      <c r="I35" s="540"/>
+      <c r="J35" s="541"/>
+      <c r="K35" s="542"/>
     </row>
     <row r="36" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="549"/>
-      <c r="B36" s="550"/>
-      <c r="C36" s="550"/>
-      <c r="D36" s="551"/>
+      <c r="A36" s="543"/>
+      <c r="B36" s="544"/>
+      <c r="C36" s="544"/>
+      <c r="D36" s="545"/>
       <c r="E36" s="27"/>
       <c r="F36" s="27"/>
       <c r="G36" s="29"/>
       <c r="H36" s="28"/>
-      <c r="I36" s="555"/>
-      <c r="J36" s="556"/>
-      <c r="K36" s="557"/>
+      <c r="I36" s="540"/>
+      <c r="J36" s="541"/>
+      <c r="K36" s="542"/>
     </row>
     <row r="37" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="549"/>
-      <c r="B37" s="550"/>
-      <c r="C37" s="550"/>
-      <c r="D37" s="551"/>
+      <c r="A37" s="543"/>
+      <c r="B37" s="544"/>
+      <c r="C37" s="544"/>
+      <c r="D37" s="545"/>
       <c r="E37" s="27"/>
       <c r="F37" s="27"/>
       <c r="G37" s="29"/>
       <c r="H37" s="28"/>
-      <c r="I37" s="555"/>
-      <c r="J37" s="556"/>
-      <c r="K37" s="557"/>
+      <c r="I37" s="540"/>
+      <c r="J37" s="541"/>
+      <c r="K37" s="542"/>
     </row>
     <row r="38" spans="1:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="596"/>
-      <c r="B38" s="597"/>
-      <c r="C38" s="597"/>
-      <c r="D38" s="598"/>
+      <c r="A38" s="546"/>
+      <c r="B38" s="547"/>
+      <c r="C38" s="547"/>
+      <c r="D38" s="548"/>
       <c r="E38" s="27"/>
       <c r="F38" s="27"/>
       <c r="G38" s="33"/>
       <c r="H38" s="34"/>
-      <c r="I38" s="599"/>
-      <c r="J38" s="600"/>
-      <c r="K38" s="601"/>
+      <c r="I38" s="549"/>
+      <c r="J38" s="550"/>
+      <c r="K38" s="551"/>
     </row>
     <row r="39" spans="1:11" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="285" t="s">
+      <c r="A39" s="455" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="286"/>
-      <c r="C39" s="286"/>
-      <c r="D39" s="286"/>
-      <c r="E39" s="286"/>
-      <c r="F39" s="286"/>
-      <c r="G39" s="286"/>
-      <c r="H39" s="286"/>
-      <c r="I39" s="286"/>
-      <c r="J39" s="286"/>
-      <c r="K39" s="287"/>
+      <c r="B39" s="456"/>
+      <c r="C39" s="456"/>
+      <c r="D39" s="456"/>
+      <c r="E39" s="456"/>
+      <c r="F39" s="456"/>
+      <c r="G39" s="456"/>
+      <c r="H39" s="456"/>
+      <c r="I39" s="456"/>
+      <c r="J39" s="456"/>
+      <c r="K39" s="457"/>
     </row>
     <row r="40" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="558" t="s">
+      <c r="A40" s="586" t="s">
         <v>332</v>
       </c>
-      <c r="B40" s="559"/>
-      <c r="C40" s="559"/>
-      <c r="D40" s="559"/>
-      <c r="E40" s="559"/>
-      <c r="F40" s="559"/>
-      <c r="G40" s="559"/>
-      <c r="H40" s="559"/>
-      <c r="I40" s="559"/>
-      <c r="J40" s="559"/>
-      <c r="K40" s="560"/>
+      <c r="B40" s="587"/>
+      <c r="C40" s="587"/>
+      <c r="D40" s="587"/>
+      <c r="E40" s="587"/>
+      <c r="F40" s="587"/>
+      <c r="G40" s="587"/>
+      <c r="H40" s="587"/>
+      <c r="I40" s="587"/>
+      <c r="J40" s="587"/>
+      <c r="K40" s="588"/>
     </row>
     <row r="41" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="144" t="s">
@@ -17209,145 +17209,145 @@
       <c r="C41" s="145" t="s">
         <v>335</v>
       </c>
-      <c r="D41" s="538" t="s">
+      <c r="D41" s="592" t="s">
         <v>336</v>
       </c>
-      <c r="E41" s="538"/>
-      <c r="F41" s="538"/>
-      <c r="G41" s="538"/>
-      <c r="H41" s="539"/>
+      <c r="E41" s="592"/>
+      <c r="F41" s="592"/>
+      <c r="G41" s="592"/>
+      <c r="H41" s="593"/>
       <c r="I41" s="145" t="s">
         <v>337</v>
       </c>
-      <c r="J41" s="538" t="s">
+      <c r="J41" s="592" t="s">
         <v>338</v>
       </c>
-      <c r="K41" s="373"/>
+      <c r="K41" s="393"/>
     </row>
     <row r="42" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="533"/>
-      <c r="B42" s="534"/>
-      <c r="C42" s="535"/>
-      <c r="D42" s="536"/>
-      <c r="E42" s="536"/>
-      <c r="F42" s="536"/>
-      <c r="G42" s="536"/>
-      <c r="H42" s="534"/>
-      <c r="I42" s="535"/>
-      <c r="J42" s="536"/>
-      <c r="K42" s="537"/>
+      <c r="A42" s="527"/>
+      <c r="B42" s="529"/>
+      <c r="C42" s="585"/>
+      <c r="D42" s="528"/>
+      <c r="E42" s="528"/>
+      <c r="F42" s="528"/>
+      <c r="G42" s="528"/>
+      <c r="H42" s="529"/>
+      <c r="I42" s="585"/>
+      <c r="J42" s="528"/>
+      <c r="K42" s="594"/>
     </row>
     <row r="43" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="533"/>
-      <c r="B43" s="534"/>
-      <c r="C43" s="535"/>
-      <c r="D43" s="536"/>
-      <c r="E43" s="536"/>
-      <c r="F43" s="536"/>
-      <c r="G43" s="536"/>
-      <c r="H43" s="534"/>
-      <c r="I43" s="535"/>
-      <c r="J43" s="536"/>
-      <c r="K43" s="537"/>
+      <c r="A43" s="527"/>
+      <c r="B43" s="529"/>
+      <c r="C43" s="585"/>
+      <c r="D43" s="528"/>
+      <c r="E43" s="528"/>
+      <c r="F43" s="528"/>
+      <c r="G43" s="528"/>
+      <c r="H43" s="529"/>
+      <c r="I43" s="585"/>
+      <c r="J43" s="528"/>
+      <c r="K43" s="594"/>
     </row>
     <row r="44" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="533"/>
-      <c r="B44" s="534"/>
-      <c r="C44" s="535"/>
-      <c r="D44" s="536"/>
-      <c r="E44" s="536"/>
-      <c r="F44" s="536"/>
-      <c r="G44" s="536"/>
-      <c r="H44" s="534"/>
-      <c r="I44" s="535"/>
-      <c r="J44" s="536"/>
-      <c r="K44" s="537"/>
+      <c r="A44" s="527"/>
+      <c r="B44" s="529"/>
+      <c r="C44" s="585"/>
+      <c r="D44" s="528"/>
+      <c r="E44" s="528"/>
+      <c r="F44" s="528"/>
+      <c r="G44" s="528"/>
+      <c r="H44" s="529"/>
+      <c r="I44" s="585"/>
+      <c r="J44" s="528"/>
+      <c r="K44" s="594"/>
     </row>
     <row r="45" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="533"/>
-      <c r="B45" s="534"/>
-      <c r="C45" s="535"/>
-      <c r="D45" s="536"/>
-      <c r="E45" s="536"/>
-      <c r="F45" s="536"/>
-      <c r="G45" s="536"/>
-      <c r="H45" s="534"/>
-      <c r="I45" s="535"/>
-      <c r="J45" s="536"/>
-      <c r="K45" s="537"/>
+      <c r="A45" s="527"/>
+      <c r="B45" s="529"/>
+      <c r="C45" s="585"/>
+      <c r="D45" s="528"/>
+      <c r="E45" s="528"/>
+      <c r="F45" s="528"/>
+      <c r="G45" s="528"/>
+      <c r="H45" s="529"/>
+      <c r="I45" s="585"/>
+      <c r="J45" s="528"/>
+      <c r="K45" s="594"/>
     </row>
     <row r="46" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="533"/>
-      <c r="B46" s="534"/>
-      <c r="C46" s="535"/>
-      <c r="D46" s="536"/>
-      <c r="E46" s="536"/>
-      <c r="F46" s="536"/>
-      <c r="G46" s="536"/>
-      <c r="H46" s="534"/>
-      <c r="I46" s="535"/>
-      <c r="J46" s="536"/>
-      <c r="K46" s="537"/>
+      <c r="A46" s="527"/>
+      <c r="B46" s="529"/>
+      <c r="C46" s="585"/>
+      <c r="D46" s="528"/>
+      <c r="E46" s="528"/>
+      <c r="F46" s="528"/>
+      <c r="G46" s="528"/>
+      <c r="H46" s="529"/>
+      <c r="I46" s="585"/>
+      <c r="J46" s="528"/>
+      <c r="K46" s="594"/>
     </row>
     <row r="47" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="533"/>
-      <c r="B47" s="534"/>
-      <c r="C47" s="535"/>
-      <c r="D47" s="536"/>
-      <c r="E47" s="536"/>
-      <c r="F47" s="536"/>
-      <c r="G47" s="536"/>
-      <c r="H47" s="534"/>
-      <c r="I47" s="535"/>
-      <c r="J47" s="536"/>
-      <c r="K47" s="537"/>
+      <c r="A47" s="527"/>
+      <c r="B47" s="529"/>
+      <c r="C47" s="585"/>
+      <c r="D47" s="528"/>
+      <c r="E47" s="528"/>
+      <c r="F47" s="528"/>
+      <c r="G47" s="528"/>
+      <c r="H47" s="529"/>
+      <c r="I47" s="585"/>
+      <c r="J47" s="528"/>
+      <c r="K47" s="594"/>
     </row>
     <row r="48" spans="1:11" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="533"/>
-      <c r="B48" s="534"/>
-      <c r="C48" s="535"/>
-      <c r="D48" s="536"/>
-      <c r="E48" s="536"/>
-      <c r="F48" s="536"/>
-      <c r="G48" s="536"/>
-      <c r="H48" s="534"/>
-      <c r="I48" s="535"/>
-      <c r="J48" s="536"/>
-      <c r="K48" s="537"/>
+      <c r="A48" s="527"/>
+      <c r="B48" s="529"/>
+      <c r="C48" s="585"/>
+      <c r="D48" s="528"/>
+      <c r="E48" s="528"/>
+      <c r="F48" s="528"/>
+      <c r="G48" s="528"/>
+      <c r="H48" s="529"/>
+      <c r="I48" s="585"/>
+      <c r="J48" s="528"/>
+      <c r="K48" s="594"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="285" t="s">
+      <c r="A49" s="455" t="s">
         <v>114</v>
       </c>
-      <c r="B49" s="286"/>
-      <c r="C49" s="286"/>
-      <c r="D49" s="286"/>
-      <c r="E49" s="286"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="513"/>
+      <c r="B49" s="456"/>
+      <c r="C49" s="456"/>
+      <c r="D49" s="456"/>
+      <c r="E49" s="456"/>
+      <c r="F49" s="456"/>
+      <c r="G49" s="456"/>
+      <c r="H49" s="456"/>
+      <c r="I49" s="456"/>
+      <c r="J49" s="456"/>
+      <c r="K49" s="500"/>
     </row>
     <row r="50" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="282" t="s">
+      <c r="A50" s="452" t="s">
         <v>143</v>
       </c>
-      <c r="B50" s="284"/>
-      <c r="C50" s="504" t="s">
+      <c r="B50" s="454"/>
+      <c r="C50" s="490" t="s">
         <v>144</v>
       </c>
-      <c r="D50" s="528"/>
-      <c r="E50" s="528"/>
-      <c r="F50" s="529"/>
-      <c r="G50" s="526" t="s">
+      <c r="D50" s="597"/>
+      <c r="E50" s="597"/>
+      <c r="F50" s="598"/>
+      <c r="G50" s="595" t="s">
         <v>145</v>
       </c>
-      <c r="H50" s="527"/>
-      <c r="I50" s="530"/>
-      <c r="J50" s="531"/>
-      <c r="K50" s="532"/>
+      <c r="H50" s="596"/>
+      <c r="I50" s="599"/>
+      <c r="J50" s="600"/>
+      <c r="K50" s="601"/>
       <c r="L50" s="255"/>
       <c r="M50" s="255"/>
     </row>
@@ -17368,6 +17368,73 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="83">
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:H46"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="C48:H48"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="C47:H47"/>
+    <mergeCell ref="C45:H45"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B15:D17"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="H3:K5"/>
+    <mergeCell ref="E3:F4"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I15:K17"/>
+    <mergeCell ref="E15:F16"/>
+    <mergeCell ref="B5:D5"/>
     <mergeCell ref="A39:K39"/>
     <mergeCell ref="H12:K12"/>
     <mergeCell ref="A14:K14"/>
@@ -17384,73 +17451,6 @@
     <mergeCell ref="I38:K38"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B15:D17"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="H3:K5"/>
-    <mergeCell ref="E3:F4"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I15:K17"/>
-    <mergeCell ref="E15:F16"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="C48:H48"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:H43"/>
-    <mergeCell ref="C47:H47"/>
-    <mergeCell ref="C45:H45"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="C50:F50"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="A49:K49"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="C44:H44"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C46:H46"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="I47:K47"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -17483,35 +17483,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="718"/>
-      <c r="B1" s="719"/>
-      <c r="C1" s="719"/>
-      <c r="D1" s="719"/>
-      <c r="E1" s="719"/>
-      <c r="F1" s="719"/>
-      <c r="G1" s="719"/>
-      <c r="H1" s="719"/>
-      <c r="I1" s="719"/>
-      <c r="J1" s="719"/>
-      <c r="K1" s="719"/>
-      <c r="L1" s="719"/>
-      <c r="M1" s="720"/>
+      <c r="A1" s="609"/>
+      <c r="B1" s="610"/>
+      <c r="C1" s="610"/>
+      <c r="D1" s="610"/>
+      <c r="E1" s="610"/>
+      <c r="F1" s="610"/>
+      <c r="G1" s="610"/>
+      <c r="H1" s="610"/>
+      <c r="I1" s="610"/>
+      <c r="J1" s="610"/>
+      <c r="K1" s="610"/>
+      <c r="L1" s="610"/>
+      <c r="M1" s="611"/>
     </row>
     <row r="2" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="695" t="s">
+      <c r="A2" s="634" t="s">
         <v>339</v>
       </c>
-      <c r="B2" s="696"/>
-      <c r="C2" s="723" t="s">
+      <c r="B2" s="635"/>
+      <c r="C2" s="614" t="s">
         <v>340</v>
       </c>
-      <c r="D2" s="723"/>
-      <c r="E2" s="723"/>
-      <c r="F2" s="724"/>
+      <c r="D2" s="614"/>
+      <c r="E2" s="614"/>
+      <c r="F2" s="615"/>
       <c r="G2" s="38"/>
       <c r="H2" s="38"/>
-      <c r="I2" s="721"/>
-      <c r="J2" s="721"/>
+      <c r="I2" s="612"/>
+      <c r="J2" s="612"/>
       <c r="K2" s="39"/>
       <c r="L2" s="39"/>
       <c r="M2" s="40"/>
@@ -17519,16 +17519,16 @@
     <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="41"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="711" t="s">
+      <c r="C3" s="618" t="s">
         <v>341</v>
       </c>
-      <c r="D3" s="711"/>
-      <c r="E3" s="711"/>
-      <c r="F3" s="712"/>
+      <c r="D3" s="618"/>
+      <c r="E3" s="618"/>
+      <c r="F3" s="619"/>
       <c r="G3" s="43"/>
       <c r="H3" s="43"/>
-      <c r="I3" s="722"/>
-      <c r="J3" s="722"/>
+      <c r="I3" s="613"/>
+      <c r="J3" s="613"/>
       <c r="K3" s="44"/>
       <c r="L3" s="44"/>
       <c r="M3" s="45"/>
@@ -17536,42 +17536,42 @@
     <row r="4" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41"/>
       <c r="B4" s="42"/>
-      <c r="C4" s="711" t="s">
+      <c r="C4" s="618" t="s">
         <v>342</v>
       </c>
-      <c r="D4" s="711"/>
-      <c r="E4" s="711"/>
-      <c r="F4" s="712"/>
+      <c r="D4" s="618"/>
+      <c r="E4" s="618"/>
+      <c r="F4" s="619"/>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="41"/>
       <c r="B5" s="42"/>
-      <c r="C5" s="711"/>
-      <c r="D5" s="711"/>
-      <c r="E5" s="711"/>
-      <c r="F5" s="712"/>
-      <c r="G5" s="627"/>
-      <c r="H5" s="627"/>
-      <c r="I5" s="627"/>
-      <c r="J5" s="627"/>
-      <c r="K5" s="627"/>
-      <c r="L5" s="627"/>
+      <c r="C5" s="618"/>
+      <c r="D5" s="618"/>
+      <c r="E5" s="618"/>
+      <c r="F5" s="619"/>
+      <c r="G5" s="606"/>
+      <c r="H5" s="606"/>
+      <c r="I5" s="606"/>
+      <c r="J5" s="606"/>
+      <c r="K5" s="606"/>
+      <c r="L5" s="606"/>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
-      <c r="C6" s="711" t="s">
+      <c r="C6" s="618" t="s">
         <v>343</v>
       </c>
-      <c r="D6" s="711"/>
-      <c r="E6" s="711"/>
-      <c r="F6" s="712"/>
-      <c r="I6" s="717"/>
-      <c r="J6" s="717"/>
-      <c r="K6" s="717"/>
-      <c r="L6" s="717"/>
+      <c r="D6" s="618"/>
+      <c r="E6" s="618"/>
+      <c r="F6" s="619"/>
+      <c r="I6" s="640"/>
+      <c r="J6" s="640"/>
+      <c r="K6" s="640"/>
+      <c r="L6" s="640"/>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -17590,12 +17590,12 @@
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41"/>
       <c r="B8" s="42"/>
-      <c r="C8" s="711" t="s">
+      <c r="C8" s="618" t="s">
         <v>344</v>
       </c>
-      <c r="D8" s="711"/>
-      <c r="E8" s="711"/>
-      <c r="F8" s="712"/>
+      <c r="D8" s="618"/>
+      <c r="E8" s="618"/>
+      <c r="F8" s="619"/>
       <c r="M8" s="46"/>
     </row>
     <row r="9" spans="1:13" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -17610,61 +17610,61 @@
     <row r="10" spans="1:13" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="41"/>
       <c r="B10" s="42"/>
-      <c r="C10" s="711"/>
-      <c r="D10" s="711"/>
-      <c r="E10" s="711"/>
-      <c r="F10" s="712"/>
-      <c r="G10" s="627" t="s">
+      <c r="C10" s="618"/>
+      <c r="D10" s="618"/>
+      <c r="E10" s="618"/>
+      <c r="F10" s="619"/>
+      <c r="G10" s="606" t="s">
         <v>345</v>
       </c>
-      <c r="H10" s="627"/>
-      <c r="I10" s="627"/>
-      <c r="J10" s="627"/>
-      <c r="K10" s="627"/>
-      <c r="L10" s="627"/>
+      <c r="H10" s="606"/>
+      <c r="I10" s="606"/>
+      <c r="J10" s="606"/>
+      <c r="K10" s="606"/>
+      <c r="L10" s="606"/>
       <c r="M10" s="93"/>
     </row>
     <row r="11" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="41"/>
       <c r="B11" s="42"/>
-      <c r="C11" s="711"/>
-      <c r="D11" s="711"/>
-      <c r="E11" s="711"/>
-      <c r="F11" s="712"/>
+      <c r="C11" s="618"/>
+      <c r="D11" s="618"/>
+      <c r="E11" s="618"/>
+      <c r="F11" s="619"/>
       <c r="G11" s="152"/>
       <c r="H11" s="153"/>
-      <c r="I11" s="715"/>
-      <c r="J11" s="715"/>
-      <c r="K11" s="715"/>
-      <c r="L11" s="715"/>
+      <c r="I11" s="638"/>
+      <c r="J11" s="638"/>
+      <c r="K11" s="638"/>
+      <c r="L11" s="638"/>
       <c r="M11" s="93"/>
     </row>
     <row r="12" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="47"/>
       <c r="B12" s="48"/>
-      <c r="C12" s="713"/>
-      <c r="D12" s="713"/>
-      <c r="E12" s="713"/>
-      <c r="F12" s="714"/>
+      <c r="C12" s="636"/>
+      <c r="D12" s="636"/>
+      <c r="E12" s="636"/>
+      <c r="F12" s="637"/>
       <c r="G12" s="153"/>
       <c r="H12" s="153"/>
-      <c r="I12" s="716"/>
-      <c r="J12" s="716"/>
-      <c r="K12" s="716"/>
-      <c r="L12" s="716"/>
+      <c r="I12" s="639"/>
+      <c r="J12" s="639"/>
+      <c r="K12" s="639"/>
+      <c r="L12" s="639"/>
       <c r="M12" s="131"/>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="735" t="s">
+      <c r="A13" s="602" t="s">
         <v>346</v>
       </c>
-      <c r="B13" s="736"/>
-      <c r="C13" s="731" t="s">
+      <c r="B13" s="603"/>
+      <c r="C13" s="604" t="s">
         <v>347</v>
       </c>
-      <c r="D13" s="731"/>
-      <c r="E13" s="564"/>
-      <c r="F13" s="565"/>
+      <c r="D13" s="604"/>
+      <c r="E13" s="556"/>
+      <c r="F13" s="557"/>
       <c r="G13" s="49"/>
       <c r="H13" s="49"/>
       <c r="I13" s="49"/>
@@ -17676,48 +17676,48 @@
     <row r="14" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="64"/>
       <c r="B14" s="65"/>
-      <c r="C14" s="731"/>
-      <c r="D14" s="731"/>
-      <c r="E14" s="564"/>
-      <c r="F14" s="565"/>
-      <c r="G14" s="626" t="s">
+      <c r="C14" s="604"/>
+      <c r="D14" s="604"/>
+      <c r="E14" s="556"/>
+      <c r="F14" s="557"/>
+      <c r="G14" s="605" t="s">
         <v>345</v>
       </c>
-      <c r="H14" s="627"/>
-      <c r="I14" s="627"/>
-      <c r="J14" s="627"/>
-      <c r="K14" s="627"/>
-      <c r="L14" s="627"/>
+      <c r="H14" s="606"/>
+      <c r="I14" s="606"/>
+      <c r="J14" s="606"/>
+      <c r="K14" s="606"/>
+      <c r="L14" s="606"/>
       <c r="M14" s="130"/>
     </row>
     <row r="15" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="64"/>
       <c r="B15" s="65"/>
-      <c r="C15" s="731"/>
-      <c r="D15" s="731"/>
-      <c r="E15" s="564"/>
-      <c r="F15" s="565"/>
+      <c r="C15" s="604"/>
+      <c r="D15" s="604"/>
+      <c r="E15" s="556"/>
+      <c r="F15" s="557"/>
       <c r="G15" s="43"/>
       <c r="H15" s="270"/>
-      <c r="I15" s="737"/>
-      <c r="J15" s="737"/>
-      <c r="K15" s="737"/>
-      <c r="L15" s="737"/>
+      <c r="I15" s="607"/>
+      <c r="J15" s="607"/>
+      <c r="K15" s="607"/>
+      <c r="L15" s="607"/>
       <c r="M15" s="130"/>
     </row>
     <row r="16" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="51"/>
       <c r="B16" s="52"/>
-      <c r="C16" s="564"/>
-      <c r="D16" s="564"/>
-      <c r="E16" s="564"/>
-      <c r="F16" s="565"/>
+      <c r="C16" s="556"/>
+      <c r="D16" s="556"/>
+      <c r="E16" s="556"/>
+      <c r="F16" s="557"/>
       <c r="G16" s="127"/>
       <c r="H16" s="260"/>
-      <c r="I16" s="728"/>
-      <c r="J16" s="728"/>
-      <c r="K16" s="728"/>
-      <c r="L16" s="728"/>
+      <c r="I16" s="608"/>
+      <c r="J16" s="608"/>
+      <c r="K16" s="608"/>
+      <c r="L16" s="608"/>
       <c r="M16" s="128"/>
     </row>
     <row r="17" spans="1:13" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -17738,12 +17738,12 @@
     <row r="18" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="53"/>
       <c r="B18" s="54"/>
-      <c r="C18" s="629" t="s">
+      <c r="C18" s="732" t="s">
         <v>348</v>
       </c>
-      <c r="D18" s="629"/>
-      <c r="E18" s="630"/>
-      <c r="F18" s="631"/>
+      <c r="D18" s="732"/>
+      <c r="E18" s="733"/>
+      <c r="F18" s="734"/>
       <c r="G18" s="58"/>
       <c r="H18" s="58"/>
       <c r="I18" s="58"/>
@@ -17755,32 +17755,32 @@
     <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="53"/>
       <c r="B19" s="54"/>
-      <c r="C19" s="629"/>
-      <c r="D19" s="629"/>
-      <c r="E19" s="630"/>
-      <c r="F19" s="631"/>
-      <c r="G19" s="626" t="s">
+      <c r="C19" s="732"/>
+      <c r="D19" s="732"/>
+      <c r="E19" s="733"/>
+      <c r="F19" s="734"/>
+      <c r="G19" s="605" t="s">
         <v>345</v>
       </c>
-      <c r="H19" s="627"/>
-      <c r="I19" s="627"/>
-      <c r="J19" s="627"/>
-      <c r="K19" s="627"/>
-      <c r="L19" s="627"/>
+      <c r="H19" s="606"/>
+      <c r="I19" s="606"/>
+      <c r="J19" s="606"/>
+      <c r="K19" s="606"/>
+      <c r="L19" s="606"/>
       <c r="M19" s="59"/>
     </row>
     <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="53"/>
       <c r="B20" s="54"/>
-      <c r="C20" s="629"/>
-      <c r="D20" s="629"/>
-      <c r="E20" s="630"/>
-      <c r="F20" s="631"/>
+      <c r="C20" s="732"/>
+      <c r="D20" s="732"/>
+      <c r="E20" s="733"/>
+      <c r="F20" s="734"/>
       <c r="G20" s="58"/>
-      <c r="H20" s="602" t="s">
+      <c r="H20" s="710" t="s">
         <v>349</v>
       </c>
-      <c r="I20" s="602"/>
+      <c r="I20" s="710"/>
       <c r="J20" s="271"/>
       <c r="K20" s="272"/>
       <c r="L20" s="132"/>
@@ -17789,15 +17789,15 @@
     <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="53"/>
       <c r="B21" s="54"/>
-      <c r="C21" s="629"/>
-      <c r="D21" s="629"/>
-      <c r="E21" s="630"/>
-      <c r="F21" s="631"/>
-      <c r="G21" s="603" t="s">
+      <c r="C21" s="732"/>
+      <c r="D21" s="732"/>
+      <c r="E21" s="733"/>
+      <c r="F21" s="734"/>
+      <c r="G21" s="711" t="s">
         <v>350</v>
       </c>
-      <c r="H21" s="604"/>
-      <c r="I21" s="604"/>
+      <c r="H21" s="712"/>
+      <c r="I21" s="712"/>
       <c r="J21" s="271"/>
       <c r="K21" s="273"/>
       <c r="L21" s="132"/>
@@ -17806,31 +17806,31 @@
     <row r="22" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="60"/>
       <c r="B22" s="61"/>
-      <c r="C22" s="632"/>
-      <c r="D22" s="632"/>
-      <c r="E22" s="632"/>
-      <c r="F22" s="633"/>
+      <c r="C22" s="735"/>
+      <c r="D22" s="735"/>
+      <c r="E22" s="735"/>
+      <c r="F22" s="736"/>
       <c r="G22" s="127" t="s">
         <v>351</v>
       </c>
       <c r="H22" s="260"/>
-      <c r="I22" s="634"/>
-      <c r="J22" s="634"/>
-      <c r="K22" s="634"/>
+      <c r="I22" s="737"/>
+      <c r="J22" s="737"/>
+      <c r="K22" s="737"/>
       <c r="L22" s="133"/>
       <c r="M22" s="128"/>
     </row>
     <row r="23" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="622" t="s">
+      <c r="A23" s="641" t="s">
         <v>352</v>
       </c>
-      <c r="B23" s="623"/>
-      <c r="C23" s="636" t="s">
+      <c r="B23" s="642"/>
+      <c r="C23" s="630" t="s">
         <v>353</v>
       </c>
-      <c r="D23" s="636"/>
-      <c r="E23" s="636"/>
-      <c r="F23" s="637"/>
+      <c r="D23" s="630"/>
+      <c r="E23" s="630"/>
+      <c r="F23" s="631"/>
       <c r="G23" s="49"/>
       <c r="H23" s="49"/>
       <c r="I23" s="49"/>
@@ -17842,61 +17842,61 @@
     <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="51"/>
       <c r="B24" s="52"/>
-      <c r="C24" s="638"/>
-      <c r="D24" s="638"/>
-      <c r="E24" s="638"/>
-      <c r="F24" s="639"/>
-      <c r="G24" s="626" t="s">
+      <c r="C24" s="621"/>
+      <c r="D24" s="621"/>
+      <c r="E24" s="621"/>
+      <c r="F24" s="620"/>
+      <c r="G24" s="605" t="s">
         <v>345</v>
       </c>
-      <c r="H24" s="627"/>
-      <c r="I24" s="627"/>
-      <c r="J24" s="627"/>
-      <c r="K24" s="627"/>
-      <c r="L24" s="627"/>
+      <c r="H24" s="606"/>
+      <c r="I24" s="606"/>
+      <c r="J24" s="606"/>
+      <c r="K24" s="606"/>
+      <c r="L24" s="606"/>
       <c r="M24" s="126"/>
     </row>
     <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="51"/>
       <c r="B25" s="52"/>
-      <c r="C25" s="638"/>
-      <c r="D25" s="638"/>
-      <c r="E25" s="638"/>
-      <c r="F25" s="639"/>
+      <c r="C25" s="621"/>
+      <c r="D25" s="621"/>
+      <c r="E25" s="621"/>
+      <c r="F25" s="620"/>
       <c r="G25" s="125"/>
       <c r="H25" s="260"/>
-      <c r="I25" s="635"/>
-      <c r="J25" s="635"/>
-      <c r="K25" s="635"/>
-      <c r="L25" s="635"/>
+      <c r="I25" s="629"/>
+      <c r="J25" s="629"/>
+      <c r="K25" s="629"/>
+      <c r="L25" s="629"/>
       <c r="M25" s="126"/>
     </row>
     <row r="26" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="62"/>
       <c r="B26" s="63"/>
-      <c r="C26" s="640"/>
-      <c r="D26" s="640"/>
-      <c r="E26" s="640"/>
-      <c r="F26" s="641"/>
+      <c r="C26" s="632"/>
+      <c r="D26" s="632"/>
+      <c r="E26" s="632"/>
+      <c r="F26" s="633"/>
       <c r="G26" s="127"/>
       <c r="H26" s="260"/>
-      <c r="I26" s="728"/>
-      <c r="J26" s="728"/>
-      <c r="K26" s="728"/>
-      <c r="L26" s="728"/>
+      <c r="I26" s="608"/>
+      <c r="J26" s="608"/>
+      <c r="K26" s="608"/>
+      <c r="L26" s="608"/>
       <c r="M26" s="128"/>
     </row>
     <row r="27" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="622" t="s">
+      <c r="A27" s="641" t="s">
         <v>354</v>
       </c>
-      <c r="B27" s="623"/>
-      <c r="C27" s="636" t="s">
+      <c r="B27" s="642"/>
+      <c r="C27" s="630" t="s">
         <v>355</v>
       </c>
-      <c r="D27" s="636"/>
-      <c r="E27" s="636"/>
-      <c r="F27" s="637"/>
+      <c r="D27" s="630"/>
+      <c r="E27" s="630"/>
+      <c r="F27" s="631"/>
       <c r="G27" s="49"/>
       <c r="H27" s="49"/>
       <c r="I27" s="49"/>
@@ -17908,41 +17908,41 @@
     <row r="28" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="51"/>
       <c r="B28" s="52"/>
-      <c r="C28" s="638"/>
-      <c r="D28" s="638"/>
-      <c r="E28" s="638"/>
-      <c r="F28" s="639"/>
-      <c r="G28" s="626" t="s">
+      <c r="C28" s="621"/>
+      <c r="D28" s="621"/>
+      <c r="E28" s="621"/>
+      <c r="F28" s="620"/>
+      <c r="G28" s="605" t="s">
         <v>345</v>
       </c>
-      <c r="H28" s="627"/>
-      <c r="I28" s="627"/>
-      <c r="J28" s="627"/>
-      <c r="K28" s="627"/>
-      <c r="L28" s="627"/>
+      <c r="H28" s="606"/>
+      <c r="I28" s="606"/>
+      <c r="J28" s="606"/>
+      <c r="K28" s="606"/>
+      <c r="L28" s="606"/>
       <c r="M28" s="2"/>
     </row>
     <row r="29" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="51"/>
       <c r="B29" s="52"/>
-      <c r="C29" s="638"/>
-      <c r="D29" s="638"/>
-      <c r="E29" s="638"/>
-      <c r="F29" s="639"/>
+      <c r="C29" s="621"/>
+      <c r="D29" s="621"/>
+      <c r="E29" s="621"/>
+      <c r="F29" s="620"/>
       <c r="H29" s="189"/>
-      <c r="I29" s="635"/>
-      <c r="J29" s="635"/>
-      <c r="K29" s="635"/>
-      <c r="L29" s="635"/>
+      <c r="I29" s="629"/>
+      <c r="J29" s="629"/>
+      <c r="K29" s="629"/>
+      <c r="L29" s="629"/>
       <c r="M29" s="126"/>
     </row>
     <row r="30" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="62"/>
       <c r="B30" s="63"/>
-      <c r="C30" s="640"/>
-      <c r="D30" s="640"/>
-      <c r="E30" s="640"/>
-      <c r="F30" s="641"/>
+      <c r="C30" s="632"/>
+      <c r="D30" s="632"/>
+      <c r="E30" s="632"/>
+      <c r="F30" s="633"/>
       <c r="G30" s="147"/>
       <c r="H30" s="262"/>
       <c r="I30" s="189"/>
@@ -17952,16 +17952,16 @@
       <c r="M30" s="128"/>
     </row>
     <row r="31" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="622" t="s">
+      <c r="A31" s="641" t="s">
         <v>356</v>
       </c>
-      <c r="B31" s="623"/>
-      <c r="C31" s="636" t="s">
+      <c r="B31" s="642"/>
+      <c r="C31" s="630" t="s">
         <v>357</v>
       </c>
-      <c r="D31" s="636"/>
-      <c r="E31" s="636"/>
-      <c r="F31" s="637"/>
+      <c r="D31" s="630"/>
+      <c r="E31" s="630"/>
+      <c r="F31" s="631"/>
       <c r="G31" s="49"/>
       <c r="H31" s="49"/>
       <c r="I31" s="49"/>
@@ -17973,18 +17973,18 @@
     <row r="32" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="51"/>
       <c r="B32" s="52"/>
-      <c r="C32" s="638"/>
-      <c r="D32" s="638"/>
-      <c r="E32" s="638"/>
-      <c r="F32" s="639"/>
-      <c r="G32" s="674" t="s">
+      <c r="C32" s="621"/>
+      <c r="D32" s="621"/>
+      <c r="E32" s="621"/>
+      <c r="F32" s="620"/>
+      <c r="G32" s="677" t="s">
         <v>358</v>
       </c>
-      <c r="H32" s="675"/>
-      <c r="I32" s="675"/>
-      <c r="J32" s="675"/>
-      <c r="K32" s="673"/>
-      <c r="L32" s="673"/>
+      <c r="H32" s="678"/>
+      <c r="I32" s="678"/>
+      <c r="J32" s="678"/>
+      <c r="K32" s="643"/>
+      <c r="L32" s="643"/>
       <c r="M32" s="126"/>
     </row>
     <row r="33" spans="1:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18005,44 +18005,44 @@
     <row r="34" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="51"/>
       <c r="B34" s="52"/>
-      <c r="C34" s="638" t="s">
+      <c r="C34" s="621" t="s">
         <v>359</v>
       </c>
-      <c r="D34" s="638"/>
-      <c r="E34" s="638"/>
-      <c r="F34" s="639"/>
+      <c r="D34" s="621"/>
+      <c r="E34" s="621"/>
+      <c r="F34" s="620"/>
       <c r="G34" s="125"/>
       <c r="H34" s="261"/>
-      <c r="I34" s="672"/>
-      <c r="J34" s="672"/>
-      <c r="K34" s="672"/>
-      <c r="L34" s="672"/>
+      <c r="I34" s="676"/>
+      <c r="J34" s="676"/>
+      <c r="K34" s="676"/>
+      <c r="L34" s="676"/>
       <c r="M34" s="126"/>
     </row>
     <row r="35" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="51"/>
       <c r="B35" s="52"/>
-      <c r="C35" s="638"/>
-      <c r="D35" s="638"/>
-      <c r="E35" s="638"/>
-      <c r="F35" s="639"/>
-      <c r="G35" s="674" t="s">
+      <c r="C35" s="621"/>
+      <c r="D35" s="621"/>
+      <c r="E35" s="621"/>
+      <c r="F35" s="620"/>
+      <c r="G35" s="677" t="s">
         <v>358</v>
       </c>
-      <c r="H35" s="675"/>
-      <c r="I35" s="675"/>
-      <c r="J35" s="675"/>
-      <c r="K35" s="673"/>
-      <c r="L35" s="673"/>
+      <c r="H35" s="678"/>
+      <c r="I35" s="678"/>
+      <c r="J35" s="678"/>
+      <c r="K35" s="643"/>
+      <c r="L35" s="643"/>
       <c r="M35" s="126"/>
     </row>
     <row r="36" spans="1:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="62"/>
       <c r="B36" s="63"/>
-      <c r="C36" s="640"/>
-      <c r="D36" s="640"/>
-      <c r="E36" s="640"/>
-      <c r="F36" s="641"/>
+      <c r="C36" s="632"/>
+      <c r="D36" s="632"/>
+      <c r="E36" s="632"/>
+      <c r="F36" s="633"/>
       <c r="G36" s="129"/>
       <c r="H36" s="73"/>
       <c r="I36" s="120"/>
@@ -18051,16 +18051,16 @@
       <c r="M36" s="128"/>
     </row>
     <row r="37" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="622" t="s">
+      <c r="A37" s="641" t="s">
         <v>360</v>
       </c>
-      <c r="B37" s="623"/>
-      <c r="C37" s="729" t="s">
+      <c r="B37" s="642"/>
+      <c r="C37" s="624" t="s">
         <v>361</v>
       </c>
-      <c r="D37" s="729"/>
-      <c r="E37" s="729"/>
-      <c r="F37" s="730"/>
+      <c r="D37" s="624"/>
+      <c r="E37" s="624"/>
+      <c r="F37" s="625"/>
       <c r="G37" s="49"/>
       <c r="H37" s="49"/>
       <c r="I37" s="49"/>
@@ -18072,61 +18072,61 @@
     <row r="38" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="51"/>
       <c r="B38" s="52"/>
-      <c r="C38" s="731"/>
-      <c r="D38" s="731"/>
-      <c r="E38" s="731"/>
-      <c r="F38" s="732"/>
-      <c r="G38" s="626" t="s">
+      <c r="C38" s="604"/>
+      <c r="D38" s="604"/>
+      <c r="E38" s="604"/>
+      <c r="F38" s="626"/>
+      <c r="G38" s="605" t="s">
         <v>362</v>
       </c>
-      <c r="H38" s="627"/>
-      <c r="I38" s="627"/>
-      <c r="J38" s="627"/>
-      <c r="K38" s="627"/>
-      <c r="L38" s="627"/>
-      <c r="M38" s="628"/>
+      <c r="H38" s="606"/>
+      <c r="I38" s="606"/>
+      <c r="J38" s="606"/>
+      <c r="K38" s="606"/>
+      <c r="L38" s="606"/>
+      <c r="M38" s="731"/>
     </row>
     <row r="39" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="51"/>
       <c r="B39" s="52"/>
-      <c r="C39" s="731"/>
-      <c r="D39" s="731"/>
-      <c r="E39" s="731"/>
-      <c r="F39" s="732"/>
+      <c r="C39" s="604"/>
+      <c r="D39" s="604"/>
+      <c r="E39" s="604"/>
+      <c r="F39" s="626"/>
       <c r="G39" s="125"/>
       <c r="H39" s="260"/>
-      <c r="I39" s="635"/>
-      <c r="J39" s="635"/>
-      <c r="K39" s="635"/>
-      <c r="L39" s="635"/>
+      <c r="I39" s="629"/>
+      <c r="J39" s="629"/>
+      <c r="K39" s="629"/>
+      <c r="L39" s="629"/>
       <c r="M39" s="126"/>
     </row>
     <row r="40" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="62"/>
       <c r="B40" s="63"/>
-      <c r="C40" s="733"/>
-      <c r="D40" s="733"/>
-      <c r="E40" s="733"/>
-      <c r="F40" s="734"/>
+      <c r="C40" s="627"/>
+      <c r="D40" s="627"/>
+      <c r="E40" s="627"/>
+      <c r="F40" s="628"/>
       <c r="G40" s="127"/>
       <c r="H40" s="260"/>
-      <c r="I40" s="728"/>
-      <c r="J40" s="728"/>
-      <c r="K40" s="728"/>
-      <c r="L40" s="728"/>
+      <c r="I40" s="608"/>
+      <c r="J40" s="608"/>
+      <c r="K40" s="608"/>
+      <c r="L40" s="608"/>
       <c r="M40" s="128"/>
     </row>
     <row r="41" spans="1:14" ht="41.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="726" t="s">
+      <c r="A41" s="622" t="s">
         <v>363</v>
       </c>
-      <c r="B41" s="727"/>
-      <c r="C41" s="638" t="s">
+      <c r="B41" s="623"/>
+      <c r="C41" s="621" t="s">
         <v>364</v>
       </c>
-      <c r="D41" s="638"/>
-      <c r="E41" s="638"/>
-      <c r="F41" s="639"/>
+      <c r="D41" s="621"/>
+      <c r="E41" s="621"/>
+      <c r="F41" s="620"/>
       <c r="G41" s="49"/>
       <c r="H41" s="49"/>
       <c r="I41" s="68"/>
@@ -18138,10 +18138,10 @@
     <row r="42" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="66"/>
       <c r="B42" s="67"/>
-      <c r="C42" s="638"/>
-      <c r="D42" s="638"/>
-      <c r="E42" s="638"/>
-      <c r="F42" s="639"/>
+      <c r="C42" s="621"/>
+      <c r="D42" s="621"/>
+      <c r="E42" s="621"/>
+      <c r="F42" s="620"/>
       <c r="G42" s="71"/>
       <c r="H42" s="71"/>
       <c r="I42" s="71"/>
@@ -18155,21 +18155,21 @@
         <v>365</v>
       </c>
       <c r="B43" s="67"/>
-      <c r="C43" s="638" t="s">
+      <c r="C43" s="621" t="s">
         <v>366</v>
       </c>
-      <c r="D43" s="638"/>
-      <c r="E43" s="638"/>
-      <c r="F43" s="639"/>
+      <c r="D43" s="621"/>
+      <c r="E43" s="621"/>
+      <c r="F43" s="620"/>
       <c r="M43" s="2"/>
     </row>
     <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="66"/>
       <c r="B44" s="67"/>
-      <c r="C44" s="638"/>
-      <c r="D44" s="638"/>
-      <c r="E44" s="638"/>
-      <c r="F44" s="639"/>
+      <c r="C44" s="621"/>
+      <c r="D44" s="621"/>
+      <c r="E44" s="621"/>
+      <c r="F44" s="620"/>
       <c r="G44" s="199" t="s">
         <v>367</v>
       </c>
@@ -18185,21 +18185,21 @@
         <v>368</v>
       </c>
       <c r="B45" s="67"/>
-      <c r="C45" s="639" t="s">
+      <c r="C45" s="620" t="s">
         <v>369</v>
       </c>
-      <c r="D45" s="639"/>
-      <c r="E45" s="639"/>
-      <c r="F45" s="639"/>
+      <c r="D45" s="620"/>
+      <c r="E45" s="620"/>
+      <c r="F45" s="620"/>
       <c r="M45" s="2"/>
     </row>
     <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="66"/>
       <c r="B46" s="67"/>
-      <c r="C46" s="639"/>
-      <c r="D46" s="639"/>
-      <c r="E46" s="639"/>
-      <c r="F46" s="639"/>
+      <c r="C46" s="620"/>
+      <c r="D46" s="620"/>
+      <c r="E46" s="620"/>
+      <c r="F46" s="620"/>
       <c r="G46" s="200" t="s">
         <v>370</v>
       </c>
@@ -18216,21 +18216,21 @@
         <v>371</v>
       </c>
       <c r="B47" s="67"/>
-      <c r="C47" s="638" t="s">
+      <c r="C47" s="621" t="s">
         <v>372</v>
       </c>
-      <c r="D47" s="638"/>
+      <c r="D47" s="621"/>
       <c r="E47" s="117"/>
       <c r="F47" s="118"/>
       <c r="M47" s="2"/>
     </row>
     <row r="48" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="689"/>
-      <c r="B48" s="690"/>
-      <c r="C48" s="690"/>
-      <c r="D48" s="690"/>
-      <c r="E48" s="690"/>
-      <c r="F48" s="691"/>
+      <c r="A48" s="656"/>
+      <c r="B48" s="657"/>
+      <c r="C48" s="657"/>
+      <c r="D48" s="657"/>
+      <c r="E48" s="657"/>
+      <c r="F48" s="658"/>
       <c r="G48" s="201" t="s">
         <v>370</v>
       </c>
@@ -18243,12 +18243,12 @@
       <c r="N48" s="73"/>
     </row>
     <row r="49" spans="1:14" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="692"/>
-      <c r="B49" s="693"/>
-      <c r="C49" s="693"/>
-      <c r="D49" s="693"/>
-      <c r="E49" s="693"/>
-      <c r="F49" s="694"/>
+      <c r="A49" s="659"/>
+      <c r="B49" s="660"/>
+      <c r="C49" s="660"/>
+      <c r="D49" s="660"/>
+      <c r="E49" s="660"/>
+      <c r="F49" s="661"/>
       <c r="G49" s="119"/>
       <c r="H49" s="115"/>
       <c r="I49" s="115"/>
@@ -18259,10 +18259,10 @@
       <c r="N49" s="73"/>
     </row>
     <row r="50" spans="1:14" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="624" t="s">
+      <c r="A50" s="729" t="s">
         <v>373</v>
       </c>
-      <c r="B50" s="625"/>
+      <c r="B50" s="730"/>
       <c r="C50" s="197" t="s">
         <v>374</v>
       </c>
@@ -18272,127 +18272,127 @@
       <c r="G50" s="197"/>
       <c r="H50" s="197"/>
       <c r="I50" s="198"/>
-      <c r="J50" s="676"/>
-      <c r="K50" s="677"/>
-      <c r="L50" s="677"/>
-      <c r="M50" s="678"/>
+      <c r="J50" s="644"/>
+      <c r="K50" s="645"/>
+      <c r="L50" s="645"/>
+      <c r="M50" s="646"/>
     </row>
     <row r="51" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="686" t="s">
+      <c r="A51" s="653" t="s">
         <v>375</v>
       </c>
-      <c r="B51" s="687"/>
-      <c r="C51" s="687"/>
-      <c r="D51" s="687"/>
-      <c r="E51" s="688"/>
+      <c r="B51" s="654"/>
+      <c r="C51" s="654"/>
+      <c r="D51" s="654"/>
+      <c r="E51" s="655"/>
       <c r="F51" s="278" t="s">
         <v>376</v>
       </c>
-      <c r="G51" s="372" t="s">
+      <c r="G51" s="392" t="s">
         <v>377</v>
       </c>
-      <c r="H51" s="538"/>
-      <c r="I51" s="373"/>
-      <c r="J51" s="679"/>
-      <c r="K51" s="680"/>
-      <c r="L51" s="680"/>
-      <c r="M51" s="681"/>
+      <c r="H51" s="592"/>
+      <c r="I51" s="393"/>
+      <c r="J51" s="647"/>
+      <c r="K51" s="648"/>
+      <c r="L51" s="648"/>
+      <c r="M51" s="649"/>
     </row>
     <row r="52" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="704"/>
-      <c r="B52" s="705"/>
-      <c r="C52" s="707"/>
-      <c r="D52" s="707"/>
-      <c r="E52" s="708"/>
+      <c r="A52" s="669"/>
+      <c r="B52" s="670"/>
+      <c r="C52" s="672"/>
+      <c r="D52" s="672"/>
+      <c r="E52" s="673"/>
       <c r="F52" s="74"/>
-      <c r="G52" s="697"/>
-      <c r="H52" s="698"/>
-      <c r="I52" s="699"/>
-      <c r="J52" s="679"/>
-      <c r="K52" s="680"/>
-      <c r="L52" s="680"/>
-      <c r="M52" s="681"/>
+      <c r="G52" s="662"/>
+      <c r="H52" s="663"/>
+      <c r="I52" s="664"/>
+      <c r="J52" s="647"/>
+      <c r="K52" s="648"/>
+      <c r="L52" s="648"/>
+      <c r="M52" s="649"/>
     </row>
     <row r="53" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="704"/>
-      <c r="B53" s="705"/>
-      <c r="C53" s="705"/>
-      <c r="D53" s="705"/>
-      <c r="E53" s="706"/>
+      <c r="A53" s="669"/>
+      <c r="B53" s="670"/>
+      <c r="C53" s="670"/>
+      <c r="D53" s="670"/>
+      <c r="E53" s="671"/>
       <c r="F53" s="74"/>
-      <c r="G53" s="697"/>
-      <c r="H53" s="698"/>
-      <c r="I53" s="699"/>
-      <c r="J53" s="679"/>
-      <c r="K53" s="680"/>
-      <c r="L53" s="680"/>
-      <c r="M53" s="681"/>
+      <c r="G53" s="662"/>
+      <c r="H53" s="663"/>
+      <c r="I53" s="664"/>
+      <c r="J53" s="647"/>
+      <c r="K53" s="648"/>
+      <c r="L53" s="648"/>
+      <c r="M53" s="649"/>
     </row>
     <row r="54" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="700"/>
-      <c r="B54" s="701"/>
-      <c r="C54" s="702"/>
-      <c r="D54" s="702"/>
-      <c r="E54" s="703"/>
+      <c r="A54" s="665"/>
+      <c r="B54" s="666"/>
+      <c r="C54" s="667"/>
+      <c r="D54" s="667"/>
+      <c r="E54" s="668"/>
       <c r="F54" s="209"/>
-      <c r="G54" s="683"/>
-      <c r="H54" s="684"/>
-      <c r="I54" s="685"/>
-      <c r="J54" s="679"/>
-      <c r="K54" s="680"/>
-      <c r="L54" s="680"/>
-      <c r="M54" s="681"/>
+      <c r="G54" s="650"/>
+      <c r="H54" s="651"/>
+      <c r="I54" s="652"/>
+      <c r="J54" s="647"/>
+      <c r="K54" s="648"/>
+      <c r="L54" s="648"/>
+      <c r="M54" s="649"/>
     </row>
     <row r="55" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="695" t="s">
+      <c r="A55" s="634" t="s">
         <v>378</v>
       </c>
-      <c r="B55" s="696"/>
-      <c r="C55" s="709" t="s">
+      <c r="B55" s="635"/>
+      <c r="C55" s="674" t="s">
         <v>399</v>
       </c>
-      <c r="D55" s="709"/>
-      <c r="E55" s="709"/>
-      <c r="F55" s="709"/>
-      <c r="G55" s="709"/>
-      <c r="H55" s="709"/>
+      <c r="D55" s="674"/>
+      <c r="E55" s="674"/>
+      <c r="F55" s="674"/>
+      <c r="G55" s="674"/>
+      <c r="H55" s="674"/>
       <c r="I55" s="266"/>
-      <c r="J55" s="680"/>
-      <c r="K55" s="680"/>
-      <c r="L55" s="680"/>
-      <c r="M55" s="681"/>
+      <c r="J55" s="648"/>
+      <c r="K55" s="648"/>
+      <c r="L55" s="648"/>
+      <c r="M55" s="649"/>
     </row>
     <row r="56" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="75"/>
       <c r="B56" s="76"/>
-      <c r="C56" s="710"/>
-      <c r="D56" s="710"/>
-      <c r="E56" s="710"/>
-      <c r="F56" s="710"/>
-      <c r="G56" s="710"/>
-      <c r="H56" s="710"/>
+      <c r="C56" s="675"/>
+      <c r="D56" s="675"/>
+      <c r="E56" s="675"/>
+      <c r="F56" s="675"/>
+      <c r="G56" s="675"/>
+      <c r="H56" s="675"/>
       <c r="I56" s="267"/>
       <c r="J56" s="208"/>
-      <c r="K56" s="682" t="s">
+      <c r="K56" s="616" t="s">
         <v>379</v>
       </c>
-      <c r="L56" s="682"/>
+      <c r="L56" s="616"/>
       <c r="M56" s="188"/>
     </row>
     <row r="57" spans="1:14" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="75"/>
       <c r="B57" s="76"/>
-      <c r="C57" s="710"/>
-      <c r="D57" s="710"/>
-      <c r="E57" s="710"/>
-      <c r="F57" s="710"/>
-      <c r="G57" s="710"/>
-      <c r="H57" s="710"/>
+      <c r="C57" s="675"/>
+      <c r="D57" s="675"/>
+      <c r="E57" s="675"/>
+      <c r="F57" s="675"/>
+      <c r="G57" s="675"/>
+      <c r="H57" s="675"/>
       <c r="I57" s="267"/>
-      <c r="J57" s="682"/>
-      <c r="K57" s="682"/>
-      <c r="L57" s="682"/>
-      <c r="M57" s="725"/>
+      <c r="J57" s="616"/>
+      <c r="K57" s="616"/>
+      <c r="L57" s="616"/>
+      <c r="M57" s="617"/>
     </row>
     <row r="58" spans="1:14" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="186"/>
@@ -18404,8 +18404,8 @@
       <c r="G58" s="268"/>
       <c r="H58" s="268"/>
       <c r="I58" s="269"/>
-      <c r="K58" s="662"/>
-      <c r="L58" s="663"/>
+      <c r="K58" s="700"/>
+      <c r="L58" s="701"/>
       <c r="M58" s="2"/>
     </row>
     <row r="59" spans="1:14" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -18417,104 +18417,104 @@
       <c r="G59" s="44"/>
       <c r="H59" s="44"/>
       <c r="I59" s="44"/>
-      <c r="K59" s="664"/>
-      <c r="L59" s="665"/>
+      <c r="K59" s="702"/>
+      <c r="L59" s="703"/>
       <c r="M59" s="2"/>
     </row>
     <row r="60" spans="1:14" ht="32.549999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="77"/>
-      <c r="B60" s="614" t="s">
+      <c r="B60" s="722" t="s">
         <v>400</v>
       </c>
-      <c r="C60" s="615"/>
-      <c r="D60" s="616"/>
-      <c r="F60" s="605" t="s">
+      <c r="C60" s="723"/>
+      <c r="D60" s="724"/>
+      <c r="F60" s="713" t="s">
         <v>144</v>
       </c>
-      <c r="G60" s="606"/>
-      <c r="H60" s="606"/>
-      <c r="I60" s="607"/>
-      <c r="K60" s="664"/>
-      <c r="L60" s="665"/>
+      <c r="G60" s="714"/>
+      <c r="H60" s="714"/>
+      <c r="I60" s="715"/>
+      <c r="K60" s="702"/>
+      <c r="L60" s="703"/>
       <c r="M60" s="78"/>
     </row>
     <row r="61" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="77"/>
-      <c r="B61" s="668" t="s">
+      <c r="B61" s="706" t="s">
         <v>380</v>
       </c>
-      <c r="C61" s="669"/>
+      <c r="C61" s="707"/>
       <c r="D61" s="134"/>
-      <c r="F61" s="608"/>
-      <c r="G61" s="609"/>
-      <c r="H61" s="609"/>
-      <c r="I61" s="610"/>
-      <c r="K61" s="664"/>
-      <c r="L61" s="665"/>
+      <c r="F61" s="716"/>
+      <c r="G61" s="717"/>
+      <c r="H61" s="717"/>
+      <c r="I61" s="718"/>
+      <c r="K61" s="702"/>
+      <c r="L61" s="703"/>
       <c r="M61" s="78"/>
     </row>
     <row r="62" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="77"/>
-      <c r="B62" s="657" t="s">
+      <c r="B62" s="694" t="s">
         <v>381</v>
       </c>
-      <c r="C62" s="658"/>
-      <c r="D62" s="617"/>
-      <c r="F62" s="611"/>
-      <c r="G62" s="612"/>
-      <c r="H62" s="612"/>
-      <c r="I62" s="613"/>
-      <c r="K62" s="664"/>
-      <c r="L62" s="665"/>
+      <c r="C62" s="695"/>
+      <c r="D62" s="698"/>
+      <c r="F62" s="719"/>
+      <c r="G62" s="720"/>
+      <c r="H62" s="720"/>
+      <c r="I62" s="721"/>
+      <c r="K62" s="702"/>
+      <c r="L62" s="703"/>
       <c r="M62" s="78"/>
     </row>
     <row r="63" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="77"/>
-      <c r="B63" s="670"/>
-      <c r="C63" s="671"/>
-      <c r="D63" s="618"/>
-      <c r="F63" s="619" t="s">
+      <c r="B63" s="708"/>
+      <c r="C63" s="709"/>
+      <c r="D63" s="725"/>
+      <c r="F63" s="726" t="s">
         <v>382</v>
       </c>
-      <c r="G63" s="620"/>
-      <c r="H63" s="620"/>
-      <c r="I63" s="621"/>
-      <c r="K63" s="664"/>
-      <c r="L63" s="665"/>
+      <c r="G63" s="727"/>
+      <c r="H63" s="727"/>
+      <c r="I63" s="728"/>
+      <c r="K63" s="702"/>
+      <c r="L63" s="703"/>
       <c r="M63" s="78"/>
     </row>
     <row r="64" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="77"/>
-      <c r="B64" s="657" t="s">
+      <c r="B64" s="694" t="s">
         <v>383</v>
       </c>
-      <c r="C64" s="658"/>
-      <c r="D64" s="617"/>
+      <c r="C64" s="695"/>
+      <c r="D64" s="698"/>
       <c r="F64" s="79"/>
       <c r="G64" s="189"/>
       <c r="H64" s="189"/>
       <c r="I64" s="190"/>
       <c r="J64" s="80"/>
-      <c r="K64" s="666"/>
-      <c r="L64" s="667"/>
+      <c r="K64" s="704"/>
+      <c r="L64" s="705"/>
       <c r="M64" s="78"/>
     </row>
     <row r="65" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="77"/>
-      <c r="B65" s="659"/>
-      <c r="C65" s="660"/>
-      <c r="D65" s="661"/>
-      <c r="F65" s="654" t="s">
+      <c r="B65" s="696"/>
+      <c r="C65" s="697"/>
+      <c r="D65" s="699"/>
+      <c r="F65" s="691" t="s">
         <v>384</v>
       </c>
-      <c r="G65" s="655"/>
-      <c r="H65" s="655"/>
-      <c r="I65" s="656"/>
+      <c r="G65" s="692"/>
+      <c r="H65" s="692"/>
+      <c r="I65" s="693"/>
       <c r="J65" s="80"/>
-      <c r="K65" s="652" t="s">
+      <c r="K65" s="689" t="s">
         <v>385</v>
       </c>
-      <c r="L65" s="653"/>
+      <c r="L65" s="690"/>
       <c r="M65" s="78"/>
     </row>
     <row r="66" spans="1:13" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -18533,34 +18533,34 @@
       <c r="M66" s="86"/>
     </row>
     <row r="67" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="649" t="s">
+      <c r="A67" s="686" t="s">
         <v>386</v>
       </c>
-      <c r="B67" s="650"/>
-      <c r="C67" s="650"/>
-      <c r="D67" s="650"/>
-      <c r="E67" s="650"/>
-      <c r="F67" s="650"/>
-      <c r="G67" s="650"/>
-      <c r="H67" s="650"/>
-      <c r="I67" s="650"/>
-      <c r="J67" s="650"/>
-      <c r="K67" s="650"/>
-      <c r="L67" s="650"/>
-      <c r="M67" s="651"/>
+      <c r="B67" s="687"/>
+      <c r="C67" s="687"/>
+      <c r="D67" s="687"/>
+      <c r="E67" s="687"/>
+      <c r="F67" s="687"/>
+      <c r="G67" s="687"/>
+      <c r="H67" s="687"/>
+      <c r="I67" s="687"/>
+      <c r="J67" s="687"/>
+      <c r="K67" s="687"/>
+      <c r="L67" s="687"/>
+      <c r="M67" s="688"/>
     </row>
     <row r="68" spans="1:13" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="77"/>
       <c r="B68" s="80"/>
       <c r="C68" s="87"/>
       <c r="D68" s="87"/>
-      <c r="E68" s="646" t="s">
+      <c r="E68" s="683" t="s">
         <v>387</v>
       </c>
-      <c r="F68" s="647"/>
-      <c r="G68" s="647"/>
-      <c r="H68" s="647"/>
-      <c r="I68" s="648"/>
+      <c r="F68" s="684"/>
+      <c r="G68" s="684"/>
+      <c r="H68" s="684"/>
+      <c r="I68" s="685"/>
       <c r="J68" s="135"/>
       <c r="K68" s="135"/>
       <c r="M68" s="78"/>
@@ -18570,13 +18570,13 @@
       <c r="B69" s="80"/>
       <c r="C69" s="251"/>
       <c r="D69" s="251"/>
-      <c r="E69" s="643" t="s">
+      <c r="E69" s="680" t="s">
         <v>388</v>
       </c>
-      <c r="F69" s="644"/>
-      <c r="G69" s="644"/>
-      <c r="H69" s="644"/>
-      <c r="I69" s="645"/>
+      <c r="F69" s="681"/>
+      <c r="G69" s="681"/>
+      <c r="H69" s="681"/>
+      <c r="I69" s="682"/>
       <c r="J69" s="137"/>
       <c r="K69" s="136"/>
       <c r="L69" s="88"/>
@@ -18598,21 +18598,21 @@
       <c r="M70" s="91"/>
     </row>
     <row r="71" spans="1:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="642" t="s">
+      <c r="A71" s="679" t="s">
         <v>402</v>
       </c>
-      <c r="B71" s="642"/>
-      <c r="C71" s="642"/>
-      <c r="D71" s="642"/>
-      <c r="E71" s="642"/>
-      <c r="F71" s="642"/>
-      <c r="G71" s="642"/>
-      <c r="H71" s="642"/>
-      <c r="I71" s="642"/>
-      <c r="J71" s="642"/>
-      <c r="K71" s="642"/>
-      <c r="L71" s="642"/>
-      <c r="M71" s="642"/>
+      <c r="B71" s="679"/>
+      <c r="C71" s="679"/>
+      <c r="D71" s="679"/>
+      <c r="E71" s="679"/>
+      <c r="F71" s="679"/>
+      <c r="G71" s="679"/>
+      <c r="H71" s="679"/>
+      <c r="I71" s="679"/>
+      <c r="J71" s="679"/>
+      <c r="K71" s="679"/>
+      <c r="L71" s="679"/>
+      <c r="M71" s="679"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -18625,11 +18625,70 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="85">
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:F16"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="F60:I62"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="G38:M38"/>
+    <mergeCell ref="C18:F22"/>
+    <mergeCell ref="G28:L28"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="G19:L19"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="C23:F26"/>
+    <mergeCell ref="A71:M71"/>
+    <mergeCell ref="E69:I69"/>
+    <mergeCell ref="E68:I68"/>
+    <mergeCell ref="A67:M67"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="B64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="K58:L64"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C63"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="C31:F32"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C34:F36"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="J50:M55"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A48:F49"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="C55:H57"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="C8:F8"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="I3:J3"/>
@@ -18646,70 +18705,11 @@
     <mergeCell ref="I29:L29"/>
     <mergeCell ref="I26:L26"/>
     <mergeCell ref="C27:F30"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="J50:M55"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A48:F49"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="C55:H57"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="C31:F32"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C34:F36"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="A71:M71"/>
-    <mergeCell ref="E69:I69"/>
-    <mergeCell ref="E68:I68"/>
-    <mergeCell ref="A67:M67"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="F65:I65"/>
-    <mergeCell ref="B64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="K58:L64"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C63"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="F60:I62"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="G38:M38"/>
-    <mergeCell ref="C18:F22"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="G19:L19"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="C23:F26"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:F16"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I16:L16"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -19346,6 +19346,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="61535973-5223-4bf4-bdcc-6c7df9166676">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004061E9AFAF7CA04B82F43B8373745610" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3807037a0979b6ce9196f65959799221">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="61535973-5223-4bf4-bdcc-6c7df9166676" xmlns:ns3="ab5b6d4b-4285-4680-b1ee-6fe31a63f7d7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0698124c94b6a25b909cbe33b647c32f" ns2:_="" ns3:_="">
     <xsd:import namespace="61535973-5223-4bf4-bdcc-6c7df9166676"/>
@@ -19576,16 +19586,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="61535973-5223-4bf4-bdcc-6c7df9166676">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -19596,6 +19596,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CF60C-2A54-4479-8975-DF3B2608842A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="ab5b6d4b-4285-4680-b1ee-6fe31a63f7d7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="61535973-5223-4bf4-bdcc-6c7df9166676"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99101B7C-E13F-4ECC-92B9-66DA7C9E1E4F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19614,23 +19631,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CF60C-2A54-4479-8975-DF3B2608842A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="ab5b6d4b-4285-4680-b1ee-6fe31a63f7d7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="61535973-5223-4bf4-bdcc-6c7df9166676"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE1AC42-07AD-4118-96D5-B1BB6CECCAA7}">
   <ds:schemaRefs>

--- a/ANNEX H-1 - CS Form No. 212 Revised 2025 - Personal Data Sheet.xlsx
+++ b/ANNEX H-1 - CS Form No. 212 Revised 2025 - Personal Data Sheet.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\DILG-CAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84813997-61C2-4407-96B0-D4C364176BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBFFB3A-A449-4EEB-8B42-87E5B3700E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C1" sheetId="1" r:id="rId1"/>
@@ -3405,37 +3405,122 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="55" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="31" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3446,340 +3531,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3787,118 +3549,20 @@
     <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="5" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3915,10 +3579,20 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -3956,6 +3630,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -3966,6 +3652,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3981,102 +3671,587 @@
     <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="18" fillId="5" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="55" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="30" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4084,12 +4259,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4112,118 +4281,26 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4237,14 +4314,47 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
@@ -4252,6 +4362,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4259,9 +4381,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4285,6 +4404,18 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -4308,91 +4439,82 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4400,268 +4522,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -4679,229 +4541,367 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="30" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="30" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5138,7 +5138,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10051,20 +10051,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="330"/>
-      <c r="B1" s="331"/>
-      <c r="C1" s="331"/>
-      <c r="D1" s="331"/>
-      <c r="E1" s="331"/>
-      <c r="F1" s="331"/>
-      <c r="G1" s="331"/>
-      <c r="H1" s="331"/>
-      <c r="I1" s="331"/>
-      <c r="J1" s="331"/>
-      <c r="K1" s="331"/>
-      <c r="L1" s="331"/>
-      <c r="M1" s="331"/>
-      <c r="N1" s="332"/>
+      <c r="A1" s="375"/>
+      <c r="B1" s="376"/>
+      <c r="C1" s="376"/>
+      <c r="D1" s="376"/>
+      <c r="E1" s="376"/>
+      <c r="F1" s="376"/>
+      <c r="G1" s="376"/>
+      <c r="H1" s="376"/>
+      <c r="I1" s="376"/>
+      <c r="J1" s="376"/>
+      <c r="K1" s="376"/>
+      <c r="L1" s="376"/>
+      <c r="M1" s="376"/>
+      <c r="N1" s="377"/>
     </row>
     <row r="2" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="145"/>
@@ -10094,58 +10094,58 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="333" t="s">
+      <c r="A3" s="378" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="334"/>
-      <c r="C3" s="334"/>
-      <c r="D3" s="334"/>
-      <c r="E3" s="334"/>
-      <c r="F3" s="334"/>
-      <c r="G3" s="334"/>
-      <c r="H3" s="334"/>
-      <c r="I3" s="334"/>
-      <c r="J3" s="334"/>
-      <c r="K3" s="334"/>
-      <c r="L3" s="334"/>
-      <c r="M3" s="334"/>
-      <c r="N3" s="335"/>
+      <c r="B3" s="379"/>
+      <c r="C3" s="379"/>
+      <c r="D3" s="379"/>
+      <c r="E3" s="379"/>
+      <c r="F3" s="379"/>
+      <c r="G3" s="379"/>
+      <c r="H3" s="379"/>
+      <c r="I3" s="379"/>
+      <c r="J3" s="379"/>
+      <c r="K3" s="379"/>
+      <c r="L3" s="379"/>
+      <c r="M3" s="379"/>
+      <c r="N3" s="380"/>
     </row>
     <row r="4" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="364" t="s">
+      <c r="A4" s="408" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="365"/>
-      <c r="C4" s="365"/>
-      <c r="D4" s="365"/>
-      <c r="E4" s="365"/>
-      <c r="F4" s="365"/>
-      <c r="G4" s="365"/>
-      <c r="H4" s="365"/>
-      <c r="I4" s="365"/>
-      <c r="J4" s="365"/>
-      <c r="K4" s="365"/>
-      <c r="L4" s="365"/>
-      <c r="M4" s="365"/>
-      <c r="N4" s="366"/>
+      <c r="B4" s="409"/>
+      <c r="C4" s="409"/>
+      <c r="D4" s="409"/>
+      <c r="E4" s="409"/>
+      <c r="F4" s="409"/>
+      <c r="G4" s="409"/>
+      <c r="H4" s="409"/>
+      <c r="I4" s="409"/>
+      <c r="J4" s="409"/>
+      <c r="K4" s="409"/>
+      <c r="L4" s="409"/>
+      <c r="M4" s="409"/>
+      <c r="N4" s="410"/>
     </row>
     <row r="5" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="406" t="s">
+      <c r="A5" s="291" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="407"/>
-      <c r="C5" s="407"/>
-      <c r="D5" s="407"/>
-      <c r="E5" s="407"/>
-      <c r="F5" s="407"/>
-      <c r="G5" s="407"/>
-      <c r="H5" s="407"/>
-      <c r="I5" s="407"/>
-      <c r="J5" s="407"/>
-      <c r="K5" s="407"/>
-      <c r="L5" s="407"/>
-      <c r="M5" s="407"/>
-      <c r="N5" s="408"/>
+      <c r="B5" s="292"/>
+      <c r="C5" s="292"/>
+      <c r="D5" s="292"/>
+      <c r="E5" s="292"/>
+      <c r="F5" s="292"/>
+      <c r="G5" s="292"/>
+      <c r="H5" s="292"/>
+      <c r="I5" s="292"/>
+      <c r="J5" s="292"/>
+      <c r="K5" s="292"/>
+      <c r="L5" s="292"/>
+      <c r="M5" s="292"/>
+      <c r="N5" s="293"/>
     </row>
     <row r="6" spans="1:18" ht="3" hidden="1" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A6" s="177"/>
@@ -10182,42 +10182,42 @@
       <c r="N8" s="141"/>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="336" t="s">
+      <c r="A9" s="381" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="337"/>
-      <c r="C9" s="337"/>
-      <c r="D9" s="337"/>
-      <c r="E9" s="337"/>
-      <c r="F9" s="337"/>
-      <c r="G9" s="337"/>
-      <c r="H9" s="337"/>
-      <c r="I9" s="337"/>
-      <c r="J9" s="337"/>
-      <c r="K9" s="337"/>
-      <c r="L9" s="337"/>
-      <c r="M9" s="337"/>
-      <c r="N9" s="338"/>
+      <c r="B9" s="382"/>
+      <c r="C9" s="382"/>
+      <c r="D9" s="382"/>
+      <c r="E9" s="382"/>
+      <c r="F9" s="382"/>
+      <c r="G9" s="382"/>
+      <c r="H9" s="382"/>
+      <c r="I9" s="382"/>
+      <c r="J9" s="382"/>
+      <c r="K9" s="382"/>
+      <c r="L9" s="382"/>
+      <c r="M9" s="382"/>
+      <c r="N9" s="383"/>
     </row>
     <row r="10" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="150" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="355" t="s">
+      <c r="B10" s="399" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="356"/>
-      <c r="D10" s="347"/>
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
-      <c r="G10" s="347"/>
-      <c r="H10" s="347"/>
-      <c r="I10" s="347"/>
-      <c r="J10" s="347"/>
-      <c r="K10" s="347"/>
-      <c r="L10" s="347"/>
-      <c r="M10" s="347"/>
-      <c r="N10" s="348"/>
+      <c r="C10" s="331"/>
+      <c r="D10" s="392"/>
+      <c r="E10" s="392"/>
+      <c r="F10" s="392"/>
+      <c r="G10" s="392"/>
+      <c r="H10" s="392"/>
+      <c r="I10" s="392"/>
+      <c r="J10" s="392"/>
+      <c r="K10" s="392"/>
+      <c r="L10" s="392"/>
+      <c r="M10" s="392"/>
+      <c r="N10" s="393"/>
       <c r="P10" s="77" t="s">
         <v>11</v>
       </c>
@@ -10226,10 +10226,10 @@
       <c r="A11" s="150" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="357" t="s">
+      <c r="B11" s="400" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="358"/>
+      <c r="C11" s="401"/>
       <c r="D11" s="185"/>
       <c r="E11" s="186"/>
       <c r="F11" s="186"/>
@@ -10238,11 +10238,11 @@
       <c r="I11" s="186"/>
       <c r="J11" s="186"/>
       <c r="K11" s="186"/>
-      <c r="L11" s="379" t="s">
+      <c r="L11" s="332" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="380"/>
-      <c r="N11" s="381"/>
+      <c r="M11" s="333"/>
+      <c r="N11" s="334"/>
       <c r="P11" s="78" t="s">
         <v>15</v>
       </c>
@@ -10252,10 +10252,10 @@
     </row>
     <row r="12" spans="1:18" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="151"/>
-      <c r="B12" s="359" t="s">
+      <c r="B12" s="402" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="360"/>
+      <c r="C12" s="403"/>
       <c r="D12" s="182"/>
       <c r="E12" s="183"/>
       <c r="F12" s="183"/>
@@ -10278,23 +10278,23 @@
       <c r="A13" s="219" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="436" t="s">
+      <c r="B13" s="330" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="356"/>
-      <c r="D13" s="382"/>
-      <c r="E13" s="382"/>
-      <c r="F13" s="383"/>
+      <c r="C13" s="331"/>
+      <c r="D13" s="335"/>
+      <c r="E13" s="335"/>
+      <c r="F13" s="336"/>
       <c r="G13" s="84" t="s">
         <v>22</v>
       </c>
       <c r="H13" s="128"/>
       <c r="I13" s="128"/>
-      <c r="J13" s="389"/>
-      <c r="K13" s="390"/>
-      <c r="L13" s="390"/>
-      <c r="M13" s="390"/>
-      <c r="N13" s="391"/>
+      <c r="J13" s="342"/>
+      <c r="K13" s="343"/>
+      <c r="L13" s="343"/>
+      <c r="M13" s="343"/>
+      <c r="N13" s="344"/>
       <c r="P13" s="78" t="s">
         <v>23</v>
       </c>
@@ -10328,21 +10328,21 @@
         <v>26</v>
       </c>
       <c r="C15" s="79"/>
-      <c r="D15" s="401"/>
-      <c r="E15" s="401"/>
-      <c r="F15" s="402"/>
-      <c r="G15" s="387" t="s">
+      <c r="D15" s="359"/>
+      <c r="E15" s="359"/>
+      <c r="F15" s="360"/>
+      <c r="G15" s="340" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="388"/>
-      <c r="I15" s="388"/>
+      <c r="H15" s="341"/>
+      <c r="I15" s="341"/>
       <c r="J15" s="129"/>
       <c r="K15" s="130"/>
-      <c r="L15" s="392" t="s">
+      <c r="L15" s="345" t="s">
         <v>28</v>
       </c>
-      <c r="M15" s="392"/>
-      <c r="N15" s="393"/>
+      <c r="M15" s="345"/>
+      <c r="N15" s="346"/>
       <c r="P15" s="78" t="s">
         <v>29</v>
       </c>
@@ -10358,14 +10358,14 @@
         <v>32</v>
       </c>
       <c r="C16" s="80"/>
-      <c r="D16" s="349"/>
-      <c r="E16" s="349"/>
-      <c r="F16" s="350"/>
-      <c r="G16" s="384" t="s">
+      <c r="D16" s="394"/>
+      <c r="E16" s="394"/>
+      <c r="F16" s="395"/>
+      <c r="G16" s="337" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="385"/>
-      <c r="I16" s="386"/>
+      <c r="H16" s="338"/>
+      <c r="I16" s="339"/>
       <c r="N16" s="141"/>
       <c r="P16" s="78" t="s">
         <v>34</v>
@@ -10375,49 +10375,49 @@
       </c>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="423">
+      <c r="A17" s="313">
         <v>6</v>
       </c>
-      <c r="B17" s="432" t="s">
+      <c r="B17" s="326" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="433"/>
-      <c r="D17" s="431"/>
-      <c r="E17" s="431"/>
-      <c r="F17" s="431"/>
+      <c r="C17" s="327"/>
+      <c r="D17" s="324"/>
+      <c r="E17" s="324"/>
+      <c r="F17" s="324"/>
       <c r="G17" s="85" t="s">
         <v>37</v>
       </c>
       <c r="H17" s="86"/>
-      <c r="I17" s="309"/>
-      <c r="J17" s="310"/>
-      <c r="K17" s="310"/>
-      <c r="L17" s="310"/>
-      <c r="M17" s="310"/>
-      <c r="N17" s="311"/>
+      <c r="I17" s="355"/>
+      <c r="J17" s="347"/>
+      <c r="K17" s="347"/>
+      <c r="L17" s="347"/>
+      <c r="M17" s="347"/>
+      <c r="N17" s="348"/>
       <c r="Q17" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="424"/>
-      <c r="B18" s="434"/>
-      <c r="C18" s="435"/>
-      <c r="D18" s="353"/>
-      <c r="E18" s="353"/>
-      <c r="F18" s="353"/>
+      <c r="A18" s="314"/>
+      <c r="B18" s="328"/>
+      <c r="C18" s="329"/>
+      <c r="D18" s="325"/>
+      <c r="E18" s="325"/>
+      <c r="F18" s="325"/>
       <c r="G18" s="137"/>
       <c r="H18" s="87"/>
-      <c r="I18" s="394" t="s">
+      <c r="I18" s="350" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="395"/>
-      <c r="K18" s="395"/>
-      <c r="L18" s="395" t="s">
+      <c r="J18" s="294"/>
+      <c r="K18" s="294"/>
+      <c r="L18" s="294" t="s">
         <v>40</v>
       </c>
-      <c r="M18" s="395"/>
-      <c r="N18" s="396"/>
+      <c r="M18" s="294"/>
+      <c r="N18" s="295"/>
       <c r="Q18" s="3" t="s">
         <v>41</v>
       </c>
@@ -10431,100 +10431,100 @@
       <c r="F19" s="142"/>
       <c r="G19" s="137"/>
       <c r="H19" s="87"/>
-      <c r="I19" s="409"/>
-      <c r="J19" s="410"/>
-      <c r="K19" s="410"/>
-      <c r="L19" s="413"/>
-      <c r="M19" s="410"/>
-      <c r="N19" s="414"/>
+      <c r="I19" s="296"/>
+      <c r="J19" s="297"/>
+      <c r="K19" s="297"/>
+      <c r="L19" s="300"/>
+      <c r="M19" s="297"/>
+      <c r="N19" s="301"/>
       <c r="Q19" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="424"/>
+      <c r="A20" s="314"/>
       <c r="B20" s="201"/>
       <c r="C20" s="120"/>
       <c r="D20" s="121"/>
-      <c r="E20" s="353"/>
-      <c r="F20" s="353"/>
+      <c r="E20" s="325"/>
+      <c r="F20" s="325"/>
       <c r="G20" s="135"/>
       <c r="H20" s="140"/>
-      <c r="I20" s="411"/>
-      <c r="J20" s="412"/>
-      <c r="K20" s="412"/>
-      <c r="L20" s="412"/>
-      <c r="M20" s="412"/>
-      <c r="N20" s="415"/>
+      <c r="I20" s="298"/>
+      <c r="J20" s="299"/>
+      <c r="K20" s="299"/>
+      <c r="L20" s="299"/>
+      <c r="M20" s="299"/>
+      <c r="N20" s="302"/>
       <c r="Q20" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="425"/>
+      <c r="A21" s="315"/>
       <c r="B21" s="202"/>
       <c r="C21" s="118"/>
       <c r="D21" s="122"/>
-      <c r="E21" s="354"/>
-      <c r="F21" s="354"/>
+      <c r="E21" s="398"/>
+      <c r="F21" s="398"/>
       <c r="G21" s="135"/>
       <c r="H21" s="140"/>
-      <c r="I21" s="416" t="s">
+      <c r="I21" s="303" t="s">
         <v>44</v>
       </c>
-      <c r="J21" s="417"/>
-      <c r="K21" s="417"/>
-      <c r="L21" s="306" t="s">
+      <c r="J21" s="304"/>
+      <c r="K21" s="304"/>
+      <c r="L21" s="431" t="s">
         <v>45</v>
       </c>
-      <c r="M21" s="307"/>
-      <c r="N21" s="308"/>
+      <c r="M21" s="432"/>
+      <c r="N21" s="433"/>
       <c r="Q21" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="429" t="s">
+      <c r="A22" s="322" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="371" t="s">
+      <c r="B22" s="289" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="372"/>
-      <c r="D22" s="367"/>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
+      <c r="C22" s="290"/>
+      <c r="D22" s="366"/>
+      <c r="E22" s="366"/>
+      <c r="F22" s="366"/>
       <c r="G22" s="135"/>
       <c r="H22" s="140"/>
-      <c r="I22" s="309"/>
-      <c r="J22" s="310"/>
-      <c r="K22" s="310"/>
-      <c r="L22" s="310"/>
-      <c r="M22" s="310"/>
-      <c r="N22" s="311"/>
+      <c r="I22" s="355"/>
+      <c r="J22" s="347"/>
+      <c r="K22" s="347"/>
+      <c r="L22" s="347"/>
+      <c r="M22" s="347"/>
+      <c r="N22" s="348"/>
       <c r="Q22" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="430"/>
-      <c r="B23" s="373"/>
-      <c r="C23" s="374"/>
-      <c r="D23" s="368"/>
-      <c r="E23" s="368"/>
-      <c r="F23" s="368"/>
+      <c r="A23" s="323"/>
+      <c r="B23" s="367"/>
+      <c r="C23" s="368"/>
+      <c r="D23" s="308"/>
+      <c r="E23" s="308"/>
+      <c r="F23" s="308"/>
       <c r="G23" s="135"/>
       <c r="H23" s="140"/>
-      <c r="I23" s="314" t="s">
+      <c r="I23" s="436" t="s">
         <v>50</v>
       </c>
-      <c r="J23" s="315"/>
-      <c r="K23" s="315"/>
-      <c r="L23" s="312" t="s">
+      <c r="J23" s="437"/>
+      <c r="K23" s="437"/>
+      <c r="L23" s="434" t="s">
         <v>51</v>
       </c>
-      <c r="M23" s="312"/>
-      <c r="N23" s="313"/>
+      <c r="M23" s="434"/>
+      <c r="N23" s="435"/>
       <c r="Q23" s="3" t="s">
         <v>52</v>
       </c>
@@ -10533,163 +10533,163 @@
       <c r="A24" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="362" t="s">
+      <c r="B24" s="369" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="363"/>
-      <c r="D24" s="682"/>
-      <c r="E24" s="682"/>
-      <c r="F24" s="682"/>
-      <c r="G24" s="320" t="s">
+      <c r="C24" s="370"/>
+      <c r="D24" s="349"/>
+      <c r="E24" s="349"/>
+      <c r="F24" s="349"/>
+      <c r="G24" s="404" t="s">
         <v>55</v>
       </c>
-      <c r="H24" s="299"/>
-      <c r="I24" s="321"/>
-      <c r="J24" s="322"/>
-      <c r="K24" s="322"/>
-      <c r="L24" s="322"/>
-      <c r="M24" s="322"/>
-      <c r="N24" s="323"/>
+      <c r="H24" s="405"/>
+      <c r="I24" s="356"/>
+      <c r="J24" s="357"/>
+      <c r="K24" s="357"/>
+      <c r="L24" s="357"/>
+      <c r="M24" s="357"/>
+      <c r="N24" s="358"/>
       <c r="Q24" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="369" t="s">
+      <c r="A25" s="305" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="371" t="s">
+      <c r="B25" s="289" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="372"/>
-      <c r="D25" s="418"/>
-      <c r="E25" s="418"/>
-      <c r="F25" s="418"/>
+      <c r="C25" s="290"/>
+      <c r="D25" s="307"/>
+      <c r="E25" s="307"/>
+      <c r="F25" s="307"/>
       <c r="G25" s="92" t="s">
         <v>59</v>
       </c>
       <c r="H25" s="81"/>
-      <c r="I25" s="324"/>
-      <c r="J25" s="318"/>
-      <c r="K25" s="318"/>
-      <c r="L25" s="318"/>
-      <c r="M25" s="318"/>
-      <c r="N25" s="319"/>
+      <c r="I25" s="361"/>
+      <c r="J25" s="362"/>
+      <c r="K25" s="362"/>
+      <c r="L25" s="362"/>
+      <c r="M25" s="362"/>
+      <c r="N25" s="440"/>
       <c r="Q25" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="370"/>
-      <c r="B26" s="373"/>
-      <c r="C26" s="374"/>
-      <c r="D26" s="368"/>
-      <c r="E26" s="368"/>
-      <c r="F26" s="368"/>
+      <c r="A26" s="306"/>
+      <c r="B26" s="367"/>
+      <c r="C26" s="368"/>
+      <c r="D26" s="308"/>
+      <c r="E26" s="308"/>
+      <c r="F26" s="308"/>
       <c r="G26" s="135"/>
       <c r="H26" s="140"/>
-      <c r="I26" s="394" t="s">
+      <c r="I26" s="350" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="395"/>
-      <c r="K26" s="395"/>
-      <c r="L26" s="395" t="s">
+      <c r="J26" s="294"/>
+      <c r="K26" s="294"/>
+      <c r="L26" s="294" t="s">
         <v>40</v>
       </c>
-      <c r="M26" s="395"/>
-      <c r="N26" s="396"/>
+      <c r="M26" s="294"/>
+      <c r="N26" s="295"/>
       <c r="Q26" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="369" t="s">
+      <c r="A27" s="305" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="375" t="s">
+      <c r="B27" s="371" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="372"/>
-      <c r="D27" s="418"/>
-      <c r="E27" s="418"/>
-      <c r="F27" s="418"/>
+      <c r="C27" s="290"/>
+      <c r="D27" s="307"/>
+      <c r="E27" s="307"/>
+      <c r="F27" s="307"/>
       <c r="G27" s="137"/>
       <c r="H27" s="87"/>
-      <c r="I27" s="324"/>
-      <c r="J27" s="318"/>
-      <c r="K27" s="318"/>
-      <c r="L27" s="318"/>
-      <c r="M27" s="318"/>
-      <c r="N27" s="319"/>
+      <c r="I27" s="361"/>
+      <c r="J27" s="362"/>
+      <c r="K27" s="362"/>
+      <c r="L27" s="362"/>
+      <c r="M27" s="362"/>
+      <c r="N27" s="440"/>
       <c r="Q27" s="3" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="370"/>
-      <c r="B28" s="373"/>
-      <c r="C28" s="374"/>
-      <c r="D28" s="368"/>
-      <c r="E28" s="368"/>
-      <c r="F28" s="368"/>
+      <c r="A28" s="306"/>
+      <c r="B28" s="367"/>
+      <c r="C28" s="368"/>
+      <c r="D28" s="308"/>
+      <c r="E28" s="308"/>
+      <c r="F28" s="308"/>
       <c r="G28" s="137"/>
       <c r="H28" s="87"/>
-      <c r="I28" s="397" t="s">
+      <c r="I28" s="351" t="s">
         <v>44</v>
       </c>
-      <c r="J28" s="398"/>
-      <c r="K28" s="398"/>
-      <c r="L28" s="399" t="s">
+      <c r="J28" s="352"/>
+      <c r="K28" s="352"/>
+      <c r="L28" s="353" t="s">
         <v>45</v>
       </c>
-      <c r="M28" s="398"/>
-      <c r="N28" s="400"/>
+      <c r="M28" s="352"/>
+      <c r="N28" s="354"/>
       <c r="Q28" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="369" t="s">
+      <c r="A29" s="305" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="371" t="s">
+      <c r="B29" s="289" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="372"/>
-      <c r="D29" s="419"/>
-      <c r="E29" s="418"/>
-      <c r="F29" s="420"/>
+      <c r="C29" s="290"/>
+      <c r="D29" s="309"/>
+      <c r="E29" s="307"/>
+      <c r="F29" s="310"/>
       <c r="G29" s="137"/>
       <c r="H29" s="144"/>
-      <c r="I29" s="378"/>
-      <c r="J29" s="376"/>
-      <c r="K29" s="376"/>
-      <c r="L29" s="376"/>
-      <c r="M29" s="376"/>
-      <c r="N29" s="377"/>
+      <c r="I29" s="374"/>
+      <c r="J29" s="372"/>
+      <c r="K29" s="372"/>
+      <c r="L29" s="372"/>
+      <c r="M29" s="372"/>
+      <c r="N29" s="373"/>
       <c r="Q29" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="370"/>
-      <c r="B30" s="373"/>
-      <c r="C30" s="374"/>
-      <c r="D30" s="421"/>
-      <c r="E30" s="368"/>
-      <c r="F30" s="422"/>
+      <c r="A30" s="306"/>
+      <c r="B30" s="367"/>
+      <c r="C30" s="368"/>
+      <c r="D30" s="311"/>
+      <c r="E30" s="308"/>
+      <c r="F30" s="312"/>
       <c r="G30" s="137"/>
       <c r="H30" s="144"/>
-      <c r="I30" s="316" t="s">
+      <c r="I30" s="438" t="s">
         <v>50</v>
       </c>
-      <c r="J30" s="316"/>
-      <c r="K30" s="316"/>
-      <c r="L30" s="316" t="s">
+      <c r="J30" s="438"/>
+      <c r="K30" s="438"/>
+      <c r="L30" s="438" t="s">
         <v>51</v>
       </c>
-      <c r="M30" s="316"/>
-      <c r="N30" s="317"/>
+      <c r="M30" s="438"/>
+      <c r="N30" s="439"/>
       <c r="Q30" s="3" t="s">
         <v>69</v>
       </c>
@@ -10702,19 +10702,19 @@
         <v>71</v>
       </c>
       <c r="C31" s="80"/>
-      <c r="D31" s="418"/>
-      <c r="E31" s="418"/>
-      <c r="F31" s="418"/>
-      <c r="G31" s="320" t="s">
+      <c r="D31" s="307"/>
+      <c r="E31" s="307"/>
+      <c r="F31" s="307"/>
+      <c r="G31" s="404" t="s">
         <v>55</v>
       </c>
-      <c r="H31" s="299"/>
-      <c r="I31" s="327"/>
-      <c r="J31" s="328"/>
-      <c r="K31" s="328"/>
-      <c r="L31" s="328"/>
-      <c r="M31" s="328"/>
-      <c r="N31" s="329"/>
+      <c r="H31" s="405"/>
+      <c r="I31" s="443"/>
+      <c r="J31" s="444"/>
+      <c r="K31" s="444"/>
+      <c r="L31" s="444"/>
+      <c r="M31" s="444"/>
+      <c r="N31" s="445"/>
       <c r="Q31" s="3" t="s">
         <v>72</v>
       </c>
@@ -10727,42 +10727,42 @@
         <v>74</v>
       </c>
       <c r="C32" s="80"/>
-      <c r="D32" s="682"/>
-      <c r="E32" s="682"/>
-      <c r="F32" s="682"/>
+      <c r="D32" s="349"/>
+      <c r="E32" s="349"/>
+      <c r="F32" s="349"/>
       <c r="G32" s="134" t="s">
         <v>75</v>
       </c>
       <c r="H32" s="138"/>
-      <c r="I32" s="321"/>
-      <c r="J32" s="322"/>
-      <c r="K32" s="322"/>
-      <c r="L32" s="322"/>
-      <c r="M32" s="322"/>
-      <c r="N32" s="323"/>
+      <c r="I32" s="356"/>
+      <c r="J32" s="357"/>
+      <c r="K32" s="357"/>
+      <c r="L32" s="357"/>
+      <c r="M32" s="357"/>
+      <c r="N32" s="358"/>
       <c r="Q32" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="361" t="s">
+      <c r="A33" s="407" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="362"/>
-      <c r="C33" s="363"/>
-      <c r="D33" s="682"/>
-      <c r="E33" s="682"/>
-      <c r="F33" s="682"/>
+      <c r="B33" s="369"/>
+      <c r="C33" s="370"/>
+      <c r="D33" s="349"/>
+      <c r="E33" s="349"/>
+      <c r="F33" s="349"/>
       <c r="G33" s="184" t="s">
         <v>78</v>
       </c>
       <c r="H33" s="136"/>
-      <c r="I33" s="321"/>
-      <c r="J33" s="322"/>
-      <c r="K33" s="322"/>
-      <c r="L33" s="322"/>
-      <c r="M33" s="322"/>
-      <c r="N33" s="323"/>
+      <c r="I33" s="356"/>
+      <c r="J33" s="357"/>
+      <c r="K33" s="357"/>
+      <c r="L33" s="357"/>
+      <c r="M33" s="357"/>
+      <c r="N33" s="358"/>
       <c r="Q33" s="3" t="s">
         <v>79</v>
       </c>
@@ -10773,19 +10773,19 @@
       </c>
       <c r="B34" s="203"/>
       <c r="C34" s="139"/>
-      <c r="D34" s="418"/>
-      <c r="E34" s="418"/>
-      <c r="F34" s="418"/>
+      <c r="D34" s="307"/>
+      <c r="E34" s="307"/>
+      <c r="F34" s="307"/>
       <c r="G34" s="92" t="s">
         <v>81</v>
       </c>
       <c r="H34" s="81"/>
-      <c r="I34" s="403"/>
-      <c r="J34" s="404"/>
-      <c r="K34" s="404"/>
-      <c r="L34" s="404"/>
-      <c r="M34" s="404"/>
-      <c r="N34" s="405"/>
+      <c r="I34" s="363"/>
+      <c r="J34" s="364"/>
+      <c r="K34" s="364"/>
+      <c r="L34" s="364"/>
+      <c r="M34" s="364"/>
+      <c r="N34" s="365"/>
       <c r="Q34" s="3" t="s">
         <v>82</v>
       </c>
@@ -10819,21 +10819,21 @@
         <v>86</v>
       </c>
       <c r="C36" s="208"/>
-      <c r="D36" s="426"/>
-      <c r="E36" s="427"/>
-      <c r="F36" s="427"/>
-      <c r="G36" s="427"/>
-      <c r="H36" s="428"/>
-      <c r="I36" s="325" t="s">
+      <c r="D36" s="316"/>
+      <c r="E36" s="317"/>
+      <c r="F36" s="317"/>
+      <c r="G36" s="317"/>
+      <c r="H36" s="318"/>
+      <c r="I36" s="441" t="s">
         <v>87</v>
       </c>
-      <c r="J36" s="325"/>
-      <c r="K36" s="325"/>
-      <c r="L36" s="326"/>
-      <c r="M36" s="341" t="s">
+      <c r="J36" s="441"/>
+      <c r="K36" s="441"/>
+      <c r="L36" s="442"/>
+      <c r="M36" s="386" t="s">
         <v>88</v>
       </c>
-      <c r="N36" s="342"/>
+      <c r="N36" s="387"/>
       <c r="Q36" s="3" t="s">
         <v>89</v>
       </c>
@@ -10844,19 +10844,19 @@
         <v>90</v>
       </c>
       <c r="C37" s="144"/>
-      <c r="D37" s="265"/>
-      <c r="E37" s="266"/>
-      <c r="F37" s="267"/>
-      <c r="G37" s="278" t="s">
+      <c r="D37" s="319"/>
+      <c r="E37" s="320"/>
+      <c r="F37" s="321"/>
+      <c r="G37" s="406" t="s">
         <v>91</v>
       </c>
-      <c r="H37" s="278"/>
-      <c r="I37" s="688"/>
-      <c r="J37" s="688"/>
-      <c r="K37" s="688"/>
-      <c r="L37" s="689"/>
-      <c r="M37" s="263"/>
-      <c r="N37" s="264"/>
+      <c r="H37" s="406"/>
+      <c r="I37" s="276"/>
+      <c r="J37" s="276"/>
+      <c r="K37" s="276"/>
+      <c r="L37" s="277"/>
+      <c r="M37" s="283"/>
+      <c r="N37" s="284"/>
       <c r="Q37" s="3" t="s">
         <v>92</v>
       </c>
@@ -10867,17 +10867,17 @@
         <v>93</v>
       </c>
       <c r="C38" s="198"/>
-      <c r="D38" s="265"/>
-      <c r="E38" s="266"/>
-      <c r="F38" s="266"/>
-      <c r="G38" s="266"/>
-      <c r="H38" s="267"/>
-      <c r="I38" s="688"/>
-      <c r="J38" s="688"/>
-      <c r="K38" s="688"/>
-      <c r="L38" s="689"/>
-      <c r="M38" s="263"/>
-      <c r="N38" s="264"/>
+      <c r="D38" s="319"/>
+      <c r="E38" s="320"/>
+      <c r="F38" s="320"/>
+      <c r="G38" s="320"/>
+      <c r="H38" s="321"/>
+      <c r="I38" s="276"/>
+      <c r="J38" s="276"/>
+      <c r="K38" s="276"/>
+      <c r="L38" s="277"/>
+      <c r="M38" s="283"/>
+      <c r="N38" s="284"/>
       <c r="Q38" s="3" t="s">
         <v>94</v>
       </c>
@@ -10888,17 +10888,17 @@
         <v>95</v>
       </c>
       <c r="C39" s="80"/>
-      <c r="D39" s="265"/>
-      <c r="E39" s="266"/>
-      <c r="F39" s="266"/>
-      <c r="G39" s="266"/>
-      <c r="H39" s="267"/>
-      <c r="I39" s="688"/>
-      <c r="J39" s="688"/>
-      <c r="K39" s="688"/>
-      <c r="L39" s="689"/>
-      <c r="M39" s="263"/>
-      <c r="N39" s="264"/>
+      <c r="D39" s="319"/>
+      <c r="E39" s="320"/>
+      <c r="F39" s="320"/>
+      <c r="G39" s="320"/>
+      <c r="H39" s="321"/>
+      <c r="I39" s="276"/>
+      <c r="J39" s="276"/>
+      <c r="K39" s="276"/>
+      <c r="L39" s="277"/>
+      <c r="M39" s="283"/>
+      <c r="N39" s="284"/>
       <c r="Q39" s="3" t="s">
         <v>96</v>
       </c>
@@ -10909,17 +10909,17 @@
         <v>97</v>
       </c>
       <c r="C40" s="80"/>
-      <c r="D40" s="265"/>
-      <c r="E40" s="266"/>
-      <c r="F40" s="266"/>
-      <c r="G40" s="266"/>
-      <c r="H40" s="267"/>
-      <c r="I40" s="688"/>
-      <c r="J40" s="688"/>
-      <c r="K40" s="688"/>
-      <c r="L40" s="689"/>
-      <c r="M40" s="263"/>
-      <c r="N40" s="264"/>
+      <c r="D40" s="319"/>
+      <c r="E40" s="320"/>
+      <c r="F40" s="320"/>
+      <c r="G40" s="320"/>
+      <c r="H40" s="321"/>
+      <c r="I40" s="276"/>
+      <c r="J40" s="276"/>
+      <c r="K40" s="276"/>
+      <c r="L40" s="277"/>
+      <c r="M40" s="283"/>
+      <c r="N40" s="284"/>
       <c r="Q40" s="3" t="s">
         <v>98</v>
       </c>
@@ -10930,17 +10930,17 @@
         <v>99</v>
       </c>
       <c r="C41" s="80"/>
-      <c r="D41" s="265"/>
-      <c r="E41" s="266"/>
-      <c r="F41" s="266"/>
-      <c r="G41" s="266"/>
-      <c r="H41" s="267"/>
-      <c r="I41" s="688"/>
-      <c r="J41" s="688"/>
-      <c r="K41" s="688"/>
-      <c r="L41" s="689"/>
-      <c r="M41" s="263"/>
-      <c r="N41" s="264"/>
+      <c r="D41" s="319"/>
+      <c r="E41" s="320"/>
+      <c r="F41" s="320"/>
+      <c r="G41" s="320"/>
+      <c r="H41" s="321"/>
+      <c r="I41" s="276"/>
+      <c r="J41" s="276"/>
+      <c r="K41" s="276"/>
+      <c r="L41" s="277"/>
+      <c r="M41" s="283"/>
+      <c r="N41" s="284"/>
       <c r="Q41" s="3" t="s">
         <v>100</v>
       </c>
@@ -10951,17 +10951,17 @@
         <v>101</v>
       </c>
       <c r="C42" s="119"/>
-      <c r="D42" s="265"/>
-      <c r="E42" s="266"/>
-      <c r="F42" s="266"/>
-      <c r="G42" s="266"/>
-      <c r="H42" s="267"/>
-      <c r="I42" s="688"/>
-      <c r="J42" s="688"/>
-      <c r="K42" s="688"/>
-      <c r="L42" s="689"/>
-      <c r="M42" s="263"/>
-      <c r="N42" s="264"/>
+      <c r="D42" s="319"/>
+      <c r="E42" s="320"/>
+      <c r="F42" s="320"/>
+      <c r="G42" s="320"/>
+      <c r="H42" s="321"/>
+      <c r="I42" s="276"/>
+      <c r="J42" s="276"/>
+      <c r="K42" s="276"/>
+      <c r="L42" s="277"/>
+      <c r="M42" s="283"/>
+      <c r="N42" s="284"/>
       <c r="Q42" s="3" t="s">
         <v>102</v>
       </c>
@@ -10974,17 +10974,17 @@
         <v>104</v>
       </c>
       <c r="C43" s="86"/>
-      <c r="D43" s="265"/>
-      <c r="E43" s="266"/>
-      <c r="F43" s="266"/>
-      <c r="G43" s="266"/>
-      <c r="H43" s="267"/>
-      <c r="I43" s="688"/>
-      <c r="J43" s="688"/>
-      <c r="K43" s="688"/>
-      <c r="L43" s="689"/>
-      <c r="M43" s="263"/>
-      <c r="N43" s="264"/>
+      <c r="D43" s="319"/>
+      <c r="E43" s="320"/>
+      <c r="F43" s="320"/>
+      <c r="G43" s="320"/>
+      <c r="H43" s="321"/>
+      <c r="I43" s="276"/>
+      <c r="J43" s="276"/>
+      <c r="K43" s="276"/>
+      <c r="L43" s="277"/>
+      <c r="M43" s="283"/>
+      <c r="N43" s="284"/>
       <c r="Q43" s="3" t="s">
         <v>105</v>
       </c>
@@ -10995,19 +10995,19 @@
         <v>13</v>
       </c>
       <c r="C44" s="140"/>
-      <c r="D44" s="265"/>
-      <c r="E44" s="266"/>
-      <c r="F44" s="267"/>
-      <c r="G44" s="278" t="s">
+      <c r="D44" s="319"/>
+      <c r="E44" s="320"/>
+      <c r="F44" s="321"/>
+      <c r="G44" s="406" t="s">
         <v>106</v>
       </c>
-      <c r="H44" s="278"/>
-      <c r="I44" s="688"/>
-      <c r="J44" s="688"/>
-      <c r="K44" s="688"/>
-      <c r="L44" s="689"/>
-      <c r="M44" s="263"/>
-      <c r="N44" s="264"/>
+      <c r="H44" s="406"/>
+      <c r="I44" s="276"/>
+      <c r="J44" s="276"/>
+      <c r="K44" s="276"/>
+      <c r="L44" s="277"/>
+      <c r="M44" s="283"/>
+      <c r="N44" s="284"/>
       <c r="Q44" s="3" t="s">
         <v>107</v>
       </c>
@@ -11018,17 +11018,17 @@
         <v>17</v>
       </c>
       <c r="C45" s="191"/>
-      <c r="D45" s="265"/>
-      <c r="E45" s="266"/>
-      <c r="F45" s="266"/>
-      <c r="G45" s="266"/>
-      <c r="H45" s="267"/>
-      <c r="I45" s="688"/>
-      <c r="J45" s="688"/>
-      <c r="K45" s="688"/>
-      <c r="L45" s="689"/>
-      <c r="M45" s="263"/>
-      <c r="N45" s="264"/>
+      <c r="D45" s="319"/>
+      <c r="E45" s="320"/>
+      <c r="F45" s="320"/>
+      <c r="G45" s="320"/>
+      <c r="H45" s="321"/>
+      <c r="I45" s="276"/>
+      <c r="J45" s="276"/>
+      <c r="K45" s="276"/>
+      <c r="L45" s="277"/>
+      <c r="M45" s="283"/>
+      <c r="N45" s="284"/>
       <c r="Q45" s="3" t="s">
         <v>108</v>
       </c>
@@ -11037,21 +11037,21 @@
       <c r="A46" s="135" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="371" t="s">
+      <c r="B46" s="289" t="s">
         <v>110</v>
       </c>
-      <c r="C46" s="371"/>
-      <c r="D46" s="371"/>
-      <c r="E46" s="371"/>
-      <c r="F46" s="371"/>
-      <c r="G46" s="371"/>
-      <c r="H46" s="372"/>
-      <c r="I46" s="688"/>
-      <c r="J46" s="688"/>
-      <c r="K46" s="688"/>
-      <c r="L46" s="689"/>
-      <c r="M46" s="263"/>
-      <c r="N46" s="264"/>
+      <c r="C46" s="289"/>
+      <c r="D46" s="289"/>
+      <c r="E46" s="289"/>
+      <c r="F46" s="289"/>
+      <c r="G46" s="289"/>
+      <c r="H46" s="290"/>
+      <c r="I46" s="276"/>
+      <c r="J46" s="276"/>
+      <c r="K46" s="276"/>
+      <c r="L46" s="277"/>
+      <c r="M46" s="283"/>
+      <c r="N46" s="284"/>
       <c r="Q46" s="3" t="s">
         <v>111</v>
       </c>
@@ -11062,17 +11062,17 @@
         <v>10</v>
       </c>
       <c r="C47" s="140"/>
-      <c r="D47" s="275"/>
-      <c r="E47" s="276"/>
-      <c r="F47" s="276"/>
-      <c r="G47" s="276"/>
-      <c r="H47" s="277"/>
-      <c r="I47" s="688"/>
-      <c r="J47" s="688"/>
-      <c r="K47" s="688"/>
-      <c r="L47" s="689"/>
-      <c r="M47" s="263"/>
-      <c r="N47" s="264"/>
+      <c r="D47" s="466"/>
+      <c r="E47" s="467"/>
+      <c r="F47" s="467"/>
+      <c r="G47" s="467"/>
+      <c r="H47" s="468"/>
+      <c r="I47" s="276"/>
+      <c r="J47" s="276"/>
+      <c r="K47" s="276"/>
+      <c r="L47" s="277"/>
+      <c r="M47" s="283"/>
+      <c r="N47" s="284"/>
       <c r="Q47" s="3" t="s">
         <v>112</v>
       </c>
@@ -11083,17 +11083,17 @@
         <v>13</v>
       </c>
       <c r="C48" s="140"/>
-      <c r="D48" s="275"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="277"/>
-      <c r="I48" s="688"/>
-      <c r="J48" s="688"/>
-      <c r="K48" s="688"/>
-      <c r="L48" s="689"/>
-      <c r="M48" s="263"/>
-      <c r="N48" s="264"/>
+      <c r="D48" s="466"/>
+      <c r="E48" s="467"/>
+      <c r="F48" s="467"/>
+      <c r="G48" s="467"/>
+      <c r="H48" s="468"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="276"/>
+      <c r="L48" s="277"/>
+      <c r="M48" s="283"/>
+      <c r="N48" s="284"/>
       <c r="Q48" s="3" t="s">
         <v>113</v>
       </c>
@@ -11104,19 +11104,19 @@
         <v>17</v>
       </c>
       <c r="C49" s="193"/>
-      <c r="D49" s="439"/>
-      <c r="E49" s="440"/>
-      <c r="F49" s="440"/>
-      <c r="G49" s="440"/>
-      <c r="H49" s="441"/>
-      <c r="I49" s="437" t="s">
+      <c r="D49" s="280"/>
+      <c r="E49" s="281"/>
+      <c r="F49" s="281"/>
+      <c r="G49" s="281"/>
+      <c r="H49" s="282"/>
+      <c r="I49" s="278" t="s">
         <v>114</v>
       </c>
-      <c r="J49" s="437"/>
-      <c r="K49" s="437"/>
-      <c r="L49" s="437"/>
-      <c r="M49" s="437"/>
-      <c r="N49" s="438"/>
+      <c r="J49" s="278"/>
+      <c r="K49" s="278"/>
+      <c r="L49" s="278"/>
+      <c r="M49" s="278"/>
+      <c r="N49" s="279"/>
       <c r="Q49" s="3" t="s">
         <v>115</v>
       </c>
@@ -11132,47 +11132,47 @@
       <c r="F50" s="83"/>
       <c r="G50" s="83"/>
       <c r="H50" s="83"/>
-      <c r="I50" s="351" t="s">
+      <c r="I50" s="396" t="s">
         <v>117</v>
       </c>
-      <c r="J50" s="351"/>
-      <c r="K50" s="351"/>
-      <c r="L50" s="351"/>
-      <c r="M50" s="351"/>
-      <c r="N50" s="352"/>
+      <c r="J50" s="396"/>
+      <c r="K50" s="396"/>
+      <c r="L50" s="396"/>
+      <c r="M50" s="396"/>
+      <c r="N50" s="397"/>
       <c r="Q50" s="3" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="343" t="s">
+      <c r="A51" s="388" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="294" t="s">
+      <c r="B51" s="414" t="s">
         <v>120</v>
       </c>
-      <c r="C51" s="294"/>
-      <c r="D51" s="279" t="s">
+      <c r="C51" s="414"/>
+      <c r="D51" s="417" t="s">
         <v>121</v>
       </c>
-      <c r="E51" s="280"/>
-      <c r="F51" s="297"/>
-      <c r="G51" s="279" t="s">
+      <c r="E51" s="418"/>
+      <c r="F51" s="419"/>
+      <c r="G51" s="417" t="s">
         <v>122</v>
       </c>
-      <c r="H51" s="280"/>
-      <c r="I51" s="281"/>
-      <c r="J51" s="442" t="s">
+      <c r="H51" s="418"/>
+      <c r="I51" s="469"/>
+      <c r="J51" s="285" t="s">
         <v>123</v>
       </c>
-      <c r="K51" s="443"/>
-      <c r="L51" s="273" t="s">
+      <c r="K51" s="286"/>
+      <c r="L51" s="461" t="s">
         <v>124</v>
       </c>
-      <c r="M51" s="345" t="s">
+      <c r="M51" s="390" t="s">
         <v>125</v>
       </c>
-      <c r="N51" s="339" t="s">
+      <c r="N51" s="384" t="s">
         <v>126</v>
       </c>
       <c r="Q51" s="3" t="s">
@@ -11180,43 +11180,43 @@
       </c>
     </row>
     <row r="52" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="344"/>
-      <c r="B52" s="295"/>
-      <c r="C52" s="295"/>
-      <c r="D52" s="282"/>
-      <c r="E52" s="283"/>
-      <c r="F52" s="298"/>
-      <c r="G52" s="282"/>
-      <c r="H52" s="283"/>
-      <c r="I52" s="284"/>
-      <c r="J52" s="444"/>
-      <c r="K52" s="445"/>
-      <c r="L52" s="273"/>
-      <c r="M52" s="345"/>
-      <c r="N52" s="339"/>
+      <c r="A52" s="389"/>
+      <c r="B52" s="415"/>
+      <c r="C52" s="415"/>
+      <c r="D52" s="420"/>
+      <c r="E52" s="421"/>
+      <c r="F52" s="422"/>
+      <c r="G52" s="420"/>
+      <c r="H52" s="421"/>
+      <c r="I52" s="470"/>
+      <c r="J52" s="287"/>
+      <c r="K52" s="288"/>
+      <c r="L52" s="461"/>
+      <c r="M52" s="390"/>
+      <c r="N52" s="384"/>
       <c r="Q52" s="3" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="206"/>
-      <c r="B53" s="296"/>
-      <c r="C53" s="296"/>
-      <c r="D53" s="285"/>
-      <c r="E53" s="286"/>
-      <c r="F53" s="299"/>
-      <c r="G53" s="285"/>
-      <c r="H53" s="286"/>
-      <c r="I53" s="287"/>
+      <c r="B53" s="416"/>
+      <c r="C53" s="416"/>
+      <c r="D53" s="423"/>
+      <c r="E53" s="424"/>
+      <c r="F53" s="405"/>
+      <c r="G53" s="423"/>
+      <c r="H53" s="424"/>
+      <c r="I53" s="471"/>
       <c r="J53" s="88" t="s">
         <v>129</v>
       </c>
       <c r="K53" s="89" t="s">
         <v>130</v>
       </c>
-      <c r="L53" s="274"/>
-      <c r="M53" s="346"/>
-      <c r="N53" s="340"/>
+      <c r="L53" s="462"/>
+      <c r="M53" s="391"/>
+      <c r="N53" s="385"/>
       <c r="O53" s="90"/>
       <c r="P53" s="90"/>
       <c r="Q53" s="3" t="s">
@@ -11229,17 +11229,17 @@
         <v>132</v>
       </c>
       <c r="C54" s="210"/>
-      <c r="D54" s="300"/>
-      <c r="E54" s="301"/>
-      <c r="F54" s="302"/>
-      <c r="G54" s="690"/>
-      <c r="H54" s="691"/>
-      <c r="I54" s="692"/>
+      <c r="D54" s="425"/>
+      <c r="E54" s="426"/>
+      <c r="F54" s="427"/>
+      <c r="G54" s="463"/>
+      <c r="H54" s="464"/>
+      <c r="I54" s="465"/>
       <c r="J54" s="249"/>
       <c r="K54" s="205"/>
-      <c r="L54" s="693"/>
-      <c r="M54" s="694"/>
-      <c r="N54" s="695"/>
+      <c r="L54" s="253"/>
+      <c r="M54" s="254"/>
+      <c r="N54" s="255"/>
       <c r="Q54" s="3" t="s">
         <v>133</v>
       </c>
@@ -11250,17 +11250,17 @@
         <v>134</v>
       </c>
       <c r="C55" s="210"/>
-      <c r="D55" s="300"/>
-      <c r="E55" s="301"/>
-      <c r="F55" s="302"/>
-      <c r="G55" s="690"/>
-      <c r="H55" s="691"/>
-      <c r="I55" s="692"/>
+      <c r="D55" s="425"/>
+      <c r="E55" s="426"/>
+      <c r="F55" s="427"/>
+      <c r="G55" s="463"/>
+      <c r="H55" s="464"/>
+      <c r="I55" s="465"/>
       <c r="J55" s="249"/>
       <c r="K55" s="205"/>
-      <c r="L55" s="696"/>
-      <c r="M55" s="697"/>
-      <c r="N55" s="695"/>
+      <c r="L55" s="256"/>
+      <c r="M55" s="257"/>
+      <c r="N55" s="255"/>
       <c r="Q55" s="3" t="s">
         <v>135</v>
       </c>
@@ -11271,17 +11271,17 @@
         <v>136</v>
       </c>
       <c r="C56" s="210"/>
-      <c r="D56" s="300"/>
-      <c r="E56" s="301"/>
-      <c r="F56" s="302"/>
-      <c r="G56" s="288"/>
-      <c r="H56" s="289"/>
-      <c r="I56" s="290"/>
+      <c r="D56" s="425"/>
+      <c r="E56" s="426"/>
+      <c r="F56" s="427"/>
+      <c r="G56" s="273"/>
+      <c r="H56" s="274"/>
+      <c r="I56" s="275"/>
       <c r="J56" s="249"/>
       <c r="K56" s="205"/>
-      <c r="L56" s="693"/>
-      <c r="M56" s="694"/>
-      <c r="N56" s="695"/>
+      <c r="L56" s="253"/>
+      <c r="M56" s="254"/>
+      <c r="N56" s="255"/>
       <c r="Q56" s="3" t="s">
         <v>137</v>
       </c>
@@ -11292,17 +11292,17 @@
         <v>138</v>
       </c>
       <c r="C57" s="210"/>
-      <c r="D57" s="300"/>
-      <c r="E57" s="301"/>
-      <c r="F57" s="302"/>
-      <c r="G57" s="288"/>
-      <c r="H57" s="289"/>
-      <c r="I57" s="290"/>
+      <c r="D57" s="425"/>
+      <c r="E57" s="426"/>
+      <c r="F57" s="427"/>
+      <c r="G57" s="273"/>
+      <c r="H57" s="274"/>
+      <c r="I57" s="275"/>
       <c r="J57" s="249"/>
       <c r="K57" s="205"/>
-      <c r="L57" s="693"/>
-      <c r="M57" s="697"/>
-      <c r="N57" s="695"/>
+      <c r="L57" s="253"/>
+      <c r="M57" s="257"/>
+      <c r="N57" s="255"/>
       <c r="Q57" s="3" t="s">
         <v>139</v>
       </c>
@@ -11313,82 +11313,82 @@
         <v>140</v>
       </c>
       <c r="C58" s="212"/>
-      <c r="D58" s="303"/>
-      <c r="E58" s="304"/>
-      <c r="F58" s="305"/>
-      <c r="G58" s="291"/>
-      <c r="H58" s="292"/>
-      <c r="I58" s="293"/>
-      <c r="J58" s="698"/>
-      <c r="K58" s="699"/>
-      <c r="L58" s="700"/>
-      <c r="M58" s="701"/>
-      <c r="N58" s="695"/>
+      <c r="D58" s="428"/>
+      <c r="E58" s="429"/>
+      <c r="F58" s="430"/>
+      <c r="G58" s="411"/>
+      <c r="H58" s="412"/>
+      <c r="I58" s="413"/>
+      <c r="J58" s="258"/>
+      <c r="K58" s="259"/>
+      <c r="L58" s="260"/>
+      <c r="M58" s="261"/>
+      <c r="N58" s="255"/>
       <c r="Q58" s="3" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="257" t="s">
+      <c r="A59" s="450" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="258"/>
-      <c r="C59" s="258"/>
-      <c r="D59" s="258"/>
-      <c r="E59" s="258"/>
-      <c r="F59" s="258"/>
-      <c r="G59" s="258"/>
-      <c r="H59" s="258"/>
-      <c r="I59" s="258"/>
-      <c r="J59" s="258"/>
-      <c r="K59" s="258"/>
-      <c r="L59" s="258"/>
-      <c r="M59" s="258"/>
-      <c r="N59" s="259"/>
+      <c r="B59" s="451"/>
+      <c r="C59" s="451"/>
+      <c r="D59" s="451"/>
+      <c r="E59" s="451"/>
+      <c r="F59" s="451"/>
+      <c r="G59" s="451"/>
+      <c r="H59" s="451"/>
+      <c r="I59" s="451"/>
+      <c r="J59" s="451"/>
+      <c r="K59" s="451"/>
+      <c r="L59" s="451"/>
+      <c r="M59" s="451"/>
+      <c r="N59" s="452"/>
       <c r="Q59" s="3" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="254" t="s">
+      <c r="A60" s="447" t="s">
         <v>143</v>
       </c>
-      <c r="B60" s="255"/>
-      <c r="C60" s="256"/>
-      <c r="D60" s="268"/>
-      <c r="E60" s="269"/>
-      <c r="F60" s="269"/>
-      <c r="G60" s="269"/>
-      <c r="H60" s="269"/>
-      <c r="I60" s="270"/>
-      <c r="J60" s="271" t="s">
+      <c r="B60" s="448"/>
+      <c r="C60" s="449"/>
+      <c r="D60" s="456"/>
+      <c r="E60" s="457"/>
+      <c r="F60" s="457"/>
+      <c r="G60" s="457"/>
+      <c r="H60" s="457"/>
+      <c r="I60" s="458"/>
+      <c r="J60" s="459" t="s">
         <v>144</v>
       </c>
-      <c r="K60" s="272"/>
-      <c r="L60" s="260"/>
-      <c r="M60" s="261"/>
-      <c r="N60" s="262"/>
+      <c r="K60" s="460"/>
+      <c r="L60" s="453"/>
+      <c r="M60" s="454"/>
+      <c r="N60" s="455"/>
       <c r="Q60" s="3" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="126" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="253" t="s">
+      <c r="A61" s="446" t="s">
         <v>402</v>
       </c>
-      <c r="B61" s="253"/>
-      <c r="C61" s="253"/>
-      <c r="D61" s="253"/>
-      <c r="E61" s="253"/>
-      <c r="F61" s="253"/>
-      <c r="G61" s="253"/>
-      <c r="H61" s="253"/>
-      <c r="I61" s="253"/>
-      <c r="J61" s="253"/>
-      <c r="K61" s="253"/>
-      <c r="L61" s="253"/>
-      <c r="M61" s="253"/>
-      <c r="N61" s="253"/>
+      <c r="B61" s="446"/>
+      <c r="C61" s="446"/>
+      <c r="D61" s="446"/>
+      <c r="E61" s="446"/>
+      <c r="F61" s="446"/>
+      <c r="G61" s="446"/>
+      <c r="H61" s="446"/>
+      <c r="I61" s="446"/>
+      <c r="J61" s="446"/>
+      <c r="K61" s="446"/>
+      <c r="L61" s="446"/>
+      <c r="M61" s="446"/>
+      <c r="N61" s="446"/>
       <c r="Q61" s="225" t="s">
         <v>146</v>
       </c>
@@ -15117,15 +15117,114 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="141">
-    <mergeCell ref="G57:I57"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I49:N49"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="J51:K52"/>
-    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="A61:N61"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A59:N59"/>
+    <mergeCell ref="L60:N60"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="M45:N45"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="L51:L53"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="G51:I53"/>
+    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="G58:I58"/>
+    <mergeCell ref="B51:C53"/>
+    <mergeCell ref="D51:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="I32:N32"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I31:N31"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="N51:N53"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="M51:M53"/>
+    <mergeCell ref="D10:N10"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="I50:N50"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="E20:F21"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="D22:F23"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C26"/>
+    <mergeCell ref="B27:C28"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I24:N24"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I33:N33"/>
+    <mergeCell ref="I34:N34"/>
     <mergeCell ref="I41:L41"/>
     <mergeCell ref="M41:N41"/>
     <mergeCell ref="M42:N42"/>
@@ -15150,114 +15249,15 @@
     <mergeCell ref="D17:F18"/>
     <mergeCell ref="B17:C18"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I24:N24"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I33:N33"/>
-    <mergeCell ref="I34:N34"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="D22:F23"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C26"/>
-    <mergeCell ref="B27:C28"/>
-    <mergeCell ref="B29:C30"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="N51:N53"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="M51:M53"/>
-    <mergeCell ref="D10:N10"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="I50:N50"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="E20:F21"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="G58:I58"/>
-    <mergeCell ref="B51:C53"/>
-    <mergeCell ref="D51:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="I32:N32"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I31:N31"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="A61:N61"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A59:N59"/>
-    <mergeCell ref="L60:N60"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="M45:N45"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="L51:L53"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="G51:I53"/>
-    <mergeCell ref="G55:I55"/>
-    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="G57:I57"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="I49:N49"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="J51:K52"/>
+    <mergeCell ref="B46:H46"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -15766,68 +15766,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="446"/>
-      <c r="B1" s="447"/>
-      <c r="C1" s="447"/>
-      <c r="D1" s="447"/>
-      <c r="E1" s="447"/>
-      <c r="F1" s="447"/>
-      <c r="G1" s="447"/>
-      <c r="H1" s="447"/>
-      <c r="I1" s="447"/>
-      <c r="J1" s="447"/>
-      <c r="K1" s="448"/>
+      <c r="A1" s="498"/>
+      <c r="B1" s="499"/>
+      <c r="C1" s="499"/>
+      <c r="D1" s="499"/>
+      <c r="E1" s="499"/>
+      <c r="F1" s="499"/>
+      <c r="G1" s="499"/>
+      <c r="H1" s="499"/>
+      <c r="I1" s="499"/>
+      <c r="J1" s="499"/>
+      <c r="K1" s="500"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="459" t="s">
+      <c r="A2" s="509" t="s">
         <v>303</v>
       </c>
-      <c r="B2" s="460"/>
-      <c r="C2" s="460"/>
-      <c r="D2" s="460"/>
-      <c r="E2" s="460"/>
-      <c r="F2" s="460"/>
-      <c r="G2" s="460"/>
-      <c r="H2" s="460"/>
-      <c r="I2" s="460"/>
-      <c r="J2" s="460"/>
-      <c r="K2" s="461"/>
+      <c r="B2" s="510"/>
+      <c r="C2" s="510"/>
+      <c r="D2" s="510"/>
+      <c r="E2" s="510"/>
+      <c r="F2" s="510"/>
+      <c r="G2" s="510"/>
+      <c r="H2" s="510"/>
+      <c r="I2" s="510"/>
+      <c r="J2" s="510"/>
+      <c r="K2" s="511"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="123" t="s">
         <v>304</v>
       </c>
-      <c r="B3" s="449" t="s">
+      <c r="B3" s="501" t="s">
         <v>305</v>
       </c>
-      <c r="C3" s="449"/>
-      <c r="D3" s="449"/>
-      <c r="E3" s="450"/>
-      <c r="F3" s="455" t="s">
+      <c r="C3" s="501"/>
+      <c r="D3" s="501"/>
+      <c r="E3" s="502"/>
+      <c r="F3" s="505" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="453" t="s">
+      <c r="G3" s="503" t="s">
         <v>307</v>
       </c>
-      <c r="H3" s="450"/>
-      <c r="I3" s="455" t="s">
+      <c r="H3" s="502"/>
+      <c r="I3" s="505" t="s">
         <v>308</v>
       </c>
-      <c r="J3" s="457" t="s">
+      <c r="J3" s="507" t="s">
         <v>309</v>
       </c>
-      <c r="K3" s="458"/>
+      <c r="K3" s="508"/>
     </row>
     <row r="4" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
-      <c r="B4" s="451"/>
-      <c r="C4" s="451"/>
-      <c r="D4" s="451"/>
-      <c r="E4" s="452"/>
-      <c r="F4" s="456"/>
-      <c r="G4" s="454"/>
-      <c r="H4" s="452"/>
-      <c r="I4" s="456"/>
+      <c r="B4" s="490"/>
+      <c r="C4" s="490"/>
+      <c r="D4" s="490"/>
+      <c r="E4" s="491"/>
+      <c r="F4" s="506"/>
+      <c r="G4" s="504"/>
+      <c r="H4" s="491"/>
+      <c r="I4" s="506"/>
       <c r="J4" s="5" t="s">
         <v>310</v>
       </c>
@@ -15836,125 +15836,125 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="474"/>
-      <c r="B5" s="475"/>
-      <c r="C5" s="475"/>
-      <c r="D5" s="475"/>
-      <c r="E5" s="476"/>
+      <c r="A5" s="520"/>
+      <c r="B5" s="521"/>
+      <c r="C5" s="521"/>
+      <c r="D5" s="521"/>
+      <c r="E5" s="522"/>
       <c r="F5" s="13"/>
-      <c r="G5" s="472"/>
-      <c r="H5" s="473"/>
+      <c r="G5" s="518"/>
+      <c r="H5" s="519"/>
       <c r="I5" s="240"/>
       <c r="J5" s="8"/>
       <c r="K5" s="15"/>
     </row>
     <row r="6" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="465"/>
-      <c r="B6" s="466"/>
-      <c r="C6" s="466"/>
-      <c r="D6" s="466"/>
-      <c r="E6" s="466"/>
+      <c r="A6" s="514"/>
+      <c r="B6" s="472"/>
+      <c r="C6" s="472"/>
+      <c r="D6" s="472"/>
+      <c r="E6" s="472"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="472"/>
-      <c r="H6" s="473"/>
+      <c r="G6" s="518"/>
+      <c r="H6" s="519"/>
       <c r="I6" s="240"/>
       <c r="J6" s="8"/>
       <c r="K6" s="15"/>
     </row>
     <row r="7" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="465"/>
-      <c r="B7" s="466"/>
-      <c r="C7" s="466"/>
-      <c r="D7" s="466"/>
-      <c r="E7" s="466"/>
+      <c r="A7" s="514"/>
+      <c r="B7" s="472"/>
+      <c r="C7" s="472"/>
+      <c r="D7" s="472"/>
+      <c r="E7" s="472"/>
       <c r="F7" s="13"/>
-      <c r="G7" s="464"/>
-      <c r="H7" s="464"/>
+      <c r="G7" s="474"/>
+      <c r="H7" s="474"/>
       <c r="I7" s="240"/>
       <c r="J7" s="8"/>
       <c r="K7" s="15"/>
     </row>
     <row r="8" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="465"/>
-      <c r="B8" s="466"/>
-      <c r="C8" s="466"/>
-      <c r="D8" s="466"/>
-      <c r="E8" s="466"/>
+      <c r="A8" s="514"/>
+      <c r="B8" s="472"/>
+      <c r="C8" s="472"/>
+      <c r="D8" s="472"/>
+      <c r="E8" s="472"/>
       <c r="F8" s="13"/>
-      <c r="G8" s="464"/>
-      <c r="H8" s="464"/>
+      <c r="G8" s="474"/>
+      <c r="H8" s="474"/>
       <c r="I8" s="240"/>
       <c r="J8" s="8"/>
       <c r="K8" s="15"/>
     </row>
     <row r="9" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="465"/>
-      <c r="B9" s="466"/>
-      <c r="C9" s="466"/>
-      <c r="D9" s="466"/>
-      <c r="E9" s="466"/>
+      <c r="A9" s="514"/>
+      <c r="B9" s="472"/>
+      <c r="C9" s="472"/>
+      <c r="D9" s="472"/>
+      <c r="E9" s="472"/>
       <c r="F9" s="13"/>
-      <c r="G9" s="464"/>
-      <c r="H9" s="464"/>
+      <c r="G9" s="474"/>
+      <c r="H9" s="474"/>
       <c r="I9" s="240"/>
       <c r="J9" s="8"/>
       <c r="K9" s="15"/>
     </row>
     <row r="10" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="465"/>
-      <c r="B10" s="466"/>
-      <c r="C10" s="466"/>
-      <c r="D10" s="466"/>
-      <c r="E10" s="466"/>
+      <c r="A10" s="514"/>
+      <c r="B10" s="472"/>
+      <c r="C10" s="472"/>
+      <c r="D10" s="472"/>
+      <c r="E10" s="472"/>
       <c r="F10" s="13"/>
-      <c r="G10" s="464"/>
-      <c r="H10" s="464"/>
+      <c r="G10" s="474"/>
+      <c r="H10" s="474"/>
       <c r="I10" s="240"/>
       <c r="J10" s="8"/>
       <c r="K10" s="15"/>
     </row>
     <row r="11" spans="1:11" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="480"/>
-      <c r="B11" s="481"/>
-      <c r="C11" s="481"/>
-      <c r="D11" s="481"/>
-      <c r="E11" s="481"/>
+      <c r="A11" s="487"/>
+      <c r="B11" s="479"/>
+      <c r="C11" s="479"/>
+      <c r="D11" s="479"/>
+      <c r="E11" s="479"/>
       <c r="F11" s="14"/>
-      <c r="G11" s="488"/>
-      <c r="H11" s="488"/>
+      <c r="G11" s="476"/>
+      <c r="H11" s="476"/>
       <c r="I11" s="241"/>
       <c r="J11" s="10"/>
       <c r="K11" s="16"/>
     </row>
     <row r="12" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="482" t="s">
+      <c r="A12" s="492" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="483"/>
-      <c r="C12" s="483"/>
-      <c r="D12" s="483"/>
-      <c r="E12" s="483"/>
-      <c r="F12" s="483"/>
-      <c r="G12" s="483"/>
-      <c r="H12" s="483"/>
-      <c r="I12" s="483"/>
-      <c r="J12" s="483"/>
-      <c r="K12" s="484"/>
+      <c r="B12" s="493"/>
+      <c r="C12" s="493"/>
+      <c r="D12" s="493"/>
+      <c r="E12" s="493"/>
+      <c r="F12" s="493"/>
+      <c r="G12" s="493"/>
+      <c r="H12" s="493"/>
+      <c r="I12" s="493"/>
+      <c r="J12" s="493"/>
+      <c r="K12" s="494"/>
     </row>
     <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="485" t="s">
+      <c r="A13" s="495" t="s">
         <v>312</v>
       </c>
-      <c r="B13" s="486"/>
-      <c r="C13" s="486"/>
-      <c r="D13" s="486"/>
-      <c r="E13" s="486"/>
-      <c r="F13" s="486"/>
-      <c r="G13" s="486"/>
-      <c r="H13" s="486"/>
-      <c r="I13" s="486"/>
-      <c r="J13" s="486"/>
-      <c r="K13" s="487"/>
+      <c r="B13" s="496"/>
+      <c r="C13" s="496"/>
+      <c r="D13" s="496"/>
+      <c r="E13" s="496"/>
+      <c r="F13" s="496"/>
+      <c r="G13" s="496"/>
+      <c r="H13" s="496"/>
+      <c r="I13" s="496"/>
+      <c r="J13" s="496"/>
+      <c r="K13" s="497"/>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="190" t="s">
@@ -15975,447 +15975,447 @@
       <c r="A15" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="B15" s="470" t="s">
+      <c r="B15" s="488" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="471"/>
-      <c r="D15" s="469" t="s">
+      <c r="C15" s="489"/>
+      <c r="D15" s="517" t="s">
         <v>315</v>
       </c>
-      <c r="E15" s="470"/>
-      <c r="F15" s="471"/>
-      <c r="G15" s="469" t="s">
+      <c r="E15" s="488"/>
+      <c r="F15" s="489"/>
+      <c r="G15" s="517" t="s">
         <v>316</v>
       </c>
-      <c r="H15" s="470"/>
-      <c r="I15" s="471"/>
-      <c r="J15" s="489" t="s">
+      <c r="H15" s="488"/>
+      <c r="I15" s="489"/>
+      <c r="J15" s="477" t="s">
         <v>317</v>
       </c>
-      <c r="K15" s="462" t="s">
+      <c r="K15" s="512" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="451"/>
-      <c r="C16" s="452"/>
-      <c r="D16" s="469"/>
-      <c r="E16" s="470"/>
-      <c r="F16" s="471"/>
-      <c r="G16" s="469"/>
-      <c r="H16" s="470"/>
-      <c r="I16" s="471"/>
-      <c r="J16" s="489"/>
-      <c r="K16" s="462"/>
+      <c r="B16" s="490"/>
+      <c r="C16" s="491"/>
+      <c r="D16" s="517"/>
+      <c r="E16" s="488"/>
+      <c r="F16" s="489"/>
+      <c r="G16" s="517"/>
+      <c r="H16" s="488"/>
+      <c r="I16" s="489"/>
+      <c r="J16" s="477"/>
+      <c r="K16" s="512"/>
     </row>
     <row r="17" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="467" t="s">
+      <c r="A17" s="515" t="s">
         <v>129</v>
       </c>
-      <c r="B17" s="468"/>
+      <c r="B17" s="516"/>
       <c r="C17" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D17" s="454"/>
-      <c r="E17" s="451"/>
-      <c r="F17" s="452"/>
-      <c r="G17" s="454"/>
-      <c r="H17" s="451"/>
-      <c r="I17" s="452"/>
-      <c r="J17" s="490"/>
-      <c r="K17" s="463"/>
+      <c r="D17" s="504"/>
+      <c r="E17" s="490"/>
+      <c r="F17" s="491"/>
+      <c r="G17" s="504"/>
+      <c r="H17" s="490"/>
+      <c r="I17" s="491"/>
+      <c r="J17" s="478"/>
+      <c r="K17" s="513"/>
     </row>
     <row r="18" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="702"/>
-      <c r="B18" s="464"/>
+      <c r="A18" s="473"/>
+      <c r="B18" s="474"/>
       <c r="C18" s="248"/>
-      <c r="D18" s="466"/>
-      <c r="E18" s="466"/>
-      <c r="F18" s="466"/>
-      <c r="G18" s="466"/>
-      <c r="H18" s="466"/>
-      <c r="I18" s="466"/>
+      <c r="D18" s="472"/>
+      <c r="E18" s="472"/>
+      <c r="F18" s="472"/>
+      <c r="G18" s="472"/>
+      <c r="H18" s="472"/>
+      <c r="I18" s="472"/>
       <c r="J18" s="8"/>
       <c r="K18" s="9"/>
     </row>
     <row r="19" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="702"/>
-      <c r="B19" s="464"/>
+      <c r="A19" s="473"/>
+      <c r="B19" s="474"/>
       <c r="C19" s="248"/>
-      <c r="D19" s="466"/>
-      <c r="E19" s="466"/>
-      <c r="F19" s="466"/>
-      <c r="G19" s="466"/>
-      <c r="H19" s="466"/>
-      <c r="I19" s="466"/>
+      <c r="D19" s="472"/>
+      <c r="E19" s="472"/>
+      <c r="F19" s="472"/>
+      <c r="G19" s="472"/>
+      <c r="H19" s="472"/>
+      <c r="I19" s="472"/>
       <c r="J19" s="8"/>
       <c r="K19" s="9"/>
     </row>
     <row r="20" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="702"/>
-      <c r="B20" s="464"/>
+      <c r="A20" s="473"/>
+      <c r="B20" s="474"/>
       <c r="C20" s="248"/>
-      <c r="D20" s="466"/>
-      <c r="E20" s="466"/>
-      <c r="F20" s="466"/>
-      <c r="G20" s="466"/>
-      <c r="H20" s="466"/>
-      <c r="I20" s="466"/>
+      <c r="D20" s="472"/>
+      <c r="E20" s="472"/>
+      <c r="F20" s="472"/>
+      <c r="G20" s="472"/>
+      <c r="H20" s="472"/>
+      <c r="I20" s="472"/>
       <c r="J20" s="8"/>
       <c r="K20" s="9"/>
     </row>
     <row r="21" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="702"/>
-      <c r="B21" s="464"/>
+      <c r="A21" s="473"/>
+      <c r="B21" s="474"/>
       <c r="C21" s="248"/>
-      <c r="D21" s="466"/>
-      <c r="E21" s="466"/>
-      <c r="F21" s="466"/>
-      <c r="G21" s="466"/>
-      <c r="H21" s="466"/>
-      <c r="I21" s="466"/>
+      <c r="D21" s="472"/>
+      <c r="E21" s="472"/>
+      <c r="F21" s="472"/>
+      <c r="G21" s="472"/>
+      <c r="H21" s="472"/>
+      <c r="I21" s="472"/>
       <c r="J21" s="8"/>
       <c r="K21" s="9"/>
     </row>
     <row r="22" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="702"/>
-      <c r="B22" s="464"/>
+      <c r="A22" s="473"/>
+      <c r="B22" s="474"/>
       <c r="C22" s="248"/>
-      <c r="D22" s="466"/>
-      <c r="E22" s="466"/>
-      <c r="F22" s="466"/>
-      <c r="G22" s="466"/>
-      <c r="H22" s="466"/>
-      <c r="I22" s="466"/>
+      <c r="D22" s="472"/>
+      <c r="E22" s="472"/>
+      <c r="F22" s="472"/>
+      <c r="G22" s="472"/>
+      <c r="H22" s="472"/>
+      <c r="I22" s="472"/>
       <c r="J22" s="8"/>
       <c r="K22" s="9"/>
     </row>
     <row r="23" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="702"/>
-      <c r="B23" s="464"/>
+      <c r="A23" s="473"/>
+      <c r="B23" s="474"/>
       <c r="C23" s="248"/>
-      <c r="D23" s="466"/>
-      <c r="E23" s="466"/>
-      <c r="F23" s="466"/>
-      <c r="G23" s="466"/>
-      <c r="H23" s="466"/>
-      <c r="I23" s="466"/>
+      <c r="D23" s="472"/>
+      <c r="E23" s="472"/>
+      <c r="F23" s="472"/>
+      <c r="G23" s="472"/>
+      <c r="H23" s="472"/>
+      <c r="I23" s="472"/>
       <c r="J23" s="8"/>
       <c r="K23" s="9"/>
     </row>
     <row r="24" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="702"/>
-      <c r="B24" s="464"/>
+      <c r="A24" s="473"/>
+      <c r="B24" s="474"/>
       <c r="C24" s="248"/>
-      <c r="D24" s="466"/>
-      <c r="E24" s="466"/>
-      <c r="F24" s="466"/>
-      <c r="G24" s="466"/>
-      <c r="H24" s="466"/>
-      <c r="I24" s="466"/>
+      <c r="D24" s="472"/>
+      <c r="E24" s="472"/>
+      <c r="F24" s="472"/>
+      <c r="G24" s="472"/>
+      <c r="H24" s="472"/>
+      <c r="I24" s="472"/>
       <c r="J24" s="8"/>
       <c r="K24" s="9"/>
     </row>
     <row r="25" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="702"/>
-      <c r="B25" s="464"/>
+      <c r="A25" s="473"/>
+      <c r="B25" s="474"/>
       <c r="C25" s="248"/>
-      <c r="D25" s="466"/>
-      <c r="E25" s="466"/>
-      <c r="F25" s="466"/>
-      <c r="G25" s="466"/>
-      <c r="H25" s="466"/>
-      <c r="I25" s="466"/>
+      <c r="D25" s="472"/>
+      <c r="E25" s="472"/>
+      <c r="F25" s="472"/>
+      <c r="G25" s="472"/>
+      <c r="H25" s="472"/>
+      <c r="I25" s="472"/>
       <c r="J25" s="8"/>
       <c r="K25" s="9"/>
     </row>
     <row r="26" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="702"/>
-      <c r="B26" s="464"/>
+      <c r="A26" s="473"/>
+      <c r="B26" s="474"/>
       <c r="C26" s="248"/>
-      <c r="D26" s="466"/>
-      <c r="E26" s="466"/>
-      <c r="F26" s="466"/>
-      <c r="G26" s="466"/>
-      <c r="H26" s="466"/>
-      <c r="I26" s="466"/>
+      <c r="D26" s="472"/>
+      <c r="E26" s="472"/>
+      <c r="F26" s="472"/>
+      <c r="G26" s="472"/>
+      <c r="H26" s="472"/>
+      <c r="I26" s="472"/>
       <c r="J26" s="8"/>
       <c r="K26" s="9"/>
     </row>
     <row r="27" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="702"/>
-      <c r="B27" s="464"/>
+      <c r="A27" s="473"/>
+      <c r="B27" s="474"/>
       <c r="C27" s="248"/>
-      <c r="D27" s="466"/>
-      <c r="E27" s="466"/>
-      <c r="F27" s="466"/>
-      <c r="G27" s="466"/>
-      <c r="H27" s="466"/>
-      <c r="I27" s="466"/>
+      <c r="D27" s="472"/>
+      <c r="E27" s="472"/>
+      <c r="F27" s="472"/>
+      <c r="G27" s="472"/>
+      <c r="H27" s="472"/>
+      <c r="I27" s="472"/>
       <c r="J27" s="8"/>
       <c r="K27" s="9"/>
     </row>
     <row r="28" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="702"/>
-      <c r="B28" s="464"/>
+      <c r="A28" s="473"/>
+      <c r="B28" s="474"/>
       <c r="C28" s="248"/>
-      <c r="D28" s="466"/>
-      <c r="E28" s="466"/>
-      <c r="F28" s="466"/>
-      <c r="G28" s="466"/>
-      <c r="H28" s="466"/>
-      <c r="I28" s="466"/>
+      <c r="D28" s="472"/>
+      <c r="E28" s="472"/>
+      <c r="F28" s="472"/>
+      <c r="G28" s="472"/>
+      <c r="H28" s="472"/>
+      <c r="I28" s="472"/>
       <c r="J28" s="8"/>
       <c r="K28" s="9"/>
     </row>
     <row r="29" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="702"/>
-      <c r="B29" s="464"/>
+      <c r="A29" s="473"/>
+      <c r="B29" s="474"/>
       <c r="C29" s="248"/>
-      <c r="D29" s="466"/>
-      <c r="E29" s="466"/>
-      <c r="F29" s="466"/>
-      <c r="G29" s="466"/>
-      <c r="H29" s="466"/>
-      <c r="I29" s="466"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
+      <c r="G29" s="472"/>
+      <c r="H29" s="472"/>
+      <c r="I29" s="472"/>
       <c r="J29" s="8"/>
       <c r="K29" s="9"/>
     </row>
     <row r="30" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="702"/>
-      <c r="B30" s="464"/>
+      <c r="A30" s="473"/>
+      <c r="B30" s="474"/>
       <c r="C30" s="248"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
-      <c r="G30" s="466"/>
-      <c r="H30" s="466"/>
-      <c r="I30" s="466"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
+      <c r="G30" s="472"/>
+      <c r="H30" s="472"/>
+      <c r="I30" s="472"/>
       <c r="J30" s="8"/>
       <c r="K30" s="9"/>
     </row>
     <row r="31" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="702"/>
-      <c r="B31" s="464"/>
+      <c r="A31" s="473"/>
+      <c r="B31" s="474"/>
       <c r="C31" s="248"/>
-      <c r="D31" s="466"/>
-      <c r="E31" s="466"/>
-      <c r="F31" s="466"/>
-      <c r="G31" s="466"/>
-      <c r="H31" s="466"/>
-      <c r="I31" s="466"/>
+      <c r="D31" s="472"/>
+      <c r="E31" s="472"/>
+      <c r="F31" s="472"/>
+      <c r="G31" s="472"/>
+      <c r="H31" s="472"/>
+      <c r="I31" s="472"/>
       <c r="J31" s="8"/>
       <c r="K31" s="9"/>
     </row>
     <row r="32" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="702"/>
-      <c r="B32" s="464"/>
+      <c r="A32" s="473"/>
+      <c r="B32" s="474"/>
       <c r="C32" s="248"/>
-      <c r="D32" s="466"/>
-      <c r="E32" s="466"/>
-      <c r="F32" s="466"/>
-      <c r="G32" s="466"/>
-      <c r="H32" s="466"/>
-      <c r="I32" s="466"/>
+      <c r="D32" s="472"/>
+      <c r="E32" s="472"/>
+      <c r="F32" s="472"/>
+      <c r="G32" s="472"/>
+      <c r="H32" s="472"/>
+      <c r="I32" s="472"/>
       <c r="J32" s="8"/>
       <c r="K32" s="9"/>
     </row>
     <row r="33" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="702"/>
-      <c r="B33" s="464"/>
+      <c r="A33" s="473"/>
+      <c r="B33" s="474"/>
       <c r="C33" s="248"/>
-      <c r="D33" s="466"/>
-      <c r="E33" s="466"/>
-      <c r="F33" s="466"/>
-      <c r="G33" s="466"/>
-      <c r="H33" s="466"/>
-      <c r="I33" s="466"/>
+      <c r="D33" s="472"/>
+      <c r="E33" s="472"/>
+      <c r="F33" s="472"/>
+      <c r="G33" s="472"/>
+      <c r="H33" s="472"/>
+      <c r="I33" s="472"/>
       <c r="J33" s="8"/>
       <c r="K33" s="9"/>
     </row>
     <row r="34" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="702"/>
-      <c r="B34" s="464"/>
+      <c r="A34" s="473"/>
+      <c r="B34" s="474"/>
       <c r="C34" s="248"/>
-      <c r="D34" s="466"/>
-      <c r="E34" s="466"/>
-      <c r="F34" s="466"/>
-      <c r="G34" s="466"/>
-      <c r="H34" s="466"/>
-      <c r="I34" s="466"/>
+      <c r="D34" s="472"/>
+      <c r="E34" s="472"/>
+      <c r="F34" s="472"/>
+      <c r="G34" s="472"/>
+      <c r="H34" s="472"/>
+      <c r="I34" s="472"/>
       <c r="J34" s="8"/>
       <c r="K34" s="9"/>
     </row>
     <row r="35" spans="1:12" s="12" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="702"/>
-      <c r="B35" s="464"/>
+      <c r="A35" s="473"/>
+      <c r="B35" s="474"/>
       <c r="C35" s="248"/>
-      <c r="D35" s="466"/>
-      <c r="E35" s="466"/>
-      <c r="F35" s="466"/>
-      <c r="G35" s="466"/>
-      <c r="H35" s="466"/>
-      <c r="I35" s="466"/>
+      <c r="D35" s="472"/>
+      <c r="E35" s="472"/>
+      <c r="F35" s="472"/>
+      <c r="G35" s="472"/>
+      <c r="H35" s="472"/>
+      <c r="I35" s="472"/>
       <c r="J35" s="8"/>
       <c r="K35" s="9"/>
     </row>
     <row r="36" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="702"/>
-      <c r="B36" s="464"/>
+      <c r="A36" s="473"/>
+      <c r="B36" s="474"/>
       <c r="C36" s="248"/>
-      <c r="D36" s="466"/>
-      <c r="E36" s="466"/>
-      <c r="F36" s="466"/>
-      <c r="G36" s="466"/>
-      <c r="H36" s="466"/>
-      <c r="I36" s="466"/>
+      <c r="D36" s="472"/>
+      <c r="E36" s="472"/>
+      <c r="F36" s="472"/>
+      <c r="G36" s="472"/>
+      <c r="H36" s="472"/>
+      <c r="I36" s="472"/>
       <c r="J36" s="8"/>
       <c r="K36" s="9"/>
     </row>
     <row r="37" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="702"/>
-      <c r="B37" s="464"/>
+      <c r="A37" s="473"/>
+      <c r="B37" s="474"/>
       <c r="C37" s="248"/>
-      <c r="D37" s="466"/>
-      <c r="E37" s="466"/>
-      <c r="F37" s="466"/>
-      <c r="G37" s="466"/>
-      <c r="H37" s="466"/>
-      <c r="I37" s="466"/>
+      <c r="D37" s="472"/>
+      <c r="E37" s="472"/>
+      <c r="F37" s="472"/>
+      <c r="G37" s="472"/>
+      <c r="H37" s="472"/>
+      <c r="I37" s="472"/>
       <c r="J37" s="8"/>
       <c r="K37" s="9"/>
     </row>
     <row r="38" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="702"/>
-      <c r="B38" s="464"/>
+      <c r="A38" s="473"/>
+      <c r="B38" s="474"/>
       <c r="C38" s="248"/>
-      <c r="D38" s="466"/>
-      <c r="E38" s="466"/>
-      <c r="F38" s="466"/>
-      <c r="G38" s="466"/>
-      <c r="H38" s="466"/>
-      <c r="I38" s="466"/>
+      <c r="D38" s="472"/>
+      <c r="E38" s="472"/>
+      <c r="F38" s="472"/>
+      <c r="G38" s="472"/>
+      <c r="H38" s="472"/>
+      <c r="I38" s="472"/>
       <c r="J38" s="8"/>
       <c r="K38" s="9"/>
     </row>
     <row r="39" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="702"/>
-      <c r="B39" s="464"/>
+      <c r="A39" s="473"/>
+      <c r="B39" s="474"/>
       <c r="C39" s="248"/>
-      <c r="D39" s="466"/>
-      <c r="E39" s="466"/>
-      <c r="F39" s="466"/>
-      <c r="G39" s="466"/>
-      <c r="H39" s="466"/>
-      <c r="I39" s="466"/>
+      <c r="D39" s="472"/>
+      <c r="E39" s="472"/>
+      <c r="F39" s="472"/>
+      <c r="G39" s="472"/>
+      <c r="H39" s="472"/>
+      <c r="I39" s="472"/>
       <c r="J39" s="8"/>
       <c r="K39" s="9"/>
     </row>
     <row r="40" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="702"/>
-      <c r="B40" s="464"/>
+      <c r="A40" s="473"/>
+      <c r="B40" s="474"/>
       <c r="C40" s="248"/>
-      <c r="D40" s="466"/>
-      <c r="E40" s="466"/>
-      <c r="F40" s="466"/>
-      <c r="G40" s="466"/>
-      <c r="H40" s="466"/>
-      <c r="I40" s="466"/>
+      <c r="D40" s="472"/>
+      <c r="E40" s="472"/>
+      <c r="F40" s="472"/>
+      <c r="G40" s="472"/>
+      <c r="H40" s="472"/>
+      <c r="I40" s="472"/>
       <c r="J40" s="8"/>
       <c r="K40" s="9"/>
     </row>
     <row r="41" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="702"/>
-      <c r="B41" s="464"/>
+      <c r="A41" s="473"/>
+      <c r="B41" s="474"/>
       <c r="C41" s="248"/>
-      <c r="D41" s="466"/>
-      <c r="E41" s="466"/>
-      <c r="F41" s="466"/>
-      <c r="G41" s="466"/>
-      <c r="H41" s="466"/>
-      <c r="I41" s="466"/>
+      <c r="D41" s="472"/>
+      <c r="E41" s="472"/>
+      <c r="F41" s="472"/>
+      <c r="G41" s="472"/>
+      <c r="H41" s="472"/>
+      <c r="I41" s="472"/>
       <c r="J41" s="8"/>
       <c r="K41" s="9"/>
     </row>
     <row r="42" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="702"/>
-      <c r="B42" s="464"/>
+      <c r="A42" s="473"/>
+      <c r="B42" s="474"/>
       <c r="C42" s="248"/>
-      <c r="D42" s="466"/>
-      <c r="E42" s="466"/>
-      <c r="F42" s="466"/>
-      <c r="G42" s="466"/>
-      <c r="H42" s="466"/>
-      <c r="I42" s="466"/>
+      <c r="D42" s="472"/>
+      <c r="E42" s="472"/>
+      <c r="F42" s="472"/>
+      <c r="G42" s="472"/>
+      <c r="H42" s="472"/>
+      <c r="I42" s="472"/>
       <c r="J42" s="8"/>
       <c r="K42" s="9"/>
     </row>
     <row r="43" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="702"/>
-      <c r="B43" s="464"/>
+      <c r="A43" s="473"/>
+      <c r="B43" s="474"/>
       <c r="C43" s="248"/>
-      <c r="D43" s="466"/>
-      <c r="E43" s="466"/>
-      <c r="F43" s="466"/>
-      <c r="G43" s="466"/>
-      <c r="H43" s="466"/>
-      <c r="I43" s="466"/>
+      <c r="D43" s="472"/>
+      <c r="E43" s="472"/>
+      <c r="F43" s="472"/>
+      <c r="G43" s="472"/>
+      <c r="H43" s="472"/>
+      <c r="I43" s="472"/>
       <c r="J43" s="8"/>
       <c r="K43" s="9"/>
     </row>
     <row r="44" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="702"/>
-      <c r="B44" s="464"/>
+      <c r="A44" s="473"/>
+      <c r="B44" s="474"/>
       <c r="C44" s="248"/>
-      <c r="D44" s="466"/>
-      <c r="E44" s="466"/>
-      <c r="F44" s="466"/>
-      <c r="G44" s="466"/>
-      <c r="H44" s="466"/>
-      <c r="I44" s="466"/>
+      <c r="D44" s="472"/>
+      <c r="E44" s="472"/>
+      <c r="F44" s="472"/>
+      <c r="G44" s="472"/>
+      <c r="H44" s="472"/>
+      <c r="I44" s="472"/>
       <c r="J44" s="8"/>
       <c r="K44" s="9"/>
     </row>
     <row r="45" spans="1:12" s="12" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="703"/>
-      <c r="B45" s="488"/>
+      <c r="A45" s="475"/>
+      <c r="B45" s="476"/>
       <c r="C45" s="247"/>
-      <c r="D45" s="481"/>
-      <c r="E45" s="481"/>
-      <c r="F45" s="481"/>
-      <c r="G45" s="481"/>
-      <c r="H45" s="481"/>
-      <c r="I45" s="481"/>
+      <c r="D45" s="479"/>
+      <c r="E45" s="479"/>
+      <c r="F45" s="479"/>
+      <c r="G45" s="479"/>
+      <c r="H45" s="479"/>
+      <c r="I45" s="479"/>
       <c r="J45" s="10"/>
       <c r="K45" s="11"/>
     </row>
     <row r="46" spans="1:12" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="491" t="s">
+      <c r="A46" s="480" t="s">
         <v>114</v>
       </c>
-      <c r="B46" s="492"/>
-      <c r="C46" s="492"/>
-      <c r="D46" s="492"/>
-      <c r="E46" s="492"/>
-      <c r="F46" s="492"/>
-      <c r="G46" s="492"/>
-      <c r="H46" s="492"/>
-      <c r="I46" s="492"/>
-      <c r="J46" s="493"/>
-      <c r="K46" s="494"/>
+      <c r="B46" s="481"/>
+      <c r="C46" s="481"/>
+      <c r="D46" s="481"/>
+      <c r="E46" s="481"/>
+      <c r="F46" s="481"/>
+      <c r="G46" s="481"/>
+      <c r="H46" s="481"/>
+      <c r="I46" s="481"/>
+      <c r="J46" s="482"/>
+      <c r="K46" s="483"/>
     </row>
     <row r="47" spans="1:12" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="254" t="s">
+      <c r="A47" s="447" t="s">
         <v>143</v>
       </c>
-      <c r="B47" s="255"/>
-      <c r="C47" s="256"/>
-      <c r="D47" s="477"/>
-      <c r="E47" s="478"/>
-      <c r="F47" s="478"/>
-      <c r="G47" s="478"/>
-      <c r="H47" s="479"/>
+      <c r="B47" s="448"/>
+      <c r="C47" s="449"/>
+      <c r="D47" s="484"/>
+      <c r="E47" s="485"/>
+      <c r="F47" s="485"/>
+      <c r="G47" s="485"/>
+      <c r="H47" s="486"/>
       <c r="I47" s="221" t="s">
         <v>144</v>
       </c>
@@ -16424,19 +16424,19 @@
       <c r="L47" s="223"/>
     </row>
     <row r="48" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="253" t="s">
+      <c r="A48" s="446" t="s">
         <v>401</v>
       </c>
-      <c r="B48" s="253"/>
-      <c r="C48" s="253"/>
-      <c r="D48" s="253"/>
-      <c r="E48" s="253"/>
-      <c r="F48" s="253"/>
-      <c r="G48" s="253"/>
-      <c r="H48" s="253"/>
-      <c r="I48" s="253"/>
-      <c r="J48" s="253"/>
-      <c r="K48" s="253"/>
+      <c r="B48" s="446"/>
+      <c r="C48" s="446"/>
+      <c r="D48" s="446"/>
+      <c r="E48" s="446"/>
+      <c r="F48" s="446"/>
+      <c r="G48" s="446"/>
+      <c r="H48" s="446"/>
+      <c r="I48" s="446"/>
+      <c r="J48" s="446"/>
+      <c r="K48" s="446"/>
       <c r="L48" s="226"/>
     </row>
   </sheetData>
@@ -16450,6 +16450,99 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="117">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B3:E4"/>
+    <mergeCell ref="G3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="K15:K17"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D15:F17"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="G15:I17"/>
+    <mergeCell ref="A48:K48"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B15:C16"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="D44:F44"/>
     <mergeCell ref="G44:I44"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="D37:F37"/>
@@ -16474,99 +16567,6 @@
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="D42:F42"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G41:I41"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="A48:K48"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B15:C16"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B3:E4"/>
-    <mergeCell ref="G3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="K15:K17"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D15:F17"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="G15:I17"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -16598,564 +16598,564 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="518"/>
-      <c r="B1" s="519"/>
-      <c r="C1" s="519"/>
-      <c r="D1" s="519"/>
-      <c r="E1" s="519"/>
-      <c r="F1" s="519"/>
-      <c r="G1" s="519"/>
-      <c r="H1" s="519"/>
-      <c r="I1" s="519"/>
-      <c r="J1" s="519"/>
-      <c r="K1" s="520"/>
+      <c r="A1" s="543"/>
+      <c r="B1" s="544"/>
+      <c r="C1" s="544"/>
+      <c r="D1" s="544"/>
+      <c r="E1" s="544"/>
+      <c r="F1" s="544"/>
+      <c r="G1" s="544"/>
+      <c r="H1" s="544"/>
+      <c r="I1" s="544"/>
+      <c r="J1" s="544"/>
+      <c r="K1" s="545"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="540" t="s">
+      <c r="A2" s="570" t="s">
         <v>319</v>
       </c>
-      <c r="B2" s="541"/>
-      <c r="C2" s="541"/>
-      <c r="D2" s="541"/>
-      <c r="E2" s="541"/>
-      <c r="F2" s="541"/>
-      <c r="G2" s="541"/>
-      <c r="H2" s="541"/>
-      <c r="I2" s="541"/>
-      <c r="J2" s="541"/>
-      <c r="K2" s="542"/>
+      <c r="B2" s="571"/>
+      <c r="C2" s="571"/>
+      <c r="D2" s="571"/>
+      <c r="E2" s="571"/>
+      <c r="F2" s="571"/>
+      <c r="G2" s="571"/>
+      <c r="H2" s="571"/>
+      <c r="I2" s="571"/>
+      <c r="J2" s="571"/>
+      <c r="K2" s="572"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="526" t="s">
+      <c r="A3" s="554" t="s">
         <v>320</v>
       </c>
-      <c r="B3" s="528" t="s">
+      <c r="B3" s="555" t="s">
         <v>321</v>
       </c>
-      <c r="C3" s="528"/>
-      <c r="D3" s="529"/>
-      <c r="E3" s="449" t="s">
+      <c r="C3" s="555"/>
+      <c r="D3" s="556"/>
+      <c r="E3" s="501" t="s">
         <v>322</v>
       </c>
-      <c r="F3" s="450"/>
-      <c r="G3" s="509" t="s">
+      <c r="F3" s="502"/>
+      <c r="G3" s="579" t="s">
         <v>323</v>
       </c>
-      <c r="H3" s="453" t="s">
+      <c r="H3" s="503" t="s">
         <v>324</v>
       </c>
-      <c r="I3" s="535"/>
-      <c r="J3" s="535"/>
-      <c r="K3" s="536"/>
+      <c r="I3" s="565"/>
+      <c r="J3" s="565"/>
+      <c r="K3" s="566"/>
     </row>
     <row r="4" spans="1:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="527"/>
-      <c r="B4" s="530"/>
-      <c r="C4" s="530"/>
-      <c r="D4" s="531"/>
-      <c r="E4" s="451"/>
-      <c r="F4" s="452"/>
-      <c r="G4" s="510"/>
-      <c r="H4" s="537"/>
-      <c r="I4" s="521"/>
-      <c r="J4" s="521"/>
-      <c r="K4" s="538"/>
+      <c r="A4" s="542"/>
+      <c r="B4" s="557"/>
+      <c r="C4" s="557"/>
+      <c r="D4" s="558"/>
+      <c r="E4" s="490"/>
+      <c r="F4" s="491"/>
+      <c r="G4" s="580"/>
+      <c r="H4" s="567"/>
+      <c r="I4" s="546"/>
+      <c r="J4" s="546"/>
+      <c r="K4" s="568"/>
     </row>
     <row r="5" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17"/>
-      <c r="B5" s="543"/>
-      <c r="C5" s="543"/>
-      <c r="D5" s="544"/>
+      <c r="B5" s="573"/>
+      <c r="C5" s="573"/>
+      <c r="D5" s="574"/>
       <c r="E5" s="18" t="s">
         <v>129</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G5" s="511"/>
-      <c r="H5" s="539"/>
-      <c r="I5" s="307"/>
-      <c r="J5" s="307"/>
-      <c r="K5" s="308"/>
+      <c r="G5" s="581"/>
+      <c r="H5" s="569"/>
+      <c r="I5" s="432"/>
+      <c r="J5" s="432"/>
+      <c r="K5" s="433"/>
     </row>
     <row r="6" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="506"/>
-      <c r="B6" s="507"/>
-      <c r="C6" s="507"/>
-      <c r="D6" s="508"/>
-      <c r="E6" s="704"/>
-      <c r="F6" s="704"/>
-      <c r="G6" s="705"/>
-      <c r="H6" s="706"/>
-      <c r="I6" s="707"/>
-      <c r="J6" s="707"/>
-      <c r="K6" s="708"/>
+      <c r="A6" s="562"/>
+      <c r="B6" s="563"/>
+      <c r="C6" s="563"/>
+      <c r="D6" s="564"/>
+      <c r="E6" s="262"/>
+      <c r="F6" s="262"/>
+      <c r="G6" s="263"/>
+      <c r="H6" s="549"/>
+      <c r="I6" s="550"/>
+      <c r="J6" s="550"/>
+      <c r="K6" s="551"/>
     </row>
     <row r="7" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="506"/>
-      <c r="B7" s="507"/>
-      <c r="C7" s="507"/>
-      <c r="D7" s="508"/>
-      <c r="E7" s="704"/>
-      <c r="F7" s="704"/>
-      <c r="G7" s="705"/>
-      <c r="H7" s="706"/>
-      <c r="I7" s="707"/>
-      <c r="J7" s="707"/>
-      <c r="K7" s="708"/>
+      <c r="A7" s="562"/>
+      <c r="B7" s="563"/>
+      <c r="C7" s="563"/>
+      <c r="D7" s="564"/>
+      <c r="E7" s="262"/>
+      <c r="F7" s="262"/>
+      <c r="G7" s="263"/>
+      <c r="H7" s="549"/>
+      <c r="I7" s="550"/>
+      <c r="J7" s="550"/>
+      <c r="K7" s="551"/>
     </row>
     <row r="8" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="506"/>
-      <c r="B8" s="507"/>
-      <c r="C8" s="507"/>
-      <c r="D8" s="508"/>
-      <c r="E8" s="704"/>
-      <c r="F8" s="704"/>
-      <c r="G8" s="705"/>
-      <c r="H8" s="706"/>
-      <c r="I8" s="707"/>
-      <c r="J8" s="707"/>
-      <c r="K8" s="708"/>
+      <c r="A8" s="562"/>
+      <c r="B8" s="563"/>
+      <c r="C8" s="563"/>
+      <c r="D8" s="564"/>
+      <c r="E8" s="262"/>
+      <c r="F8" s="262"/>
+      <c r="G8" s="263"/>
+      <c r="H8" s="549"/>
+      <c r="I8" s="550"/>
+      <c r="J8" s="550"/>
+      <c r="K8" s="551"/>
     </row>
     <row r="9" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="506"/>
-      <c r="B9" s="507"/>
-      <c r="C9" s="507"/>
-      <c r="D9" s="508"/>
-      <c r="E9" s="704"/>
-      <c r="F9" s="704"/>
-      <c r="G9" s="705"/>
-      <c r="H9" s="706"/>
-      <c r="I9" s="707"/>
-      <c r="J9" s="707"/>
-      <c r="K9" s="708"/>
+      <c r="A9" s="562"/>
+      <c r="B9" s="563"/>
+      <c r="C9" s="563"/>
+      <c r="D9" s="564"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="262"/>
+      <c r="G9" s="263"/>
+      <c r="H9" s="549"/>
+      <c r="I9" s="550"/>
+      <c r="J9" s="550"/>
+      <c r="K9" s="551"/>
     </row>
     <row r="10" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="506"/>
-      <c r="B10" s="507"/>
-      <c r="C10" s="507"/>
-      <c r="D10" s="508"/>
-      <c r="E10" s="704"/>
-      <c r="F10" s="704"/>
-      <c r="G10" s="705"/>
-      <c r="H10" s="706"/>
-      <c r="I10" s="707"/>
-      <c r="J10" s="707"/>
-      <c r="K10" s="708"/>
+      <c r="A10" s="562"/>
+      <c r="B10" s="563"/>
+      <c r="C10" s="563"/>
+      <c r="D10" s="564"/>
+      <c r="E10" s="262"/>
+      <c r="F10" s="262"/>
+      <c r="G10" s="263"/>
+      <c r="H10" s="549"/>
+      <c r="I10" s="550"/>
+      <c r="J10" s="550"/>
+      <c r="K10" s="551"/>
     </row>
     <row r="11" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="506"/>
-      <c r="B11" s="507"/>
-      <c r="C11" s="507"/>
-      <c r="D11" s="508"/>
-      <c r="E11" s="704"/>
-      <c r="F11" s="704"/>
-      <c r="G11" s="705"/>
-      <c r="H11" s="706"/>
-      <c r="I11" s="707"/>
-      <c r="J11" s="707"/>
-      <c r="K11" s="708"/>
+      <c r="A11" s="562"/>
+      <c r="B11" s="563"/>
+      <c r="C11" s="563"/>
+      <c r="D11" s="564"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="262"/>
+      <c r="G11" s="263"/>
+      <c r="H11" s="549"/>
+      <c r="I11" s="550"/>
+      <c r="J11" s="550"/>
+      <c r="K11" s="551"/>
     </row>
     <row r="12" spans="1:11" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="532"/>
-      <c r="B12" s="533"/>
-      <c r="C12" s="533"/>
-      <c r="D12" s="534"/>
-      <c r="E12" s="704"/>
-      <c r="F12" s="704"/>
-      <c r="G12" s="709"/>
-      <c r="H12" s="710"/>
-      <c r="I12" s="711"/>
-      <c r="J12" s="711"/>
-      <c r="K12" s="712"/>
+      <c r="A12" s="559"/>
+      <c r="B12" s="560"/>
+      <c r="C12" s="560"/>
+      <c r="D12" s="561"/>
+      <c r="E12" s="262"/>
+      <c r="F12" s="262"/>
+      <c r="G12" s="264"/>
+      <c r="H12" s="523"/>
+      <c r="I12" s="524"/>
+      <c r="J12" s="524"/>
+      <c r="K12" s="525"/>
     </row>
     <row r="13" spans="1:11" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="482" t="s">
+      <c r="A13" s="492" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="483"/>
-      <c r="C13" s="483"/>
-      <c r="D13" s="483"/>
-      <c r="E13" s="483"/>
-      <c r="F13" s="483"/>
-      <c r="G13" s="483"/>
-      <c r="H13" s="483"/>
-      <c r="I13" s="483"/>
-      <c r="J13" s="483"/>
-      <c r="K13" s="484"/>
+      <c r="B13" s="493"/>
+      <c r="C13" s="493"/>
+      <c r="D13" s="493"/>
+      <c r="E13" s="493"/>
+      <c r="F13" s="493"/>
+      <c r="G13" s="493"/>
+      <c r="H13" s="493"/>
+      <c r="I13" s="493"/>
+      <c r="J13" s="493"/>
+      <c r="K13" s="494"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="545" t="s">
+      <c r="A14" s="526" t="s">
         <v>325</v>
       </c>
-      <c r="B14" s="546"/>
-      <c r="C14" s="546"/>
-      <c r="D14" s="546"/>
-      <c r="E14" s="546"/>
-      <c r="F14" s="546"/>
-      <c r="G14" s="546"/>
-      <c r="H14" s="546"/>
-      <c r="I14" s="546"/>
-      <c r="J14" s="546"/>
-      <c r="K14" s="547"/>
+      <c r="B14" s="527"/>
+      <c r="C14" s="527"/>
+      <c r="D14" s="527"/>
+      <c r="E14" s="527"/>
+      <c r="F14" s="527"/>
+      <c r="G14" s="527"/>
+      <c r="H14" s="527"/>
+      <c r="I14" s="527"/>
+      <c r="J14" s="527"/>
+      <c r="K14" s="528"/>
     </row>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="527" t="s">
+      <c r="A15" s="542" t="s">
         <v>326</v>
       </c>
-      <c r="B15" s="470" t="s">
+      <c r="B15" s="488" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="521"/>
-      <c r="D15" s="522"/>
-      <c r="E15" s="470" t="s">
+      <c r="C15" s="546"/>
+      <c r="D15" s="547"/>
+      <c r="E15" s="488" t="s">
         <v>328</v>
       </c>
-      <c r="F15" s="471"/>
-      <c r="G15" s="548" t="s">
+      <c r="F15" s="489"/>
+      <c r="G15" s="532" t="s">
         <v>323</v>
       </c>
-      <c r="H15" s="524" t="s">
+      <c r="H15" s="552" t="s">
         <v>329</v>
       </c>
-      <c r="I15" s="469" t="s">
+      <c r="I15" s="517" t="s">
         <v>330</v>
       </c>
-      <c r="J15" s="521"/>
-      <c r="K15" s="538"/>
+      <c r="J15" s="546"/>
+      <c r="K15" s="568"/>
     </row>
     <row r="16" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="527"/>
-      <c r="B16" s="521"/>
-      <c r="C16" s="521"/>
-      <c r="D16" s="522"/>
-      <c r="E16" s="451"/>
-      <c r="F16" s="452"/>
-      <c r="G16" s="548"/>
-      <c r="H16" s="524"/>
-      <c r="I16" s="537"/>
-      <c r="J16" s="521"/>
-      <c r="K16" s="538"/>
+      <c r="A16" s="542"/>
+      <c r="B16" s="546"/>
+      <c r="C16" s="546"/>
+      <c r="D16" s="547"/>
+      <c r="E16" s="490"/>
+      <c r="F16" s="491"/>
+      <c r="G16" s="532"/>
+      <c r="H16" s="552"/>
+      <c r="I16" s="567"/>
+      <c r="J16" s="546"/>
+      <c r="K16" s="568"/>
     </row>
     <row r="17" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
-      <c r="B17" s="307"/>
-      <c r="C17" s="307"/>
-      <c r="D17" s="523"/>
+      <c r="B17" s="432"/>
+      <c r="C17" s="432"/>
+      <c r="D17" s="548"/>
       <c r="E17" s="18" t="s">
         <v>129</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G17" s="456"/>
-      <c r="H17" s="525"/>
-      <c r="I17" s="539"/>
-      <c r="J17" s="307"/>
-      <c r="K17" s="308"/>
+      <c r="G17" s="506"/>
+      <c r="H17" s="553"/>
+      <c r="I17" s="569"/>
+      <c r="J17" s="432"/>
+      <c r="K17" s="433"/>
     </row>
     <row r="18" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="512"/>
-      <c r="B18" s="513"/>
-      <c r="C18" s="513"/>
-      <c r="D18" s="514"/>
-      <c r="E18" s="713"/>
-      <c r="F18" s="713"/>
-      <c r="G18" s="714"/>
-      <c r="H18" s="715"/>
-      <c r="I18" s="716"/>
-      <c r="J18" s="717"/>
-      <c r="K18" s="718"/>
+      <c r="A18" s="529"/>
+      <c r="B18" s="530"/>
+      <c r="C18" s="530"/>
+      <c r="D18" s="531"/>
+      <c r="E18" s="265"/>
+      <c r="F18" s="265"/>
+      <c r="G18" s="266"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="533"/>
+      <c r="J18" s="534"/>
+      <c r="K18" s="535"/>
     </row>
     <row r="19" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="512"/>
-      <c r="B19" s="513"/>
-      <c r="C19" s="513"/>
-      <c r="D19" s="514"/>
-      <c r="E19" s="713"/>
-      <c r="F19" s="713"/>
-      <c r="G19" s="714"/>
-      <c r="H19" s="715"/>
-      <c r="I19" s="719"/>
-      <c r="J19" s="720"/>
-      <c r="K19" s="721"/>
+      <c r="A19" s="529"/>
+      <c r="B19" s="530"/>
+      <c r="C19" s="530"/>
+      <c r="D19" s="531"/>
+      <c r="E19" s="265"/>
+      <c r="F19" s="265"/>
+      <c r="G19" s="266"/>
+      <c r="H19" s="267"/>
+      <c r="I19" s="268"/>
+      <c r="J19" s="269"/>
+      <c r="K19" s="270"/>
     </row>
     <row r="20" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="512"/>
-      <c r="B20" s="513"/>
-      <c r="C20" s="513"/>
-      <c r="D20" s="514"/>
-      <c r="E20" s="713"/>
-      <c r="F20" s="713"/>
-      <c r="G20" s="714"/>
-      <c r="H20" s="715"/>
-      <c r="I20" s="719"/>
-      <c r="J20" s="720"/>
-      <c r="K20" s="721"/>
+      <c r="A20" s="529"/>
+      <c r="B20" s="530"/>
+      <c r="C20" s="530"/>
+      <c r="D20" s="531"/>
+      <c r="E20" s="265"/>
+      <c r="F20" s="265"/>
+      <c r="G20" s="266"/>
+      <c r="H20" s="267"/>
+      <c r="I20" s="268"/>
+      <c r="J20" s="269"/>
+      <c r="K20" s="270"/>
     </row>
     <row r="21" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="512"/>
-      <c r="B21" s="513"/>
-      <c r="C21" s="513"/>
-      <c r="D21" s="514"/>
-      <c r="E21" s="713"/>
-      <c r="F21" s="713"/>
-      <c r="G21" s="714"/>
-      <c r="H21" s="715"/>
-      <c r="I21" s="719"/>
-      <c r="J21" s="720"/>
-      <c r="K21" s="721"/>
+      <c r="A21" s="529"/>
+      <c r="B21" s="530"/>
+      <c r="C21" s="530"/>
+      <c r="D21" s="531"/>
+      <c r="E21" s="265"/>
+      <c r="F21" s="265"/>
+      <c r="G21" s="266"/>
+      <c r="H21" s="267"/>
+      <c r="I21" s="268"/>
+      <c r="J21" s="269"/>
+      <c r="K21" s="270"/>
     </row>
     <row r="22" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="512"/>
-      <c r="B22" s="513"/>
-      <c r="C22" s="513"/>
-      <c r="D22" s="514"/>
-      <c r="E22" s="713"/>
-      <c r="F22" s="713"/>
-      <c r="G22" s="714"/>
-      <c r="H22" s="715"/>
-      <c r="I22" s="719"/>
-      <c r="J22" s="720"/>
-      <c r="K22" s="721"/>
+      <c r="A22" s="529"/>
+      <c r="B22" s="530"/>
+      <c r="C22" s="530"/>
+      <c r="D22" s="531"/>
+      <c r="E22" s="265"/>
+      <c r="F22" s="265"/>
+      <c r="G22" s="266"/>
+      <c r="H22" s="267"/>
+      <c r="I22" s="268"/>
+      <c r="J22" s="269"/>
+      <c r="K22" s="270"/>
     </row>
     <row r="23" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="512"/>
-      <c r="B23" s="513"/>
-      <c r="C23" s="513"/>
-      <c r="D23" s="514"/>
-      <c r="E23" s="713"/>
-      <c r="F23" s="713"/>
-      <c r="G23" s="714"/>
-      <c r="H23" s="715"/>
-      <c r="I23" s="719"/>
-      <c r="J23" s="720"/>
-      <c r="K23" s="721"/>
+      <c r="A23" s="529"/>
+      <c r="B23" s="530"/>
+      <c r="C23" s="530"/>
+      <c r="D23" s="531"/>
+      <c r="E23" s="265"/>
+      <c r="F23" s="265"/>
+      <c r="G23" s="266"/>
+      <c r="H23" s="267"/>
+      <c r="I23" s="268"/>
+      <c r="J23" s="269"/>
+      <c r="K23" s="270"/>
     </row>
     <row r="24" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="512"/>
-      <c r="B24" s="513"/>
-      <c r="C24" s="513"/>
-      <c r="D24" s="514"/>
-      <c r="E24" s="713"/>
-      <c r="F24" s="713"/>
-      <c r="G24" s="714"/>
-      <c r="H24" s="715"/>
-      <c r="I24" s="719"/>
-      <c r="J24" s="720"/>
-      <c r="K24" s="721"/>
+      <c r="A24" s="529"/>
+      <c r="B24" s="530"/>
+      <c r="C24" s="530"/>
+      <c r="D24" s="531"/>
+      <c r="E24" s="265"/>
+      <c r="F24" s="265"/>
+      <c r="G24" s="266"/>
+      <c r="H24" s="267"/>
+      <c r="I24" s="268"/>
+      <c r="J24" s="269"/>
+      <c r="K24" s="270"/>
     </row>
     <row r="25" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="512"/>
-      <c r="B25" s="513"/>
-      <c r="C25" s="513"/>
-      <c r="D25" s="514"/>
-      <c r="E25" s="713"/>
-      <c r="F25" s="713"/>
-      <c r="G25" s="714"/>
-      <c r="H25" s="715"/>
-      <c r="I25" s="719"/>
-      <c r="J25" s="720"/>
-      <c r="K25" s="721"/>
+      <c r="A25" s="529"/>
+      <c r="B25" s="530"/>
+      <c r="C25" s="530"/>
+      <c r="D25" s="531"/>
+      <c r="E25" s="265"/>
+      <c r="F25" s="265"/>
+      <c r="G25" s="266"/>
+      <c r="H25" s="267"/>
+      <c r="I25" s="268"/>
+      <c r="J25" s="269"/>
+      <c r="K25" s="270"/>
     </row>
     <row r="26" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="512"/>
-      <c r="B26" s="513"/>
-      <c r="C26" s="513"/>
-      <c r="D26" s="514"/>
-      <c r="E26" s="713"/>
-      <c r="F26" s="713"/>
-      <c r="G26" s="714"/>
-      <c r="H26" s="715"/>
-      <c r="I26" s="716"/>
-      <c r="J26" s="717"/>
-      <c r="K26" s="718"/>
+      <c r="A26" s="529"/>
+      <c r="B26" s="530"/>
+      <c r="C26" s="530"/>
+      <c r="D26" s="531"/>
+      <c r="E26" s="265"/>
+      <c r="F26" s="265"/>
+      <c r="G26" s="266"/>
+      <c r="H26" s="267"/>
+      <c r="I26" s="533"/>
+      <c r="J26" s="534"/>
+      <c r="K26" s="535"/>
     </row>
     <row r="27" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="512"/>
-      <c r="B27" s="513"/>
-      <c r="C27" s="513"/>
-      <c r="D27" s="514"/>
-      <c r="E27" s="713"/>
-      <c r="F27" s="713"/>
-      <c r="G27" s="714"/>
-      <c r="H27" s="715"/>
-      <c r="I27" s="716"/>
-      <c r="J27" s="717"/>
-      <c r="K27" s="718"/>
+      <c r="A27" s="529"/>
+      <c r="B27" s="530"/>
+      <c r="C27" s="530"/>
+      <c r="D27" s="531"/>
+      <c r="E27" s="265"/>
+      <c r="F27" s="265"/>
+      <c r="G27" s="266"/>
+      <c r="H27" s="267"/>
+      <c r="I27" s="533"/>
+      <c r="J27" s="534"/>
+      <c r="K27" s="535"/>
     </row>
     <row r="28" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="512"/>
-      <c r="B28" s="513"/>
-      <c r="C28" s="513"/>
-      <c r="D28" s="514"/>
-      <c r="E28" s="713"/>
-      <c r="F28" s="713"/>
-      <c r="G28" s="714"/>
-      <c r="H28" s="715"/>
-      <c r="I28" s="716"/>
-      <c r="J28" s="717"/>
-      <c r="K28" s="718"/>
+      <c r="A28" s="529"/>
+      <c r="B28" s="530"/>
+      <c r="C28" s="530"/>
+      <c r="D28" s="531"/>
+      <c r="E28" s="265"/>
+      <c r="F28" s="265"/>
+      <c r="G28" s="266"/>
+      <c r="H28" s="267"/>
+      <c r="I28" s="533"/>
+      <c r="J28" s="534"/>
+      <c r="K28" s="535"/>
     </row>
     <row r="29" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="250"/>
       <c r="B29" s="251"/>
       <c r="C29" s="251"/>
       <c r="D29" s="252"/>
-      <c r="E29" s="713"/>
-      <c r="F29" s="713"/>
-      <c r="G29" s="714"/>
-      <c r="H29" s="715"/>
-      <c r="I29" s="719"/>
-      <c r="J29" s="720"/>
-      <c r="K29" s="721"/>
+      <c r="E29" s="265"/>
+      <c r="F29" s="265"/>
+      <c r="G29" s="266"/>
+      <c r="H29" s="267"/>
+      <c r="I29" s="268"/>
+      <c r="J29" s="269"/>
+      <c r="K29" s="270"/>
     </row>
     <row r="30" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="250"/>
       <c r="B30" s="251"/>
       <c r="C30" s="251"/>
       <c r="D30" s="252"/>
-      <c r="E30" s="713"/>
-      <c r="F30" s="713"/>
-      <c r="G30" s="714"/>
-      <c r="H30" s="715"/>
-      <c r="I30" s="719"/>
-      <c r="J30" s="720"/>
-      <c r="K30" s="721"/>
+      <c r="E30" s="265"/>
+      <c r="F30" s="265"/>
+      <c r="G30" s="266"/>
+      <c r="H30" s="267"/>
+      <c r="I30" s="268"/>
+      <c r="J30" s="269"/>
+      <c r="K30" s="270"/>
     </row>
     <row r="31" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="250"/>
       <c r="B31" s="251"/>
       <c r="C31" s="251"/>
       <c r="D31" s="252"/>
-      <c r="E31" s="713"/>
-      <c r="F31" s="713"/>
-      <c r="G31" s="714"/>
-      <c r="H31" s="715"/>
-      <c r="I31" s="719"/>
-      <c r="J31" s="720"/>
-      <c r="K31" s="721"/>
+      <c r="E31" s="265"/>
+      <c r="F31" s="265"/>
+      <c r="G31" s="266"/>
+      <c r="H31" s="267"/>
+      <c r="I31" s="268"/>
+      <c r="J31" s="269"/>
+      <c r="K31" s="270"/>
     </row>
     <row r="32" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="250"/>
       <c r="B32" s="251"/>
       <c r="C32" s="251"/>
       <c r="D32" s="252"/>
-      <c r="E32" s="713"/>
-      <c r="F32" s="713"/>
-      <c r="G32" s="714"/>
-      <c r="H32" s="715"/>
-      <c r="I32" s="719"/>
-      <c r="J32" s="720"/>
-      <c r="K32" s="721"/>
+      <c r="E32" s="265"/>
+      <c r="F32" s="265"/>
+      <c r="G32" s="266"/>
+      <c r="H32" s="267"/>
+      <c r="I32" s="268"/>
+      <c r="J32" s="269"/>
+      <c r="K32" s="270"/>
     </row>
     <row r="33" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="250"/>
       <c r="B33" s="251"/>
       <c r="C33" s="251"/>
       <c r="D33" s="252"/>
-      <c r="E33" s="713"/>
-      <c r="F33" s="713"/>
-      <c r="G33" s="714"/>
-      <c r="H33" s="715"/>
-      <c r="I33" s="719"/>
-      <c r="J33" s="720"/>
-      <c r="K33" s="721"/>
+      <c r="E33" s="265"/>
+      <c r="F33" s="265"/>
+      <c r="G33" s="266"/>
+      <c r="H33" s="267"/>
+      <c r="I33" s="268"/>
+      <c r="J33" s="269"/>
+      <c r="K33" s="270"/>
     </row>
     <row r="34" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="250"/>
       <c r="B34" s="251"/>
       <c r="C34" s="251"/>
       <c r="D34" s="252"/>
-      <c r="E34" s="713"/>
-      <c r="F34" s="713"/>
-      <c r="G34" s="714"/>
-      <c r="H34" s="715"/>
-      <c r="I34" s="719"/>
-      <c r="J34" s="720"/>
-      <c r="K34" s="721"/>
+      <c r="E34" s="265"/>
+      <c r="F34" s="265"/>
+      <c r="G34" s="266"/>
+      <c r="H34" s="267"/>
+      <c r="I34" s="268"/>
+      <c r="J34" s="269"/>
+      <c r="K34" s="270"/>
     </row>
     <row r="35" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="512"/>
-      <c r="B35" s="513"/>
-      <c r="C35" s="513"/>
-      <c r="D35" s="514"/>
-      <c r="E35" s="713"/>
-      <c r="F35" s="713"/>
-      <c r="G35" s="714"/>
-      <c r="H35" s="715"/>
-      <c r="I35" s="716"/>
-      <c r="J35" s="717"/>
-      <c r="K35" s="718"/>
+      <c r="A35" s="529"/>
+      <c r="B35" s="530"/>
+      <c r="C35" s="530"/>
+      <c r="D35" s="531"/>
+      <c r="E35" s="265"/>
+      <c r="F35" s="265"/>
+      <c r="G35" s="266"/>
+      <c r="H35" s="267"/>
+      <c r="I35" s="533"/>
+      <c r="J35" s="534"/>
+      <c r="K35" s="535"/>
     </row>
     <row r="36" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="512"/>
-      <c r="B36" s="513"/>
-      <c r="C36" s="513"/>
-      <c r="D36" s="514"/>
-      <c r="E36" s="713"/>
-      <c r="F36" s="713"/>
-      <c r="G36" s="714"/>
-      <c r="H36" s="715"/>
-      <c r="I36" s="716"/>
-      <c r="J36" s="717"/>
-      <c r="K36" s="718"/>
+      <c r="A36" s="529"/>
+      <c r="B36" s="530"/>
+      <c r="C36" s="530"/>
+      <c r="D36" s="531"/>
+      <c r="E36" s="265"/>
+      <c r="F36" s="265"/>
+      <c r="G36" s="266"/>
+      <c r="H36" s="267"/>
+      <c r="I36" s="533"/>
+      <c r="J36" s="534"/>
+      <c r="K36" s="535"/>
     </row>
     <row r="37" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="512"/>
-      <c r="B37" s="513"/>
-      <c r="C37" s="513"/>
-      <c r="D37" s="514"/>
-      <c r="E37" s="713"/>
-      <c r="F37" s="713"/>
-      <c r="G37" s="714"/>
-      <c r="H37" s="715"/>
-      <c r="I37" s="716"/>
-      <c r="J37" s="717"/>
-      <c r="K37" s="718"/>
+      <c r="A37" s="529"/>
+      <c r="B37" s="530"/>
+      <c r="C37" s="530"/>
+      <c r="D37" s="531"/>
+      <c r="E37" s="265"/>
+      <c r="F37" s="265"/>
+      <c r="G37" s="266"/>
+      <c r="H37" s="267"/>
+      <c r="I37" s="533"/>
+      <c r="J37" s="534"/>
+      <c r="K37" s="535"/>
     </row>
     <row r="38" spans="1:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="722"/>
-      <c r="B38" s="723"/>
-      <c r="C38" s="723"/>
-      <c r="D38" s="724"/>
-      <c r="E38" s="713"/>
-      <c r="F38" s="713"/>
-      <c r="G38" s="725"/>
-      <c r="H38" s="726"/>
-      <c r="I38" s="727"/>
-      <c r="J38" s="728"/>
-      <c r="K38" s="729"/>
+      <c r="A38" s="536"/>
+      <c r="B38" s="537"/>
+      <c r="C38" s="537"/>
+      <c r="D38" s="538"/>
+      <c r="E38" s="265"/>
+      <c r="F38" s="265"/>
+      <c r="G38" s="271"/>
+      <c r="H38" s="272"/>
+      <c r="I38" s="539"/>
+      <c r="J38" s="540"/>
+      <c r="K38" s="541"/>
     </row>
     <row r="39" spans="1:11" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="257" t="s">
+      <c r="A39" s="450" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="258"/>
-      <c r="C39" s="258"/>
-      <c r="D39" s="258"/>
-      <c r="E39" s="258"/>
-      <c r="F39" s="258"/>
-      <c r="G39" s="258"/>
-      <c r="H39" s="258"/>
-      <c r="I39" s="258"/>
-      <c r="J39" s="258"/>
-      <c r="K39" s="259"/>
+      <c r="B39" s="451"/>
+      <c r="C39" s="451"/>
+      <c r="D39" s="451"/>
+      <c r="E39" s="451"/>
+      <c r="F39" s="451"/>
+      <c r="G39" s="451"/>
+      <c r="H39" s="451"/>
+      <c r="I39" s="451"/>
+      <c r="J39" s="451"/>
+      <c r="K39" s="452"/>
     </row>
     <row r="40" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="515" t="s">
+      <c r="A40" s="576" t="s">
         <v>331</v>
       </c>
-      <c r="B40" s="516"/>
-      <c r="C40" s="516"/>
-      <c r="D40" s="516"/>
-      <c r="E40" s="516"/>
-      <c r="F40" s="516"/>
-      <c r="G40" s="516"/>
-      <c r="H40" s="516"/>
-      <c r="I40" s="516"/>
-      <c r="J40" s="516"/>
-      <c r="K40" s="517"/>
+      <c r="B40" s="577"/>
+      <c r="C40" s="577"/>
+      <c r="D40" s="577"/>
+      <c r="E40" s="577"/>
+      <c r="F40" s="577"/>
+      <c r="G40" s="577"/>
+      <c r="H40" s="577"/>
+      <c r="I40" s="577"/>
+      <c r="J40" s="577"/>
+      <c r="K40" s="578"/>
     </row>
     <row r="41" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="124" t="s">
@@ -17167,143 +17167,143 @@
       <c r="C41" s="125" t="s">
         <v>334</v>
       </c>
-      <c r="D41" s="504" t="s">
+      <c r="D41" s="582" t="s">
         <v>335</v>
       </c>
-      <c r="E41" s="504"/>
-      <c r="F41" s="504"/>
-      <c r="G41" s="504"/>
-      <c r="H41" s="505"/>
+      <c r="E41" s="582"/>
+      <c r="F41" s="582"/>
+      <c r="G41" s="582"/>
+      <c r="H41" s="583"/>
       <c r="I41" s="125" t="s">
         <v>336</v>
       </c>
-      <c r="J41" s="504" t="s">
+      <c r="J41" s="582" t="s">
         <v>337</v>
       </c>
-      <c r="K41" s="342"/>
+      <c r="K41" s="387"/>
     </row>
     <row r="42" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="474"/>
-      <c r="B42" s="476"/>
-      <c r="C42" s="502"/>
-      <c r="D42" s="475"/>
-      <c r="E42" s="475"/>
-      <c r="F42" s="475"/>
-      <c r="G42" s="475"/>
-      <c r="H42" s="476"/>
-      <c r="I42" s="502"/>
-      <c r="J42" s="475"/>
-      <c r="K42" s="503"/>
+      <c r="A42" s="520"/>
+      <c r="B42" s="522"/>
+      <c r="C42" s="575"/>
+      <c r="D42" s="521"/>
+      <c r="E42" s="521"/>
+      <c r="F42" s="521"/>
+      <c r="G42" s="521"/>
+      <c r="H42" s="522"/>
+      <c r="I42" s="575"/>
+      <c r="J42" s="521"/>
+      <c r="K42" s="584"/>
     </row>
     <row r="43" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="474"/>
-      <c r="B43" s="476"/>
-      <c r="C43" s="502"/>
-      <c r="D43" s="475"/>
-      <c r="E43" s="475"/>
-      <c r="F43" s="475"/>
-      <c r="G43" s="475"/>
-      <c r="H43" s="476"/>
-      <c r="I43" s="502"/>
-      <c r="J43" s="475"/>
-      <c r="K43" s="503"/>
+      <c r="A43" s="520"/>
+      <c r="B43" s="522"/>
+      <c r="C43" s="575"/>
+      <c r="D43" s="521"/>
+      <c r="E43" s="521"/>
+      <c r="F43" s="521"/>
+      <c r="G43" s="521"/>
+      <c r="H43" s="522"/>
+      <c r="I43" s="575"/>
+      <c r="J43" s="521"/>
+      <c r="K43" s="584"/>
     </row>
     <row r="44" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="474"/>
-      <c r="B44" s="476"/>
-      <c r="C44" s="502"/>
-      <c r="D44" s="475"/>
-      <c r="E44" s="475"/>
-      <c r="F44" s="475"/>
-      <c r="G44" s="475"/>
-      <c r="H44" s="476"/>
-      <c r="I44" s="502"/>
-      <c r="J44" s="475"/>
-      <c r="K44" s="503"/>
+      <c r="A44" s="520"/>
+      <c r="B44" s="522"/>
+      <c r="C44" s="575"/>
+      <c r="D44" s="521"/>
+      <c r="E44" s="521"/>
+      <c r="F44" s="521"/>
+      <c r="G44" s="521"/>
+      <c r="H44" s="522"/>
+      <c r="I44" s="575"/>
+      <c r="J44" s="521"/>
+      <c r="K44" s="584"/>
     </row>
     <row r="45" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="474"/>
-      <c r="B45" s="476"/>
-      <c r="C45" s="502"/>
-      <c r="D45" s="475"/>
-      <c r="E45" s="475"/>
-      <c r="F45" s="475"/>
-      <c r="G45" s="475"/>
-      <c r="H45" s="476"/>
-      <c r="I45" s="502"/>
-      <c r="J45" s="475"/>
-      <c r="K45" s="503"/>
+      <c r="A45" s="520"/>
+      <c r="B45" s="522"/>
+      <c r="C45" s="575"/>
+      <c r="D45" s="521"/>
+      <c r="E45" s="521"/>
+      <c r="F45" s="521"/>
+      <c r="G45" s="521"/>
+      <c r="H45" s="522"/>
+      <c r="I45" s="575"/>
+      <c r="J45" s="521"/>
+      <c r="K45" s="584"/>
     </row>
     <row r="46" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="474"/>
-      <c r="B46" s="476"/>
-      <c r="C46" s="502"/>
-      <c r="D46" s="475"/>
-      <c r="E46" s="475"/>
-      <c r="F46" s="475"/>
-      <c r="G46" s="475"/>
-      <c r="H46" s="476"/>
-      <c r="I46" s="502"/>
-      <c r="J46" s="475"/>
-      <c r="K46" s="503"/>
+      <c r="A46" s="520"/>
+      <c r="B46" s="522"/>
+      <c r="C46" s="575"/>
+      <c r="D46" s="521"/>
+      <c r="E46" s="521"/>
+      <c r="F46" s="521"/>
+      <c r="G46" s="521"/>
+      <c r="H46" s="522"/>
+      <c r="I46" s="575"/>
+      <c r="J46" s="521"/>
+      <c r="K46" s="584"/>
     </row>
     <row r="47" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="474"/>
-      <c r="B47" s="476"/>
-      <c r="C47" s="502"/>
-      <c r="D47" s="475"/>
-      <c r="E47" s="475"/>
-      <c r="F47" s="475"/>
-      <c r="G47" s="475"/>
-      <c r="H47" s="476"/>
-      <c r="I47" s="502"/>
-      <c r="J47" s="475"/>
-      <c r="K47" s="503"/>
+      <c r="A47" s="520"/>
+      <c r="B47" s="522"/>
+      <c r="C47" s="575"/>
+      <c r="D47" s="521"/>
+      <c r="E47" s="521"/>
+      <c r="F47" s="521"/>
+      <c r="G47" s="521"/>
+      <c r="H47" s="522"/>
+      <c r="I47" s="575"/>
+      <c r="J47" s="521"/>
+      <c r="K47" s="584"/>
     </row>
     <row r="48" spans="1:11" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="474"/>
-      <c r="B48" s="476"/>
-      <c r="C48" s="502"/>
-      <c r="D48" s="475"/>
-      <c r="E48" s="475"/>
-      <c r="F48" s="475"/>
-      <c r="G48" s="475"/>
-      <c r="H48" s="476"/>
-      <c r="I48" s="502"/>
-      <c r="J48" s="475"/>
-      <c r="K48" s="503"/>
+      <c r="A48" s="520"/>
+      <c r="B48" s="522"/>
+      <c r="C48" s="575"/>
+      <c r="D48" s="521"/>
+      <c r="E48" s="521"/>
+      <c r="F48" s="521"/>
+      <c r="G48" s="521"/>
+      <c r="H48" s="522"/>
+      <c r="I48" s="575"/>
+      <c r="J48" s="521"/>
+      <c r="K48" s="584"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="257" t="s">
+      <c r="A49" s="450" t="s">
         <v>114</v>
       </c>
-      <c r="B49" s="258"/>
-      <c r="C49" s="258"/>
-      <c r="D49" s="258"/>
-      <c r="E49" s="258"/>
-      <c r="F49" s="258"/>
-      <c r="G49" s="258"/>
-      <c r="H49" s="258"/>
-      <c r="I49" s="258"/>
-      <c r="J49" s="258"/>
-      <c r="K49" s="484"/>
+      <c r="B49" s="451"/>
+      <c r="C49" s="451"/>
+      <c r="D49" s="451"/>
+      <c r="E49" s="451"/>
+      <c r="F49" s="451"/>
+      <c r="G49" s="451"/>
+      <c r="H49" s="451"/>
+      <c r="I49" s="451"/>
+      <c r="J49" s="451"/>
+      <c r="K49" s="494"/>
     </row>
     <row r="50" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="254" t="s">
+      <c r="A50" s="447" t="s">
         <v>143</v>
       </c>
-      <c r="B50" s="256"/>
-      <c r="C50" s="477"/>
-      <c r="D50" s="497"/>
-      <c r="E50" s="497"/>
-      <c r="F50" s="498"/>
-      <c r="G50" s="495" t="s">
+      <c r="B50" s="449"/>
+      <c r="C50" s="484"/>
+      <c r="D50" s="587"/>
+      <c r="E50" s="587"/>
+      <c r="F50" s="588"/>
+      <c r="G50" s="585" t="s">
         <v>144</v>
       </c>
-      <c r="H50" s="496"/>
-      <c r="I50" s="499"/>
-      <c r="J50" s="500"/>
-      <c r="K50" s="501"/>
+      <c r="H50" s="586"/>
+      <c r="I50" s="589"/>
+      <c r="J50" s="590"/>
+      <c r="K50" s="591"/>
       <c r="L50" s="224"/>
       <c r="M50" s="224"/>
     </row>
@@ -17324,6 +17324,73 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="83">
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:H46"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="C48:H48"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="C47:H47"/>
+    <mergeCell ref="C45:H45"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B15:D17"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="H3:K5"/>
+    <mergeCell ref="E3:F4"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I15:K17"/>
+    <mergeCell ref="E15:F16"/>
+    <mergeCell ref="B5:D5"/>
     <mergeCell ref="A39:K39"/>
     <mergeCell ref="H12:K12"/>
     <mergeCell ref="A14:K14"/>
@@ -17340,73 +17407,6 @@
     <mergeCell ref="I38:K38"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B15:D17"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="H3:K5"/>
-    <mergeCell ref="E3:F4"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I15:K17"/>
-    <mergeCell ref="E15:F16"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="C48:H48"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:H43"/>
-    <mergeCell ref="C47:H47"/>
-    <mergeCell ref="C45:H45"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="C50:F50"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="A49:K49"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="C44:H44"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C46:H46"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="I47:K47"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -17439,35 +17439,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="663"/>
-      <c r="B1" s="664"/>
-      <c r="C1" s="664"/>
-      <c r="D1" s="664"/>
-      <c r="E1" s="664"/>
-      <c r="F1" s="664"/>
-      <c r="G1" s="664"/>
-      <c r="H1" s="664"/>
-      <c r="I1" s="664"/>
-      <c r="J1" s="664"/>
-      <c r="K1" s="664"/>
-      <c r="L1" s="664"/>
-      <c r="M1" s="665"/>
+      <c r="A1" s="603"/>
+      <c r="B1" s="604"/>
+      <c r="C1" s="604"/>
+      <c r="D1" s="604"/>
+      <c r="E1" s="604"/>
+      <c r="F1" s="604"/>
+      <c r="G1" s="604"/>
+      <c r="H1" s="604"/>
+      <c r="I1" s="604"/>
+      <c r="J1" s="604"/>
+      <c r="K1" s="604"/>
+      <c r="L1" s="604"/>
+      <c r="M1" s="605"/>
     </row>
     <row r="2" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="641" t="s">
+      <c r="A2" s="627" t="s">
         <v>338</v>
       </c>
-      <c r="B2" s="642"/>
-      <c r="C2" s="668" t="s">
+      <c r="B2" s="628"/>
+      <c r="C2" s="608" t="s">
         <v>339</v>
       </c>
-      <c r="D2" s="668"/>
-      <c r="E2" s="668"/>
-      <c r="F2" s="669"/>
+      <c r="D2" s="608"/>
+      <c r="E2" s="608"/>
+      <c r="F2" s="609"/>
       <c r="G2" s="19"/>
       <c r="H2" s="19"/>
-      <c r="I2" s="666"/>
-      <c r="J2" s="666"/>
+      <c r="I2" s="606"/>
+      <c r="J2" s="606"/>
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
       <c r="M2" s="21"/>
@@ -17475,16 +17475,16 @@
     <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22"/>
       <c r="B3" s="23"/>
-      <c r="C3" s="657" t="s">
+      <c r="C3" s="612" t="s">
         <v>340</v>
       </c>
-      <c r="D3" s="657"/>
-      <c r="E3" s="657"/>
-      <c r="F3" s="658"/>
+      <c r="D3" s="612"/>
+      <c r="E3" s="612"/>
+      <c r="F3" s="613"/>
       <c r="G3" s="24"/>
       <c r="H3" s="24"/>
-      <c r="I3" s="667"/>
-      <c r="J3" s="667"/>
+      <c r="I3" s="607"/>
+      <c r="J3" s="607"/>
       <c r="K3" s="25"/>
       <c r="L3" s="25"/>
       <c r="M3" s="26"/>
@@ -17492,42 +17492,42 @@
     <row r="4" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
-      <c r="C4" s="657" t="s">
+      <c r="C4" s="612" t="s">
         <v>341</v>
       </c>
-      <c r="D4" s="657"/>
-      <c r="E4" s="657"/>
-      <c r="F4" s="658"/>
+      <c r="D4" s="612"/>
+      <c r="E4" s="612"/>
+      <c r="F4" s="613"/>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22"/>
       <c r="B5" s="23"/>
-      <c r="C5" s="657"/>
-      <c r="D5" s="657"/>
-      <c r="E5" s="657"/>
-      <c r="F5" s="658"/>
-      <c r="G5" s="574"/>
-      <c r="H5" s="574"/>
-      <c r="I5" s="574"/>
-      <c r="J5" s="574"/>
-      <c r="K5" s="574"/>
-      <c r="L5" s="574"/>
+      <c r="C5" s="612"/>
+      <c r="D5" s="612"/>
+      <c r="E5" s="612"/>
+      <c r="F5" s="613"/>
+      <c r="G5" s="601"/>
+      <c r="H5" s="601"/>
+      <c r="I5" s="601"/>
+      <c r="J5" s="601"/>
+      <c r="K5" s="601"/>
+      <c r="L5" s="601"/>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="22"/>
       <c r="B6" s="23"/>
-      <c r="C6" s="657" t="s">
+      <c r="C6" s="612" t="s">
         <v>342</v>
       </c>
-      <c r="D6" s="657"/>
-      <c r="E6" s="657"/>
-      <c r="F6" s="658"/>
-      <c r="I6" s="662"/>
-      <c r="J6" s="662"/>
-      <c r="K6" s="662"/>
-      <c r="L6" s="662"/>
+      <c r="D6" s="612"/>
+      <c r="E6" s="612"/>
+      <c r="F6" s="613"/>
+      <c r="I6" s="632"/>
+      <c r="J6" s="632"/>
+      <c r="K6" s="632"/>
+      <c r="L6" s="632"/>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -17546,12 +17546,12 @@
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="22"/>
       <c r="B8" s="23"/>
-      <c r="C8" s="657" t="s">
+      <c r="C8" s="612" t="s">
         <v>343</v>
       </c>
-      <c r="D8" s="657"/>
-      <c r="E8" s="657"/>
-      <c r="F8" s="658"/>
+      <c r="D8" s="612"/>
+      <c r="E8" s="612"/>
+      <c r="F8" s="613"/>
       <c r="M8" s="27"/>
     </row>
     <row r="9" spans="1:13" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -17566,61 +17566,61 @@
     <row r="10" spans="1:13" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="22"/>
       <c r="B10" s="23"/>
-      <c r="C10" s="657"/>
-      <c r="D10" s="657"/>
-      <c r="E10" s="657"/>
-      <c r="F10" s="658"/>
-      <c r="G10" s="574" t="s">
+      <c r="C10" s="612"/>
+      <c r="D10" s="612"/>
+      <c r="E10" s="612"/>
+      <c r="F10" s="613"/>
+      <c r="G10" s="601" t="s">
         <v>344</v>
       </c>
-      <c r="H10" s="574"/>
-      <c r="I10" s="574"/>
-      <c r="J10" s="574"/>
-      <c r="K10" s="574"/>
-      <c r="L10" s="574"/>
+      <c r="H10" s="601"/>
+      <c r="I10" s="601"/>
+      <c r="J10" s="601"/>
+      <c r="K10" s="601"/>
+      <c r="L10" s="601"/>
       <c r="M10" s="74"/>
     </row>
     <row r="11" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22"/>
       <c r="B11" s="23"/>
-      <c r="C11" s="657"/>
-      <c r="D11" s="657"/>
-      <c r="E11" s="657"/>
-      <c r="F11" s="658"/>
+      <c r="C11" s="612"/>
+      <c r="D11" s="612"/>
+      <c r="E11" s="612"/>
+      <c r="F11" s="613"/>
       <c r="G11" s="132"/>
-      <c r="H11" s="685"/>
-      <c r="I11" s="685"/>
-      <c r="J11" s="685"/>
-      <c r="K11" s="685"/>
-      <c r="L11" s="685"/>
+      <c r="H11" s="633"/>
+      <c r="I11" s="633"/>
+      <c r="J11" s="633"/>
+      <c r="K11" s="633"/>
+      <c r="L11" s="633"/>
       <c r="M11" s="74"/>
     </row>
     <row r="12" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28"/>
       <c r="B12" s="29"/>
-      <c r="C12" s="659"/>
-      <c r="D12" s="659"/>
-      <c r="E12" s="659"/>
-      <c r="F12" s="660"/>
+      <c r="C12" s="629"/>
+      <c r="D12" s="629"/>
+      <c r="E12" s="629"/>
+      <c r="F12" s="630"/>
       <c r="G12" s="133"/>
       <c r="H12" s="133"/>
-      <c r="I12" s="661"/>
-      <c r="J12" s="661"/>
-      <c r="K12" s="661"/>
-      <c r="L12" s="661"/>
+      <c r="I12" s="631"/>
+      <c r="J12" s="631"/>
+      <c r="K12" s="631"/>
+      <c r="L12" s="631"/>
       <c r="M12" s="112"/>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="680" t="s">
+      <c r="A13" s="597" t="s">
         <v>345</v>
       </c>
-      <c r="B13" s="681"/>
-      <c r="C13" s="676" t="s">
+      <c r="B13" s="598"/>
+      <c r="C13" s="599" t="s">
         <v>346</v>
       </c>
-      <c r="D13" s="676"/>
-      <c r="E13" s="521"/>
-      <c r="F13" s="522"/>
+      <c r="D13" s="599"/>
+      <c r="E13" s="546"/>
+      <c r="F13" s="547"/>
       <c r="G13" s="30"/>
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
@@ -17632,48 +17632,48 @@
     <row r="14" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="45"/>
       <c r="B14" s="46"/>
-      <c r="C14" s="676"/>
-      <c r="D14" s="676"/>
-      <c r="E14" s="521"/>
-      <c r="F14" s="522"/>
-      <c r="G14" s="573" t="s">
+      <c r="C14" s="599"/>
+      <c r="D14" s="599"/>
+      <c r="E14" s="546"/>
+      <c r="F14" s="547"/>
+      <c r="G14" s="600" t="s">
         <v>344</v>
       </c>
-      <c r="H14" s="574"/>
-      <c r="I14" s="574"/>
-      <c r="J14" s="574"/>
-      <c r="K14" s="574"/>
-      <c r="L14" s="574"/>
+      <c r="H14" s="601"/>
+      <c r="I14" s="601"/>
+      <c r="J14" s="601"/>
+      <c r="K14" s="601"/>
+      <c r="L14" s="601"/>
       <c r="M14" s="111"/>
     </row>
     <row r="15" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="45"/>
       <c r="B15" s="46"/>
-      <c r="C15" s="676"/>
-      <c r="D15" s="676"/>
-      <c r="E15" s="521"/>
-      <c r="F15" s="522"/>
+      <c r="C15" s="599"/>
+      <c r="D15" s="599"/>
+      <c r="E15" s="546"/>
+      <c r="F15" s="547"/>
       <c r="G15" s="24"/>
-      <c r="H15" s="686"/>
-      <c r="I15" s="686"/>
-      <c r="J15" s="686"/>
-      <c r="K15" s="686"/>
-      <c r="L15" s="686"/>
+      <c r="H15" s="595"/>
+      <c r="I15" s="595"/>
+      <c r="J15" s="595"/>
+      <c r="K15" s="595"/>
+      <c r="L15" s="595"/>
       <c r="M15" s="111"/>
     </row>
     <row r="16" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32"/>
       <c r="B16" s="33"/>
-      <c r="C16" s="521"/>
-      <c r="D16" s="521"/>
-      <c r="E16" s="521"/>
-      <c r="F16" s="522"/>
+      <c r="C16" s="546"/>
+      <c r="D16" s="546"/>
+      <c r="E16" s="546"/>
+      <c r="F16" s="547"/>
       <c r="G16" s="108"/>
       <c r="H16" s="229"/>
-      <c r="I16" s="673"/>
-      <c r="J16" s="673"/>
-      <c r="K16" s="673"/>
-      <c r="L16" s="673"/>
+      <c r="I16" s="602"/>
+      <c r="J16" s="602"/>
+      <c r="K16" s="602"/>
+      <c r="L16" s="602"/>
       <c r="M16" s="109"/>
     </row>
     <row r="17" spans="1:13" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -17694,12 +17694,12 @@
     <row r="18" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="34"/>
       <c r="B18" s="35"/>
-      <c r="C18" s="576" t="s">
+      <c r="C18" s="724" t="s">
         <v>347</v>
       </c>
-      <c r="D18" s="576"/>
-      <c r="E18" s="577"/>
-      <c r="F18" s="578"/>
+      <c r="D18" s="724"/>
+      <c r="E18" s="725"/>
+      <c r="F18" s="726"/>
       <c r="G18" s="39"/>
       <c r="H18" s="39"/>
       <c r="I18" s="39"/>
@@ -17711,82 +17711,82 @@
     <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34"/>
       <c r="B19" s="35"/>
-      <c r="C19" s="576"/>
-      <c r="D19" s="576"/>
-      <c r="E19" s="577"/>
-      <c r="F19" s="578"/>
-      <c r="G19" s="573" t="s">
+      <c r="C19" s="724"/>
+      <c r="D19" s="724"/>
+      <c r="E19" s="725"/>
+      <c r="F19" s="726"/>
+      <c r="G19" s="600" t="s">
         <v>344</v>
       </c>
-      <c r="H19" s="574"/>
-      <c r="I19" s="574"/>
-      <c r="J19" s="574"/>
-      <c r="K19" s="574"/>
-      <c r="L19" s="574"/>
+      <c r="H19" s="601"/>
+      <c r="I19" s="601"/>
+      <c r="J19" s="601"/>
+      <c r="K19" s="601"/>
+      <c r="L19" s="601"/>
       <c r="M19" s="40"/>
     </row>
     <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="34"/>
       <c r="B20" s="35"/>
-      <c r="C20" s="576"/>
-      <c r="D20" s="576"/>
-      <c r="E20" s="577"/>
-      <c r="F20" s="578"/>
+      <c r="C20" s="724"/>
+      <c r="D20" s="724"/>
+      <c r="E20" s="725"/>
+      <c r="F20" s="726"/>
       <c r="G20" s="39"/>
-      <c r="H20" s="549" t="s">
+      <c r="H20" s="702" t="s">
         <v>348</v>
       </c>
-      <c r="I20" s="549"/>
+      <c r="I20" s="702"/>
       <c r="J20" s="239"/>
-      <c r="K20" s="683"/>
-      <c r="L20" s="683"/>
+      <c r="K20" s="593"/>
+      <c r="L20" s="593"/>
       <c r="M20" s="40"/>
     </row>
     <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34"/>
       <c r="B21" s="35"/>
-      <c r="C21" s="576"/>
-      <c r="D21" s="576"/>
-      <c r="E21" s="577"/>
-      <c r="F21" s="578"/>
-      <c r="G21" s="550" t="s">
+      <c r="C21" s="724"/>
+      <c r="D21" s="724"/>
+      <c r="E21" s="725"/>
+      <c r="F21" s="726"/>
+      <c r="G21" s="703" t="s">
         <v>349</v>
       </c>
-      <c r="H21" s="551"/>
-      <c r="I21" s="551"/>
+      <c r="H21" s="704"/>
+      <c r="I21" s="704"/>
       <c r="J21" s="239"/>
-      <c r="K21" s="684"/>
-      <c r="L21" s="684"/>
+      <c r="K21" s="594"/>
+      <c r="L21" s="594"/>
       <c r="M21" s="40"/>
     </row>
     <row r="22" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41"/>
       <c r="B22" s="42"/>
-      <c r="C22" s="579"/>
-      <c r="D22" s="579"/>
-      <c r="E22" s="579"/>
-      <c r="F22" s="580"/>
+      <c r="C22" s="727"/>
+      <c r="D22" s="727"/>
+      <c r="E22" s="727"/>
+      <c r="F22" s="728"/>
       <c r="G22" s="108" t="s">
         <v>350</v>
       </c>
       <c r="H22" s="229"/>
-      <c r="I22" s="581"/>
-      <c r="J22" s="581"/>
-      <c r="K22" s="581"/>
+      <c r="I22" s="729"/>
+      <c r="J22" s="729"/>
+      <c r="K22" s="729"/>
       <c r="L22" s="113"/>
       <c r="M22" s="109"/>
     </row>
     <row r="23" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="569" t="s">
+      <c r="A23" s="634" t="s">
         <v>351</v>
       </c>
-      <c r="B23" s="570"/>
-      <c r="C23" s="582" t="s">
+      <c r="B23" s="635"/>
+      <c r="C23" s="623" t="s">
         <v>352</v>
       </c>
-      <c r="D23" s="582"/>
-      <c r="E23" s="582"/>
-      <c r="F23" s="583"/>
+      <c r="D23" s="623"/>
+      <c r="E23" s="623"/>
+      <c r="F23" s="624"/>
       <c r="G23" s="30"/>
       <c r="H23" s="30"/>
       <c r="I23" s="30"/>
@@ -17798,61 +17798,61 @@
     <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="32"/>
       <c r="B24" s="33"/>
-      <c r="C24" s="584"/>
-      <c r="D24" s="584"/>
-      <c r="E24" s="584"/>
-      <c r="F24" s="585"/>
-      <c r="G24" s="573" t="s">
+      <c r="C24" s="615"/>
+      <c r="D24" s="615"/>
+      <c r="E24" s="615"/>
+      <c r="F24" s="614"/>
+      <c r="G24" s="600" t="s">
         <v>344</v>
       </c>
-      <c r="H24" s="574"/>
-      <c r="I24" s="574"/>
-      <c r="J24" s="574"/>
-      <c r="K24" s="574"/>
-      <c r="L24" s="574"/>
+      <c r="H24" s="601"/>
+      <c r="I24" s="601"/>
+      <c r="J24" s="601"/>
+      <c r="K24" s="601"/>
+      <c r="L24" s="601"/>
       <c r="M24" s="107"/>
     </row>
     <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="32"/>
       <c r="B25" s="33"/>
-      <c r="C25" s="584"/>
-      <c r="D25" s="584"/>
-      <c r="E25" s="584"/>
-      <c r="F25" s="585"/>
+      <c r="C25" s="615"/>
+      <c r="D25" s="615"/>
+      <c r="E25" s="615"/>
+      <c r="F25" s="614"/>
       <c r="G25" s="106"/>
-      <c r="H25" s="687"/>
-      <c r="I25" s="687"/>
-      <c r="J25" s="687"/>
-      <c r="K25" s="687"/>
-      <c r="L25" s="687"/>
+      <c r="H25" s="592"/>
+      <c r="I25" s="592"/>
+      <c r="J25" s="592"/>
+      <c r="K25" s="592"/>
+      <c r="L25" s="592"/>
       <c r="M25" s="107"/>
     </row>
     <row r="26" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="43"/>
       <c r="B26" s="44"/>
-      <c r="C26" s="586"/>
-      <c r="D26" s="586"/>
-      <c r="E26" s="586"/>
-      <c r="F26" s="587"/>
+      <c r="C26" s="625"/>
+      <c r="D26" s="625"/>
+      <c r="E26" s="625"/>
+      <c r="F26" s="626"/>
       <c r="G26" s="108"/>
       <c r="H26" s="229"/>
-      <c r="I26" s="673"/>
-      <c r="J26" s="673"/>
-      <c r="K26" s="673"/>
-      <c r="L26" s="673"/>
+      <c r="I26" s="602"/>
+      <c r="J26" s="602"/>
+      <c r="K26" s="602"/>
+      <c r="L26" s="602"/>
       <c r="M26" s="109"/>
     </row>
     <row r="27" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="569" t="s">
+      <c r="A27" s="634" t="s">
         <v>353</v>
       </c>
-      <c r="B27" s="570"/>
-      <c r="C27" s="582" t="s">
+      <c r="B27" s="635"/>
+      <c r="C27" s="623" t="s">
         <v>354</v>
       </c>
-      <c r="D27" s="582"/>
-      <c r="E27" s="582"/>
-      <c r="F27" s="583"/>
+      <c r="D27" s="623"/>
+      <c r="E27" s="623"/>
+      <c r="F27" s="624"/>
       <c r="G27" s="30"/>
       <c r="H27" s="30"/>
       <c r="I27" s="30"/>
@@ -17864,41 +17864,41 @@
     <row r="28" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="32"/>
       <c r="B28" s="33"/>
-      <c r="C28" s="584"/>
-      <c r="D28" s="584"/>
-      <c r="E28" s="584"/>
-      <c r="F28" s="585"/>
-      <c r="G28" s="573" t="s">
+      <c r="C28" s="615"/>
+      <c r="D28" s="615"/>
+      <c r="E28" s="615"/>
+      <c r="F28" s="614"/>
+      <c r="G28" s="600" t="s">
         <v>344</v>
       </c>
-      <c r="H28" s="574"/>
-      <c r="I28" s="574"/>
-      <c r="J28" s="574"/>
-      <c r="K28" s="574"/>
-      <c r="L28" s="574"/>
+      <c r="H28" s="601"/>
+      <c r="I28" s="601"/>
+      <c r="J28" s="601"/>
+      <c r="K28" s="601"/>
+      <c r="L28" s="601"/>
       <c r="M28" s="2"/>
     </row>
     <row r="29" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="32"/>
       <c r="B29" s="33"/>
-      <c r="C29" s="584"/>
-      <c r="D29" s="584"/>
-      <c r="E29" s="584"/>
-      <c r="F29" s="585"/>
-      <c r="H29" s="619"/>
-      <c r="I29" s="619"/>
-      <c r="J29" s="619"/>
-      <c r="K29" s="619"/>
-      <c r="L29" s="619"/>
+      <c r="C29" s="615"/>
+      <c r="D29" s="615"/>
+      <c r="E29" s="615"/>
+      <c r="F29" s="614"/>
+      <c r="H29" s="596"/>
+      <c r="I29" s="596"/>
+      <c r="J29" s="596"/>
+      <c r="K29" s="596"/>
+      <c r="L29" s="596"/>
       <c r="M29" s="107"/>
     </row>
     <row r="30" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="43"/>
       <c r="B30" s="44"/>
-      <c r="C30" s="586"/>
-      <c r="D30" s="586"/>
-      <c r="E30" s="586"/>
-      <c r="F30" s="587"/>
+      <c r="C30" s="625"/>
+      <c r="D30" s="625"/>
+      <c r="E30" s="625"/>
+      <c r="F30" s="626"/>
       <c r="G30" s="127"/>
       <c r="H30" s="231"/>
       <c r="I30" s="164"/>
@@ -17908,16 +17908,16 @@
       <c r="M30" s="109"/>
     </row>
     <row r="31" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="569" t="s">
+      <c r="A31" s="634" t="s">
         <v>355</v>
       </c>
-      <c r="B31" s="570"/>
-      <c r="C31" s="582" t="s">
+      <c r="B31" s="635"/>
+      <c r="C31" s="623" t="s">
         <v>356</v>
       </c>
-      <c r="D31" s="582"/>
-      <c r="E31" s="582"/>
-      <c r="F31" s="583"/>
+      <c r="D31" s="623"/>
+      <c r="E31" s="623"/>
+      <c r="F31" s="624"/>
       <c r="G31" s="30"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -17929,18 +17929,18 @@
     <row r="32" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="32"/>
       <c r="B32" s="33"/>
-      <c r="C32" s="584"/>
-      <c r="D32" s="584"/>
-      <c r="E32" s="584"/>
-      <c r="F32" s="585"/>
-      <c r="G32" s="620" t="s">
+      <c r="C32" s="615"/>
+      <c r="D32" s="615"/>
+      <c r="E32" s="615"/>
+      <c r="F32" s="614"/>
+      <c r="G32" s="669" t="s">
         <v>357</v>
       </c>
-      <c r="H32" s="621"/>
-      <c r="I32" s="621"/>
-      <c r="J32" s="621"/>
-      <c r="K32" s="619"/>
-      <c r="L32" s="619"/>
+      <c r="H32" s="670"/>
+      <c r="I32" s="670"/>
+      <c r="J32" s="670"/>
+      <c r="K32" s="596"/>
+      <c r="L32" s="596"/>
       <c r="M32" s="107"/>
     </row>
     <row r="33" spans="1:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17961,44 +17961,44 @@
     <row r="34" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="32"/>
       <c r="B34" s="33"/>
-      <c r="C34" s="584" t="s">
+      <c r="C34" s="615" t="s">
         <v>358</v>
       </c>
-      <c r="D34" s="584"/>
-      <c r="E34" s="584"/>
-      <c r="F34" s="585"/>
+      <c r="D34" s="615"/>
+      <c r="E34" s="615"/>
+      <c r="F34" s="614"/>
       <c r="G34" s="106"/>
       <c r="H34" s="230"/>
-      <c r="I34" s="618"/>
-      <c r="J34" s="618"/>
-      <c r="K34" s="618"/>
-      <c r="L34" s="618"/>
+      <c r="I34" s="668"/>
+      <c r="J34" s="668"/>
+      <c r="K34" s="668"/>
+      <c r="L34" s="668"/>
       <c r="M34" s="107"/>
     </row>
     <row r="35" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="32"/>
       <c r="B35" s="33"/>
-      <c r="C35" s="584"/>
-      <c r="D35" s="584"/>
-      <c r="E35" s="584"/>
-      <c r="F35" s="585"/>
-      <c r="G35" s="620" t="s">
+      <c r="C35" s="615"/>
+      <c r="D35" s="615"/>
+      <c r="E35" s="615"/>
+      <c r="F35" s="614"/>
+      <c r="G35" s="669" t="s">
         <v>357</v>
       </c>
-      <c r="H35" s="621"/>
-      <c r="I35" s="621"/>
-      <c r="J35" s="621"/>
-      <c r="K35" s="619"/>
-      <c r="L35" s="619"/>
+      <c r="H35" s="670"/>
+      <c r="I35" s="670"/>
+      <c r="J35" s="670"/>
+      <c r="K35" s="596"/>
+      <c r="L35" s="596"/>
       <c r="M35" s="107"/>
     </row>
     <row r="36" spans="1:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="43"/>
       <c r="B36" s="44"/>
-      <c r="C36" s="586"/>
-      <c r="D36" s="586"/>
-      <c r="E36" s="586"/>
-      <c r="F36" s="587"/>
+      <c r="C36" s="625"/>
+      <c r="D36" s="625"/>
+      <c r="E36" s="625"/>
+      <c r="F36" s="626"/>
       <c r="G36" s="110"/>
       <c r="H36" s="54"/>
       <c r="I36" s="101"/>
@@ -18007,16 +18007,16 @@
       <c r="M36" s="109"/>
     </row>
     <row r="37" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="569" t="s">
+      <c r="A37" s="634" t="s">
         <v>359</v>
       </c>
-      <c r="B37" s="570"/>
-      <c r="C37" s="674" t="s">
+      <c r="B37" s="635"/>
+      <c r="C37" s="618" t="s">
         <v>360</v>
       </c>
-      <c r="D37" s="674"/>
-      <c r="E37" s="674"/>
-      <c r="F37" s="675"/>
+      <c r="D37" s="618"/>
+      <c r="E37" s="618"/>
+      <c r="F37" s="619"/>
       <c r="G37" s="30"/>
       <c r="H37" s="30"/>
       <c r="I37" s="30"/>
@@ -18028,61 +18028,61 @@
     <row r="38" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="32"/>
       <c r="B38" s="33"/>
-      <c r="C38" s="676"/>
-      <c r="D38" s="676"/>
-      <c r="E38" s="676"/>
-      <c r="F38" s="677"/>
-      <c r="G38" s="573" t="s">
+      <c r="C38" s="599"/>
+      <c r="D38" s="599"/>
+      <c r="E38" s="599"/>
+      <c r="F38" s="620"/>
+      <c r="G38" s="600" t="s">
         <v>361</v>
       </c>
-      <c r="H38" s="574"/>
-      <c r="I38" s="574"/>
-      <c r="J38" s="574"/>
-      <c r="K38" s="574"/>
-      <c r="L38" s="574"/>
-      <c r="M38" s="575"/>
+      <c r="H38" s="601"/>
+      <c r="I38" s="601"/>
+      <c r="J38" s="601"/>
+      <c r="K38" s="601"/>
+      <c r="L38" s="601"/>
+      <c r="M38" s="723"/>
     </row>
     <row r="39" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="32"/>
       <c r="B39" s="33"/>
-      <c r="C39" s="676"/>
-      <c r="D39" s="676"/>
-      <c r="E39" s="676"/>
-      <c r="F39" s="677"/>
+      <c r="C39" s="599"/>
+      <c r="D39" s="599"/>
+      <c r="E39" s="599"/>
+      <c r="F39" s="620"/>
       <c r="G39" s="106"/>
-      <c r="H39" s="687"/>
-      <c r="I39" s="687"/>
-      <c r="J39" s="687"/>
-      <c r="K39" s="687"/>
-      <c r="L39" s="687"/>
+      <c r="H39" s="592"/>
+      <c r="I39" s="592"/>
+      <c r="J39" s="592"/>
+      <c r="K39" s="592"/>
+      <c r="L39" s="592"/>
       <c r="M39" s="107"/>
     </row>
     <row r="40" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="43"/>
       <c r="B40" s="44"/>
-      <c r="C40" s="678"/>
-      <c r="D40" s="678"/>
-      <c r="E40" s="678"/>
-      <c r="F40" s="679"/>
+      <c r="C40" s="621"/>
+      <c r="D40" s="621"/>
+      <c r="E40" s="621"/>
+      <c r="F40" s="622"/>
       <c r="G40" s="108"/>
       <c r="H40" s="229"/>
-      <c r="I40" s="673"/>
-      <c r="J40" s="673"/>
-      <c r="K40" s="673"/>
-      <c r="L40" s="673"/>
+      <c r="I40" s="602"/>
+      <c r="J40" s="602"/>
+      <c r="K40" s="602"/>
+      <c r="L40" s="602"/>
       <c r="M40" s="109"/>
     </row>
     <row r="41" spans="1:14" ht="41.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="671" t="s">
+      <c r="A41" s="616" t="s">
         <v>362</v>
       </c>
-      <c r="B41" s="672"/>
-      <c r="C41" s="584" t="s">
+      <c r="B41" s="617"/>
+      <c r="C41" s="615" t="s">
         <v>363</v>
       </c>
-      <c r="D41" s="584"/>
-      <c r="E41" s="584"/>
-      <c r="F41" s="585"/>
+      <c r="D41" s="615"/>
+      <c r="E41" s="615"/>
+      <c r="F41" s="614"/>
       <c r="G41" s="30"/>
       <c r="H41" s="30"/>
       <c r="I41" s="49"/>
@@ -18094,10 +18094,10 @@
     <row r="42" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="47"/>
       <c r="B42" s="48"/>
-      <c r="C42" s="584"/>
-      <c r="D42" s="584"/>
-      <c r="E42" s="584"/>
-      <c r="F42" s="585"/>
+      <c r="C42" s="615"/>
+      <c r="D42" s="615"/>
+      <c r="E42" s="615"/>
+      <c r="F42" s="614"/>
       <c r="G42" s="52"/>
       <c r="H42" s="52"/>
       <c r="I42" s="52"/>
@@ -18111,21 +18111,21 @@
         <v>364</v>
       </c>
       <c r="B43" s="48"/>
-      <c r="C43" s="584" t="s">
+      <c r="C43" s="615" t="s">
         <v>365</v>
       </c>
-      <c r="D43" s="584"/>
-      <c r="E43" s="584"/>
-      <c r="F43" s="585"/>
+      <c r="D43" s="615"/>
+      <c r="E43" s="615"/>
+      <c r="F43" s="614"/>
       <c r="M43" s="2"/>
     </row>
     <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="47"/>
       <c r="B44" s="48"/>
-      <c r="C44" s="584"/>
-      <c r="D44" s="584"/>
-      <c r="E44" s="584"/>
-      <c r="F44" s="585"/>
+      <c r="C44" s="615"/>
+      <c r="D44" s="615"/>
+      <c r="E44" s="615"/>
+      <c r="F44" s="614"/>
       <c r="G44" s="174" t="s">
         <v>366</v>
       </c>
@@ -18141,21 +18141,21 @@
         <v>367</v>
       </c>
       <c r="B45" s="48"/>
-      <c r="C45" s="585" t="s">
+      <c r="C45" s="614" t="s">
         <v>368</v>
       </c>
-      <c r="D45" s="585"/>
-      <c r="E45" s="585"/>
-      <c r="F45" s="585"/>
+      <c r="D45" s="614"/>
+      <c r="E45" s="614"/>
+      <c r="F45" s="614"/>
       <c r="M45" s="2"/>
     </row>
     <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="47"/>
       <c r="B46" s="48"/>
-      <c r="C46" s="585"/>
-      <c r="D46" s="585"/>
-      <c r="E46" s="585"/>
-      <c r="F46" s="585"/>
+      <c r="C46" s="614"/>
+      <c r="D46" s="614"/>
+      <c r="E46" s="614"/>
+      <c r="F46" s="614"/>
       <c r="G46" s="175" t="s">
         <v>369</v>
       </c>
@@ -18172,21 +18172,21 @@
         <v>370</v>
       </c>
       <c r="B47" s="48"/>
-      <c r="C47" s="584" t="s">
+      <c r="C47" s="615" t="s">
         <v>371</v>
       </c>
-      <c r="D47" s="584"/>
+      <c r="D47" s="615"/>
       <c r="E47" s="98"/>
       <c r="F47" s="99"/>
       <c r="M47" s="2"/>
     </row>
     <row r="48" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="635"/>
-      <c r="B48" s="636"/>
-      <c r="C48" s="636"/>
-      <c r="D48" s="636"/>
-      <c r="E48" s="636"/>
-      <c r="F48" s="637"/>
+      <c r="A48" s="648"/>
+      <c r="B48" s="649"/>
+      <c r="C48" s="649"/>
+      <c r="D48" s="649"/>
+      <c r="E48" s="649"/>
+      <c r="F48" s="650"/>
       <c r="G48" s="176" t="s">
         <v>369</v>
       </c>
@@ -18199,12 +18199,12 @@
       <c r="N48" s="54"/>
     </row>
     <row r="49" spans="1:14" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="638"/>
-      <c r="B49" s="639"/>
-      <c r="C49" s="639"/>
-      <c r="D49" s="639"/>
-      <c r="E49" s="639"/>
-      <c r="F49" s="640"/>
+      <c r="A49" s="651"/>
+      <c r="B49" s="652"/>
+      <c r="C49" s="652"/>
+      <c r="D49" s="652"/>
+      <c r="E49" s="652"/>
+      <c r="F49" s="653"/>
       <c r="G49" s="100"/>
       <c r="H49" s="96"/>
       <c r="I49" s="96"/>
@@ -18215,10 +18215,10 @@
       <c r="N49" s="54"/>
     </row>
     <row r="50" spans="1:14" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="571" t="s">
+      <c r="A50" s="721" t="s">
         <v>372</v>
       </c>
-      <c r="B50" s="572"/>
+      <c r="B50" s="722"/>
       <c r="C50" s="172" t="s">
         <v>373</v>
       </c>
@@ -18228,127 +18228,127 @@
       <c r="G50" s="172"/>
       <c r="H50" s="172"/>
       <c r="I50" s="173"/>
-      <c r="J50" s="622"/>
-      <c r="K50" s="623"/>
-      <c r="L50" s="623"/>
-      <c r="M50" s="624"/>
+      <c r="J50" s="636"/>
+      <c r="K50" s="637"/>
+      <c r="L50" s="637"/>
+      <c r="M50" s="638"/>
     </row>
     <row r="51" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="632" t="s">
+      <c r="A51" s="645" t="s">
         <v>374</v>
       </c>
-      <c r="B51" s="633"/>
-      <c r="C51" s="633"/>
-      <c r="D51" s="633"/>
-      <c r="E51" s="634"/>
+      <c r="B51" s="646"/>
+      <c r="C51" s="646"/>
+      <c r="D51" s="646"/>
+      <c r="E51" s="647"/>
       <c r="F51" s="244" t="s">
         <v>375</v>
       </c>
-      <c r="G51" s="341" t="s">
+      <c r="G51" s="386" t="s">
         <v>376</v>
       </c>
-      <c r="H51" s="504"/>
-      <c r="I51" s="342"/>
-      <c r="J51" s="625"/>
-      <c r="K51" s="626"/>
-      <c r="L51" s="626"/>
-      <c r="M51" s="627"/>
+      <c r="H51" s="582"/>
+      <c r="I51" s="387"/>
+      <c r="J51" s="639"/>
+      <c r="K51" s="640"/>
+      <c r="L51" s="640"/>
+      <c r="M51" s="641"/>
     </row>
     <row r="52" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="650"/>
-      <c r="B52" s="651"/>
-      <c r="C52" s="653"/>
-      <c r="D52" s="653"/>
-      <c r="E52" s="654"/>
+      <c r="A52" s="661"/>
+      <c r="B52" s="662"/>
+      <c r="C52" s="664"/>
+      <c r="D52" s="664"/>
+      <c r="E52" s="665"/>
       <c r="F52" s="55"/>
-      <c r="G52" s="643"/>
-      <c r="H52" s="644"/>
-      <c r="I52" s="645"/>
-      <c r="J52" s="625"/>
-      <c r="K52" s="626"/>
-      <c r="L52" s="626"/>
-      <c r="M52" s="627"/>
+      <c r="G52" s="654"/>
+      <c r="H52" s="655"/>
+      <c r="I52" s="656"/>
+      <c r="J52" s="639"/>
+      <c r="K52" s="640"/>
+      <c r="L52" s="640"/>
+      <c r="M52" s="641"/>
     </row>
     <row r="53" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="650"/>
-      <c r="B53" s="651"/>
-      <c r="C53" s="651"/>
-      <c r="D53" s="651"/>
-      <c r="E53" s="652"/>
+      <c r="A53" s="661"/>
+      <c r="B53" s="662"/>
+      <c r="C53" s="662"/>
+      <c r="D53" s="662"/>
+      <c r="E53" s="663"/>
       <c r="F53" s="55"/>
-      <c r="G53" s="643"/>
-      <c r="H53" s="644"/>
-      <c r="I53" s="645"/>
-      <c r="J53" s="625"/>
-      <c r="K53" s="626"/>
-      <c r="L53" s="626"/>
-      <c r="M53" s="627"/>
+      <c r="G53" s="654"/>
+      <c r="H53" s="655"/>
+      <c r="I53" s="656"/>
+      <c r="J53" s="639"/>
+      <c r="K53" s="640"/>
+      <c r="L53" s="640"/>
+      <c r="M53" s="641"/>
     </row>
     <row r="54" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="646"/>
-      <c r="B54" s="647"/>
-      <c r="C54" s="648"/>
-      <c r="D54" s="648"/>
-      <c r="E54" s="649"/>
+      <c r="A54" s="657"/>
+      <c r="B54" s="658"/>
+      <c r="C54" s="659"/>
+      <c r="D54" s="659"/>
+      <c r="E54" s="660"/>
       <c r="F54" s="181"/>
-      <c r="G54" s="629"/>
-      <c r="H54" s="630"/>
-      <c r="I54" s="631"/>
-      <c r="J54" s="625"/>
-      <c r="K54" s="626"/>
-      <c r="L54" s="626"/>
-      <c r="M54" s="627"/>
+      <c r="G54" s="642"/>
+      <c r="H54" s="643"/>
+      <c r="I54" s="644"/>
+      <c r="J54" s="639"/>
+      <c r="K54" s="640"/>
+      <c r="L54" s="640"/>
+      <c r="M54" s="641"/>
     </row>
     <row r="55" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="641" t="s">
+      <c r="A55" s="627" t="s">
         <v>377</v>
       </c>
-      <c r="B55" s="642"/>
-      <c r="C55" s="655" t="s">
+      <c r="B55" s="628"/>
+      <c r="C55" s="666" t="s">
         <v>397</v>
       </c>
-      <c r="D55" s="655"/>
-      <c r="E55" s="655"/>
-      <c r="F55" s="655"/>
-      <c r="G55" s="655"/>
-      <c r="H55" s="655"/>
+      <c r="D55" s="666"/>
+      <c r="E55" s="666"/>
+      <c r="F55" s="666"/>
+      <c r="G55" s="666"/>
+      <c r="H55" s="666"/>
       <c r="I55" s="235"/>
-      <c r="J55" s="626"/>
-      <c r="K55" s="626"/>
-      <c r="L55" s="626"/>
-      <c r="M55" s="627"/>
+      <c r="J55" s="640"/>
+      <c r="K55" s="640"/>
+      <c r="L55" s="640"/>
+      <c r="M55" s="641"/>
     </row>
     <row r="56" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="56"/>
       <c r="B56" s="57"/>
-      <c r="C56" s="656"/>
-      <c r="D56" s="656"/>
-      <c r="E56" s="656"/>
-      <c r="F56" s="656"/>
-      <c r="G56" s="656"/>
-      <c r="H56" s="656"/>
+      <c r="C56" s="667"/>
+      <c r="D56" s="667"/>
+      <c r="E56" s="667"/>
+      <c r="F56" s="667"/>
+      <c r="G56" s="667"/>
+      <c r="H56" s="667"/>
       <c r="I56" s="236"/>
       <c r="J56" s="180"/>
-      <c r="K56" s="628" t="s">
+      <c r="K56" s="610" t="s">
         <v>378</v>
       </c>
-      <c r="L56" s="628"/>
+      <c r="L56" s="610"/>
       <c r="M56" s="163"/>
     </row>
     <row r="57" spans="1:14" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="56"/>
       <c r="B57" s="57"/>
-      <c r="C57" s="656"/>
-      <c r="D57" s="656"/>
-      <c r="E57" s="656"/>
-      <c r="F57" s="656"/>
-      <c r="G57" s="656"/>
-      <c r="H57" s="656"/>
+      <c r="C57" s="667"/>
+      <c r="D57" s="667"/>
+      <c r="E57" s="667"/>
+      <c r="F57" s="667"/>
+      <c r="G57" s="667"/>
+      <c r="H57" s="667"/>
       <c r="I57" s="236"/>
-      <c r="J57" s="628"/>
-      <c r="K57" s="628"/>
-      <c r="L57" s="628"/>
-      <c r="M57" s="670"/>
+      <c r="J57" s="610"/>
+      <c r="K57" s="610"/>
+      <c r="L57" s="610"/>
+      <c r="M57" s="611"/>
     </row>
     <row r="58" spans="1:14" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="161"/>
@@ -18360,8 +18360,8 @@
       <c r="G58" s="237"/>
       <c r="H58" s="237"/>
       <c r="I58" s="238"/>
-      <c r="K58" s="608"/>
-      <c r="L58" s="609"/>
+      <c r="K58" s="692"/>
+      <c r="L58" s="693"/>
       <c r="M58" s="2"/>
     </row>
     <row r="59" spans="1:14" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -18373,102 +18373,102 @@
       <c r="G59" s="25"/>
       <c r="H59" s="25"/>
       <c r="I59" s="25"/>
-      <c r="K59" s="610"/>
-      <c r="L59" s="611"/>
+      <c r="K59" s="694"/>
+      <c r="L59" s="695"/>
       <c r="M59" s="2"/>
     </row>
     <row r="60" spans="1:14" ht="32.549999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="58"/>
-      <c r="B60" s="561" t="s">
+      <c r="B60" s="714" t="s">
         <v>398</v>
       </c>
-      <c r="C60" s="562"/>
-      <c r="D60" s="563"/>
-      <c r="F60" s="552"/>
-      <c r="G60" s="553"/>
-      <c r="H60" s="553"/>
-      <c r="I60" s="554"/>
-      <c r="K60" s="610"/>
-      <c r="L60" s="611"/>
+      <c r="C60" s="715"/>
+      <c r="D60" s="716"/>
+      <c r="F60" s="705"/>
+      <c r="G60" s="706"/>
+      <c r="H60" s="706"/>
+      <c r="I60" s="707"/>
+      <c r="K60" s="694"/>
+      <c r="L60" s="695"/>
       <c r="M60" s="59"/>
     </row>
     <row r="61" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="58"/>
-      <c r="B61" s="614" t="s">
+      <c r="B61" s="698" t="s">
         <v>379</v>
       </c>
-      <c r="C61" s="615"/>
+      <c r="C61" s="699"/>
       <c r="D61" s="114"/>
-      <c r="F61" s="555"/>
-      <c r="G61" s="556"/>
-      <c r="H61" s="556"/>
-      <c r="I61" s="557"/>
-      <c r="K61" s="610"/>
-      <c r="L61" s="611"/>
+      <c r="F61" s="708"/>
+      <c r="G61" s="709"/>
+      <c r="H61" s="709"/>
+      <c r="I61" s="710"/>
+      <c r="K61" s="694"/>
+      <c r="L61" s="695"/>
       <c r="M61" s="59"/>
     </row>
     <row r="62" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="58"/>
-      <c r="B62" s="603" t="s">
+      <c r="B62" s="686" t="s">
         <v>380</v>
       </c>
-      <c r="C62" s="604"/>
-      <c r="D62" s="564"/>
-      <c r="F62" s="558"/>
-      <c r="G62" s="559"/>
-      <c r="H62" s="559"/>
-      <c r="I62" s="560"/>
-      <c r="K62" s="610"/>
-      <c r="L62" s="611"/>
+      <c r="C62" s="687"/>
+      <c r="D62" s="690"/>
+      <c r="F62" s="711"/>
+      <c r="G62" s="712"/>
+      <c r="H62" s="712"/>
+      <c r="I62" s="713"/>
+      <c r="K62" s="694"/>
+      <c r="L62" s="695"/>
       <c r="M62" s="59"/>
     </row>
     <row r="63" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="58"/>
-      <c r="B63" s="616"/>
-      <c r="C63" s="617"/>
-      <c r="D63" s="565"/>
-      <c r="F63" s="566" t="s">
+      <c r="B63" s="700"/>
+      <c r="C63" s="701"/>
+      <c r="D63" s="717"/>
+      <c r="F63" s="718" t="s">
         <v>381</v>
       </c>
-      <c r="G63" s="567"/>
-      <c r="H63" s="567"/>
-      <c r="I63" s="568"/>
-      <c r="K63" s="610"/>
-      <c r="L63" s="611"/>
+      <c r="G63" s="719"/>
+      <c r="H63" s="719"/>
+      <c r="I63" s="720"/>
+      <c r="K63" s="694"/>
+      <c r="L63" s="695"/>
       <c r="M63" s="59"/>
     </row>
     <row r="64" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="58"/>
-      <c r="B64" s="603" t="s">
+      <c r="B64" s="686" t="s">
         <v>382</v>
       </c>
-      <c r="C64" s="604"/>
-      <c r="D64" s="564"/>
+      <c r="C64" s="687"/>
+      <c r="D64" s="690"/>
       <c r="F64" s="60"/>
       <c r="G64" s="164"/>
       <c r="H64" s="164"/>
       <c r="I64" s="165"/>
       <c r="J64" s="61"/>
-      <c r="K64" s="612"/>
-      <c r="L64" s="613"/>
+      <c r="K64" s="696"/>
+      <c r="L64" s="697"/>
       <c r="M64" s="59"/>
     </row>
     <row r="65" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="58"/>
-      <c r="B65" s="605"/>
-      <c r="C65" s="606"/>
-      <c r="D65" s="607"/>
-      <c r="F65" s="600" t="s">
+      <c r="B65" s="688"/>
+      <c r="C65" s="689"/>
+      <c r="D65" s="691"/>
+      <c r="F65" s="683" t="s">
         <v>383</v>
       </c>
-      <c r="G65" s="601"/>
-      <c r="H65" s="601"/>
-      <c r="I65" s="602"/>
+      <c r="G65" s="684"/>
+      <c r="H65" s="684"/>
+      <c r="I65" s="685"/>
       <c r="J65" s="61"/>
-      <c r="K65" s="598" t="s">
+      <c r="K65" s="681" t="s">
         <v>384</v>
       </c>
-      <c r="L65" s="599"/>
+      <c r="L65" s="682"/>
       <c r="M65" s="59"/>
     </row>
     <row r="66" spans="1:13" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -18487,32 +18487,32 @@
       <c r="M66" s="67"/>
     </row>
     <row r="67" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="595" t="s">
+      <c r="A67" s="678" t="s">
         <v>385</v>
       </c>
-      <c r="B67" s="596"/>
-      <c r="C67" s="596"/>
-      <c r="D67" s="596"/>
-      <c r="E67" s="596"/>
-      <c r="F67" s="596"/>
-      <c r="G67" s="596"/>
-      <c r="H67" s="596"/>
-      <c r="I67" s="596"/>
-      <c r="J67" s="596"/>
-      <c r="K67" s="596"/>
-      <c r="L67" s="596"/>
-      <c r="M67" s="597"/>
+      <c r="B67" s="679"/>
+      <c r="C67" s="679"/>
+      <c r="D67" s="679"/>
+      <c r="E67" s="679"/>
+      <c r="F67" s="679"/>
+      <c r="G67" s="679"/>
+      <c r="H67" s="679"/>
+      <c r="I67" s="679"/>
+      <c r="J67" s="679"/>
+      <c r="K67" s="679"/>
+      <c r="L67" s="679"/>
+      <c r="M67" s="680"/>
     </row>
     <row r="68" spans="1:13" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="58"/>
       <c r="B68" s="61"/>
       <c r="C68" s="68"/>
       <c r="D68" s="68"/>
-      <c r="E68" s="592"/>
-      <c r="F68" s="593"/>
-      <c r="G68" s="593"/>
-      <c r="H68" s="593"/>
-      <c r="I68" s="594"/>
+      <c r="E68" s="675"/>
+      <c r="F68" s="676"/>
+      <c r="G68" s="676"/>
+      <c r="H68" s="676"/>
+      <c r="I68" s="677"/>
       <c r="J68" s="115"/>
       <c r="K68" s="115"/>
       <c r="M68" s="59"/>
@@ -18522,13 +18522,13 @@
       <c r="B69" s="61"/>
       <c r="C69" s="220"/>
       <c r="D69" s="220"/>
-      <c r="E69" s="589" t="s">
+      <c r="E69" s="672" t="s">
         <v>386</v>
       </c>
-      <c r="F69" s="590"/>
-      <c r="G69" s="590"/>
-      <c r="H69" s="590"/>
-      <c r="I69" s="591"/>
+      <c r="F69" s="673"/>
+      <c r="G69" s="673"/>
+      <c r="H69" s="673"/>
+      <c r="I69" s="674"/>
       <c r="J69" s="117"/>
       <c r="K69" s="116"/>
       <c r="L69" s="69"/>
@@ -18550,21 +18550,21 @@
       <c r="M70" s="72"/>
     </row>
     <row r="71" spans="1:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="588" t="s">
+      <c r="A71" s="671" t="s">
         <v>400</v>
       </c>
-      <c r="B71" s="588"/>
-      <c r="C71" s="588"/>
-      <c r="D71" s="588"/>
-      <c r="E71" s="588"/>
-      <c r="F71" s="588"/>
-      <c r="G71" s="588"/>
-      <c r="H71" s="588"/>
-      <c r="I71" s="588"/>
-      <c r="J71" s="588"/>
-      <c r="K71" s="588"/>
-      <c r="L71" s="588"/>
-      <c r="M71" s="588"/>
+      <c r="B71" s="671"/>
+      <c r="C71" s="671"/>
+      <c r="D71" s="671"/>
+      <c r="E71" s="671"/>
+      <c r="F71" s="671"/>
+      <c r="G71" s="671"/>
+      <c r="H71" s="671"/>
+      <c r="I71" s="671"/>
+      <c r="J71" s="671"/>
+      <c r="K71" s="671"/>
+      <c r="L71" s="671"/>
+      <c r="M71" s="671"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -18577,44 +18577,37 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="87">
-    <mergeCell ref="H39:L39"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="H15:L15"/>
-    <mergeCell ref="H25:L25"/>
-    <mergeCell ref="H29:L29"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:F16"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="J57:M57"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C45:F46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="C37:F40"/>
-    <mergeCell ref="C41:F42"/>
-    <mergeCell ref="C43:F44"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="C27:F30"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="H11:L11"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="G38:M38"/>
+    <mergeCell ref="C18:F22"/>
+    <mergeCell ref="G28:L28"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="G19:L19"/>
+    <mergeCell ref="C23:F26"/>
+    <mergeCell ref="A71:M71"/>
+    <mergeCell ref="E69:I69"/>
+    <mergeCell ref="E68:I68"/>
+    <mergeCell ref="A67:M67"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="B64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="K58:L64"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C63"/>
+    <mergeCell ref="F60:I62"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="C31:F32"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C34:F36"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="G35:J35"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="K32:L32"/>
     <mergeCell ref="J50:M55"/>
@@ -18631,39 +18624,46 @@
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="C55:H57"/>
     <mergeCell ref="I34:L34"/>
-    <mergeCell ref="C31:F32"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C34:F36"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="A71:M71"/>
-    <mergeCell ref="E69:I69"/>
-    <mergeCell ref="E68:I68"/>
-    <mergeCell ref="A67:M67"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="F65:I65"/>
-    <mergeCell ref="B64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="K58:L64"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C63"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C45:F46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="C37:F40"/>
+    <mergeCell ref="C41:F42"/>
+    <mergeCell ref="C43:F44"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="C27:F30"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:F16"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="H11:L11"/>
+    <mergeCell ref="H39:L39"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="H15:L15"/>
+    <mergeCell ref="H25:L25"/>
+    <mergeCell ref="H29:L29"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="G21:I21"/>
-    <mergeCell ref="F60:I62"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="G38:M38"/>
-    <mergeCell ref="C18:F22"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="G19:L19"/>
-    <mergeCell ref="C23:F26"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -19300,25 +19300,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="61535973-5223-4bf4-bdcc-6c7df9166676">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004061E9AFAF7CA04B82F43B8373745610" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3807037a0979b6ce9196f65959799221">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="61535973-5223-4bf4-bdcc-6c7df9166676" xmlns:ns3="ab5b6d4b-4285-4680-b1ee-6fe31a63f7d7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0698124c94b6a25b909cbe33b647c32f" ns2:_="" ns3:_="">
     <xsd:import namespace="61535973-5223-4bf4-bdcc-6c7df9166676"/>
@@ -19549,32 +19530,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CF60C-2A54-4479-8975-DF3B2608842A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="ab5b6d4b-4285-4680-b1ee-6fe31a63f7d7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="61535973-5223-4bf4-bdcc-6c7df9166676"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE1AC42-07AD-4118-96D5-B1BB6CECCAA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="61535973-5223-4bf4-bdcc-6c7df9166676">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99101B7C-E13F-4ECC-92B9-66DA7C9E1E4F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19591,4 +19566,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE1AC42-07AD-4118-96D5-B1BB6CECCAA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CF60C-2A54-4479-8975-DF3B2608842A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="ab5b6d4b-4285-4680-b1ee-6fe31a63f7d7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="61535973-5223-4bf4-bdcc-6c7df9166676"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ANNEX H-1 - CS Form No. 212 Revised 2025 - Personal Data Sheet.xlsx
+++ b/ANNEX H-1 - CS Form No. 212 Revised 2025 - Personal Data Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\DILG-CAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBFFB3A-A449-4EEB-8B42-87E5B3700E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5669D8A-9208-4E98-94DE-B61A2E1B7503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -2649,7 +2649,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="730">
+  <cellXfs count="733">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
@@ -3485,6 +3485,143 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="42" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="31" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="31" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -3497,57 +3634,370 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="6" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="55" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="18" fillId="5" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="31" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3557,12 +4007,6 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3579,20 +4023,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -3630,18 +4060,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -3652,10 +4070,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3671,459 +4085,177 @@
     <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="5" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="55" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="30" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -4131,176 +4263,91 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4314,9 +4361,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -4329,32 +4373,14 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
@@ -4362,18 +4388,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4381,6 +4395,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4404,18 +4421,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -4439,92 +4444,417 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
@@ -4541,69 +4871,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -4615,208 +4882,17 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -4827,81 +4903,14 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4994,7 +5003,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="50" dropStyle="combo" dx="16" fmlaRange="Q11:Q216" noThreeD="1" sel="4" val="3"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5094,11 +5103,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Label"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Label"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5110,10 +5119,6 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -5759,8 +5764,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7648575" y="2247900"/>
-          <a:ext cx="0" cy="476250"/>
+          <a:off x="8008620" y="2535555"/>
+          <a:ext cx="0" cy="655320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5972,64 +5977,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>22860</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>13</xdr:col>
-          <xdr:colOff>594360</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>304800</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1055" name="Drop Down 31" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1055"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData fLocksWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
@@ -10051,20 +9998,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="375"/>
-      <c r="B1" s="376"/>
-      <c r="C1" s="376"/>
-      <c r="D1" s="376"/>
-      <c r="E1" s="376"/>
-      <c r="F1" s="376"/>
-      <c r="G1" s="376"/>
-      <c r="H1" s="376"/>
-      <c r="I1" s="376"/>
-      <c r="J1" s="376"/>
-      <c r="K1" s="376"/>
-      <c r="L1" s="376"/>
-      <c r="M1" s="376"/>
-      <c r="N1" s="377"/>
+      <c r="A1" s="355"/>
+      <c r="B1" s="356"/>
+      <c r="C1" s="356"/>
+      <c r="D1" s="356"/>
+      <c r="E1" s="356"/>
+      <c r="F1" s="356"/>
+      <c r="G1" s="356"/>
+      <c r="H1" s="356"/>
+      <c r="I1" s="356"/>
+      <c r="J1" s="356"/>
+      <c r="K1" s="356"/>
+      <c r="L1" s="356"/>
+      <c r="M1" s="356"/>
+      <c r="N1" s="357"/>
     </row>
     <row r="2" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="145"/>
@@ -10094,58 +10041,58 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="378" t="s">
+      <c r="A3" s="358" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="379"/>
-      <c r="C3" s="379"/>
-      <c r="D3" s="379"/>
-      <c r="E3" s="379"/>
-      <c r="F3" s="379"/>
-      <c r="G3" s="379"/>
-      <c r="H3" s="379"/>
-      <c r="I3" s="379"/>
-      <c r="J3" s="379"/>
-      <c r="K3" s="379"/>
-      <c r="L3" s="379"/>
-      <c r="M3" s="379"/>
-      <c r="N3" s="380"/>
+      <c r="B3" s="359"/>
+      <c r="C3" s="359"/>
+      <c r="D3" s="359"/>
+      <c r="E3" s="359"/>
+      <c r="F3" s="359"/>
+      <c r="G3" s="359"/>
+      <c r="H3" s="359"/>
+      <c r="I3" s="359"/>
+      <c r="J3" s="359"/>
+      <c r="K3" s="359"/>
+      <c r="L3" s="359"/>
+      <c r="M3" s="359"/>
+      <c r="N3" s="360"/>
     </row>
     <row r="4" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="391" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="409"/>
-      <c r="C4" s="409"/>
-      <c r="D4" s="409"/>
-      <c r="E4" s="409"/>
-      <c r="F4" s="409"/>
-      <c r="G4" s="409"/>
-      <c r="H4" s="409"/>
-      <c r="I4" s="409"/>
-      <c r="J4" s="409"/>
-      <c r="K4" s="409"/>
-      <c r="L4" s="409"/>
-      <c r="M4" s="409"/>
-      <c r="N4" s="410"/>
+      <c r="B4" s="392"/>
+      <c r="C4" s="392"/>
+      <c r="D4" s="392"/>
+      <c r="E4" s="392"/>
+      <c r="F4" s="392"/>
+      <c r="G4" s="392"/>
+      <c r="H4" s="392"/>
+      <c r="I4" s="392"/>
+      <c r="J4" s="392"/>
+      <c r="K4" s="392"/>
+      <c r="L4" s="392"/>
+      <c r="M4" s="392"/>
+      <c r="N4" s="393"/>
     </row>
     <row r="5" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="291" t="s">
+      <c r="A5" s="433" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="292"/>
-      <c r="C5" s="292"/>
-      <c r="D5" s="292"/>
-      <c r="E5" s="292"/>
-      <c r="F5" s="292"/>
-      <c r="G5" s="292"/>
-      <c r="H5" s="292"/>
-      <c r="I5" s="292"/>
-      <c r="J5" s="292"/>
-      <c r="K5" s="292"/>
-      <c r="L5" s="292"/>
-      <c r="M5" s="292"/>
-      <c r="N5" s="293"/>
+      <c r="B5" s="434"/>
+      <c r="C5" s="434"/>
+      <c r="D5" s="434"/>
+      <c r="E5" s="434"/>
+      <c r="F5" s="434"/>
+      <c r="G5" s="434"/>
+      <c r="H5" s="434"/>
+      <c r="I5" s="434"/>
+      <c r="J5" s="434"/>
+      <c r="K5" s="434"/>
+      <c r="L5" s="434"/>
+      <c r="M5" s="434"/>
+      <c r="N5" s="435"/>
     </row>
     <row r="6" spans="1:18" ht="3" hidden="1" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A6" s="177"/>
@@ -10182,42 +10129,42 @@
       <c r="N8" s="141"/>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="381" t="s">
+      <c r="A9" s="361" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="382"/>
-      <c r="C9" s="382"/>
-      <c r="D9" s="382"/>
-      <c r="E9" s="382"/>
-      <c r="F9" s="382"/>
-      <c r="G9" s="382"/>
-      <c r="H9" s="382"/>
-      <c r="I9" s="382"/>
-      <c r="J9" s="382"/>
-      <c r="K9" s="382"/>
-      <c r="L9" s="382"/>
-      <c r="M9" s="382"/>
-      <c r="N9" s="383"/>
+      <c r="B9" s="362"/>
+      <c r="C9" s="362"/>
+      <c r="D9" s="362"/>
+      <c r="E9" s="362"/>
+      <c r="F9" s="362"/>
+      <c r="G9" s="362"/>
+      <c r="H9" s="362"/>
+      <c r="I9" s="362"/>
+      <c r="J9" s="362"/>
+      <c r="K9" s="362"/>
+      <c r="L9" s="362"/>
+      <c r="M9" s="362"/>
+      <c r="N9" s="363"/>
     </row>
     <row r="10" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="150" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="399" t="s">
+      <c r="B10" s="381" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="331"/>
-      <c r="D10" s="392"/>
-      <c r="E10" s="392"/>
-      <c r="F10" s="392"/>
-      <c r="G10" s="392"/>
-      <c r="H10" s="392"/>
-      <c r="I10" s="392"/>
-      <c r="J10" s="392"/>
-      <c r="K10" s="392"/>
-      <c r="L10" s="392"/>
-      <c r="M10" s="392"/>
-      <c r="N10" s="393"/>
+      <c r="C10" s="382"/>
+      <c r="D10" s="372"/>
+      <c r="E10" s="372"/>
+      <c r="F10" s="372"/>
+      <c r="G10" s="372"/>
+      <c r="H10" s="372"/>
+      <c r="I10" s="372"/>
+      <c r="J10" s="372"/>
+      <c r="K10" s="372"/>
+      <c r="L10" s="372"/>
+      <c r="M10" s="372"/>
+      <c r="N10" s="373"/>
       <c r="P10" s="77" t="s">
         <v>11</v>
       </c>
@@ -10226,10 +10173,10 @@
       <c r="A11" s="150" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="400" t="s">
+      <c r="B11" s="383" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="401"/>
+      <c r="C11" s="384"/>
       <c r="D11" s="185"/>
       <c r="E11" s="186"/>
       <c r="F11" s="186"/>
@@ -10238,11 +10185,11 @@
       <c r="I11" s="186"/>
       <c r="J11" s="186"/>
       <c r="K11" s="186"/>
-      <c r="L11" s="332" t="s">
+      <c r="L11" s="406" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="333"/>
-      <c r="N11" s="334"/>
+      <c r="M11" s="407"/>
+      <c r="N11" s="408"/>
       <c r="P11" s="78" t="s">
         <v>15</v>
       </c>
@@ -10252,10 +10199,10 @@
     </row>
     <row r="12" spans="1:18" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="151"/>
-      <c r="B12" s="402" t="s">
+      <c r="B12" s="385" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="403"/>
+      <c r="C12" s="386"/>
       <c r="D12" s="182"/>
       <c r="E12" s="183"/>
       <c r="F12" s="183"/>
@@ -10278,23 +10225,23 @@
       <c r="A13" s="219" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="330" t="s">
+      <c r="B13" s="462" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="331"/>
-      <c r="D13" s="335"/>
-      <c r="E13" s="335"/>
-      <c r="F13" s="336"/>
+      <c r="C13" s="382"/>
+      <c r="D13" s="409"/>
+      <c r="E13" s="409"/>
+      <c r="F13" s="410"/>
       <c r="G13" s="84" t="s">
         <v>22</v>
       </c>
       <c r="H13" s="128"/>
       <c r="I13" s="128"/>
-      <c r="J13" s="342"/>
-      <c r="K13" s="343"/>
-      <c r="L13" s="343"/>
-      <c r="M13" s="343"/>
-      <c r="N13" s="344"/>
+      <c r="J13" s="416"/>
+      <c r="K13" s="417"/>
+      <c r="L13" s="417"/>
+      <c r="M13" s="417"/>
+      <c r="N13" s="418"/>
       <c r="P13" s="78" t="s">
         <v>23</v>
       </c>
@@ -10328,21 +10275,21 @@
         <v>26</v>
       </c>
       <c r="C15" s="79"/>
-      <c r="D15" s="359"/>
-      <c r="E15" s="359"/>
-      <c r="F15" s="360"/>
-      <c r="G15" s="340" t="s">
+      <c r="D15" s="428"/>
+      <c r="E15" s="428"/>
+      <c r="F15" s="429"/>
+      <c r="G15" s="414" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="341"/>
-      <c r="I15" s="341"/>
+      <c r="H15" s="415"/>
+      <c r="I15" s="415"/>
       <c r="J15" s="129"/>
       <c r="K15" s="130"/>
-      <c r="L15" s="345" t="s">
+      <c r="L15" s="419" t="s">
         <v>28</v>
       </c>
-      <c r="M15" s="345"/>
-      <c r="N15" s="346"/>
+      <c r="M15" s="419"/>
+      <c r="N15" s="420"/>
       <c r="P15" s="78" t="s">
         <v>29</v>
       </c>
@@ -10358,15 +10305,19 @@
         <v>32</v>
       </c>
       <c r="C16" s="80"/>
-      <c r="D16" s="394"/>
-      <c r="E16" s="394"/>
-      <c r="F16" s="395"/>
-      <c r="G16" s="337" t="s">
+      <c r="D16" s="374"/>
+      <c r="E16" s="374"/>
+      <c r="F16" s="375"/>
+      <c r="G16" s="411" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="338"/>
-      <c r="I16" s="339"/>
-      <c r="N16" s="141"/>
+      <c r="H16" s="412"/>
+      <c r="I16" s="413"/>
+      <c r="J16" s="730"/>
+      <c r="K16" s="731"/>
+      <c r="L16" s="731"/>
+      <c r="M16" s="731"/>
+      <c r="N16" s="732"/>
       <c r="P16" s="78" t="s">
         <v>34</v>
       </c>
@@ -10375,49 +10326,49 @@
       </c>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="313">
+      <c r="A17" s="449">
         <v>6</v>
       </c>
-      <c r="B17" s="326" t="s">
+      <c r="B17" s="458" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="327"/>
-      <c r="D17" s="324"/>
-      <c r="E17" s="324"/>
-      <c r="F17" s="324"/>
+      <c r="C17" s="459"/>
+      <c r="D17" s="457"/>
+      <c r="E17" s="457"/>
+      <c r="F17" s="457"/>
       <c r="G17" s="85" t="s">
         <v>37</v>
       </c>
       <c r="H17" s="86"/>
-      <c r="I17" s="355"/>
-      <c r="J17" s="347"/>
-      <c r="K17" s="347"/>
-      <c r="L17" s="347"/>
-      <c r="M17" s="347"/>
-      <c r="N17" s="348"/>
+      <c r="I17" s="334"/>
+      <c r="J17" s="335"/>
+      <c r="K17" s="335"/>
+      <c r="L17" s="335"/>
+      <c r="M17" s="335"/>
+      <c r="N17" s="336"/>
       <c r="Q17" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="314"/>
-      <c r="B18" s="328"/>
-      <c r="C18" s="329"/>
-      <c r="D18" s="325"/>
-      <c r="E18" s="325"/>
-      <c r="F18" s="325"/>
+      <c r="A18" s="450"/>
+      <c r="B18" s="460"/>
+      <c r="C18" s="461"/>
+      <c r="D18" s="379"/>
+      <c r="E18" s="379"/>
+      <c r="F18" s="379"/>
       <c r="G18" s="137"/>
       <c r="H18" s="87"/>
-      <c r="I18" s="350" t="s">
+      <c r="I18" s="421" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="294"/>
-      <c r="K18" s="294"/>
-      <c r="L18" s="294" t="s">
+      <c r="J18" s="422"/>
+      <c r="K18" s="422"/>
+      <c r="L18" s="422" t="s">
         <v>40</v>
       </c>
-      <c r="M18" s="294"/>
-      <c r="N18" s="295"/>
+      <c r="M18" s="422"/>
+      <c r="N18" s="423"/>
       <c r="Q18" s="3" t="s">
         <v>41</v>
       </c>
@@ -10431,100 +10382,100 @@
       <c r="F19" s="142"/>
       <c r="G19" s="137"/>
       <c r="H19" s="87"/>
-      <c r="I19" s="296"/>
-      <c r="J19" s="297"/>
-      <c r="K19" s="297"/>
-      <c r="L19" s="300"/>
-      <c r="M19" s="297"/>
-      <c r="N19" s="301"/>
+      <c r="I19" s="436"/>
+      <c r="J19" s="437"/>
+      <c r="K19" s="437"/>
+      <c r="L19" s="440"/>
+      <c r="M19" s="437"/>
+      <c r="N19" s="441"/>
       <c r="Q19" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="314"/>
+      <c r="A20" s="450"/>
       <c r="B20" s="201"/>
       <c r="C20" s="120"/>
       <c r="D20" s="121"/>
-      <c r="E20" s="325"/>
-      <c r="F20" s="325"/>
+      <c r="E20" s="379"/>
+      <c r="F20" s="379"/>
       <c r="G20" s="135"/>
       <c r="H20" s="140"/>
-      <c r="I20" s="298"/>
-      <c r="J20" s="299"/>
-      <c r="K20" s="299"/>
-      <c r="L20" s="299"/>
-      <c r="M20" s="299"/>
-      <c r="N20" s="302"/>
+      <c r="I20" s="438"/>
+      <c r="J20" s="439"/>
+      <c r="K20" s="439"/>
+      <c r="L20" s="439"/>
+      <c r="M20" s="439"/>
+      <c r="N20" s="442"/>
       <c r="Q20" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="315"/>
+      <c r="A21" s="451"/>
       <c r="B21" s="202"/>
       <c r="C21" s="118"/>
       <c r="D21" s="122"/>
-      <c r="E21" s="398"/>
-      <c r="F21" s="398"/>
+      <c r="E21" s="380"/>
+      <c r="F21" s="380"/>
       <c r="G21" s="135"/>
       <c r="H21" s="140"/>
-      <c r="I21" s="303" t="s">
+      <c r="I21" s="443" t="s">
         <v>44</v>
       </c>
-      <c r="J21" s="304"/>
-      <c r="K21" s="304"/>
-      <c r="L21" s="431" t="s">
+      <c r="J21" s="444"/>
+      <c r="K21" s="444"/>
+      <c r="L21" s="331" t="s">
         <v>45</v>
       </c>
-      <c r="M21" s="432"/>
-      <c r="N21" s="433"/>
+      <c r="M21" s="332"/>
+      <c r="N21" s="333"/>
       <c r="Q21" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="322" t="s">
+      <c r="A22" s="455" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="289" t="s">
+      <c r="B22" s="398" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="290"/>
-      <c r="D22" s="366"/>
-      <c r="E22" s="366"/>
-      <c r="F22" s="366"/>
+      <c r="C22" s="399"/>
+      <c r="D22" s="394"/>
+      <c r="E22" s="394"/>
+      <c r="F22" s="394"/>
       <c r="G22" s="135"/>
       <c r="H22" s="140"/>
-      <c r="I22" s="355"/>
-      <c r="J22" s="347"/>
-      <c r="K22" s="347"/>
-      <c r="L22" s="347"/>
-      <c r="M22" s="347"/>
-      <c r="N22" s="348"/>
+      <c r="I22" s="334"/>
+      <c r="J22" s="335"/>
+      <c r="K22" s="335"/>
+      <c r="L22" s="335"/>
+      <c r="M22" s="335"/>
+      <c r="N22" s="336"/>
       <c r="Q22" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="323"/>
-      <c r="B23" s="367"/>
-      <c r="C23" s="368"/>
-      <c r="D23" s="308"/>
-      <c r="E23" s="308"/>
-      <c r="F23" s="308"/>
+      <c r="A23" s="456"/>
+      <c r="B23" s="400"/>
+      <c r="C23" s="401"/>
+      <c r="D23" s="395"/>
+      <c r="E23" s="395"/>
+      <c r="F23" s="395"/>
       <c r="G23" s="135"/>
       <c r="H23" s="140"/>
-      <c r="I23" s="436" t="s">
+      <c r="I23" s="339" t="s">
         <v>50</v>
       </c>
-      <c r="J23" s="437"/>
-      <c r="K23" s="437"/>
-      <c r="L23" s="434" t="s">
+      <c r="J23" s="340"/>
+      <c r="K23" s="340"/>
+      <c r="L23" s="337" t="s">
         <v>51</v>
       </c>
-      <c r="M23" s="434"/>
-      <c r="N23" s="435"/>
+      <c r="M23" s="337"/>
+      <c r="N23" s="338"/>
       <c r="Q23" s="3" t="s">
         <v>52</v>
       </c>
@@ -10533,163 +10484,163 @@
       <c r="A24" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="369" t="s">
+      <c r="B24" s="388" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="370"/>
-      <c r="D24" s="349"/>
-      <c r="E24" s="349"/>
-      <c r="F24" s="349"/>
-      <c r="G24" s="404" t="s">
+      <c r="C24" s="389"/>
+      <c r="D24" s="390"/>
+      <c r="E24" s="390"/>
+      <c r="F24" s="390"/>
+      <c r="G24" s="345" t="s">
         <v>55</v>
       </c>
-      <c r="H24" s="405"/>
-      <c r="I24" s="356"/>
-      <c r="J24" s="357"/>
-      <c r="K24" s="357"/>
-      <c r="L24" s="357"/>
-      <c r="M24" s="357"/>
-      <c r="N24" s="358"/>
+      <c r="H24" s="324"/>
+      <c r="I24" s="346"/>
+      <c r="J24" s="347"/>
+      <c r="K24" s="347"/>
+      <c r="L24" s="347"/>
+      <c r="M24" s="347"/>
+      <c r="N24" s="348"/>
       <c r="Q24" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="305" t="s">
+      <c r="A25" s="396" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="289" t="s">
+      <c r="B25" s="398" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="290"/>
-      <c r="D25" s="307"/>
-      <c r="E25" s="307"/>
-      <c r="F25" s="307"/>
+      <c r="C25" s="399"/>
+      <c r="D25" s="378"/>
+      <c r="E25" s="378"/>
+      <c r="F25" s="378"/>
       <c r="G25" s="92" t="s">
         <v>59</v>
       </c>
       <c r="H25" s="81"/>
-      <c r="I25" s="361"/>
-      <c r="J25" s="362"/>
-      <c r="K25" s="362"/>
-      <c r="L25" s="362"/>
-      <c r="M25" s="362"/>
-      <c r="N25" s="440"/>
+      <c r="I25" s="349"/>
+      <c r="J25" s="343"/>
+      <c r="K25" s="343"/>
+      <c r="L25" s="343"/>
+      <c r="M25" s="343"/>
+      <c r="N25" s="344"/>
       <c r="Q25" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="306"/>
-      <c r="B26" s="367"/>
-      <c r="C26" s="368"/>
-      <c r="D26" s="308"/>
-      <c r="E26" s="308"/>
-      <c r="F26" s="308"/>
+      <c r="A26" s="397"/>
+      <c r="B26" s="400"/>
+      <c r="C26" s="401"/>
+      <c r="D26" s="395"/>
+      <c r="E26" s="395"/>
+      <c r="F26" s="395"/>
       <c r="G26" s="135"/>
       <c r="H26" s="140"/>
-      <c r="I26" s="350" t="s">
+      <c r="I26" s="421" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="294"/>
-      <c r="K26" s="294"/>
-      <c r="L26" s="294" t="s">
+      <c r="J26" s="422"/>
+      <c r="K26" s="422"/>
+      <c r="L26" s="422" t="s">
         <v>40</v>
       </c>
-      <c r="M26" s="294"/>
-      <c r="N26" s="295"/>
+      <c r="M26" s="422"/>
+      <c r="N26" s="423"/>
       <c r="Q26" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="305" t="s">
+      <c r="A27" s="396" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="371" t="s">
+      <c r="B27" s="402" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="290"/>
-      <c r="D27" s="307"/>
-      <c r="E27" s="307"/>
-      <c r="F27" s="307"/>
+      <c r="C27" s="399"/>
+      <c r="D27" s="378"/>
+      <c r="E27" s="378"/>
+      <c r="F27" s="378"/>
       <c r="G27" s="137"/>
       <c r="H27" s="87"/>
-      <c r="I27" s="361"/>
-      <c r="J27" s="362"/>
-      <c r="K27" s="362"/>
-      <c r="L27" s="362"/>
-      <c r="M27" s="362"/>
-      <c r="N27" s="440"/>
+      <c r="I27" s="349"/>
+      <c r="J27" s="343"/>
+      <c r="K27" s="343"/>
+      <c r="L27" s="343"/>
+      <c r="M27" s="343"/>
+      <c r="N27" s="344"/>
       <c r="Q27" s="3" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="306"/>
-      <c r="B28" s="367"/>
-      <c r="C28" s="368"/>
-      <c r="D28" s="308"/>
-      <c r="E28" s="308"/>
-      <c r="F28" s="308"/>
+      <c r="A28" s="397"/>
+      <c r="B28" s="400"/>
+      <c r="C28" s="401"/>
+      <c r="D28" s="395"/>
+      <c r="E28" s="395"/>
+      <c r="F28" s="395"/>
       <c r="G28" s="137"/>
       <c r="H28" s="87"/>
-      <c r="I28" s="351" t="s">
+      <c r="I28" s="424" t="s">
         <v>44</v>
       </c>
-      <c r="J28" s="352"/>
-      <c r="K28" s="352"/>
-      <c r="L28" s="353" t="s">
+      <c r="J28" s="425"/>
+      <c r="K28" s="425"/>
+      <c r="L28" s="426" t="s">
         <v>45</v>
       </c>
-      <c r="M28" s="352"/>
-      <c r="N28" s="354"/>
+      <c r="M28" s="425"/>
+      <c r="N28" s="427"/>
       <c r="Q28" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="305" t="s">
+      <c r="A29" s="396" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="289" t="s">
+      <c r="B29" s="398" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="290"/>
-      <c r="D29" s="309"/>
-      <c r="E29" s="307"/>
-      <c r="F29" s="310"/>
+      <c r="C29" s="399"/>
+      <c r="D29" s="445"/>
+      <c r="E29" s="378"/>
+      <c r="F29" s="446"/>
       <c r="G29" s="137"/>
       <c r="H29" s="144"/>
-      <c r="I29" s="374"/>
-      <c r="J29" s="372"/>
-      <c r="K29" s="372"/>
-      <c r="L29" s="372"/>
-      <c r="M29" s="372"/>
-      <c r="N29" s="373"/>
+      <c r="I29" s="405"/>
+      <c r="J29" s="403"/>
+      <c r="K29" s="403"/>
+      <c r="L29" s="403"/>
+      <c r="M29" s="403"/>
+      <c r="N29" s="404"/>
       <c r="Q29" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="306"/>
-      <c r="B30" s="367"/>
-      <c r="C30" s="368"/>
-      <c r="D30" s="311"/>
-      <c r="E30" s="308"/>
-      <c r="F30" s="312"/>
+      <c r="A30" s="397"/>
+      <c r="B30" s="400"/>
+      <c r="C30" s="401"/>
+      <c r="D30" s="447"/>
+      <c r="E30" s="395"/>
+      <c r="F30" s="448"/>
       <c r="G30" s="137"/>
       <c r="H30" s="144"/>
-      <c r="I30" s="438" t="s">
+      <c r="I30" s="341" t="s">
         <v>50</v>
       </c>
-      <c r="J30" s="438"/>
-      <c r="K30" s="438"/>
-      <c r="L30" s="438" t="s">
+      <c r="J30" s="341"/>
+      <c r="K30" s="341"/>
+      <c r="L30" s="341" t="s">
         <v>51</v>
       </c>
-      <c r="M30" s="438"/>
-      <c r="N30" s="439"/>
+      <c r="M30" s="341"/>
+      <c r="N30" s="342"/>
       <c r="Q30" s="3" t="s">
         <v>69</v>
       </c>
@@ -10702,19 +10653,19 @@
         <v>71</v>
       </c>
       <c r="C31" s="80"/>
-      <c r="D31" s="307"/>
-      <c r="E31" s="307"/>
-      <c r="F31" s="307"/>
-      <c r="G31" s="404" t="s">
+      <c r="D31" s="378"/>
+      <c r="E31" s="378"/>
+      <c r="F31" s="378"/>
+      <c r="G31" s="345" t="s">
         <v>55</v>
       </c>
-      <c r="H31" s="405"/>
-      <c r="I31" s="443"/>
-      <c r="J31" s="444"/>
-      <c r="K31" s="444"/>
-      <c r="L31" s="444"/>
-      <c r="M31" s="444"/>
-      <c r="N31" s="445"/>
+      <c r="H31" s="324"/>
+      <c r="I31" s="352"/>
+      <c r="J31" s="353"/>
+      <c r="K31" s="353"/>
+      <c r="L31" s="353"/>
+      <c r="M31" s="353"/>
+      <c r="N31" s="354"/>
       <c r="Q31" s="3" t="s">
         <v>72</v>
       </c>
@@ -10727,42 +10678,42 @@
         <v>74</v>
       </c>
       <c r="C32" s="80"/>
-      <c r="D32" s="349"/>
-      <c r="E32" s="349"/>
-      <c r="F32" s="349"/>
+      <c r="D32" s="390"/>
+      <c r="E32" s="390"/>
+      <c r="F32" s="390"/>
       <c r="G32" s="134" t="s">
         <v>75</v>
       </c>
       <c r="H32" s="138"/>
-      <c r="I32" s="356"/>
-      <c r="J32" s="357"/>
-      <c r="K32" s="357"/>
-      <c r="L32" s="357"/>
-      <c r="M32" s="357"/>
-      <c r="N32" s="358"/>
+      <c r="I32" s="346"/>
+      <c r="J32" s="347"/>
+      <c r="K32" s="347"/>
+      <c r="L32" s="347"/>
+      <c r="M32" s="347"/>
+      <c r="N32" s="348"/>
       <c r="Q32" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="407" t="s">
+      <c r="A33" s="387" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="369"/>
-      <c r="C33" s="370"/>
-      <c r="D33" s="349"/>
-      <c r="E33" s="349"/>
-      <c r="F33" s="349"/>
+      <c r="B33" s="388"/>
+      <c r="C33" s="389"/>
+      <c r="D33" s="390"/>
+      <c r="E33" s="390"/>
+      <c r="F33" s="390"/>
       <c r="G33" s="184" t="s">
         <v>78</v>
       </c>
       <c r="H33" s="136"/>
-      <c r="I33" s="356"/>
-      <c r="J33" s="357"/>
-      <c r="K33" s="357"/>
-      <c r="L33" s="357"/>
-      <c r="M33" s="357"/>
-      <c r="N33" s="358"/>
+      <c r="I33" s="346"/>
+      <c r="J33" s="347"/>
+      <c r="K33" s="347"/>
+      <c r="L33" s="347"/>
+      <c r="M33" s="347"/>
+      <c r="N33" s="348"/>
       <c r="Q33" s="3" t="s">
         <v>79</v>
       </c>
@@ -10773,19 +10724,19 @@
       </c>
       <c r="B34" s="203"/>
       <c r="C34" s="139"/>
-      <c r="D34" s="307"/>
-      <c r="E34" s="307"/>
-      <c r="F34" s="307"/>
+      <c r="D34" s="378"/>
+      <c r="E34" s="378"/>
+      <c r="F34" s="378"/>
       <c r="G34" s="92" t="s">
         <v>81</v>
       </c>
       <c r="H34" s="81"/>
-      <c r="I34" s="363"/>
-      <c r="J34" s="364"/>
-      <c r="K34" s="364"/>
-      <c r="L34" s="364"/>
-      <c r="M34" s="364"/>
-      <c r="N34" s="365"/>
+      <c r="I34" s="430"/>
+      <c r="J34" s="431"/>
+      <c r="K34" s="431"/>
+      <c r="L34" s="431"/>
+      <c r="M34" s="431"/>
+      <c r="N34" s="432"/>
       <c r="Q34" s="3" t="s">
         <v>82</v>
       </c>
@@ -10819,21 +10770,21 @@
         <v>86</v>
       </c>
       <c r="C36" s="208"/>
-      <c r="D36" s="316"/>
-      <c r="E36" s="317"/>
-      <c r="F36" s="317"/>
-      <c r="G36" s="317"/>
-      <c r="H36" s="318"/>
-      <c r="I36" s="441" t="s">
+      <c r="D36" s="452"/>
+      <c r="E36" s="453"/>
+      <c r="F36" s="453"/>
+      <c r="G36" s="453"/>
+      <c r="H36" s="454"/>
+      <c r="I36" s="350" t="s">
         <v>87</v>
       </c>
-      <c r="J36" s="441"/>
-      <c r="K36" s="441"/>
-      <c r="L36" s="442"/>
-      <c r="M36" s="386" t="s">
+      <c r="J36" s="350"/>
+      <c r="K36" s="350"/>
+      <c r="L36" s="351"/>
+      <c r="M36" s="366" t="s">
         <v>88</v>
       </c>
-      <c r="N36" s="387"/>
+      <c r="N36" s="367"/>
       <c r="Q36" s="3" t="s">
         <v>89</v>
       </c>
@@ -10844,17 +10795,17 @@
         <v>90</v>
       </c>
       <c r="C37" s="144"/>
-      <c r="D37" s="319"/>
-      <c r="E37" s="320"/>
-      <c r="F37" s="321"/>
-      <c r="G37" s="406" t="s">
+      <c r="D37" s="287"/>
+      <c r="E37" s="288"/>
+      <c r="F37" s="289"/>
+      <c r="G37" s="303" t="s">
         <v>91</v>
       </c>
-      <c r="H37" s="406"/>
-      <c r="I37" s="276"/>
-      <c r="J37" s="276"/>
-      <c r="K37" s="276"/>
-      <c r="L37" s="277"/>
+      <c r="H37" s="303"/>
+      <c r="I37" s="285"/>
+      <c r="J37" s="285"/>
+      <c r="K37" s="285"/>
+      <c r="L37" s="286"/>
       <c r="M37" s="283"/>
       <c r="N37" s="284"/>
       <c r="Q37" s="3" t="s">
@@ -10867,15 +10818,15 @@
         <v>93</v>
       </c>
       <c r="C38" s="198"/>
-      <c r="D38" s="319"/>
-      <c r="E38" s="320"/>
-      <c r="F38" s="320"/>
-      <c r="G38" s="320"/>
-      <c r="H38" s="321"/>
-      <c r="I38" s="276"/>
-      <c r="J38" s="276"/>
-      <c r="K38" s="276"/>
-      <c r="L38" s="277"/>
+      <c r="D38" s="287"/>
+      <c r="E38" s="288"/>
+      <c r="F38" s="288"/>
+      <c r="G38" s="288"/>
+      <c r="H38" s="289"/>
+      <c r="I38" s="285"/>
+      <c r="J38" s="285"/>
+      <c r="K38" s="285"/>
+      <c r="L38" s="286"/>
       <c r="M38" s="283"/>
       <c r="N38" s="284"/>
       <c r="Q38" s="3" t="s">
@@ -10888,15 +10839,15 @@
         <v>95</v>
       </c>
       <c r="C39" s="80"/>
-      <c r="D39" s="319"/>
-      <c r="E39" s="320"/>
-      <c r="F39" s="320"/>
-      <c r="G39" s="320"/>
-      <c r="H39" s="321"/>
-      <c r="I39" s="276"/>
-      <c r="J39" s="276"/>
-      <c r="K39" s="276"/>
-      <c r="L39" s="277"/>
+      <c r="D39" s="287"/>
+      <c r="E39" s="288"/>
+      <c r="F39" s="288"/>
+      <c r="G39" s="288"/>
+      <c r="H39" s="289"/>
+      <c r="I39" s="285"/>
+      <c r="J39" s="285"/>
+      <c r="K39" s="285"/>
+      <c r="L39" s="286"/>
       <c r="M39" s="283"/>
       <c r="N39" s="284"/>
       <c r="Q39" s="3" t="s">
@@ -10909,15 +10860,15 @@
         <v>97</v>
       </c>
       <c r="C40" s="80"/>
-      <c r="D40" s="319"/>
-      <c r="E40" s="320"/>
-      <c r="F40" s="320"/>
-      <c r="G40" s="320"/>
-      <c r="H40" s="321"/>
-      <c r="I40" s="276"/>
-      <c r="J40" s="276"/>
-      <c r="K40" s="276"/>
-      <c r="L40" s="277"/>
+      <c r="D40" s="287"/>
+      <c r="E40" s="288"/>
+      <c r="F40" s="288"/>
+      <c r="G40" s="288"/>
+      <c r="H40" s="289"/>
+      <c r="I40" s="285"/>
+      <c r="J40" s="285"/>
+      <c r="K40" s="285"/>
+      <c r="L40" s="286"/>
       <c r="M40" s="283"/>
       <c r="N40" s="284"/>
       <c r="Q40" s="3" t="s">
@@ -10930,15 +10881,15 @@
         <v>99</v>
       </c>
       <c r="C41" s="80"/>
-      <c r="D41" s="319"/>
-      <c r="E41" s="320"/>
-      <c r="F41" s="320"/>
-      <c r="G41" s="320"/>
-      <c r="H41" s="321"/>
-      <c r="I41" s="276"/>
-      <c r="J41" s="276"/>
-      <c r="K41" s="276"/>
-      <c r="L41" s="277"/>
+      <c r="D41" s="287"/>
+      <c r="E41" s="288"/>
+      <c r="F41" s="288"/>
+      <c r="G41" s="288"/>
+      <c r="H41" s="289"/>
+      <c r="I41" s="285"/>
+      <c r="J41" s="285"/>
+      <c r="K41" s="285"/>
+      <c r="L41" s="286"/>
       <c r="M41" s="283"/>
       <c r="N41" s="284"/>
       <c r="Q41" s="3" t="s">
@@ -10951,15 +10902,15 @@
         <v>101</v>
       </c>
       <c r="C42" s="119"/>
-      <c r="D42" s="319"/>
-      <c r="E42" s="320"/>
-      <c r="F42" s="320"/>
-      <c r="G42" s="320"/>
-      <c r="H42" s="321"/>
-      <c r="I42" s="276"/>
-      <c r="J42" s="276"/>
-      <c r="K42" s="276"/>
-      <c r="L42" s="277"/>
+      <c r="D42" s="287"/>
+      <c r="E42" s="288"/>
+      <c r="F42" s="288"/>
+      <c r="G42" s="288"/>
+      <c r="H42" s="289"/>
+      <c r="I42" s="285"/>
+      <c r="J42" s="285"/>
+      <c r="K42" s="285"/>
+      <c r="L42" s="286"/>
       <c r="M42" s="283"/>
       <c r="N42" s="284"/>
       <c r="Q42" s="3" t="s">
@@ -10974,15 +10925,15 @@
         <v>104</v>
       </c>
       <c r="C43" s="86"/>
-      <c r="D43" s="319"/>
-      <c r="E43" s="320"/>
-      <c r="F43" s="320"/>
-      <c r="G43" s="320"/>
-      <c r="H43" s="321"/>
-      <c r="I43" s="276"/>
-      <c r="J43" s="276"/>
-      <c r="K43" s="276"/>
-      <c r="L43" s="277"/>
+      <c r="D43" s="287"/>
+      <c r="E43" s="288"/>
+      <c r="F43" s="288"/>
+      <c r="G43" s="288"/>
+      <c r="H43" s="289"/>
+      <c r="I43" s="285"/>
+      <c r="J43" s="285"/>
+      <c r="K43" s="285"/>
+      <c r="L43" s="286"/>
       <c r="M43" s="283"/>
       <c r="N43" s="284"/>
       <c r="Q43" s="3" t="s">
@@ -10995,17 +10946,17 @@
         <v>13</v>
       </c>
       <c r="C44" s="140"/>
-      <c r="D44" s="319"/>
-      <c r="E44" s="320"/>
-      <c r="F44" s="321"/>
-      <c r="G44" s="406" t="s">
+      <c r="D44" s="287"/>
+      <c r="E44" s="288"/>
+      <c r="F44" s="289"/>
+      <c r="G44" s="303" t="s">
         <v>106</v>
       </c>
-      <c r="H44" s="406"/>
-      <c r="I44" s="276"/>
-      <c r="J44" s="276"/>
-      <c r="K44" s="276"/>
-      <c r="L44" s="277"/>
+      <c r="H44" s="303"/>
+      <c r="I44" s="285"/>
+      <c r="J44" s="285"/>
+      <c r="K44" s="285"/>
+      <c r="L44" s="286"/>
       <c r="M44" s="283"/>
       <c r="N44" s="284"/>
       <c r="Q44" s="3" t="s">
@@ -11018,15 +10969,15 @@
         <v>17</v>
       </c>
       <c r="C45" s="191"/>
-      <c r="D45" s="319"/>
-      <c r="E45" s="320"/>
-      <c r="F45" s="320"/>
-      <c r="G45" s="320"/>
-      <c r="H45" s="321"/>
-      <c r="I45" s="276"/>
-      <c r="J45" s="276"/>
-      <c r="K45" s="276"/>
-      <c r="L45" s="277"/>
+      <c r="D45" s="287"/>
+      <c r="E45" s="288"/>
+      <c r="F45" s="288"/>
+      <c r="G45" s="288"/>
+      <c r="H45" s="289"/>
+      <c r="I45" s="285"/>
+      <c r="J45" s="285"/>
+      <c r="K45" s="285"/>
+      <c r="L45" s="286"/>
       <c r="M45" s="283"/>
       <c r="N45" s="284"/>
       <c r="Q45" s="3" t="s">
@@ -11037,19 +10988,19 @@
       <c r="A46" s="135" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="289" t="s">
+      <c r="B46" s="398" t="s">
         <v>110</v>
       </c>
-      <c r="C46" s="289"/>
-      <c r="D46" s="289"/>
-      <c r="E46" s="289"/>
-      <c r="F46" s="289"/>
-      <c r="G46" s="289"/>
-      <c r="H46" s="290"/>
-      <c r="I46" s="276"/>
-      <c r="J46" s="276"/>
-      <c r="K46" s="276"/>
-      <c r="L46" s="277"/>
+      <c r="C46" s="398"/>
+      <c r="D46" s="398"/>
+      <c r="E46" s="398"/>
+      <c r="F46" s="398"/>
+      <c r="G46" s="398"/>
+      <c r="H46" s="399"/>
+      <c r="I46" s="285"/>
+      <c r="J46" s="285"/>
+      <c r="K46" s="285"/>
+      <c r="L46" s="286"/>
       <c r="M46" s="283"/>
       <c r="N46" s="284"/>
       <c r="Q46" s="3" t="s">
@@ -11062,15 +11013,15 @@
         <v>10</v>
       </c>
       <c r="C47" s="140"/>
-      <c r="D47" s="466"/>
-      <c r="E47" s="467"/>
-      <c r="F47" s="467"/>
-      <c r="G47" s="467"/>
-      <c r="H47" s="468"/>
-      <c r="I47" s="276"/>
-      <c r="J47" s="276"/>
-      <c r="K47" s="276"/>
-      <c r="L47" s="277"/>
+      <c r="D47" s="300"/>
+      <c r="E47" s="301"/>
+      <c r="F47" s="301"/>
+      <c r="G47" s="301"/>
+      <c r="H47" s="302"/>
+      <c r="I47" s="285"/>
+      <c r="J47" s="285"/>
+      <c r="K47" s="285"/>
+      <c r="L47" s="286"/>
       <c r="M47" s="283"/>
       <c r="N47" s="284"/>
       <c r="Q47" s="3" t="s">
@@ -11083,15 +11034,15 @@
         <v>13</v>
       </c>
       <c r="C48" s="140"/>
-      <c r="D48" s="466"/>
-      <c r="E48" s="467"/>
-      <c r="F48" s="467"/>
-      <c r="G48" s="467"/>
-      <c r="H48" s="468"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="276"/>
-      <c r="L48" s="277"/>
+      <c r="D48" s="300"/>
+      <c r="E48" s="301"/>
+      <c r="F48" s="301"/>
+      <c r="G48" s="301"/>
+      <c r="H48" s="302"/>
+      <c r="I48" s="285"/>
+      <c r="J48" s="285"/>
+      <c r="K48" s="285"/>
+      <c r="L48" s="286"/>
       <c r="M48" s="283"/>
       <c r="N48" s="284"/>
       <c r="Q48" s="3" t="s">
@@ -11104,19 +11055,19 @@
         <v>17</v>
       </c>
       <c r="C49" s="193"/>
-      <c r="D49" s="280"/>
-      <c r="E49" s="281"/>
-      <c r="F49" s="281"/>
-      <c r="G49" s="281"/>
-      <c r="H49" s="282"/>
-      <c r="I49" s="278" t="s">
+      <c r="D49" s="465"/>
+      <c r="E49" s="466"/>
+      <c r="F49" s="466"/>
+      <c r="G49" s="466"/>
+      <c r="H49" s="467"/>
+      <c r="I49" s="463" t="s">
         <v>114</v>
       </c>
-      <c r="J49" s="278"/>
-      <c r="K49" s="278"/>
-      <c r="L49" s="278"/>
-      <c r="M49" s="278"/>
-      <c r="N49" s="279"/>
+      <c r="J49" s="463"/>
+      <c r="K49" s="463"/>
+      <c r="L49" s="463"/>
+      <c r="M49" s="463"/>
+      <c r="N49" s="464"/>
       <c r="Q49" s="3" t="s">
         <v>115</v>
       </c>
@@ -11132,47 +11083,47 @@
       <c r="F50" s="83"/>
       <c r="G50" s="83"/>
       <c r="H50" s="83"/>
-      <c r="I50" s="396" t="s">
+      <c r="I50" s="376" t="s">
         <v>117</v>
       </c>
-      <c r="J50" s="396"/>
-      <c r="K50" s="396"/>
-      <c r="L50" s="396"/>
-      <c r="M50" s="396"/>
-      <c r="N50" s="397"/>
+      <c r="J50" s="376"/>
+      <c r="K50" s="376"/>
+      <c r="L50" s="376"/>
+      <c r="M50" s="376"/>
+      <c r="N50" s="377"/>
       <c r="Q50" s="3" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="388" t="s">
+      <c r="A51" s="368" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="414" t="s">
+      <c r="B51" s="319" t="s">
         <v>120</v>
       </c>
-      <c r="C51" s="414"/>
-      <c r="D51" s="417" t="s">
+      <c r="C51" s="319"/>
+      <c r="D51" s="304" t="s">
         <v>121</v>
       </c>
-      <c r="E51" s="418"/>
-      <c r="F51" s="419"/>
-      <c r="G51" s="417" t="s">
+      <c r="E51" s="305"/>
+      <c r="F51" s="322"/>
+      <c r="G51" s="304" t="s">
         <v>122</v>
       </c>
-      <c r="H51" s="418"/>
-      <c r="I51" s="469"/>
-      <c r="J51" s="285" t="s">
+      <c r="H51" s="305"/>
+      <c r="I51" s="306"/>
+      <c r="J51" s="468" t="s">
         <v>123</v>
       </c>
-      <c r="K51" s="286"/>
-      <c r="L51" s="461" t="s">
+      <c r="K51" s="469"/>
+      <c r="L51" s="295" t="s">
         <v>124</v>
       </c>
-      <c r="M51" s="390" t="s">
+      <c r="M51" s="370" t="s">
         <v>125</v>
       </c>
-      <c r="N51" s="384" t="s">
+      <c r="N51" s="364" t="s">
         <v>126</v>
       </c>
       <c r="Q51" s="3" t="s">
@@ -11180,43 +11131,43 @@
       </c>
     </row>
     <row r="52" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="389"/>
-      <c r="B52" s="415"/>
-      <c r="C52" s="415"/>
-      <c r="D52" s="420"/>
-      <c r="E52" s="421"/>
-      <c r="F52" s="422"/>
-      <c r="G52" s="420"/>
-      <c r="H52" s="421"/>
-      <c r="I52" s="470"/>
-      <c r="J52" s="287"/>
-      <c r="K52" s="288"/>
-      <c r="L52" s="461"/>
-      <c r="M52" s="390"/>
-      <c r="N52" s="384"/>
+      <c r="A52" s="369"/>
+      <c r="B52" s="320"/>
+      <c r="C52" s="320"/>
+      <c r="D52" s="307"/>
+      <c r="E52" s="308"/>
+      <c r="F52" s="323"/>
+      <c r="G52" s="307"/>
+      <c r="H52" s="308"/>
+      <c r="I52" s="309"/>
+      <c r="J52" s="470"/>
+      <c r="K52" s="471"/>
+      <c r="L52" s="295"/>
+      <c r="M52" s="370"/>
+      <c r="N52" s="364"/>
       <c r="Q52" s="3" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="206"/>
-      <c r="B53" s="416"/>
-      <c r="C53" s="416"/>
-      <c r="D53" s="423"/>
-      <c r="E53" s="424"/>
-      <c r="F53" s="405"/>
-      <c r="G53" s="423"/>
-      <c r="H53" s="424"/>
-      <c r="I53" s="471"/>
+      <c r="B53" s="321"/>
+      <c r="C53" s="321"/>
+      <c r="D53" s="310"/>
+      <c r="E53" s="311"/>
+      <c r="F53" s="324"/>
+      <c r="G53" s="310"/>
+      <c r="H53" s="311"/>
+      <c r="I53" s="312"/>
       <c r="J53" s="88" t="s">
         <v>129</v>
       </c>
       <c r="K53" s="89" t="s">
         <v>130</v>
       </c>
-      <c r="L53" s="462"/>
-      <c r="M53" s="391"/>
-      <c r="N53" s="385"/>
+      <c r="L53" s="296"/>
+      <c r="M53" s="371"/>
+      <c r="N53" s="365"/>
       <c r="O53" s="90"/>
       <c r="P53" s="90"/>
       <c r="Q53" s="3" t="s">
@@ -11229,12 +11180,12 @@
         <v>132</v>
       </c>
       <c r="C54" s="210"/>
-      <c r="D54" s="425"/>
-      <c r="E54" s="426"/>
-      <c r="F54" s="427"/>
-      <c r="G54" s="463"/>
-      <c r="H54" s="464"/>
-      <c r="I54" s="465"/>
+      <c r="D54" s="325"/>
+      <c r="E54" s="326"/>
+      <c r="F54" s="327"/>
+      <c r="G54" s="297"/>
+      <c r="H54" s="298"/>
+      <c r="I54" s="299"/>
       <c r="J54" s="249"/>
       <c r="K54" s="205"/>
       <c r="L54" s="253"/>
@@ -11250,12 +11201,12 @@
         <v>134</v>
       </c>
       <c r="C55" s="210"/>
-      <c r="D55" s="425"/>
-      <c r="E55" s="426"/>
-      <c r="F55" s="427"/>
-      <c r="G55" s="463"/>
-      <c r="H55" s="464"/>
-      <c r="I55" s="465"/>
+      <c r="D55" s="325"/>
+      <c r="E55" s="326"/>
+      <c r="F55" s="327"/>
+      <c r="G55" s="297"/>
+      <c r="H55" s="298"/>
+      <c r="I55" s="299"/>
       <c r="J55" s="249"/>
       <c r="K55" s="205"/>
       <c r="L55" s="256"/>
@@ -11271,12 +11222,12 @@
         <v>136</v>
       </c>
       <c r="C56" s="210"/>
-      <c r="D56" s="425"/>
-      <c r="E56" s="426"/>
-      <c r="F56" s="427"/>
-      <c r="G56" s="273"/>
-      <c r="H56" s="274"/>
-      <c r="I56" s="275"/>
+      <c r="D56" s="325"/>
+      <c r="E56" s="326"/>
+      <c r="F56" s="327"/>
+      <c r="G56" s="313"/>
+      <c r="H56" s="314"/>
+      <c r="I56" s="315"/>
       <c r="J56" s="249"/>
       <c r="K56" s="205"/>
       <c r="L56" s="253"/>
@@ -11292,12 +11243,12 @@
         <v>138</v>
       </c>
       <c r="C57" s="210"/>
-      <c r="D57" s="425"/>
-      <c r="E57" s="426"/>
-      <c r="F57" s="427"/>
-      <c r="G57" s="273"/>
-      <c r="H57" s="274"/>
-      <c r="I57" s="275"/>
+      <c r="D57" s="325"/>
+      <c r="E57" s="326"/>
+      <c r="F57" s="327"/>
+      <c r="G57" s="313"/>
+      <c r="H57" s="314"/>
+      <c r="I57" s="315"/>
       <c r="J57" s="249"/>
       <c r="K57" s="205"/>
       <c r="L57" s="253"/>
@@ -11313,12 +11264,12 @@
         <v>140</v>
       </c>
       <c r="C58" s="212"/>
-      <c r="D58" s="428"/>
-      <c r="E58" s="429"/>
-      <c r="F58" s="430"/>
-      <c r="G58" s="411"/>
-      <c r="H58" s="412"/>
-      <c r="I58" s="413"/>
+      <c r="D58" s="328"/>
+      <c r="E58" s="329"/>
+      <c r="F58" s="330"/>
+      <c r="G58" s="316"/>
+      <c r="H58" s="317"/>
+      <c r="I58" s="318"/>
       <c r="J58" s="258"/>
       <c r="K58" s="259"/>
       <c r="L58" s="260"/>
@@ -11329,66 +11280,66 @@
       </c>
     </row>
     <row r="59" spans="1:17" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="450" t="s">
+      <c r="A59" s="277" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="451"/>
-      <c r="C59" s="451"/>
-      <c r="D59" s="451"/>
-      <c r="E59" s="451"/>
-      <c r="F59" s="451"/>
-      <c r="G59" s="451"/>
-      <c r="H59" s="451"/>
-      <c r="I59" s="451"/>
-      <c r="J59" s="451"/>
-      <c r="K59" s="451"/>
-      <c r="L59" s="451"/>
-      <c r="M59" s="451"/>
-      <c r="N59" s="452"/>
+      <c r="B59" s="278"/>
+      <c r="C59" s="278"/>
+      <c r="D59" s="278"/>
+      <c r="E59" s="278"/>
+      <c r="F59" s="278"/>
+      <c r="G59" s="278"/>
+      <c r="H59" s="278"/>
+      <c r="I59" s="278"/>
+      <c r="J59" s="278"/>
+      <c r="K59" s="278"/>
+      <c r="L59" s="278"/>
+      <c r="M59" s="278"/>
+      <c r="N59" s="279"/>
       <c r="Q59" s="3" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="447" t="s">
+      <c r="A60" s="274" t="s">
         <v>143</v>
       </c>
-      <c r="B60" s="448"/>
-      <c r="C60" s="449"/>
-      <c r="D60" s="456"/>
-      <c r="E60" s="457"/>
-      <c r="F60" s="457"/>
-      <c r="G60" s="457"/>
-      <c r="H60" s="457"/>
-      <c r="I60" s="458"/>
-      <c r="J60" s="459" t="s">
+      <c r="B60" s="275"/>
+      <c r="C60" s="276"/>
+      <c r="D60" s="290"/>
+      <c r="E60" s="291"/>
+      <c r="F60" s="291"/>
+      <c r="G60" s="291"/>
+      <c r="H60" s="291"/>
+      <c r="I60" s="292"/>
+      <c r="J60" s="293" t="s">
         <v>144</v>
       </c>
-      <c r="K60" s="460"/>
-      <c r="L60" s="453"/>
-      <c r="M60" s="454"/>
-      <c r="N60" s="455"/>
+      <c r="K60" s="294"/>
+      <c r="L60" s="280"/>
+      <c r="M60" s="281"/>
+      <c r="N60" s="282"/>
       <c r="Q60" s="3" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="126" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="446" t="s">
+      <c r="A61" s="273" t="s">
         <v>402</v>
       </c>
-      <c r="B61" s="446"/>
-      <c r="C61" s="446"/>
-      <c r="D61" s="446"/>
-      <c r="E61" s="446"/>
-      <c r="F61" s="446"/>
-      <c r="G61" s="446"/>
-      <c r="H61" s="446"/>
-      <c r="I61" s="446"/>
-      <c r="J61" s="446"/>
-      <c r="K61" s="446"/>
-      <c r="L61" s="446"/>
-      <c r="M61" s="446"/>
-      <c r="N61" s="446"/>
+      <c r="B61" s="273"/>
+      <c r="C61" s="273"/>
+      <c r="D61" s="273"/>
+      <c r="E61" s="273"/>
+      <c r="F61" s="273"/>
+      <c r="G61" s="273"/>
+      <c r="H61" s="273"/>
+      <c r="I61" s="273"/>
+      <c r="J61" s="273"/>
+      <c r="K61" s="273"/>
+      <c r="L61" s="273"/>
+      <c r="M61" s="273"/>
+      <c r="N61" s="273"/>
       <c r="Q61" s="225" t="s">
         <v>146</v>
       </c>
@@ -15116,7 +15067,125 @@
       <headerFooter alignWithMargins="0"/>
     </customSheetView>
   </customSheetViews>
-  <mergeCells count="141">
+  <mergeCells count="142">
+    <mergeCell ref="J16:N16"/>
+    <mergeCell ref="G57:I57"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="I49:N49"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="J51:K52"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="I19:K20"/>
+    <mergeCell ref="L19:N20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="D25:F26"/>
+    <mergeCell ref="D27:F28"/>
+    <mergeCell ref="D29:F30"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="D17:F18"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I24:N24"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I33:N33"/>
+    <mergeCell ref="I34:N34"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="D22:F23"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C26"/>
+    <mergeCell ref="B27:C28"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="N51:N53"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="M51:M53"/>
+    <mergeCell ref="D10:N10"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="I50:N50"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="E20:F21"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="G58:I58"/>
+    <mergeCell ref="B51:C53"/>
+    <mergeCell ref="D51:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="I32:N32"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I31:N31"/>
+    <mergeCell ref="I37:L37"/>
     <mergeCell ref="A61:N61"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="A59:N59"/>
@@ -15141,123 +15210,6 @@
     <mergeCell ref="G51:I53"/>
     <mergeCell ref="G55:I55"/>
     <mergeCell ref="G56:I56"/>
-    <mergeCell ref="G58:I58"/>
-    <mergeCell ref="B51:C53"/>
-    <mergeCell ref="D51:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="I32:N32"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I31:N31"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="N51:N53"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="M51:M53"/>
-    <mergeCell ref="D10:N10"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="I50:N50"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="E20:F21"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="D22:F23"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C26"/>
-    <mergeCell ref="B27:C28"/>
-    <mergeCell ref="B29:C30"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I24:N24"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I33:N33"/>
-    <mergeCell ref="I34:N34"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="I19:K20"/>
-    <mergeCell ref="L19:N20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="D25:F26"/>
-    <mergeCell ref="D27:F28"/>
-    <mergeCell ref="D29:F30"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="D17:F18"/>
-    <mergeCell ref="B17:C18"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G57:I57"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I49:N49"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="J51:K52"/>
-    <mergeCell ref="B46:H46"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -15477,29 +15429,7 @@
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1055" r:id="rId209" name="Drop Down 31">
-              <controlPr locked="0" defaultSize="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>9</xdr:col>
-                    <xdr:colOff>22860</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>13</xdr:col>
-                    <xdr:colOff>594360</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>304800</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1045" r:id="rId210" name="Check Box 21">
+            <control shapeId="1045" r:id="rId209" name="Check Box 21">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15521,7 +15451,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1046" r:id="rId211" name="Check Box 22">
+            <control shapeId="1046" r:id="rId210" name="Check Box 22">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15543,7 +15473,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1049" r:id="rId212" name="Check Box 25">
+            <control shapeId="1049" r:id="rId211" name="Check Box 25">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15565,7 +15495,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1050" r:id="rId213" name="Check Box 26">
+            <control shapeId="1050" r:id="rId212" name="Check Box 26">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15587,7 +15517,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId214" name="Check Box 34">
+            <control shapeId="1058" r:id="rId213" name="Check Box 34">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15609,7 +15539,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId215" name="Check Box 35">
+            <control shapeId="1059" r:id="rId214" name="Check Box 35">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15631,7 +15561,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId216" name="Check Box 36">
+            <control shapeId="1060" r:id="rId215" name="Check Box 36">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15653,7 +15583,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId217" name="Check Box 37">
+            <control shapeId="1061" r:id="rId216" name="Check Box 37">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15675,7 +15605,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId218" name="Check Box 38">
+            <control shapeId="1062" r:id="rId217" name="Check Box 38">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15697,7 +15627,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId219" name="Check Box 39">
+            <control shapeId="1063" r:id="rId218" name="Check Box 39">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15719,7 +15649,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId220" name="Check Box 40">
+            <control shapeId="1064" r:id="rId219" name="Check Box 40">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15766,68 +15696,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="498"/>
-      <c r="B1" s="499"/>
-      <c r="C1" s="499"/>
-      <c r="D1" s="499"/>
-      <c r="E1" s="499"/>
-      <c r="F1" s="499"/>
-      <c r="G1" s="499"/>
-      <c r="H1" s="499"/>
-      <c r="I1" s="499"/>
-      <c r="J1" s="499"/>
-      <c r="K1" s="500"/>
+      <c r="A1" s="472"/>
+      <c r="B1" s="473"/>
+      <c r="C1" s="473"/>
+      <c r="D1" s="473"/>
+      <c r="E1" s="473"/>
+      <c r="F1" s="473"/>
+      <c r="G1" s="473"/>
+      <c r="H1" s="473"/>
+      <c r="I1" s="473"/>
+      <c r="J1" s="473"/>
+      <c r="K1" s="474"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="509" t="s">
+      <c r="A2" s="485" t="s">
         <v>303</v>
       </c>
-      <c r="B2" s="510"/>
-      <c r="C2" s="510"/>
-      <c r="D2" s="510"/>
-      <c r="E2" s="510"/>
-      <c r="F2" s="510"/>
-      <c r="G2" s="510"/>
-      <c r="H2" s="510"/>
-      <c r="I2" s="510"/>
-      <c r="J2" s="510"/>
-      <c r="K2" s="511"/>
+      <c r="B2" s="486"/>
+      <c r="C2" s="486"/>
+      <c r="D2" s="486"/>
+      <c r="E2" s="486"/>
+      <c r="F2" s="486"/>
+      <c r="G2" s="486"/>
+      <c r="H2" s="486"/>
+      <c r="I2" s="486"/>
+      <c r="J2" s="486"/>
+      <c r="K2" s="487"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="123" t="s">
         <v>304</v>
       </c>
-      <c r="B3" s="501" t="s">
+      <c r="B3" s="475" t="s">
         <v>305</v>
       </c>
-      <c r="C3" s="501"/>
-      <c r="D3" s="501"/>
-      <c r="E3" s="502"/>
-      <c r="F3" s="505" t="s">
+      <c r="C3" s="475"/>
+      <c r="D3" s="475"/>
+      <c r="E3" s="476"/>
+      <c r="F3" s="481" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="503" t="s">
+      <c r="G3" s="479" t="s">
         <v>307</v>
       </c>
-      <c r="H3" s="502"/>
-      <c r="I3" s="505" t="s">
+      <c r="H3" s="476"/>
+      <c r="I3" s="481" t="s">
         <v>308</v>
       </c>
-      <c r="J3" s="507" t="s">
+      <c r="J3" s="483" t="s">
         <v>309</v>
       </c>
-      <c r="K3" s="508"/>
+      <c r="K3" s="484"/>
     </row>
     <row r="4" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
-      <c r="B4" s="490"/>
-      <c r="C4" s="490"/>
-      <c r="D4" s="490"/>
-      <c r="E4" s="491"/>
-      <c r="F4" s="506"/>
-      <c r="G4" s="504"/>
-      <c r="H4" s="491"/>
-      <c r="I4" s="506"/>
+      <c r="B4" s="477"/>
+      <c r="C4" s="477"/>
+      <c r="D4" s="477"/>
+      <c r="E4" s="478"/>
+      <c r="F4" s="482"/>
+      <c r="G4" s="480"/>
+      <c r="H4" s="478"/>
+      <c r="I4" s="482"/>
       <c r="J4" s="5" t="s">
         <v>310</v>
       </c>
@@ -15836,125 +15766,125 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="520"/>
-      <c r="B5" s="521"/>
-      <c r="C5" s="521"/>
-      <c r="D5" s="521"/>
-      <c r="E5" s="522"/>
+      <c r="A5" s="500"/>
+      <c r="B5" s="501"/>
+      <c r="C5" s="501"/>
+      <c r="D5" s="501"/>
+      <c r="E5" s="502"/>
       <c r="F5" s="13"/>
-      <c r="G5" s="518"/>
-      <c r="H5" s="519"/>
+      <c r="G5" s="498"/>
+      <c r="H5" s="499"/>
       <c r="I5" s="240"/>
       <c r="J5" s="8"/>
       <c r="K5" s="15"/>
     </row>
     <row r="6" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="514"/>
-      <c r="B6" s="472"/>
-      <c r="C6" s="472"/>
-      <c r="D6" s="472"/>
-      <c r="E6" s="472"/>
+      <c r="A6" s="491"/>
+      <c r="B6" s="492"/>
+      <c r="C6" s="492"/>
+      <c r="D6" s="492"/>
+      <c r="E6" s="492"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="518"/>
-      <c r="H6" s="519"/>
+      <c r="G6" s="498"/>
+      <c r="H6" s="499"/>
       <c r="I6" s="240"/>
       <c r="J6" s="8"/>
       <c r="K6" s="15"/>
     </row>
     <row r="7" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="514"/>
-      <c r="B7" s="472"/>
-      <c r="C7" s="472"/>
-      <c r="D7" s="472"/>
-      <c r="E7" s="472"/>
+      <c r="A7" s="491"/>
+      <c r="B7" s="492"/>
+      <c r="C7" s="492"/>
+      <c r="D7" s="492"/>
+      <c r="E7" s="492"/>
       <c r="F7" s="13"/>
-      <c r="G7" s="474"/>
-      <c r="H7" s="474"/>
+      <c r="G7" s="490"/>
+      <c r="H7" s="490"/>
       <c r="I7" s="240"/>
       <c r="J7" s="8"/>
       <c r="K7" s="15"/>
     </row>
     <row r="8" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="514"/>
-      <c r="B8" s="472"/>
-      <c r="C8" s="472"/>
-      <c r="D8" s="472"/>
-      <c r="E8" s="472"/>
+      <c r="A8" s="491"/>
+      <c r="B8" s="492"/>
+      <c r="C8" s="492"/>
+      <c r="D8" s="492"/>
+      <c r="E8" s="492"/>
       <c r="F8" s="13"/>
-      <c r="G8" s="474"/>
-      <c r="H8" s="474"/>
+      <c r="G8" s="490"/>
+      <c r="H8" s="490"/>
       <c r="I8" s="240"/>
       <c r="J8" s="8"/>
       <c r="K8" s="15"/>
     </row>
     <row r="9" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="514"/>
-      <c r="B9" s="472"/>
-      <c r="C9" s="472"/>
-      <c r="D9" s="472"/>
-      <c r="E9" s="472"/>
+      <c r="A9" s="491"/>
+      <c r="B9" s="492"/>
+      <c r="C9" s="492"/>
+      <c r="D9" s="492"/>
+      <c r="E9" s="492"/>
       <c r="F9" s="13"/>
-      <c r="G9" s="474"/>
-      <c r="H9" s="474"/>
+      <c r="G9" s="490"/>
+      <c r="H9" s="490"/>
       <c r="I9" s="240"/>
       <c r="J9" s="8"/>
       <c r="K9" s="15"/>
     </row>
     <row r="10" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="514"/>
-      <c r="B10" s="472"/>
-      <c r="C10" s="472"/>
-      <c r="D10" s="472"/>
-      <c r="E10" s="472"/>
+      <c r="A10" s="491"/>
+      <c r="B10" s="492"/>
+      <c r="C10" s="492"/>
+      <c r="D10" s="492"/>
+      <c r="E10" s="492"/>
       <c r="F10" s="13"/>
-      <c r="G10" s="474"/>
-      <c r="H10" s="474"/>
+      <c r="G10" s="490"/>
+      <c r="H10" s="490"/>
       <c r="I10" s="240"/>
       <c r="J10" s="8"/>
       <c r="K10" s="15"/>
     </row>
     <row r="11" spans="1:11" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="487"/>
-      <c r="B11" s="479"/>
-      <c r="C11" s="479"/>
-      <c r="D11" s="479"/>
-      <c r="E11" s="479"/>
+      <c r="A11" s="507"/>
+      <c r="B11" s="508"/>
+      <c r="C11" s="508"/>
+      <c r="D11" s="508"/>
+      <c r="E11" s="508"/>
       <c r="F11" s="14"/>
-      <c r="G11" s="476"/>
-      <c r="H11" s="476"/>
+      <c r="G11" s="515"/>
+      <c r="H11" s="515"/>
       <c r="I11" s="241"/>
       <c r="J11" s="10"/>
       <c r="K11" s="16"/>
     </row>
     <row r="12" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="492" t="s">
+      <c r="A12" s="509" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="493"/>
-      <c r="C12" s="493"/>
-      <c r="D12" s="493"/>
-      <c r="E12" s="493"/>
-      <c r="F12" s="493"/>
-      <c r="G12" s="493"/>
-      <c r="H12" s="493"/>
-      <c r="I12" s="493"/>
-      <c r="J12" s="493"/>
-      <c r="K12" s="494"/>
+      <c r="B12" s="510"/>
+      <c r="C12" s="510"/>
+      <c r="D12" s="510"/>
+      <c r="E12" s="510"/>
+      <c r="F12" s="510"/>
+      <c r="G12" s="510"/>
+      <c r="H12" s="510"/>
+      <c r="I12" s="510"/>
+      <c r="J12" s="510"/>
+      <c r="K12" s="511"/>
     </row>
     <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="495" t="s">
+      <c r="A13" s="512" t="s">
         <v>312</v>
       </c>
-      <c r="B13" s="496"/>
-      <c r="C13" s="496"/>
-      <c r="D13" s="496"/>
-      <c r="E13" s="496"/>
-      <c r="F13" s="496"/>
-      <c r="G13" s="496"/>
-      <c r="H13" s="496"/>
-      <c r="I13" s="496"/>
-      <c r="J13" s="496"/>
-      <c r="K13" s="497"/>
+      <c r="B13" s="513"/>
+      <c r="C13" s="513"/>
+      <c r="D13" s="513"/>
+      <c r="E13" s="513"/>
+      <c r="F13" s="513"/>
+      <c r="G13" s="513"/>
+      <c r="H13" s="513"/>
+      <c r="I13" s="513"/>
+      <c r="J13" s="513"/>
+      <c r="K13" s="514"/>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="190" t="s">
@@ -15975,447 +15905,447 @@
       <c r="A15" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="B15" s="488" t="s">
+      <c r="B15" s="496" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="489"/>
-      <c r="D15" s="517" t="s">
+      <c r="C15" s="497"/>
+      <c r="D15" s="495" t="s">
         <v>315</v>
       </c>
-      <c r="E15" s="488"/>
-      <c r="F15" s="489"/>
-      <c r="G15" s="517" t="s">
+      <c r="E15" s="496"/>
+      <c r="F15" s="497"/>
+      <c r="G15" s="495" t="s">
         <v>316</v>
       </c>
-      <c r="H15" s="488"/>
-      <c r="I15" s="489"/>
-      <c r="J15" s="477" t="s">
+      <c r="H15" s="496"/>
+      <c r="I15" s="497"/>
+      <c r="J15" s="517" t="s">
         <v>317</v>
       </c>
-      <c r="K15" s="512" t="s">
+      <c r="K15" s="488" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="490"/>
-      <c r="C16" s="491"/>
-      <c r="D16" s="517"/>
-      <c r="E16" s="488"/>
-      <c r="F16" s="489"/>
-      <c r="G16" s="517"/>
-      <c r="H16" s="488"/>
-      <c r="I16" s="489"/>
-      <c r="J16" s="477"/>
-      <c r="K16" s="512"/>
+      <c r="B16" s="477"/>
+      <c r="C16" s="478"/>
+      <c r="D16" s="495"/>
+      <c r="E16" s="496"/>
+      <c r="F16" s="497"/>
+      <c r="G16" s="495"/>
+      <c r="H16" s="496"/>
+      <c r="I16" s="497"/>
+      <c r="J16" s="517"/>
+      <c r="K16" s="488"/>
     </row>
     <row r="17" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="515" t="s">
+      <c r="A17" s="493" t="s">
         <v>129</v>
       </c>
-      <c r="B17" s="516"/>
+      <c r="B17" s="494"/>
       <c r="C17" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D17" s="504"/>
-      <c r="E17" s="490"/>
-      <c r="F17" s="491"/>
-      <c r="G17" s="504"/>
-      <c r="H17" s="490"/>
-      <c r="I17" s="491"/>
-      <c r="J17" s="478"/>
-      <c r="K17" s="513"/>
+      <c r="D17" s="480"/>
+      <c r="E17" s="477"/>
+      <c r="F17" s="478"/>
+      <c r="G17" s="480"/>
+      <c r="H17" s="477"/>
+      <c r="I17" s="478"/>
+      <c r="J17" s="518"/>
+      <c r="K17" s="489"/>
     </row>
     <row r="18" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="473"/>
-      <c r="B18" s="474"/>
+      <c r="A18" s="506"/>
+      <c r="B18" s="490"/>
       <c r="C18" s="248"/>
-      <c r="D18" s="472"/>
-      <c r="E18" s="472"/>
-      <c r="F18" s="472"/>
-      <c r="G18" s="472"/>
-      <c r="H18" s="472"/>
-      <c r="I18" s="472"/>
+      <c r="D18" s="492"/>
+      <c r="E18" s="492"/>
+      <c r="F18" s="492"/>
+      <c r="G18" s="492"/>
+      <c r="H18" s="492"/>
+      <c r="I18" s="492"/>
       <c r="J18" s="8"/>
       <c r="K18" s="9"/>
     </row>
     <row r="19" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="473"/>
-      <c r="B19" s="474"/>
+      <c r="A19" s="506"/>
+      <c r="B19" s="490"/>
       <c r="C19" s="248"/>
-      <c r="D19" s="472"/>
-      <c r="E19" s="472"/>
-      <c r="F19" s="472"/>
-      <c r="G19" s="472"/>
-      <c r="H19" s="472"/>
-      <c r="I19" s="472"/>
+      <c r="D19" s="492"/>
+      <c r="E19" s="492"/>
+      <c r="F19" s="492"/>
+      <c r="G19" s="492"/>
+      <c r="H19" s="492"/>
+      <c r="I19" s="492"/>
       <c r="J19" s="8"/>
       <c r="K19" s="9"/>
     </row>
     <row r="20" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="473"/>
-      <c r="B20" s="474"/>
+      <c r="A20" s="506"/>
+      <c r="B20" s="490"/>
       <c r="C20" s="248"/>
-      <c r="D20" s="472"/>
-      <c r="E20" s="472"/>
-      <c r="F20" s="472"/>
-      <c r="G20" s="472"/>
-      <c r="H20" s="472"/>
-      <c r="I20" s="472"/>
+      <c r="D20" s="492"/>
+      <c r="E20" s="492"/>
+      <c r="F20" s="492"/>
+      <c r="G20" s="492"/>
+      <c r="H20" s="492"/>
+      <c r="I20" s="492"/>
       <c r="J20" s="8"/>
       <c r="K20" s="9"/>
     </row>
     <row r="21" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="473"/>
-      <c r="B21" s="474"/>
+      <c r="A21" s="506"/>
+      <c r="B21" s="490"/>
       <c r="C21" s="248"/>
-      <c r="D21" s="472"/>
-      <c r="E21" s="472"/>
-      <c r="F21" s="472"/>
-      <c r="G21" s="472"/>
-      <c r="H21" s="472"/>
-      <c r="I21" s="472"/>
+      <c r="D21" s="492"/>
+      <c r="E21" s="492"/>
+      <c r="F21" s="492"/>
+      <c r="G21" s="492"/>
+      <c r="H21" s="492"/>
+      <c r="I21" s="492"/>
       <c r="J21" s="8"/>
       <c r="K21" s="9"/>
     </row>
     <row r="22" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="473"/>
-      <c r="B22" s="474"/>
+      <c r="A22" s="506"/>
+      <c r="B22" s="490"/>
       <c r="C22" s="248"/>
-      <c r="D22" s="472"/>
-      <c r="E22" s="472"/>
-      <c r="F22" s="472"/>
-      <c r="G22" s="472"/>
-      <c r="H22" s="472"/>
-      <c r="I22" s="472"/>
+      <c r="D22" s="492"/>
+      <c r="E22" s="492"/>
+      <c r="F22" s="492"/>
+      <c r="G22" s="492"/>
+      <c r="H22" s="492"/>
+      <c r="I22" s="492"/>
       <c r="J22" s="8"/>
       <c r="K22" s="9"/>
     </row>
     <row r="23" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="473"/>
-      <c r="B23" s="474"/>
+      <c r="A23" s="506"/>
+      <c r="B23" s="490"/>
       <c r="C23" s="248"/>
-      <c r="D23" s="472"/>
-      <c r="E23" s="472"/>
-      <c r="F23" s="472"/>
-      <c r="G23" s="472"/>
-      <c r="H23" s="472"/>
-      <c r="I23" s="472"/>
+      <c r="D23" s="492"/>
+      <c r="E23" s="492"/>
+      <c r="F23" s="492"/>
+      <c r="G23" s="492"/>
+      <c r="H23" s="492"/>
+      <c r="I23" s="492"/>
       <c r="J23" s="8"/>
       <c r="K23" s="9"/>
     </row>
     <row r="24" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="473"/>
-      <c r="B24" s="474"/>
+      <c r="A24" s="506"/>
+      <c r="B24" s="490"/>
       <c r="C24" s="248"/>
-      <c r="D24" s="472"/>
-      <c r="E24" s="472"/>
-      <c r="F24" s="472"/>
-      <c r="G24" s="472"/>
-      <c r="H24" s="472"/>
-      <c r="I24" s="472"/>
+      <c r="D24" s="492"/>
+      <c r="E24" s="492"/>
+      <c r="F24" s="492"/>
+      <c r="G24" s="492"/>
+      <c r="H24" s="492"/>
+      <c r="I24" s="492"/>
       <c r="J24" s="8"/>
       <c r="K24" s="9"/>
     </row>
     <row r="25" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="473"/>
-      <c r="B25" s="474"/>
+      <c r="A25" s="506"/>
+      <c r="B25" s="490"/>
       <c r="C25" s="248"/>
-      <c r="D25" s="472"/>
-      <c r="E25" s="472"/>
-      <c r="F25" s="472"/>
-      <c r="G25" s="472"/>
-      <c r="H25" s="472"/>
-      <c r="I25" s="472"/>
+      <c r="D25" s="492"/>
+      <c r="E25" s="492"/>
+      <c r="F25" s="492"/>
+      <c r="G25" s="492"/>
+      <c r="H25" s="492"/>
+      <c r="I25" s="492"/>
       <c r="J25" s="8"/>
       <c r="K25" s="9"/>
     </row>
     <row r="26" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="473"/>
-      <c r="B26" s="474"/>
+      <c r="A26" s="506"/>
+      <c r="B26" s="490"/>
       <c r="C26" s="248"/>
-      <c r="D26" s="472"/>
-      <c r="E26" s="472"/>
-      <c r="F26" s="472"/>
-      <c r="G26" s="472"/>
-      <c r="H26" s="472"/>
-      <c r="I26" s="472"/>
+      <c r="D26" s="492"/>
+      <c r="E26" s="492"/>
+      <c r="F26" s="492"/>
+      <c r="G26" s="492"/>
+      <c r="H26" s="492"/>
+      <c r="I26" s="492"/>
       <c r="J26" s="8"/>
       <c r="K26" s="9"/>
     </row>
     <row r="27" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="473"/>
-      <c r="B27" s="474"/>
+      <c r="A27" s="506"/>
+      <c r="B27" s="490"/>
       <c r="C27" s="248"/>
-      <c r="D27" s="472"/>
-      <c r="E27" s="472"/>
-      <c r="F27" s="472"/>
-      <c r="G27" s="472"/>
-      <c r="H27" s="472"/>
-      <c r="I27" s="472"/>
+      <c r="D27" s="492"/>
+      <c r="E27" s="492"/>
+      <c r="F27" s="492"/>
+      <c r="G27" s="492"/>
+      <c r="H27" s="492"/>
+      <c r="I27" s="492"/>
       <c r="J27" s="8"/>
       <c r="K27" s="9"/>
     </row>
     <row r="28" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="473"/>
-      <c r="B28" s="474"/>
+      <c r="A28" s="506"/>
+      <c r="B28" s="490"/>
       <c r="C28" s="248"/>
-      <c r="D28" s="472"/>
-      <c r="E28" s="472"/>
-      <c r="F28" s="472"/>
-      <c r="G28" s="472"/>
-      <c r="H28" s="472"/>
-      <c r="I28" s="472"/>
+      <c r="D28" s="492"/>
+      <c r="E28" s="492"/>
+      <c r="F28" s="492"/>
+      <c r="G28" s="492"/>
+      <c r="H28" s="492"/>
+      <c r="I28" s="492"/>
       <c r="J28" s="8"/>
       <c r="K28" s="9"/>
     </row>
     <row r="29" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="473"/>
-      <c r="B29" s="474"/>
+      <c r="A29" s="506"/>
+      <c r="B29" s="490"/>
       <c r="C29" s="248"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
-      <c r="G29" s="472"/>
-      <c r="H29" s="472"/>
-      <c r="I29" s="472"/>
+      <c r="D29" s="492"/>
+      <c r="E29" s="492"/>
+      <c r="F29" s="492"/>
+      <c r="G29" s="492"/>
+      <c r="H29" s="492"/>
+      <c r="I29" s="492"/>
       <c r="J29" s="8"/>
       <c r="K29" s="9"/>
     </row>
     <row r="30" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="473"/>
-      <c r="B30" s="474"/>
+      <c r="A30" s="506"/>
+      <c r="B30" s="490"/>
       <c r="C30" s="248"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
-      <c r="G30" s="472"/>
-      <c r="H30" s="472"/>
-      <c r="I30" s="472"/>
+      <c r="D30" s="492"/>
+      <c r="E30" s="492"/>
+      <c r="F30" s="492"/>
+      <c r="G30" s="492"/>
+      <c r="H30" s="492"/>
+      <c r="I30" s="492"/>
       <c r="J30" s="8"/>
       <c r="K30" s="9"/>
     </row>
     <row r="31" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="473"/>
-      <c r="B31" s="474"/>
+      <c r="A31" s="506"/>
+      <c r="B31" s="490"/>
       <c r="C31" s="248"/>
-      <c r="D31" s="472"/>
-      <c r="E31" s="472"/>
-      <c r="F31" s="472"/>
-      <c r="G31" s="472"/>
-      <c r="H31" s="472"/>
-      <c r="I31" s="472"/>
+      <c r="D31" s="492"/>
+      <c r="E31" s="492"/>
+      <c r="F31" s="492"/>
+      <c r="G31" s="492"/>
+      <c r="H31" s="492"/>
+      <c r="I31" s="492"/>
       <c r="J31" s="8"/>
       <c r="K31" s="9"/>
     </row>
     <row r="32" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="473"/>
-      <c r="B32" s="474"/>
+      <c r="A32" s="506"/>
+      <c r="B32" s="490"/>
       <c r="C32" s="248"/>
-      <c r="D32" s="472"/>
-      <c r="E32" s="472"/>
-      <c r="F32" s="472"/>
-      <c r="G32" s="472"/>
-      <c r="H32" s="472"/>
-      <c r="I32" s="472"/>
+      <c r="D32" s="492"/>
+      <c r="E32" s="492"/>
+      <c r="F32" s="492"/>
+      <c r="G32" s="492"/>
+      <c r="H32" s="492"/>
+      <c r="I32" s="492"/>
       <c r="J32" s="8"/>
       <c r="K32" s="9"/>
     </row>
     <row r="33" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="473"/>
-      <c r="B33" s="474"/>
+      <c r="A33" s="506"/>
+      <c r="B33" s="490"/>
       <c r="C33" s="248"/>
-      <c r="D33" s="472"/>
-      <c r="E33" s="472"/>
-      <c r="F33" s="472"/>
-      <c r="G33" s="472"/>
-      <c r="H33" s="472"/>
-      <c r="I33" s="472"/>
+      <c r="D33" s="492"/>
+      <c r="E33" s="492"/>
+      <c r="F33" s="492"/>
+      <c r="G33" s="492"/>
+      <c r="H33" s="492"/>
+      <c r="I33" s="492"/>
       <c r="J33" s="8"/>
       <c r="K33" s="9"/>
     </row>
     <row r="34" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="473"/>
-      <c r="B34" s="474"/>
+      <c r="A34" s="506"/>
+      <c r="B34" s="490"/>
       <c r="C34" s="248"/>
-      <c r="D34" s="472"/>
-      <c r="E34" s="472"/>
-      <c r="F34" s="472"/>
-      <c r="G34" s="472"/>
-      <c r="H34" s="472"/>
-      <c r="I34" s="472"/>
+      <c r="D34" s="492"/>
+      <c r="E34" s="492"/>
+      <c r="F34" s="492"/>
+      <c r="G34" s="492"/>
+      <c r="H34" s="492"/>
+      <c r="I34" s="492"/>
       <c r="J34" s="8"/>
       <c r="K34" s="9"/>
     </row>
     <row r="35" spans="1:12" s="12" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="473"/>
-      <c r="B35" s="474"/>
+      <c r="A35" s="506"/>
+      <c r="B35" s="490"/>
       <c r="C35" s="248"/>
-      <c r="D35" s="472"/>
-      <c r="E35" s="472"/>
-      <c r="F35" s="472"/>
-      <c r="G35" s="472"/>
-      <c r="H35" s="472"/>
-      <c r="I35" s="472"/>
+      <c r="D35" s="492"/>
+      <c r="E35" s="492"/>
+      <c r="F35" s="492"/>
+      <c r="G35" s="492"/>
+      <c r="H35" s="492"/>
+      <c r="I35" s="492"/>
       <c r="J35" s="8"/>
       <c r="K35" s="9"/>
     </row>
     <row r="36" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="473"/>
-      <c r="B36" s="474"/>
+      <c r="A36" s="506"/>
+      <c r="B36" s="490"/>
       <c r="C36" s="248"/>
-      <c r="D36" s="472"/>
-      <c r="E36" s="472"/>
-      <c r="F36" s="472"/>
-      <c r="G36" s="472"/>
-      <c r="H36" s="472"/>
-      <c r="I36" s="472"/>
+      <c r="D36" s="492"/>
+      <c r="E36" s="492"/>
+      <c r="F36" s="492"/>
+      <c r="G36" s="492"/>
+      <c r="H36" s="492"/>
+      <c r="I36" s="492"/>
       <c r="J36" s="8"/>
       <c r="K36" s="9"/>
     </row>
     <row r="37" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="473"/>
-      <c r="B37" s="474"/>
+      <c r="A37" s="506"/>
+      <c r="B37" s="490"/>
       <c r="C37" s="248"/>
-      <c r="D37" s="472"/>
-      <c r="E37" s="472"/>
-      <c r="F37" s="472"/>
-      <c r="G37" s="472"/>
-      <c r="H37" s="472"/>
-      <c r="I37" s="472"/>
+      <c r="D37" s="492"/>
+      <c r="E37" s="492"/>
+      <c r="F37" s="492"/>
+      <c r="G37" s="492"/>
+      <c r="H37" s="492"/>
+      <c r="I37" s="492"/>
       <c r="J37" s="8"/>
       <c r="K37" s="9"/>
     </row>
     <row r="38" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="473"/>
-      <c r="B38" s="474"/>
+      <c r="A38" s="506"/>
+      <c r="B38" s="490"/>
       <c r="C38" s="248"/>
-      <c r="D38" s="472"/>
-      <c r="E38" s="472"/>
-      <c r="F38" s="472"/>
-      <c r="G38" s="472"/>
-      <c r="H38" s="472"/>
-      <c r="I38" s="472"/>
+      <c r="D38" s="492"/>
+      <c r="E38" s="492"/>
+      <c r="F38" s="492"/>
+      <c r="G38" s="492"/>
+      <c r="H38" s="492"/>
+      <c r="I38" s="492"/>
       <c r="J38" s="8"/>
       <c r="K38" s="9"/>
     </row>
     <row r="39" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="473"/>
-      <c r="B39" s="474"/>
+      <c r="A39" s="506"/>
+      <c r="B39" s="490"/>
       <c r="C39" s="248"/>
-      <c r="D39" s="472"/>
-      <c r="E39" s="472"/>
-      <c r="F39" s="472"/>
-      <c r="G39" s="472"/>
-      <c r="H39" s="472"/>
-      <c r="I39" s="472"/>
+      <c r="D39" s="492"/>
+      <c r="E39" s="492"/>
+      <c r="F39" s="492"/>
+      <c r="G39" s="492"/>
+      <c r="H39" s="492"/>
+      <c r="I39" s="492"/>
       <c r="J39" s="8"/>
       <c r="K39" s="9"/>
     </row>
     <row r="40" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="473"/>
-      <c r="B40" s="474"/>
+      <c r="A40" s="506"/>
+      <c r="B40" s="490"/>
       <c r="C40" s="248"/>
-      <c r="D40" s="472"/>
-      <c r="E40" s="472"/>
-      <c r="F40" s="472"/>
-      <c r="G40" s="472"/>
-      <c r="H40" s="472"/>
-      <c r="I40" s="472"/>
+      <c r="D40" s="492"/>
+      <c r="E40" s="492"/>
+      <c r="F40" s="492"/>
+      <c r="G40" s="492"/>
+      <c r="H40" s="492"/>
+      <c r="I40" s="492"/>
       <c r="J40" s="8"/>
       <c r="K40" s="9"/>
     </row>
     <row r="41" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="473"/>
-      <c r="B41" s="474"/>
+      <c r="A41" s="506"/>
+      <c r="B41" s="490"/>
       <c r="C41" s="248"/>
-      <c r="D41" s="472"/>
-      <c r="E41" s="472"/>
-      <c r="F41" s="472"/>
-      <c r="G41" s="472"/>
-      <c r="H41" s="472"/>
-      <c r="I41" s="472"/>
+      <c r="D41" s="492"/>
+      <c r="E41" s="492"/>
+      <c r="F41" s="492"/>
+      <c r="G41" s="492"/>
+      <c r="H41" s="492"/>
+      <c r="I41" s="492"/>
       <c r="J41" s="8"/>
       <c r="K41" s="9"/>
     </row>
     <row r="42" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="473"/>
-      <c r="B42" s="474"/>
+      <c r="A42" s="506"/>
+      <c r="B42" s="490"/>
       <c r="C42" s="248"/>
-      <c r="D42" s="472"/>
-      <c r="E42" s="472"/>
-      <c r="F42" s="472"/>
-      <c r="G42" s="472"/>
-      <c r="H42" s="472"/>
-      <c r="I42" s="472"/>
+      <c r="D42" s="492"/>
+      <c r="E42" s="492"/>
+      <c r="F42" s="492"/>
+      <c r="G42" s="492"/>
+      <c r="H42" s="492"/>
+      <c r="I42" s="492"/>
       <c r="J42" s="8"/>
       <c r="K42" s="9"/>
     </row>
     <row r="43" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="473"/>
-      <c r="B43" s="474"/>
+      <c r="A43" s="506"/>
+      <c r="B43" s="490"/>
       <c r="C43" s="248"/>
-      <c r="D43" s="472"/>
-      <c r="E43" s="472"/>
-      <c r="F43" s="472"/>
-      <c r="G43" s="472"/>
-      <c r="H43" s="472"/>
-      <c r="I43" s="472"/>
+      <c r="D43" s="492"/>
+      <c r="E43" s="492"/>
+      <c r="F43" s="492"/>
+      <c r="G43" s="492"/>
+      <c r="H43" s="492"/>
+      <c r="I43" s="492"/>
       <c r="J43" s="8"/>
       <c r="K43" s="9"/>
     </row>
     <row r="44" spans="1:12" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="473"/>
-      <c r="B44" s="474"/>
+      <c r="A44" s="506"/>
+      <c r="B44" s="490"/>
       <c r="C44" s="248"/>
-      <c r="D44" s="472"/>
-      <c r="E44" s="472"/>
-      <c r="F44" s="472"/>
-      <c r="G44" s="472"/>
-      <c r="H44" s="472"/>
-      <c r="I44" s="472"/>
+      <c r="D44" s="492"/>
+      <c r="E44" s="492"/>
+      <c r="F44" s="492"/>
+      <c r="G44" s="492"/>
+      <c r="H44" s="492"/>
+      <c r="I44" s="492"/>
       <c r="J44" s="8"/>
       <c r="K44" s="9"/>
     </row>
     <row r="45" spans="1:12" s="12" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="475"/>
-      <c r="B45" s="476"/>
+      <c r="A45" s="516"/>
+      <c r="B45" s="515"/>
       <c r="C45" s="247"/>
-      <c r="D45" s="479"/>
-      <c r="E45" s="479"/>
-      <c r="F45" s="479"/>
-      <c r="G45" s="479"/>
-      <c r="H45" s="479"/>
-      <c r="I45" s="479"/>
+      <c r="D45" s="508"/>
+      <c r="E45" s="508"/>
+      <c r="F45" s="508"/>
+      <c r="G45" s="508"/>
+      <c r="H45" s="508"/>
+      <c r="I45" s="508"/>
       <c r="J45" s="10"/>
       <c r="K45" s="11"/>
     </row>
     <row r="46" spans="1:12" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="480" t="s">
+      <c r="A46" s="519" t="s">
         <v>114</v>
       </c>
-      <c r="B46" s="481"/>
-      <c r="C46" s="481"/>
-      <c r="D46" s="481"/>
-      <c r="E46" s="481"/>
-      <c r="F46" s="481"/>
-      <c r="G46" s="481"/>
-      <c r="H46" s="481"/>
-      <c r="I46" s="481"/>
-      <c r="J46" s="482"/>
-      <c r="K46" s="483"/>
+      <c r="B46" s="520"/>
+      <c r="C46" s="520"/>
+      <c r="D46" s="520"/>
+      <c r="E46" s="520"/>
+      <c r="F46" s="520"/>
+      <c r="G46" s="520"/>
+      <c r="H46" s="520"/>
+      <c r="I46" s="520"/>
+      <c r="J46" s="521"/>
+      <c r="K46" s="522"/>
     </row>
     <row r="47" spans="1:12" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="447" t="s">
+      <c r="A47" s="274" t="s">
         <v>143</v>
       </c>
-      <c r="B47" s="448"/>
-      <c r="C47" s="449"/>
-      <c r="D47" s="484"/>
-      <c r="E47" s="485"/>
-      <c r="F47" s="485"/>
-      <c r="G47" s="485"/>
-      <c r="H47" s="486"/>
+      <c r="B47" s="275"/>
+      <c r="C47" s="276"/>
+      <c r="D47" s="503"/>
+      <c r="E47" s="504"/>
+      <c r="F47" s="504"/>
+      <c r="G47" s="504"/>
+      <c r="H47" s="505"/>
       <c r="I47" s="221" t="s">
         <v>144</v>
       </c>
@@ -16424,19 +16354,19 @@
       <c r="L47" s="223"/>
     </row>
     <row r="48" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="446" t="s">
+      <c r="A48" s="273" t="s">
         <v>401</v>
       </c>
-      <c r="B48" s="446"/>
-      <c r="C48" s="446"/>
-      <c r="D48" s="446"/>
-      <c r="E48" s="446"/>
-      <c r="F48" s="446"/>
-      <c r="G48" s="446"/>
-      <c r="H48" s="446"/>
-      <c r="I48" s="446"/>
-      <c r="J48" s="446"/>
-      <c r="K48" s="446"/>
+      <c r="B48" s="273"/>
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
       <c r="L48" s="226"/>
     </row>
   </sheetData>
@@ -16450,29 +16380,76 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="117">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B3:E4"/>
-    <mergeCell ref="G3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="K15:K17"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D15:F17"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="G15:I17"/>
+    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="G25:I25"/>
     <mergeCell ref="A48:K48"/>
     <mergeCell ref="D47:H47"/>
     <mergeCell ref="G43:I43"/>
@@ -16497,76 +16474,29 @@
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G41:I41"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="G44:I44"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B3:E4"/>
+    <mergeCell ref="G3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="K15:K17"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D15:F17"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="G15:I17"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -16598,280 +16528,280 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="543"/>
-      <c r="B1" s="544"/>
-      <c r="C1" s="544"/>
-      <c r="D1" s="544"/>
-      <c r="E1" s="544"/>
-      <c r="F1" s="544"/>
-      <c r="G1" s="544"/>
-      <c r="H1" s="544"/>
-      <c r="I1" s="544"/>
-      <c r="J1" s="544"/>
-      <c r="K1" s="545"/>
+      <c r="A1" s="552"/>
+      <c r="B1" s="553"/>
+      <c r="C1" s="553"/>
+      <c r="D1" s="553"/>
+      <c r="E1" s="553"/>
+      <c r="F1" s="553"/>
+      <c r="G1" s="553"/>
+      <c r="H1" s="553"/>
+      <c r="I1" s="553"/>
+      <c r="J1" s="553"/>
+      <c r="K1" s="554"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="570" t="s">
+      <c r="A2" s="574" t="s">
         <v>319</v>
       </c>
-      <c r="B2" s="571"/>
-      <c r="C2" s="571"/>
-      <c r="D2" s="571"/>
-      <c r="E2" s="571"/>
-      <c r="F2" s="571"/>
-      <c r="G2" s="571"/>
-      <c r="H2" s="571"/>
-      <c r="I2" s="571"/>
-      <c r="J2" s="571"/>
-      <c r="K2" s="572"/>
+      <c r="B2" s="575"/>
+      <c r="C2" s="575"/>
+      <c r="D2" s="575"/>
+      <c r="E2" s="575"/>
+      <c r="F2" s="575"/>
+      <c r="G2" s="575"/>
+      <c r="H2" s="575"/>
+      <c r="I2" s="575"/>
+      <c r="J2" s="575"/>
+      <c r="K2" s="576"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="554" t="s">
+      <c r="A3" s="560" t="s">
         <v>320</v>
       </c>
-      <c r="B3" s="555" t="s">
+      <c r="B3" s="562" t="s">
         <v>321</v>
       </c>
-      <c r="C3" s="555"/>
-      <c r="D3" s="556"/>
-      <c r="E3" s="501" t="s">
+      <c r="C3" s="562"/>
+      <c r="D3" s="563"/>
+      <c r="E3" s="475" t="s">
         <v>322</v>
       </c>
-      <c r="F3" s="502"/>
-      <c r="G3" s="579" t="s">
+      <c r="F3" s="476"/>
+      <c r="G3" s="537" t="s">
         <v>323</v>
       </c>
-      <c r="H3" s="503" t="s">
+      <c r="H3" s="479" t="s">
         <v>324</v>
       </c>
-      <c r="I3" s="565"/>
-      <c r="J3" s="565"/>
-      <c r="K3" s="566"/>
+      <c r="I3" s="569"/>
+      <c r="J3" s="569"/>
+      <c r="K3" s="570"/>
     </row>
     <row r="4" spans="1:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="542"/>
-      <c r="B4" s="557"/>
-      <c r="C4" s="557"/>
-      <c r="D4" s="558"/>
-      <c r="E4" s="490"/>
-      <c r="F4" s="491"/>
-      <c r="G4" s="580"/>
-      <c r="H4" s="567"/>
-      <c r="I4" s="546"/>
-      <c r="J4" s="546"/>
-      <c r="K4" s="568"/>
+      <c r="A4" s="561"/>
+      <c r="B4" s="564"/>
+      <c r="C4" s="564"/>
+      <c r="D4" s="565"/>
+      <c r="E4" s="477"/>
+      <c r="F4" s="478"/>
+      <c r="G4" s="538"/>
+      <c r="H4" s="571"/>
+      <c r="I4" s="555"/>
+      <c r="J4" s="555"/>
+      <c r="K4" s="572"/>
     </row>
     <row r="5" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17"/>
-      <c r="B5" s="573"/>
-      <c r="C5" s="573"/>
-      <c r="D5" s="574"/>
+      <c r="B5" s="577"/>
+      <c r="C5" s="577"/>
+      <c r="D5" s="578"/>
       <c r="E5" s="18" t="s">
         <v>129</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G5" s="581"/>
-      <c r="H5" s="569"/>
-      <c r="I5" s="432"/>
-      <c r="J5" s="432"/>
-      <c r="K5" s="433"/>
+      <c r="G5" s="539"/>
+      <c r="H5" s="573"/>
+      <c r="I5" s="332"/>
+      <c r="J5" s="332"/>
+      <c r="K5" s="333"/>
     </row>
     <row r="6" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="562"/>
-      <c r="B6" s="563"/>
-      <c r="C6" s="563"/>
-      <c r="D6" s="564"/>
+      <c r="A6" s="534"/>
+      <c r="B6" s="535"/>
+      <c r="C6" s="535"/>
+      <c r="D6" s="536"/>
       <c r="E6" s="262"/>
       <c r="F6" s="262"/>
       <c r="G6" s="263"/>
-      <c r="H6" s="549"/>
-      <c r="I6" s="550"/>
-      <c r="J6" s="550"/>
-      <c r="K6" s="551"/>
+      <c r="H6" s="540"/>
+      <c r="I6" s="541"/>
+      <c r="J6" s="541"/>
+      <c r="K6" s="542"/>
     </row>
     <row r="7" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="562"/>
-      <c r="B7" s="563"/>
-      <c r="C7" s="563"/>
-      <c r="D7" s="564"/>
+      <c r="A7" s="534"/>
+      <c r="B7" s="535"/>
+      <c r="C7" s="535"/>
+      <c r="D7" s="536"/>
       <c r="E7" s="262"/>
       <c r="F7" s="262"/>
       <c r="G7" s="263"/>
-      <c r="H7" s="549"/>
-      <c r="I7" s="550"/>
-      <c r="J7" s="550"/>
-      <c r="K7" s="551"/>
+      <c r="H7" s="540"/>
+      <c r="I7" s="541"/>
+      <c r="J7" s="541"/>
+      <c r="K7" s="542"/>
     </row>
     <row r="8" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="562"/>
-      <c r="B8" s="563"/>
-      <c r="C8" s="563"/>
-      <c r="D8" s="564"/>
+      <c r="A8" s="534"/>
+      <c r="B8" s="535"/>
+      <c r="C8" s="535"/>
+      <c r="D8" s="536"/>
       <c r="E8" s="262"/>
       <c r="F8" s="262"/>
       <c r="G8" s="263"/>
-      <c r="H8" s="549"/>
-      <c r="I8" s="550"/>
-      <c r="J8" s="550"/>
-      <c r="K8" s="551"/>
+      <c r="H8" s="540"/>
+      <c r="I8" s="541"/>
+      <c r="J8" s="541"/>
+      <c r="K8" s="542"/>
     </row>
     <row r="9" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="562"/>
-      <c r="B9" s="563"/>
-      <c r="C9" s="563"/>
-      <c r="D9" s="564"/>
+      <c r="A9" s="534"/>
+      <c r="B9" s="535"/>
+      <c r="C9" s="535"/>
+      <c r="D9" s="536"/>
       <c r="E9" s="262"/>
       <c r="F9" s="262"/>
       <c r="G9" s="263"/>
-      <c r="H9" s="549"/>
-      <c r="I9" s="550"/>
-      <c r="J9" s="550"/>
-      <c r="K9" s="551"/>
+      <c r="H9" s="540"/>
+      <c r="I9" s="541"/>
+      <c r="J9" s="541"/>
+      <c r="K9" s="542"/>
     </row>
     <row r="10" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="562"/>
-      <c r="B10" s="563"/>
-      <c r="C10" s="563"/>
-      <c r="D10" s="564"/>
+      <c r="A10" s="534"/>
+      <c r="B10" s="535"/>
+      <c r="C10" s="535"/>
+      <c r="D10" s="536"/>
       <c r="E10" s="262"/>
       <c r="F10" s="262"/>
       <c r="G10" s="263"/>
-      <c r="H10" s="549"/>
-      <c r="I10" s="550"/>
-      <c r="J10" s="550"/>
-      <c r="K10" s="551"/>
+      <c r="H10" s="540"/>
+      <c r="I10" s="541"/>
+      <c r="J10" s="541"/>
+      <c r="K10" s="542"/>
     </row>
     <row r="11" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="562"/>
-      <c r="B11" s="563"/>
-      <c r="C11" s="563"/>
-      <c r="D11" s="564"/>
+      <c r="A11" s="534"/>
+      <c r="B11" s="535"/>
+      <c r="C11" s="535"/>
+      <c r="D11" s="536"/>
       <c r="E11" s="262"/>
       <c r="F11" s="262"/>
       <c r="G11" s="263"/>
-      <c r="H11" s="549"/>
-      <c r="I11" s="550"/>
-      <c r="J11" s="550"/>
-      <c r="K11" s="551"/>
+      <c r="H11" s="540"/>
+      <c r="I11" s="541"/>
+      <c r="J11" s="541"/>
+      <c r="K11" s="542"/>
     </row>
     <row r="12" spans="1:11" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="559"/>
-      <c r="B12" s="560"/>
-      <c r="C12" s="560"/>
-      <c r="D12" s="561"/>
+      <c r="A12" s="566"/>
+      <c r="B12" s="567"/>
+      <c r="C12" s="567"/>
+      <c r="D12" s="568"/>
       <c r="E12" s="262"/>
       <c r="F12" s="262"/>
       <c r="G12" s="264"/>
-      <c r="H12" s="523"/>
-      <c r="I12" s="524"/>
-      <c r="J12" s="524"/>
-      <c r="K12" s="525"/>
+      <c r="H12" s="579"/>
+      <c r="I12" s="580"/>
+      <c r="J12" s="580"/>
+      <c r="K12" s="581"/>
     </row>
     <row r="13" spans="1:11" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="492" t="s">
+      <c r="A13" s="509" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="493"/>
-      <c r="C13" s="493"/>
-      <c r="D13" s="493"/>
-      <c r="E13" s="493"/>
-      <c r="F13" s="493"/>
-      <c r="G13" s="493"/>
-      <c r="H13" s="493"/>
-      <c r="I13" s="493"/>
-      <c r="J13" s="493"/>
-      <c r="K13" s="494"/>
+      <c r="B13" s="510"/>
+      <c r="C13" s="510"/>
+      <c r="D13" s="510"/>
+      <c r="E13" s="510"/>
+      <c r="F13" s="510"/>
+      <c r="G13" s="510"/>
+      <c r="H13" s="510"/>
+      <c r="I13" s="510"/>
+      <c r="J13" s="510"/>
+      <c r="K13" s="511"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="526" t="s">
+      <c r="A14" s="582" t="s">
         <v>325</v>
       </c>
-      <c r="B14" s="527"/>
-      <c r="C14" s="527"/>
-      <c r="D14" s="527"/>
-      <c r="E14" s="527"/>
-      <c r="F14" s="527"/>
-      <c r="G14" s="527"/>
-      <c r="H14" s="527"/>
-      <c r="I14" s="527"/>
-      <c r="J14" s="527"/>
-      <c r="K14" s="528"/>
+      <c r="B14" s="583"/>
+      <c r="C14" s="583"/>
+      <c r="D14" s="583"/>
+      <c r="E14" s="583"/>
+      <c r="F14" s="583"/>
+      <c r="G14" s="583"/>
+      <c r="H14" s="583"/>
+      <c r="I14" s="583"/>
+      <c r="J14" s="583"/>
+      <c r="K14" s="584"/>
     </row>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="542" t="s">
+      <c r="A15" s="561" t="s">
         <v>326</v>
       </c>
-      <c r="B15" s="488" t="s">
+      <c r="B15" s="496" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="546"/>
-      <c r="D15" s="547"/>
-      <c r="E15" s="488" t="s">
+      <c r="C15" s="555"/>
+      <c r="D15" s="556"/>
+      <c r="E15" s="496" t="s">
         <v>328</v>
       </c>
-      <c r="F15" s="489"/>
-      <c r="G15" s="532" t="s">
+      <c r="F15" s="497"/>
+      <c r="G15" s="585" t="s">
         <v>323</v>
       </c>
-      <c r="H15" s="552" t="s">
+      <c r="H15" s="558" t="s">
         <v>329</v>
       </c>
-      <c r="I15" s="517" t="s">
+      <c r="I15" s="495" t="s">
         <v>330</v>
       </c>
-      <c r="J15" s="546"/>
-      <c r="K15" s="568"/>
+      <c r="J15" s="555"/>
+      <c r="K15" s="572"/>
     </row>
     <row r="16" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="542"/>
-      <c r="B16" s="546"/>
-      <c r="C16" s="546"/>
-      <c r="D16" s="547"/>
-      <c r="E16" s="490"/>
-      <c r="F16" s="491"/>
-      <c r="G16" s="532"/>
-      <c r="H16" s="552"/>
-      <c r="I16" s="567"/>
-      <c r="J16" s="546"/>
-      <c r="K16" s="568"/>
+      <c r="A16" s="561"/>
+      <c r="B16" s="555"/>
+      <c r="C16" s="555"/>
+      <c r="D16" s="556"/>
+      <c r="E16" s="477"/>
+      <c r="F16" s="478"/>
+      <c r="G16" s="585"/>
+      <c r="H16" s="558"/>
+      <c r="I16" s="571"/>
+      <c r="J16" s="555"/>
+      <c r="K16" s="572"/>
     </row>
     <row r="17" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
-      <c r="B17" s="432"/>
-      <c r="C17" s="432"/>
-      <c r="D17" s="548"/>
+      <c r="B17" s="332"/>
+      <c r="C17" s="332"/>
+      <c r="D17" s="557"/>
       <c r="E17" s="18" t="s">
         <v>129</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G17" s="506"/>
-      <c r="H17" s="553"/>
-      <c r="I17" s="569"/>
-      <c r="J17" s="432"/>
-      <c r="K17" s="433"/>
+      <c r="G17" s="482"/>
+      <c r="H17" s="559"/>
+      <c r="I17" s="573"/>
+      <c r="J17" s="332"/>
+      <c r="K17" s="333"/>
     </row>
     <row r="18" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="529"/>
-      <c r="B18" s="530"/>
-      <c r="C18" s="530"/>
-      <c r="D18" s="531"/>
+      <c r="A18" s="543"/>
+      <c r="B18" s="544"/>
+      <c r="C18" s="544"/>
+      <c r="D18" s="545"/>
       <c r="E18" s="265"/>
       <c r="F18" s="265"/>
       <c r="G18" s="266"/>
       <c r="H18" s="267"/>
-      <c r="I18" s="533"/>
-      <c r="J18" s="534"/>
-      <c r="K18" s="535"/>
+      <c r="I18" s="546"/>
+      <c r="J18" s="547"/>
+      <c r="K18" s="548"/>
     </row>
     <row r="19" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="529"/>
-      <c r="B19" s="530"/>
-      <c r="C19" s="530"/>
-      <c r="D19" s="531"/>
+      <c r="A19" s="543"/>
+      <c r="B19" s="544"/>
+      <c r="C19" s="544"/>
+      <c r="D19" s="545"/>
       <c r="E19" s="265"/>
       <c r="F19" s="265"/>
       <c r="G19" s="266"/>
@@ -16881,10 +16811,10 @@
       <c r="K19" s="270"/>
     </row>
     <row r="20" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="529"/>
-      <c r="B20" s="530"/>
-      <c r="C20" s="530"/>
-      <c r="D20" s="531"/>
+      <c r="A20" s="543"/>
+      <c r="B20" s="544"/>
+      <c r="C20" s="544"/>
+      <c r="D20" s="545"/>
       <c r="E20" s="265"/>
       <c r="F20" s="265"/>
       <c r="G20" s="266"/>
@@ -16894,10 +16824,10 @@
       <c r="K20" s="270"/>
     </row>
     <row r="21" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="529"/>
-      <c r="B21" s="530"/>
-      <c r="C21" s="530"/>
-      <c r="D21" s="531"/>
+      <c r="A21" s="543"/>
+      <c r="B21" s="544"/>
+      <c r="C21" s="544"/>
+      <c r="D21" s="545"/>
       <c r="E21" s="265"/>
       <c r="F21" s="265"/>
       <c r="G21" s="266"/>
@@ -16907,10 +16837,10 @@
       <c r="K21" s="270"/>
     </row>
     <row r="22" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="529"/>
-      <c r="B22" s="530"/>
-      <c r="C22" s="530"/>
-      <c r="D22" s="531"/>
+      <c r="A22" s="543"/>
+      <c r="B22" s="544"/>
+      <c r="C22" s="544"/>
+      <c r="D22" s="545"/>
       <c r="E22" s="265"/>
       <c r="F22" s="265"/>
       <c r="G22" s="266"/>
@@ -16920,10 +16850,10 @@
       <c r="K22" s="270"/>
     </row>
     <row r="23" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="529"/>
-      <c r="B23" s="530"/>
-      <c r="C23" s="530"/>
-      <c r="D23" s="531"/>
+      <c r="A23" s="543"/>
+      <c r="B23" s="544"/>
+      <c r="C23" s="544"/>
+      <c r="D23" s="545"/>
       <c r="E23" s="265"/>
       <c r="F23" s="265"/>
       <c r="G23" s="266"/>
@@ -16933,10 +16863,10 @@
       <c r="K23" s="270"/>
     </row>
     <row r="24" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="529"/>
-      <c r="B24" s="530"/>
-      <c r="C24" s="530"/>
-      <c r="D24" s="531"/>
+      <c r="A24" s="543"/>
+      <c r="B24" s="544"/>
+      <c r="C24" s="544"/>
+      <c r="D24" s="545"/>
       <c r="E24" s="265"/>
       <c r="F24" s="265"/>
       <c r="G24" s="266"/>
@@ -16946,10 +16876,10 @@
       <c r="K24" s="270"/>
     </row>
     <row r="25" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="529"/>
-      <c r="B25" s="530"/>
-      <c r="C25" s="530"/>
-      <c r="D25" s="531"/>
+      <c r="A25" s="543"/>
+      <c r="B25" s="544"/>
+      <c r="C25" s="544"/>
+      <c r="D25" s="545"/>
       <c r="E25" s="265"/>
       <c r="F25" s="265"/>
       <c r="G25" s="266"/>
@@ -16959,43 +16889,43 @@
       <c r="K25" s="270"/>
     </row>
     <row r="26" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="529"/>
-      <c r="B26" s="530"/>
-      <c r="C26" s="530"/>
-      <c r="D26" s="531"/>
+      <c r="A26" s="543"/>
+      <c r="B26" s="544"/>
+      <c r="C26" s="544"/>
+      <c r="D26" s="545"/>
       <c r="E26" s="265"/>
       <c r="F26" s="265"/>
       <c r="G26" s="266"/>
       <c r="H26" s="267"/>
-      <c r="I26" s="533"/>
-      <c r="J26" s="534"/>
-      <c r="K26" s="535"/>
+      <c r="I26" s="546"/>
+      <c r="J26" s="547"/>
+      <c r="K26" s="548"/>
     </row>
     <row r="27" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="529"/>
-      <c r="B27" s="530"/>
-      <c r="C27" s="530"/>
-      <c r="D27" s="531"/>
+      <c r="A27" s="543"/>
+      <c r="B27" s="544"/>
+      <c r="C27" s="544"/>
+      <c r="D27" s="545"/>
       <c r="E27" s="265"/>
       <c r="F27" s="265"/>
       <c r="G27" s="266"/>
       <c r="H27" s="267"/>
-      <c r="I27" s="533"/>
-      <c r="J27" s="534"/>
-      <c r="K27" s="535"/>
+      <c r="I27" s="546"/>
+      <c r="J27" s="547"/>
+      <c r="K27" s="548"/>
     </row>
     <row r="28" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="529"/>
-      <c r="B28" s="530"/>
-      <c r="C28" s="530"/>
-      <c r="D28" s="531"/>
+      <c r="A28" s="543"/>
+      <c r="B28" s="544"/>
+      <c r="C28" s="544"/>
+      <c r="D28" s="545"/>
       <c r="E28" s="265"/>
       <c r="F28" s="265"/>
       <c r="G28" s="266"/>
       <c r="H28" s="267"/>
-      <c r="I28" s="533"/>
-      <c r="J28" s="534"/>
-      <c r="K28" s="535"/>
+      <c r="I28" s="546"/>
+      <c r="J28" s="547"/>
+      <c r="K28" s="548"/>
     </row>
     <row r="29" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="250"/>
@@ -17076,86 +17006,86 @@
       <c r="K34" s="270"/>
     </row>
     <row r="35" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="529"/>
-      <c r="B35" s="530"/>
-      <c r="C35" s="530"/>
-      <c r="D35" s="531"/>
+      <c r="A35" s="543"/>
+      <c r="B35" s="544"/>
+      <c r="C35" s="544"/>
+      <c r="D35" s="545"/>
       <c r="E35" s="265"/>
       <c r="F35" s="265"/>
       <c r="G35" s="266"/>
       <c r="H35" s="267"/>
-      <c r="I35" s="533"/>
-      <c r="J35" s="534"/>
-      <c r="K35" s="535"/>
+      <c r="I35" s="546"/>
+      <c r="J35" s="547"/>
+      <c r="K35" s="548"/>
     </row>
     <row r="36" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="529"/>
-      <c r="B36" s="530"/>
-      <c r="C36" s="530"/>
-      <c r="D36" s="531"/>
+      <c r="A36" s="543"/>
+      <c r="B36" s="544"/>
+      <c r="C36" s="544"/>
+      <c r="D36" s="545"/>
       <c r="E36" s="265"/>
       <c r="F36" s="265"/>
       <c r="G36" s="266"/>
       <c r="H36" s="267"/>
-      <c r="I36" s="533"/>
-      <c r="J36" s="534"/>
-      <c r="K36" s="535"/>
+      <c r="I36" s="546"/>
+      <c r="J36" s="547"/>
+      <c r="K36" s="548"/>
     </row>
     <row r="37" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="529"/>
-      <c r="B37" s="530"/>
-      <c r="C37" s="530"/>
-      <c r="D37" s="531"/>
+      <c r="A37" s="543"/>
+      <c r="B37" s="544"/>
+      <c r="C37" s="544"/>
+      <c r="D37" s="545"/>
       <c r="E37" s="265"/>
       <c r="F37" s="265"/>
       <c r="G37" s="266"/>
       <c r="H37" s="267"/>
-      <c r="I37" s="533"/>
-      <c r="J37" s="534"/>
-      <c r="K37" s="535"/>
+      <c r="I37" s="546"/>
+      <c r="J37" s="547"/>
+      <c r="K37" s="548"/>
     </row>
     <row r="38" spans="1:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="536"/>
-      <c r="B38" s="537"/>
-      <c r="C38" s="537"/>
-      <c r="D38" s="538"/>
+      <c r="A38" s="586"/>
+      <c r="B38" s="587"/>
+      <c r="C38" s="587"/>
+      <c r="D38" s="588"/>
       <c r="E38" s="265"/>
       <c r="F38" s="265"/>
       <c r="G38" s="271"/>
       <c r="H38" s="272"/>
-      <c r="I38" s="539"/>
-      <c r="J38" s="540"/>
-      <c r="K38" s="541"/>
+      <c r="I38" s="589"/>
+      <c r="J38" s="590"/>
+      <c r="K38" s="591"/>
     </row>
     <row r="39" spans="1:11" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="450" t="s">
+      <c r="A39" s="277" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="451"/>
-      <c r="C39" s="451"/>
-      <c r="D39" s="451"/>
-      <c r="E39" s="451"/>
-      <c r="F39" s="451"/>
-      <c r="G39" s="451"/>
-      <c r="H39" s="451"/>
-      <c r="I39" s="451"/>
-      <c r="J39" s="451"/>
-      <c r="K39" s="452"/>
+      <c r="B39" s="278"/>
+      <c r="C39" s="278"/>
+      <c r="D39" s="278"/>
+      <c r="E39" s="278"/>
+      <c r="F39" s="278"/>
+      <c r="G39" s="278"/>
+      <c r="H39" s="278"/>
+      <c r="I39" s="278"/>
+      <c r="J39" s="278"/>
+      <c r="K39" s="279"/>
     </row>
     <row r="40" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="576" t="s">
+      <c r="A40" s="549" t="s">
         <v>331</v>
       </c>
-      <c r="B40" s="577"/>
-      <c r="C40" s="577"/>
-      <c r="D40" s="577"/>
-      <c r="E40" s="577"/>
-      <c r="F40" s="577"/>
-      <c r="G40" s="577"/>
-      <c r="H40" s="577"/>
-      <c r="I40" s="577"/>
-      <c r="J40" s="577"/>
-      <c r="K40" s="578"/>
+      <c r="B40" s="550"/>
+      <c r="C40" s="550"/>
+      <c r="D40" s="550"/>
+      <c r="E40" s="550"/>
+      <c r="F40" s="550"/>
+      <c r="G40" s="550"/>
+      <c r="H40" s="550"/>
+      <c r="I40" s="550"/>
+      <c r="J40" s="550"/>
+      <c r="K40" s="551"/>
     </row>
     <row r="41" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="124" t="s">
@@ -17167,143 +17097,143 @@
       <c r="C41" s="125" t="s">
         <v>334</v>
       </c>
-      <c r="D41" s="582" t="s">
+      <c r="D41" s="532" t="s">
         <v>335</v>
       </c>
-      <c r="E41" s="582"/>
-      <c r="F41" s="582"/>
-      <c r="G41" s="582"/>
-      <c r="H41" s="583"/>
+      <c r="E41" s="532"/>
+      <c r="F41" s="532"/>
+      <c r="G41" s="532"/>
+      <c r="H41" s="533"/>
       <c r="I41" s="125" t="s">
         <v>336</v>
       </c>
-      <c r="J41" s="582" t="s">
+      <c r="J41" s="532" t="s">
         <v>337</v>
       </c>
-      <c r="K41" s="387"/>
+      <c r="K41" s="367"/>
     </row>
     <row r="42" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="520"/>
-      <c r="B42" s="522"/>
-      <c r="C42" s="575"/>
-      <c r="D42" s="521"/>
-      <c r="E42" s="521"/>
-      <c r="F42" s="521"/>
-      <c r="G42" s="521"/>
-      <c r="H42" s="522"/>
-      <c r="I42" s="575"/>
-      <c r="J42" s="521"/>
-      <c r="K42" s="584"/>
+      <c r="A42" s="500"/>
+      <c r="B42" s="502"/>
+      <c r="C42" s="530"/>
+      <c r="D42" s="501"/>
+      <c r="E42" s="501"/>
+      <c r="F42" s="501"/>
+      <c r="G42" s="501"/>
+      <c r="H42" s="502"/>
+      <c r="I42" s="530"/>
+      <c r="J42" s="501"/>
+      <c r="K42" s="531"/>
     </row>
     <row r="43" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="520"/>
-      <c r="B43" s="522"/>
-      <c r="C43" s="575"/>
-      <c r="D43" s="521"/>
-      <c r="E43" s="521"/>
-      <c r="F43" s="521"/>
-      <c r="G43" s="521"/>
-      <c r="H43" s="522"/>
-      <c r="I43" s="575"/>
-      <c r="J43" s="521"/>
-      <c r="K43" s="584"/>
+      <c r="A43" s="500"/>
+      <c r="B43" s="502"/>
+      <c r="C43" s="530"/>
+      <c r="D43" s="501"/>
+      <c r="E43" s="501"/>
+      <c r="F43" s="501"/>
+      <c r="G43" s="501"/>
+      <c r="H43" s="502"/>
+      <c r="I43" s="530"/>
+      <c r="J43" s="501"/>
+      <c r="K43" s="531"/>
     </row>
     <row r="44" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="520"/>
-      <c r="B44" s="522"/>
-      <c r="C44" s="575"/>
-      <c r="D44" s="521"/>
-      <c r="E44" s="521"/>
-      <c r="F44" s="521"/>
-      <c r="G44" s="521"/>
-      <c r="H44" s="522"/>
-      <c r="I44" s="575"/>
-      <c r="J44" s="521"/>
-      <c r="K44" s="584"/>
+      <c r="A44" s="500"/>
+      <c r="B44" s="502"/>
+      <c r="C44" s="530"/>
+      <c r="D44" s="501"/>
+      <c r="E44" s="501"/>
+      <c r="F44" s="501"/>
+      <c r="G44" s="501"/>
+      <c r="H44" s="502"/>
+      <c r="I44" s="530"/>
+      <c r="J44" s="501"/>
+      <c r="K44" s="531"/>
     </row>
     <row r="45" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="520"/>
-      <c r="B45" s="522"/>
-      <c r="C45" s="575"/>
-      <c r="D45" s="521"/>
-      <c r="E45" s="521"/>
-      <c r="F45" s="521"/>
-      <c r="G45" s="521"/>
-      <c r="H45" s="522"/>
-      <c r="I45" s="575"/>
-      <c r="J45" s="521"/>
-      <c r="K45" s="584"/>
+      <c r="A45" s="500"/>
+      <c r="B45" s="502"/>
+      <c r="C45" s="530"/>
+      <c r="D45" s="501"/>
+      <c r="E45" s="501"/>
+      <c r="F45" s="501"/>
+      <c r="G45" s="501"/>
+      <c r="H45" s="502"/>
+      <c r="I45" s="530"/>
+      <c r="J45" s="501"/>
+      <c r="K45" s="531"/>
     </row>
     <row r="46" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="520"/>
-      <c r="B46" s="522"/>
-      <c r="C46" s="575"/>
-      <c r="D46" s="521"/>
-      <c r="E46" s="521"/>
-      <c r="F46" s="521"/>
-      <c r="G46" s="521"/>
-      <c r="H46" s="522"/>
-      <c r="I46" s="575"/>
-      <c r="J46" s="521"/>
-      <c r="K46" s="584"/>
+      <c r="A46" s="500"/>
+      <c r="B46" s="502"/>
+      <c r="C46" s="530"/>
+      <c r="D46" s="501"/>
+      <c r="E46" s="501"/>
+      <c r="F46" s="501"/>
+      <c r="G46" s="501"/>
+      <c r="H46" s="502"/>
+      <c r="I46" s="530"/>
+      <c r="J46" s="501"/>
+      <c r="K46" s="531"/>
     </row>
     <row r="47" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="520"/>
-      <c r="B47" s="522"/>
-      <c r="C47" s="575"/>
-      <c r="D47" s="521"/>
-      <c r="E47" s="521"/>
-      <c r="F47" s="521"/>
-      <c r="G47" s="521"/>
-      <c r="H47" s="522"/>
-      <c r="I47" s="575"/>
-      <c r="J47" s="521"/>
-      <c r="K47" s="584"/>
+      <c r="A47" s="500"/>
+      <c r="B47" s="502"/>
+      <c r="C47" s="530"/>
+      <c r="D47" s="501"/>
+      <c r="E47" s="501"/>
+      <c r="F47" s="501"/>
+      <c r="G47" s="501"/>
+      <c r="H47" s="502"/>
+      <c r="I47" s="530"/>
+      <c r="J47" s="501"/>
+      <c r="K47" s="531"/>
     </row>
     <row r="48" spans="1:11" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="520"/>
-      <c r="B48" s="522"/>
-      <c r="C48" s="575"/>
-      <c r="D48" s="521"/>
-      <c r="E48" s="521"/>
-      <c r="F48" s="521"/>
-      <c r="G48" s="521"/>
-      <c r="H48" s="522"/>
-      <c r="I48" s="575"/>
-      <c r="J48" s="521"/>
-      <c r="K48" s="584"/>
+      <c r="A48" s="500"/>
+      <c r="B48" s="502"/>
+      <c r="C48" s="530"/>
+      <c r="D48" s="501"/>
+      <c r="E48" s="501"/>
+      <c r="F48" s="501"/>
+      <c r="G48" s="501"/>
+      <c r="H48" s="502"/>
+      <c r="I48" s="530"/>
+      <c r="J48" s="501"/>
+      <c r="K48" s="531"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="450" t="s">
+      <c r="A49" s="277" t="s">
         <v>114</v>
       </c>
-      <c r="B49" s="451"/>
-      <c r="C49" s="451"/>
-      <c r="D49" s="451"/>
-      <c r="E49" s="451"/>
-      <c r="F49" s="451"/>
-      <c r="G49" s="451"/>
-      <c r="H49" s="451"/>
-      <c r="I49" s="451"/>
-      <c r="J49" s="451"/>
-      <c r="K49" s="494"/>
+      <c r="B49" s="278"/>
+      <c r="C49" s="278"/>
+      <c r="D49" s="278"/>
+      <c r="E49" s="278"/>
+      <c r="F49" s="278"/>
+      <c r="G49" s="278"/>
+      <c r="H49" s="278"/>
+      <c r="I49" s="278"/>
+      <c r="J49" s="278"/>
+      <c r="K49" s="511"/>
     </row>
     <row r="50" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="447" t="s">
+      <c r="A50" s="274" t="s">
         <v>143</v>
       </c>
-      <c r="B50" s="449"/>
-      <c r="C50" s="484"/>
-      <c r="D50" s="587"/>
-      <c r="E50" s="587"/>
-      <c r="F50" s="588"/>
-      <c r="G50" s="585" t="s">
+      <c r="B50" s="276"/>
+      <c r="C50" s="503"/>
+      <c r="D50" s="525"/>
+      <c r="E50" s="525"/>
+      <c r="F50" s="526"/>
+      <c r="G50" s="523" t="s">
         <v>144</v>
       </c>
-      <c r="H50" s="586"/>
-      <c r="I50" s="589"/>
-      <c r="J50" s="590"/>
-      <c r="K50" s="591"/>
+      <c r="H50" s="524"/>
+      <c r="I50" s="527"/>
+      <c r="J50" s="528"/>
+      <c r="K50" s="529"/>
       <c r="L50" s="224"/>
       <c r="M50" s="224"/>
     </row>
@@ -17324,6 +17254,73 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="83">
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="H12:K12"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B15:D17"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="H3:K5"/>
+    <mergeCell ref="E3:F4"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I15:K17"/>
+    <mergeCell ref="E15:F16"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="C48:H48"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="C47:H47"/>
+    <mergeCell ref="C45:H45"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="I44:K44"/>
     <mergeCell ref="G50:H50"/>
     <mergeCell ref="C50:F50"/>
     <mergeCell ref="I50:K50"/>
@@ -17340,73 +17337,6 @@
     <mergeCell ref="I46:K46"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="I47:K47"/>
-    <mergeCell ref="C48:H48"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:H43"/>
-    <mergeCell ref="C47:H47"/>
-    <mergeCell ref="C45:H45"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B15:D17"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="H3:K5"/>
-    <mergeCell ref="E3:F4"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I15:K17"/>
-    <mergeCell ref="E15:F16"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A39:K39"/>
-    <mergeCell ref="H12:K12"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -17439,35 +17369,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="603"/>
-      <c r="B1" s="604"/>
-      <c r="C1" s="604"/>
-      <c r="D1" s="604"/>
-      <c r="E1" s="604"/>
-      <c r="F1" s="604"/>
-      <c r="G1" s="604"/>
-      <c r="H1" s="604"/>
-      <c r="I1" s="604"/>
-      <c r="J1" s="604"/>
-      <c r="K1" s="604"/>
-      <c r="L1" s="604"/>
-      <c r="M1" s="605"/>
+      <c r="A1" s="713"/>
+      <c r="B1" s="714"/>
+      <c r="C1" s="714"/>
+      <c r="D1" s="714"/>
+      <c r="E1" s="714"/>
+      <c r="F1" s="714"/>
+      <c r="G1" s="714"/>
+      <c r="H1" s="714"/>
+      <c r="I1" s="714"/>
+      <c r="J1" s="714"/>
+      <c r="K1" s="714"/>
+      <c r="L1" s="714"/>
+      <c r="M1" s="715"/>
     </row>
     <row r="2" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="627" t="s">
+      <c r="A2" s="680" t="s">
         <v>338</v>
       </c>
-      <c r="B2" s="628"/>
-      <c r="C2" s="608" t="s">
+      <c r="B2" s="681"/>
+      <c r="C2" s="718" t="s">
         <v>339</v>
       </c>
-      <c r="D2" s="608"/>
-      <c r="E2" s="608"/>
-      <c r="F2" s="609"/>
+      <c r="D2" s="718"/>
+      <c r="E2" s="718"/>
+      <c r="F2" s="719"/>
       <c r="G2" s="19"/>
       <c r="H2" s="19"/>
-      <c r="I2" s="606"/>
-      <c r="J2" s="606"/>
+      <c r="I2" s="716"/>
+      <c r="J2" s="716"/>
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
       <c r="M2" s="21"/>
@@ -17475,16 +17405,16 @@
     <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22"/>
       <c r="B3" s="23"/>
-      <c r="C3" s="612" t="s">
+      <c r="C3" s="698" t="s">
         <v>340</v>
       </c>
-      <c r="D3" s="612"/>
-      <c r="E3" s="612"/>
-      <c r="F3" s="613"/>
+      <c r="D3" s="698"/>
+      <c r="E3" s="698"/>
+      <c r="F3" s="699"/>
       <c r="G3" s="24"/>
       <c r="H3" s="24"/>
-      <c r="I3" s="607"/>
-      <c r="J3" s="607"/>
+      <c r="I3" s="717"/>
+      <c r="J3" s="717"/>
       <c r="K3" s="25"/>
       <c r="L3" s="25"/>
       <c r="M3" s="26"/>
@@ -17492,42 +17422,42 @@
     <row r="4" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
-      <c r="C4" s="612" t="s">
+      <c r="C4" s="698" t="s">
         <v>341</v>
       </c>
-      <c r="D4" s="612"/>
-      <c r="E4" s="612"/>
-      <c r="F4" s="613"/>
+      <c r="D4" s="698"/>
+      <c r="E4" s="698"/>
+      <c r="F4" s="699"/>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22"/>
       <c r="B5" s="23"/>
-      <c r="C5" s="612"/>
-      <c r="D5" s="612"/>
-      <c r="E5" s="612"/>
-      <c r="F5" s="613"/>
-      <c r="G5" s="601"/>
-      <c r="H5" s="601"/>
-      <c r="I5" s="601"/>
-      <c r="J5" s="601"/>
-      <c r="K5" s="601"/>
-      <c r="L5" s="601"/>
+      <c r="C5" s="698"/>
+      <c r="D5" s="698"/>
+      <c r="E5" s="698"/>
+      <c r="F5" s="699"/>
+      <c r="G5" s="597"/>
+      <c r="H5" s="597"/>
+      <c r="I5" s="597"/>
+      <c r="J5" s="597"/>
+      <c r="K5" s="597"/>
+      <c r="L5" s="597"/>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="22"/>
       <c r="B6" s="23"/>
-      <c r="C6" s="612" t="s">
+      <c r="C6" s="698" t="s">
         <v>342</v>
       </c>
-      <c r="D6" s="612"/>
-      <c r="E6" s="612"/>
-      <c r="F6" s="613"/>
-      <c r="I6" s="632"/>
-      <c r="J6" s="632"/>
-      <c r="K6" s="632"/>
-      <c r="L6" s="632"/>
+      <c r="D6" s="698"/>
+      <c r="E6" s="698"/>
+      <c r="F6" s="699"/>
+      <c r="I6" s="721"/>
+      <c r="J6" s="721"/>
+      <c r="K6" s="721"/>
+      <c r="L6" s="721"/>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -17546,12 +17476,12 @@
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="22"/>
       <c r="B8" s="23"/>
-      <c r="C8" s="612" t="s">
+      <c r="C8" s="698" t="s">
         <v>343</v>
       </c>
-      <c r="D8" s="612"/>
-      <c r="E8" s="612"/>
-      <c r="F8" s="613"/>
+      <c r="D8" s="698"/>
+      <c r="E8" s="698"/>
+      <c r="F8" s="699"/>
       <c r="M8" s="27"/>
     </row>
     <row r="9" spans="1:13" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -17566,61 +17496,61 @@
     <row r="10" spans="1:13" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="22"/>
       <c r="B10" s="23"/>
-      <c r="C10" s="612"/>
-      <c r="D10" s="612"/>
-      <c r="E10" s="612"/>
-      <c r="F10" s="613"/>
-      <c r="G10" s="601" t="s">
+      <c r="C10" s="698"/>
+      <c r="D10" s="698"/>
+      <c r="E10" s="698"/>
+      <c r="F10" s="699"/>
+      <c r="G10" s="597" t="s">
         <v>344</v>
       </c>
-      <c r="H10" s="601"/>
-      <c r="I10" s="601"/>
-      <c r="J10" s="601"/>
-      <c r="K10" s="601"/>
-      <c r="L10" s="601"/>
+      <c r="H10" s="597"/>
+      <c r="I10" s="597"/>
+      <c r="J10" s="597"/>
+      <c r="K10" s="597"/>
+      <c r="L10" s="597"/>
       <c r="M10" s="74"/>
     </row>
     <row r="11" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22"/>
       <c r="B11" s="23"/>
-      <c r="C11" s="612"/>
-      <c r="D11" s="612"/>
-      <c r="E11" s="612"/>
-      <c r="F11" s="613"/>
+      <c r="C11" s="698"/>
+      <c r="D11" s="698"/>
+      <c r="E11" s="698"/>
+      <c r="F11" s="699"/>
       <c r="G11" s="132"/>
-      <c r="H11" s="633"/>
-      <c r="I11" s="633"/>
-      <c r="J11" s="633"/>
-      <c r="K11" s="633"/>
-      <c r="L11" s="633"/>
+      <c r="H11" s="722"/>
+      <c r="I11" s="722"/>
+      <c r="J11" s="722"/>
+      <c r="K11" s="722"/>
+      <c r="L11" s="722"/>
       <c r="M11" s="74"/>
     </row>
     <row r="12" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28"/>
       <c r="B12" s="29"/>
-      <c r="C12" s="629"/>
-      <c r="D12" s="629"/>
-      <c r="E12" s="629"/>
-      <c r="F12" s="630"/>
+      <c r="C12" s="709"/>
+      <c r="D12" s="709"/>
+      <c r="E12" s="709"/>
+      <c r="F12" s="710"/>
       <c r="G12" s="133"/>
       <c r="H12" s="133"/>
-      <c r="I12" s="631"/>
-      <c r="J12" s="631"/>
-      <c r="K12" s="631"/>
-      <c r="L12" s="631"/>
+      <c r="I12" s="720"/>
+      <c r="J12" s="720"/>
+      <c r="K12" s="720"/>
+      <c r="L12" s="720"/>
       <c r="M12" s="112"/>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="597" t="s">
+      <c r="A13" s="711" t="s">
         <v>345</v>
       </c>
-      <c r="B13" s="598"/>
-      <c r="C13" s="599" t="s">
+      <c r="B13" s="712"/>
+      <c r="C13" s="705" t="s">
         <v>346</v>
       </c>
-      <c r="D13" s="599"/>
-      <c r="E13" s="546"/>
-      <c r="F13" s="547"/>
+      <c r="D13" s="705"/>
+      <c r="E13" s="555"/>
+      <c r="F13" s="556"/>
       <c r="G13" s="30"/>
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
@@ -17632,48 +17562,48 @@
     <row r="14" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="45"/>
       <c r="B14" s="46"/>
-      <c r="C14" s="599"/>
-      <c r="D14" s="599"/>
-      <c r="E14" s="546"/>
-      <c r="F14" s="547"/>
-      <c r="G14" s="600" t="s">
+      <c r="C14" s="705"/>
+      <c r="D14" s="705"/>
+      <c r="E14" s="555"/>
+      <c r="F14" s="556"/>
+      <c r="G14" s="596" t="s">
         <v>344</v>
       </c>
-      <c r="H14" s="601"/>
-      <c r="I14" s="601"/>
-      <c r="J14" s="601"/>
-      <c r="K14" s="601"/>
-      <c r="L14" s="601"/>
+      <c r="H14" s="597"/>
+      <c r="I14" s="597"/>
+      <c r="J14" s="597"/>
+      <c r="K14" s="597"/>
+      <c r="L14" s="597"/>
       <c r="M14" s="111"/>
     </row>
     <row r="15" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="45"/>
       <c r="B15" s="46"/>
-      <c r="C15" s="599"/>
-      <c r="D15" s="599"/>
-      <c r="E15" s="546"/>
-      <c r="F15" s="547"/>
+      <c r="C15" s="705"/>
+      <c r="D15" s="705"/>
+      <c r="E15" s="555"/>
+      <c r="F15" s="556"/>
       <c r="G15" s="24"/>
-      <c r="H15" s="595"/>
-      <c r="I15" s="595"/>
-      <c r="J15" s="595"/>
-      <c r="K15" s="595"/>
-      <c r="L15" s="595"/>
+      <c r="H15" s="726"/>
+      <c r="I15" s="726"/>
+      <c r="J15" s="726"/>
+      <c r="K15" s="726"/>
+      <c r="L15" s="726"/>
       <c r="M15" s="111"/>
     </row>
     <row r="16" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32"/>
       <c r="B16" s="33"/>
-      <c r="C16" s="546"/>
-      <c r="D16" s="546"/>
-      <c r="E16" s="546"/>
-      <c r="F16" s="547"/>
+      <c r="C16" s="555"/>
+      <c r="D16" s="555"/>
+      <c r="E16" s="555"/>
+      <c r="F16" s="556"/>
       <c r="G16" s="108"/>
       <c r="H16" s="229"/>
-      <c r="I16" s="602"/>
-      <c r="J16" s="602"/>
-      <c r="K16" s="602"/>
-      <c r="L16" s="602"/>
+      <c r="I16" s="702"/>
+      <c r="J16" s="702"/>
+      <c r="K16" s="702"/>
+      <c r="L16" s="702"/>
       <c r="M16" s="109"/>
     </row>
     <row r="17" spans="1:13" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -17694,12 +17624,12 @@
     <row r="18" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="34"/>
       <c r="B18" s="35"/>
-      <c r="C18" s="724" t="s">
+      <c r="C18" s="599" t="s">
         <v>347</v>
       </c>
-      <c r="D18" s="724"/>
-      <c r="E18" s="725"/>
-      <c r="F18" s="726"/>
+      <c r="D18" s="599"/>
+      <c r="E18" s="600"/>
+      <c r="F18" s="601"/>
       <c r="G18" s="39"/>
       <c r="H18" s="39"/>
       <c r="I18" s="39"/>
@@ -17711,82 +17641,82 @@
     <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34"/>
       <c r="B19" s="35"/>
-      <c r="C19" s="724"/>
-      <c r="D19" s="724"/>
-      <c r="E19" s="725"/>
-      <c r="F19" s="726"/>
-      <c r="G19" s="600" t="s">
+      <c r="C19" s="599"/>
+      <c r="D19" s="599"/>
+      <c r="E19" s="600"/>
+      <c r="F19" s="601"/>
+      <c r="G19" s="596" t="s">
         <v>344</v>
       </c>
-      <c r="H19" s="601"/>
-      <c r="I19" s="601"/>
-      <c r="J19" s="601"/>
-      <c r="K19" s="601"/>
-      <c r="L19" s="601"/>
+      <c r="H19" s="597"/>
+      <c r="I19" s="597"/>
+      <c r="J19" s="597"/>
+      <c r="K19" s="597"/>
+      <c r="L19" s="597"/>
       <c r="M19" s="40"/>
     </row>
     <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="34"/>
       <c r="B20" s="35"/>
-      <c r="C20" s="724"/>
-      <c r="D20" s="724"/>
-      <c r="E20" s="725"/>
-      <c r="F20" s="726"/>
+      <c r="C20" s="599"/>
+      <c r="D20" s="599"/>
+      <c r="E20" s="600"/>
+      <c r="F20" s="601"/>
       <c r="G20" s="39"/>
-      <c r="H20" s="702" t="s">
+      <c r="H20" s="727" t="s">
         <v>348</v>
       </c>
-      <c r="I20" s="702"/>
+      <c r="I20" s="727"/>
       <c r="J20" s="239"/>
-      <c r="K20" s="593"/>
-      <c r="L20" s="593"/>
+      <c r="K20" s="724"/>
+      <c r="L20" s="724"/>
       <c r="M20" s="40"/>
     </row>
     <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34"/>
       <c r="B21" s="35"/>
-      <c r="C21" s="724"/>
-      <c r="D21" s="724"/>
-      <c r="E21" s="725"/>
-      <c r="F21" s="726"/>
-      <c r="G21" s="703" t="s">
+      <c r="C21" s="599"/>
+      <c r="D21" s="599"/>
+      <c r="E21" s="600"/>
+      <c r="F21" s="601"/>
+      <c r="G21" s="728" t="s">
         <v>349</v>
       </c>
-      <c r="H21" s="704"/>
-      <c r="I21" s="704"/>
+      <c r="H21" s="729"/>
+      <c r="I21" s="729"/>
       <c r="J21" s="239"/>
-      <c r="K21" s="594"/>
-      <c r="L21" s="594"/>
+      <c r="K21" s="725"/>
+      <c r="L21" s="725"/>
       <c r="M21" s="40"/>
     </row>
     <row r="22" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41"/>
       <c r="B22" s="42"/>
-      <c r="C22" s="727"/>
-      <c r="D22" s="727"/>
-      <c r="E22" s="727"/>
-      <c r="F22" s="728"/>
+      <c r="C22" s="602"/>
+      <c r="D22" s="602"/>
+      <c r="E22" s="602"/>
+      <c r="F22" s="603"/>
       <c r="G22" s="108" t="s">
         <v>350</v>
       </c>
       <c r="H22" s="229"/>
-      <c r="I22" s="729"/>
-      <c r="J22" s="729"/>
-      <c r="K22" s="729"/>
+      <c r="I22" s="604"/>
+      <c r="J22" s="604"/>
+      <c r="K22" s="604"/>
       <c r="L22" s="113"/>
       <c r="M22" s="109"/>
     </row>
     <row r="23" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="634" t="s">
+      <c r="A23" s="592" t="s">
         <v>351</v>
       </c>
-      <c r="B23" s="635"/>
-      <c r="C23" s="623" t="s">
+      <c r="B23" s="593"/>
+      <c r="C23" s="605" t="s">
         <v>352</v>
       </c>
-      <c r="D23" s="623"/>
-      <c r="E23" s="623"/>
-      <c r="F23" s="624"/>
+      <c r="D23" s="605"/>
+      <c r="E23" s="605"/>
+      <c r="F23" s="606"/>
       <c r="G23" s="30"/>
       <c r="H23" s="30"/>
       <c r="I23" s="30"/>
@@ -17798,61 +17728,61 @@
     <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="32"/>
       <c r="B24" s="33"/>
-      <c r="C24" s="615"/>
-      <c r="D24" s="615"/>
-      <c r="E24" s="615"/>
-      <c r="F24" s="614"/>
-      <c r="G24" s="600" t="s">
+      <c r="C24" s="607"/>
+      <c r="D24" s="607"/>
+      <c r="E24" s="607"/>
+      <c r="F24" s="608"/>
+      <c r="G24" s="596" t="s">
         <v>344</v>
       </c>
-      <c r="H24" s="601"/>
-      <c r="I24" s="601"/>
-      <c r="J24" s="601"/>
-      <c r="K24" s="601"/>
-      <c r="L24" s="601"/>
+      <c r="H24" s="597"/>
+      <c r="I24" s="597"/>
+      <c r="J24" s="597"/>
+      <c r="K24" s="597"/>
+      <c r="L24" s="597"/>
       <c r="M24" s="107"/>
     </row>
     <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="32"/>
       <c r="B25" s="33"/>
-      <c r="C25" s="615"/>
-      <c r="D25" s="615"/>
-      <c r="E25" s="615"/>
-      <c r="F25" s="614"/>
+      <c r="C25" s="607"/>
+      <c r="D25" s="607"/>
+      <c r="E25" s="607"/>
+      <c r="F25" s="608"/>
       <c r="G25" s="106"/>
-      <c r="H25" s="592"/>
-      <c r="I25" s="592"/>
-      <c r="J25" s="592"/>
-      <c r="K25" s="592"/>
-      <c r="L25" s="592"/>
+      <c r="H25" s="723"/>
+      <c r="I25" s="723"/>
+      <c r="J25" s="723"/>
+      <c r="K25" s="723"/>
+      <c r="L25" s="723"/>
       <c r="M25" s="107"/>
     </row>
     <row r="26" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="43"/>
       <c r="B26" s="44"/>
-      <c r="C26" s="625"/>
-      <c r="D26" s="625"/>
-      <c r="E26" s="625"/>
-      <c r="F26" s="626"/>
+      <c r="C26" s="609"/>
+      <c r="D26" s="609"/>
+      <c r="E26" s="609"/>
+      <c r="F26" s="610"/>
       <c r="G26" s="108"/>
       <c r="H26" s="229"/>
-      <c r="I26" s="602"/>
-      <c r="J26" s="602"/>
-      <c r="K26" s="602"/>
-      <c r="L26" s="602"/>
+      <c r="I26" s="702"/>
+      <c r="J26" s="702"/>
+      <c r="K26" s="702"/>
+      <c r="L26" s="702"/>
       <c r="M26" s="109"/>
     </row>
     <row r="27" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="634" t="s">
+      <c r="A27" s="592" t="s">
         <v>353</v>
       </c>
-      <c r="B27" s="635"/>
-      <c r="C27" s="623" t="s">
+      <c r="B27" s="593"/>
+      <c r="C27" s="605" t="s">
         <v>354</v>
       </c>
-      <c r="D27" s="623"/>
-      <c r="E27" s="623"/>
-      <c r="F27" s="624"/>
+      <c r="D27" s="605"/>
+      <c r="E27" s="605"/>
+      <c r="F27" s="606"/>
       <c r="G27" s="30"/>
       <c r="H27" s="30"/>
       <c r="I27" s="30"/>
@@ -17864,41 +17794,41 @@
     <row r="28" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="32"/>
       <c r="B28" s="33"/>
-      <c r="C28" s="615"/>
-      <c r="D28" s="615"/>
-      <c r="E28" s="615"/>
-      <c r="F28" s="614"/>
-      <c r="G28" s="600" t="s">
+      <c r="C28" s="607"/>
+      <c r="D28" s="607"/>
+      <c r="E28" s="607"/>
+      <c r="F28" s="608"/>
+      <c r="G28" s="596" t="s">
         <v>344</v>
       </c>
-      <c r="H28" s="601"/>
-      <c r="I28" s="601"/>
-      <c r="J28" s="601"/>
-      <c r="K28" s="601"/>
-      <c r="L28" s="601"/>
+      <c r="H28" s="597"/>
+      <c r="I28" s="597"/>
+      <c r="J28" s="597"/>
+      <c r="K28" s="597"/>
+      <c r="L28" s="597"/>
       <c r="M28" s="2"/>
     </row>
     <row r="29" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="32"/>
       <c r="B29" s="33"/>
-      <c r="C29" s="615"/>
-      <c r="D29" s="615"/>
-      <c r="E29" s="615"/>
-      <c r="F29" s="614"/>
-      <c r="H29" s="596"/>
-      <c r="I29" s="596"/>
-      <c r="J29" s="596"/>
-      <c r="K29" s="596"/>
-      <c r="L29" s="596"/>
+      <c r="C29" s="607"/>
+      <c r="D29" s="607"/>
+      <c r="E29" s="607"/>
+      <c r="F29" s="608"/>
+      <c r="H29" s="658"/>
+      <c r="I29" s="658"/>
+      <c r="J29" s="658"/>
+      <c r="K29" s="658"/>
+      <c r="L29" s="658"/>
       <c r="M29" s="107"/>
     </row>
     <row r="30" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="43"/>
       <c r="B30" s="44"/>
-      <c r="C30" s="625"/>
-      <c r="D30" s="625"/>
-      <c r="E30" s="625"/>
-      <c r="F30" s="626"/>
+      <c r="C30" s="609"/>
+      <c r="D30" s="609"/>
+      <c r="E30" s="609"/>
+      <c r="F30" s="610"/>
       <c r="G30" s="127"/>
       <c r="H30" s="231"/>
       <c r="I30" s="164"/>
@@ -17908,16 +17838,16 @@
       <c r="M30" s="109"/>
     </row>
     <row r="31" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="634" t="s">
+      <c r="A31" s="592" t="s">
         <v>355</v>
       </c>
-      <c r="B31" s="635"/>
-      <c r="C31" s="623" t="s">
+      <c r="B31" s="593"/>
+      <c r="C31" s="605" t="s">
         <v>356</v>
       </c>
-      <c r="D31" s="623"/>
-      <c r="E31" s="623"/>
-      <c r="F31" s="624"/>
+      <c r="D31" s="605"/>
+      <c r="E31" s="605"/>
+      <c r="F31" s="606"/>
       <c r="G31" s="30"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -17929,18 +17859,18 @@
     <row r="32" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="32"/>
       <c r="B32" s="33"/>
-      <c r="C32" s="615"/>
-      <c r="D32" s="615"/>
-      <c r="E32" s="615"/>
-      <c r="F32" s="614"/>
-      <c r="G32" s="669" t="s">
+      <c r="C32" s="607"/>
+      <c r="D32" s="607"/>
+      <c r="E32" s="607"/>
+      <c r="F32" s="608"/>
+      <c r="G32" s="659" t="s">
         <v>357</v>
       </c>
-      <c r="H32" s="670"/>
-      <c r="I32" s="670"/>
-      <c r="J32" s="670"/>
-      <c r="K32" s="596"/>
-      <c r="L32" s="596"/>
+      <c r="H32" s="660"/>
+      <c r="I32" s="660"/>
+      <c r="J32" s="660"/>
+      <c r="K32" s="658"/>
+      <c r="L32" s="658"/>
       <c r="M32" s="107"/>
     </row>
     <row r="33" spans="1:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17961,44 +17891,44 @@
     <row r="34" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="32"/>
       <c r="B34" s="33"/>
-      <c r="C34" s="615" t="s">
+      <c r="C34" s="607" t="s">
         <v>358</v>
       </c>
-      <c r="D34" s="615"/>
-      <c r="E34" s="615"/>
-      <c r="F34" s="614"/>
+      <c r="D34" s="607"/>
+      <c r="E34" s="607"/>
+      <c r="F34" s="608"/>
       <c r="G34" s="106"/>
       <c r="H34" s="230"/>
-      <c r="I34" s="668"/>
-      <c r="J34" s="668"/>
-      <c r="K34" s="668"/>
-      <c r="L34" s="668"/>
+      <c r="I34" s="696"/>
+      <c r="J34" s="696"/>
+      <c r="K34" s="696"/>
+      <c r="L34" s="696"/>
       <c r="M34" s="107"/>
     </row>
     <row r="35" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="32"/>
       <c r="B35" s="33"/>
-      <c r="C35" s="615"/>
-      <c r="D35" s="615"/>
-      <c r="E35" s="615"/>
-      <c r="F35" s="614"/>
-      <c r="G35" s="669" t="s">
+      <c r="C35" s="607"/>
+      <c r="D35" s="607"/>
+      <c r="E35" s="607"/>
+      <c r="F35" s="608"/>
+      <c r="G35" s="659" t="s">
         <v>357</v>
       </c>
-      <c r="H35" s="670"/>
-      <c r="I35" s="670"/>
-      <c r="J35" s="670"/>
-      <c r="K35" s="596"/>
-      <c r="L35" s="596"/>
+      <c r="H35" s="660"/>
+      <c r="I35" s="660"/>
+      <c r="J35" s="660"/>
+      <c r="K35" s="658"/>
+      <c r="L35" s="658"/>
       <c r="M35" s="107"/>
     </row>
     <row r="36" spans="1:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="43"/>
       <c r="B36" s="44"/>
-      <c r="C36" s="625"/>
-      <c r="D36" s="625"/>
-      <c r="E36" s="625"/>
-      <c r="F36" s="626"/>
+      <c r="C36" s="609"/>
+      <c r="D36" s="609"/>
+      <c r="E36" s="609"/>
+      <c r="F36" s="610"/>
       <c r="G36" s="110"/>
       <c r="H36" s="54"/>
       <c r="I36" s="101"/>
@@ -18007,16 +17937,16 @@
       <c r="M36" s="109"/>
     </row>
     <row r="37" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="634" t="s">
+      <c r="A37" s="592" t="s">
         <v>359</v>
       </c>
-      <c r="B37" s="635"/>
-      <c r="C37" s="618" t="s">
+      <c r="B37" s="593"/>
+      <c r="C37" s="703" t="s">
         <v>360</v>
       </c>
-      <c r="D37" s="618"/>
-      <c r="E37" s="618"/>
-      <c r="F37" s="619"/>
+      <c r="D37" s="703"/>
+      <c r="E37" s="703"/>
+      <c r="F37" s="704"/>
       <c r="G37" s="30"/>
       <c r="H37" s="30"/>
       <c r="I37" s="30"/>
@@ -18028,61 +17958,61 @@
     <row r="38" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="32"/>
       <c r="B38" s="33"/>
-      <c r="C38" s="599"/>
-      <c r="D38" s="599"/>
-      <c r="E38" s="599"/>
-      <c r="F38" s="620"/>
-      <c r="G38" s="600" t="s">
+      <c r="C38" s="705"/>
+      <c r="D38" s="705"/>
+      <c r="E38" s="705"/>
+      <c r="F38" s="706"/>
+      <c r="G38" s="596" t="s">
         <v>361</v>
       </c>
-      <c r="H38" s="601"/>
-      <c r="I38" s="601"/>
-      <c r="J38" s="601"/>
-      <c r="K38" s="601"/>
-      <c r="L38" s="601"/>
-      <c r="M38" s="723"/>
+      <c r="H38" s="597"/>
+      <c r="I38" s="597"/>
+      <c r="J38" s="597"/>
+      <c r="K38" s="597"/>
+      <c r="L38" s="597"/>
+      <c r="M38" s="598"/>
     </row>
     <row r="39" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="32"/>
       <c r="B39" s="33"/>
-      <c r="C39" s="599"/>
-      <c r="D39" s="599"/>
-      <c r="E39" s="599"/>
-      <c r="F39" s="620"/>
+      <c r="C39" s="705"/>
+      <c r="D39" s="705"/>
+      <c r="E39" s="705"/>
+      <c r="F39" s="706"/>
       <c r="G39" s="106"/>
-      <c r="H39" s="592"/>
-      <c r="I39" s="592"/>
-      <c r="J39" s="592"/>
-      <c r="K39" s="592"/>
-      <c r="L39" s="592"/>
+      <c r="H39" s="723"/>
+      <c r="I39" s="723"/>
+      <c r="J39" s="723"/>
+      <c r="K39" s="723"/>
+      <c r="L39" s="723"/>
       <c r="M39" s="107"/>
     </row>
     <row r="40" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="43"/>
       <c r="B40" s="44"/>
-      <c r="C40" s="621"/>
-      <c r="D40" s="621"/>
-      <c r="E40" s="621"/>
-      <c r="F40" s="622"/>
+      <c r="C40" s="707"/>
+      <c r="D40" s="707"/>
+      <c r="E40" s="707"/>
+      <c r="F40" s="708"/>
       <c r="G40" s="108"/>
       <c r="H40" s="229"/>
-      <c r="I40" s="602"/>
-      <c r="J40" s="602"/>
-      <c r="K40" s="602"/>
-      <c r="L40" s="602"/>
+      <c r="I40" s="702"/>
+      <c r="J40" s="702"/>
+      <c r="K40" s="702"/>
+      <c r="L40" s="702"/>
       <c r="M40" s="109"/>
     </row>
     <row r="41" spans="1:14" ht="41.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="616" t="s">
+      <c r="A41" s="700" t="s">
         <v>362</v>
       </c>
-      <c r="B41" s="617"/>
-      <c r="C41" s="615" t="s">
+      <c r="B41" s="701"/>
+      <c r="C41" s="607" t="s">
         <v>363</v>
       </c>
-      <c r="D41" s="615"/>
-      <c r="E41" s="615"/>
-      <c r="F41" s="614"/>
+      <c r="D41" s="607"/>
+      <c r="E41" s="607"/>
+      <c r="F41" s="608"/>
       <c r="G41" s="30"/>
       <c r="H41" s="30"/>
       <c r="I41" s="49"/>
@@ -18094,10 +18024,10 @@
     <row r="42" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="47"/>
       <c r="B42" s="48"/>
-      <c r="C42" s="615"/>
-      <c r="D42" s="615"/>
-      <c r="E42" s="615"/>
-      <c r="F42" s="614"/>
+      <c r="C42" s="607"/>
+      <c r="D42" s="607"/>
+      <c r="E42" s="607"/>
+      <c r="F42" s="608"/>
       <c r="G42" s="52"/>
       <c r="H42" s="52"/>
       <c r="I42" s="52"/>
@@ -18111,21 +18041,21 @@
         <v>364</v>
       </c>
       <c r="B43" s="48"/>
-      <c r="C43" s="615" t="s">
+      <c r="C43" s="607" t="s">
         <v>365</v>
       </c>
-      <c r="D43" s="615"/>
-      <c r="E43" s="615"/>
-      <c r="F43" s="614"/>
+      <c r="D43" s="607"/>
+      <c r="E43" s="607"/>
+      <c r="F43" s="608"/>
       <c r="M43" s="2"/>
     </row>
     <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="47"/>
       <c r="B44" s="48"/>
-      <c r="C44" s="615"/>
-      <c r="D44" s="615"/>
-      <c r="E44" s="615"/>
-      <c r="F44" s="614"/>
+      <c r="C44" s="607"/>
+      <c r="D44" s="607"/>
+      <c r="E44" s="607"/>
+      <c r="F44" s="608"/>
       <c r="G44" s="174" t="s">
         <v>366</v>
       </c>
@@ -18141,21 +18071,21 @@
         <v>367</v>
       </c>
       <c r="B45" s="48"/>
-      <c r="C45" s="614" t="s">
+      <c r="C45" s="608" t="s">
         <v>368</v>
       </c>
-      <c r="D45" s="614"/>
-      <c r="E45" s="614"/>
-      <c r="F45" s="614"/>
+      <c r="D45" s="608"/>
+      <c r="E45" s="608"/>
+      <c r="F45" s="608"/>
       <c r="M45" s="2"/>
     </row>
     <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="47"/>
       <c r="B46" s="48"/>
-      <c r="C46" s="614"/>
-      <c r="D46" s="614"/>
-      <c r="E46" s="614"/>
-      <c r="F46" s="614"/>
+      <c r="C46" s="608"/>
+      <c r="D46" s="608"/>
+      <c r="E46" s="608"/>
+      <c r="F46" s="608"/>
       <c r="G46" s="175" t="s">
         <v>369</v>
       </c>
@@ -18172,21 +18102,21 @@
         <v>370</v>
       </c>
       <c r="B47" s="48"/>
-      <c r="C47" s="615" t="s">
+      <c r="C47" s="607" t="s">
         <v>371</v>
       </c>
-      <c r="D47" s="615"/>
+      <c r="D47" s="607"/>
       <c r="E47" s="98"/>
       <c r="F47" s="99"/>
       <c r="M47" s="2"/>
     </row>
     <row r="48" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="648"/>
-      <c r="B48" s="649"/>
-      <c r="C48" s="649"/>
-      <c r="D48" s="649"/>
-      <c r="E48" s="649"/>
-      <c r="F48" s="650"/>
+      <c r="A48" s="674"/>
+      <c r="B48" s="675"/>
+      <c r="C48" s="675"/>
+      <c r="D48" s="675"/>
+      <c r="E48" s="675"/>
+      <c r="F48" s="676"/>
       <c r="G48" s="176" t="s">
         <v>369</v>
       </c>
@@ -18199,12 +18129,12 @@
       <c r="N48" s="54"/>
     </row>
     <row r="49" spans="1:14" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="651"/>
-      <c r="B49" s="652"/>
-      <c r="C49" s="652"/>
-      <c r="D49" s="652"/>
-      <c r="E49" s="652"/>
-      <c r="F49" s="653"/>
+      <c r="A49" s="677"/>
+      <c r="B49" s="678"/>
+      <c r="C49" s="678"/>
+      <c r="D49" s="678"/>
+      <c r="E49" s="678"/>
+      <c r="F49" s="679"/>
       <c r="G49" s="100"/>
       <c r="H49" s="96"/>
       <c r="I49" s="96"/>
@@ -18215,10 +18145,10 @@
       <c r="N49" s="54"/>
     </row>
     <row r="50" spans="1:14" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="721" t="s">
+      <c r="A50" s="594" t="s">
         <v>372</v>
       </c>
-      <c r="B50" s="722"/>
+      <c r="B50" s="595"/>
       <c r="C50" s="172" t="s">
         <v>373</v>
       </c>
@@ -18228,127 +18158,127 @@
       <c r="G50" s="172"/>
       <c r="H50" s="172"/>
       <c r="I50" s="173"/>
-      <c r="J50" s="636"/>
-      <c r="K50" s="637"/>
-      <c r="L50" s="637"/>
-      <c r="M50" s="638"/>
+      <c r="J50" s="661"/>
+      <c r="K50" s="662"/>
+      <c r="L50" s="662"/>
+      <c r="M50" s="663"/>
     </row>
     <row r="51" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="645" t="s">
+      <c r="A51" s="671" t="s">
         <v>374</v>
       </c>
-      <c r="B51" s="646"/>
-      <c r="C51" s="646"/>
-      <c r="D51" s="646"/>
-      <c r="E51" s="647"/>
+      <c r="B51" s="672"/>
+      <c r="C51" s="672"/>
+      <c r="D51" s="672"/>
+      <c r="E51" s="673"/>
       <c r="F51" s="244" t="s">
         <v>375</v>
       </c>
-      <c r="G51" s="386" t="s">
+      <c r="G51" s="366" t="s">
         <v>376</v>
       </c>
-      <c r="H51" s="582"/>
-      <c r="I51" s="387"/>
-      <c r="J51" s="639"/>
-      <c r="K51" s="640"/>
-      <c r="L51" s="640"/>
-      <c r="M51" s="641"/>
+      <c r="H51" s="532"/>
+      <c r="I51" s="367"/>
+      <c r="J51" s="664"/>
+      <c r="K51" s="665"/>
+      <c r="L51" s="665"/>
+      <c r="M51" s="666"/>
     </row>
     <row r="52" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="661"/>
-      <c r="B52" s="662"/>
-      <c r="C52" s="664"/>
-      <c r="D52" s="664"/>
-      <c r="E52" s="665"/>
+      <c r="A52" s="689"/>
+      <c r="B52" s="690"/>
+      <c r="C52" s="692"/>
+      <c r="D52" s="692"/>
+      <c r="E52" s="693"/>
       <c r="F52" s="55"/>
-      <c r="G52" s="654"/>
-      <c r="H52" s="655"/>
-      <c r="I52" s="656"/>
-      <c r="J52" s="639"/>
-      <c r="K52" s="640"/>
-      <c r="L52" s="640"/>
-      <c r="M52" s="641"/>
+      <c r="G52" s="682"/>
+      <c r="H52" s="683"/>
+      <c r="I52" s="684"/>
+      <c r="J52" s="664"/>
+      <c r="K52" s="665"/>
+      <c r="L52" s="665"/>
+      <c r="M52" s="666"/>
     </row>
     <row r="53" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="661"/>
-      <c r="B53" s="662"/>
-      <c r="C53" s="662"/>
-      <c r="D53" s="662"/>
-      <c r="E53" s="663"/>
+      <c r="A53" s="689"/>
+      <c r="B53" s="690"/>
+      <c r="C53" s="690"/>
+      <c r="D53" s="690"/>
+      <c r="E53" s="691"/>
       <c r="F53" s="55"/>
-      <c r="G53" s="654"/>
-      <c r="H53" s="655"/>
-      <c r="I53" s="656"/>
-      <c r="J53" s="639"/>
-      <c r="K53" s="640"/>
-      <c r="L53" s="640"/>
-      <c r="M53" s="641"/>
+      <c r="G53" s="682"/>
+      <c r="H53" s="683"/>
+      <c r="I53" s="684"/>
+      <c r="J53" s="664"/>
+      <c r="K53" s="665"/>
+      <c r="L53" s="665"/>
+      <c r="M53" s="666"/>
     </row>
     <row r="54" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="657"/>
-      <c r="B54" s="658"/>
-      <c r="C54" s="659"/>
-      <c r="D54" s="659"/>
-      <c r="E54" s="660"/>
+      <c r="A54" s="685"/>
+      <c r="B54" s="686"/>
+      <c r="C54" s="687"/>
+      <c r="D54" s="687"/>
+      <c r="E54" s="688"/>
       <c r="F54" s="181"/>
-      <c r="G54" s="642"/>
-      <c r="H54" s="643"/>
-      <c r="I54" s="644"/>
-      <c r="J54" s="639"/>
-      <c r="K54" s="640"/>
-      <c r="L54" s="640"/>
-      <c r="M54" s="641"/>
+      <c r="G54" s="668"/>
+      <c r="H54" s="669"/>
+      <c r="I54" s="670"/>
+      <c r="J54" s="664"/>
+      <c r="K54" s="665"/>
+      <c r="L54" s="665"/>
+      <c r="M54" s="666"/>
     </row>
     <row r="55" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="627" t="s">
+      <c r="A55" s="680" t="s">
         <v>377</v>
       </c>
-      <c r="B55" s="628"/>
-      <c r="C55" s="666" t="s">
+      <c r="B55" s="681"/>
+      <c r="C55" s="694" t="s">
         <v>397</v>
       </c>
-      <c r="D55" s="666"/>
-      <c r="E55" s="666"/>
-      <c r="F55" s="666"/>
-      <c r="G55" s="666"/>
-      <c r="H55" s="666"/>
+      <c r="D55" s="694"/>
+      <c r="E55" s="694"/>
+      <c r="F55" s="694"/>
+      <c r="G55" s="694"/>
+      <c r="H55" s="694"/>
       <c r="I55" s="235"/>
-      <c r="J55" s="640"/>
-      <c r="K55" s="640"/>
-      <c r="L55" s="640"/>
-      <c r="M55" s="641"/>
+      <c r="J55" s="665"/>
+      <c r="K55" s="665"/>
+      <c r="L55" s="665"/>
+      <c r="M55" s="666"/>
     </row>
     <row r="56" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="56"/>
       <c r="B56" s="57"/>
-      <c r="C56" s="667"/>
-      <c r="D56" s="667"/>
-      <c r="E56" s="667"/>
-      <c r="F56" s="667"/>
-      <c r="G56" s="667"/>
-      <c r="H56" s="667"/>
+      <c r="C56" s="695"/>
+      <c r="D56" s="695"/>
+      <c r="E56" s="695"/>
+      <c r="F56" s="695"/>
+      <c r="G56" s="695"/>
+      <c r="H56" s="695"/>
       <c r="I56" s="236"/>
       <c r="J56" s="180"/>
-      <c r="K56" s="610" t="s">
+      <c r="K56" s="667" t="s">
         <v>378</v>
       </c>
-      <c r="L56" s="610"/>
+      <c r="L56" s="667"/>
       <c r="M56" s="163"/>
     </row>
     <row r="57" spans="1:14" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="56"/>
       <c r="B57" s="57"/>
-      <c r="C57" s="667"/>
-      <c r="D57" s="667"/>
-      <c r="E57" s="667"/>
-      <c r="F57" s="667"/>
-      <c r="G57" s="667"/>
-      <c r="H57" s="667"/>
+      <c r="C57" s="695"/>
+      <c r="D57" s="695"/>
+      <c r="E57" s="695"/>
+      <c r="F57" s="695"/>
+      <c r="G57" s="695"/>
+      <c r="H57" s="695"/>
       <c r="I57" s="236"/>
-      <c r="J57" s="610"/>
-      <c r="K57" s="610"/>
-      <c r="L57" s="610"/>
-      <c r="M57" s="611"/>
+      <c r="J57" s="667"/>
+      <c r="K57" s="667"/>
+      <c r="L57" s="667"/>
+      <c r="M57" s="697"/>
     </row>
     <row r="58" spans="1:14" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="161"/>
@@ -18360,8 +18290,8 @@
       <c r="G58" s="237"/>
       <c r="H58" s="237"/>
       <c r="I58" s="238"/>
-      <c r="K58" s="692"/>
-      <c r="L58" s="693"/>
+      <c r="K58" s="632"/>
+      <c r="L58" s="633"/>
       <c r="M58" s="2"/>
     </row>
     <row r="59" spans="1:14" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -18373,102 +18303,102 @@
       <c r="G59" s="25"/>
       <c r="H59" s="25"/>
       <c r="I59" s="25"/>
-      <c r="K59" s="694"/>
-      <c r="L59" s="695"/>
+      <c r="K59" s="634"/>
+      <c r="L59" s="635"/>
       <c r="M59" s="2"/>
     </row>
     <row r="60" spans="1:14" ht="32.549999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="58"/>
-      <c r="B60" s="714" t="s">
+      <c r="B60" s="651" t="s">
         <v>398</v>
       </c>
-      <c r="C60" s="715"/>
-      <c r="D60" s="716"/>
-      <c r="F60" s="705"/>
-      <c r="G60" s="706"/>
-      <c r="H60" s="706"/>
-      <c r="I60" s="707"/>
-      <c r="K60" s="694"/>
-      <c r="L60" s="695"/>
+      <c r="C60" s="652"/>
+      <c r="D60" s="653"/>
+      <c r="F60" s="642"/>
+      <c r="G60" s="643"/>
+      <c r="H60" s="643"/>
+      <c r="I60" s="644"/>
+      <c r="K60" s="634"/>
+      <c r="L60" s="635"/>
       <c r="M60" s="59"/>
     </row>
     <row r="61" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="58"/>
-      <c r="B61" s="698" t="s">
+      <c r="B61" s="638" t="s">
         <v>379</v>
       </c>
-      <c r="C61" s="699"/>
+      <c r="C61" s="639"/>
       <c r="D61" s="114"/>
-      <c r="F61" s="708"/>
-      <c r="G61" s="709"/>
-      <c r="H61" s="709"/>
-      <c r="I61" s="710"/>
-      <c r="K61" s="694"/>
-      <c r="L61" s="695"/>
+      <c r="F61" s="645"/>
+      <c r="G61" s="646"/>
+      <c r="H61" s="646"/>
+      <c r="I61" s="647"/>
+      <c r="K61" s="634"/>
+      <c r="L61" s="635"/>
       <c r="M61" s="59"/>
     </row>
     <row r="62" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="58"/>
-      <c r="B62" s="686" t="s">
+      <c r="B62" s="626" t="s">
         <v>380</v>
       </c>
-      <c r="C62" s="687"/>
-      <c r="D62" s="690"/>
-      <c r="F62" s="711"/>
-      <c r="G62" s="712"/>
-      <c r="H62" s="712"/>
-      <c r="I62" s="713"/>
-      <c r="K62" s="694"/>
-      <c r="L62" s="695"/>
+      <c r="C62" s="627"/>
+      <c r="D62" s="630"/>
+      <c r="F62" s="648"/>
+      <c r="G62" s="649"/>
+      <c r="H62" s="649"/>
+      <c r="I62" s="650"/>
+      <c r="K62" s="634"/>
+      <c r="L62" s="635"/>
       <c r="M62" s="59"/>
     </row>
     <row r="63" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="58"/>
-      <c r="B63" s="700"/>
-      <c r="C63" s="701"/>
-      <c r="D63" s="717"/>
-      <c r="F63" s="718" t="s">
+      <c r="B63" s="640"/>
+      <c r="C63" s="641"/>
+      <c r="D63" s="654"/>
+      <c r="F63" s="655" t="s">
         <v>381</v>
       </c>
-      <c r="G63" s="719"/>
-      <c r="H63" s="719"/>
-      <c r="I63" s="720"/>
-      <c r="K63" s="694"/>
-      <c r="L63" s="695"/>
+      <c r="G63" s="656"/>
+      <c r="H63" s="656"/>
+      <c r="I63" s="657"/>
+      <c r="K63" s="634"/>
+      <c r="L63" s="635"/>
       <c r="M63" s="59"/>
     </row>
     <row r="64" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="58"/>
-      <c r="B64" s="686" t="s">
+      <c r="B64" s="626" t="s">
         <v>382</v>
       </c>
-      <c r="C64" s="687"/>
-      <c r="D64" s="690"/>
+      <c r="C64" s="627"/>
+      <c r="D64" s="630"/>
       <c r="F64" s="60"/>
       <c r="G64" s="164"/>
       <c r="H64" s="164"/>
       <c r="I64" s="165"/>
       <c r="J64" s="61"/>
-      <c r="K64" s="696"/>
-      <c r="L64" s="697"/>
+      <c r="K64" s="636"/>
+      <c r="L64" s="637"/>
       <c r="M64" s="59"/>
     </row>
     <row r="65" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="58"/>
-      <c r="B65" s="688"/>
-      <c r="C65" s="689"/>
-      <c r="D65" s="691"/>
-      <c r="F65" s="683" t="s">
+      <c r="B65" s="628"/>
+      <c r="C65" s="629"/>
+      <c r="D65" s="631"/>
+      <c r="F65" s="623" t="s">
         <v>383</v>
       </c>
-      <c r="G65" s="684"/>
-      <c r="H65" s="684"/>
-      <c r="I65" s="685"/>
+      <c r="G65" s="624"/>
+      <c r="H65" s="624"/>
+      <c r="I65" s="625"/>
       <c r="J65" s="61"/>
-      <c r="K65" s="681" t="s">
+      <c r="K65" s="621" t="s">
         <v>384</v>
       </c>
-      <c r="L65" s="682"/>
+      <c r="L65" s="622"/>
       <c r="M65" s="59"/>
     </row>
     <row r="66" spans="1:13" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -18487,32 +18417,32 @@
       <c r="M66" s="67"/>
     </row>
     <row r="67" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="678" t="s">
+      <c r="A67" s="618" t="s">
         <v>385</v>
       </c>
-      <c r="B67" s="679"/>
-      <c r="C67" s="679"/>
-      <c r="D67" s="679"/>
-      <c r="E67" s="679"/>
-      <c r="F67" s="679"/>
-      <c r="G67" s="679"/>
-      <c r="H67" s="679"/>
-      <c r="I67" s="679"/>
-      <c r="J67" s="679"/>
-      <c r="K67" s="679"/>
-      <c r="L67" s="679"/>
-      <c r="M67" s="680"/>
+      <c r="B67" s="619"/>
+      <c r="C67" s="619"/>
+      <c r="D67" s="619"/>
+      <c r="E67" s="619"/>
+      <c r="F67" s="619"/>
+      <c r="G67" s="619"/>
+      <c r="H67" s="619"/>
+      <c r="I67" s="619"/>
+      <c r="J67" s="619"/>
+      <c r="K67" s="619"/>
+      <c r="L67" s="619"/>
+      <c r="M67" s="620"/>
     </row>
     <row r="68" spans="1:13" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="58"/>
       <c r="B68" s="61"/>
       <c r="C68" s="68"/>
       <c r="D68" s="68"/>
-      <c r="E68" s="675"/>
-      <c r="F68" s="676"/>
-      <c r="G68" s="676"/>
-      <c r="H68" s="676"/>
-      <c r="I68" s="677"/>
+      <c r="E68" s="615"/>
+      <c r="F68" s="616"/>
+      <c r="G68" s="616"/>
+      <c r="H68" s="616"/>
+      <c r="I68" s="617"/>
       <c r="J68" s="115"/>
       <c r="K68" s="115"/>
       <c r="M68" s="59"/>
@@ -18522,13 +18452,13 @@
       <c r="B69" s="61"/>
       <c r="C69" s="220"/>
       <c r="D69" s="220"/>
-      <c r="E69" s="672" t="s">
+      <c r="E69" s="612" t="s">
         <v>386</v>
       </c>
-      <c r="F69" s="673"/>
-      <c r="G69" s="673"/>
-      <c r="H69" s="673"/>
-      <c r="I69" s="674"/>
+      <c r="F69" s="613"/>
+      <c r="G69" s="613"/>
+      <c r="H69" s="613"/>
+      <c r="I69" s="614"/>
       <c r="J69" s="117"/>
       <c r="K69" s="116"/>
       <c r="L69" s="69"/>
@@ -18550,21 +18480,21 @@
       <c r="M70" s="72"/>
     </row>
     <row r="71" spans="1:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="671" t="s">
+      <c r="A71" s="611" t="s">
         <v>400</v>
       </c>
-      <c r="B71" s="671"/>
-      <c r="C71" s="671"/>
-      <c r="D71" s="671"/>
-      <c r="E71" s="671"/>
-      <c r="F71" s="671"/>
-      <c r="G71" s="671"/>
-      <c r="H71" s="671"/>
-      <c r="I71" s="671"/>
-      <c r="J71" s="671"/>
-      <c r="K71" s="671"/>
-      <c r="L71" s="671"/>
-      <c r="M71" s="671"/>
+      <c r="B71" s="611"/>
+      <c r="C71" s="611"/>
+      <c r="D71" s="611"/>
+      <c r="E71" s="611"/>
+      <c r="F71" s="611"/>
+      <c r="G71" s="611"/>
+      <c r="H71" s="611"/>
+      <c r="I71" s="611"/>
+      <c r="J71" s="611"/>
+      <c r="K71" s="611"/>
+      <c r="L71" s="611"/>
+      <c r="M71" s="611"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -18577,37 +18507,46 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="87">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="G38:M38"/>
-    <mergeCell ref="C18:F22"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="G19:L19"/>
-    <mergeCell ref="C23:F26"/>
-    <mergeCell ref="A71:M71"/>
-    <mergeCell ref="E69:I69"/>
-    <mergeCell ref="E68:I68"/>
-    <mergeCell ref="A67:M67"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="F65:I65"/>
-    <mergeCell ref="B64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="K58:L64"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C63"/>
-    <mergeCell ref="F60:I62"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="C31:F32"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C34:F36"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="H39:L39"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="H15:L15"/>
+    <mergeCell ref="H25:L25"/>
+    <mergeCell ref="H29:L29"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:F16"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="H11:L11"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C45:F46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="C37:F40"/>
+    <mergeCell ref="C41:F42"/>
+    <mergeCell ref="C43:F44"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="C27:F30"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C6:F6"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="K32:L32"/>
     <mergeCell ref="J50:M55"/>
@@ -18624,46 +18563,37 @@
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="C55:H57"/>
     <mergeCell ref="I34:L34"/>
-    <mergeCell ref="J57:M57"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C45:F46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="C37:F40"/>
-    <mergeCell ref="C41:F42"/>
-    <mergeCell ref="C43:F44"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="C27:F30"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:F16"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="H11:L11"/>
-    <mergeCell ref="H39:L39"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="H15:L15"/>
-    <mergeCell ref="H25:L25"/>
-    <mergeCell ref="H29:L29"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="A71:M71"/>
+    <mergeCell ref="E69:I69"/>
+    <mergeCell ref="E68:I68"/>
+    <mergeCell ref="A67:M67"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="B64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="K58:L64"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C63"/>
+    <mergeCell ref="F60:I62"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="G38:M38"/>
+    <mergeCell ref="C18:F22"/>
+    <mergeCell ref="G28:L28"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="G19:L19"/>
+    <mergeCell ref="C23:F26"/>
+    <mergeCell ref="C31:F32"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C34:F36"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="G35:J35"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -19531,15 +19461,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="61535973-5223-4bf4-bdcc-6c7df9166676">
@@ -19547,6 +19468,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19569,14 +19499,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE1AC42-07AD-4118-96D5-B1BB6CECCAA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CF60C-2A54-4479-8975-DF3B2608842A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="ab5b6d4b-4285-4680-b1ee-6fe31a63f7d7"/>
@@ -19591,4 +19513,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE1AC42-07AD-4118-96D5-B1BB6CECCAA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>